--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA92C49E-9F55-4751-A36A-65121472975D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFD879D-DFFA-4CC0-BEBD-5C5A706C2401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -16763,6 +16763,9 @@
       <c r="A884" s="8">
         <v>46081</v>
       </c>
+      <c r="B884" s="8">
+        <v>46085</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="A2:E876">

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFD879D-DFFA-4CC0-BEBD-5C5A706C2401}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC1E8A9-AC5E-774C-BBBB-001F81F49A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="11760" yWindow="6500" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +80,6 @@
   </si>
   <si>
     <t>https://ycharts.com/indicators/us_weekly_rail_traffic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -77,12 +87,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -180,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -197,68 +207,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -274,9 +284,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -314,7 +324,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -420,7 +430,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -562,7 +572,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -571,17 +581,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E884"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="5" max="5" width="12.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -598,7 +608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="14">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -631,7 +641,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="14">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -649,7 +659,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="14">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -667,7 +677,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="14">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -685,7 +695,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="14">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -703,7 +713,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="14">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -721,7 +731,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="14">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -739,7 +749,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="14">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -757,7 +767,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="14">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -775,7 +785,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="14">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -793,7 +803,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="14">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -811,7 +821,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="14">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -829,7 +839,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="14">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -847,7 +857,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="14">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -865,7 +875,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="14">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -883,7 +893,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="14">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -901,7 +911,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="14">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -919,7 +929,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="14">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -937,7 +947,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="14">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -955,7 +965,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="14">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -973,7 +983,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="14">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -991,7 +1001,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="14">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -1009,7 +1019,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="14">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -1027,7 +1037,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="14">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -1045,7 +1055,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="14">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -1063,7 +1073,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="14">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -1081,7 +1091,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="14">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -1099,7 +1109,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="14">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -1117,7 +1127,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="14">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -1135,7 +1145,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="14">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -1153,7 +1163,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="14">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -1171,7 +1181,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="14">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -1189,7 +1199,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="14">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -1207,7 +1217,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="14">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -1225,7 +1235,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="14">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -1243,7 +1253,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="14">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -1261,7 +1271,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="14">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -1279,7 +1289,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="14">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -1297,7 +1307,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="14">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -1315,7 +1325,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="14">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -1333,7 +1343,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" ht="14">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -1351,7 +1361,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="14">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -1369,7 +1379,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="14">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -1387,7 +1397,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="14">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -1405,7 +1415,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="14">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -1423,7 +1433,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="14">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -1441,7 +1451,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" ht="14">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -1459,7 +1469,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="14">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -1477,7 +1487,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="14">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -1495,7 +1505,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="14">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -1513,7 +1523,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="14">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -1531,7 +1541,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="14">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -1549,7 +1559,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="14">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -1567,7 +1577,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="14">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -1585,7 +1595,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="14">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -1603,7 +1613,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="14">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -1621,7 +1631,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="14">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -1639,7 +1649,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="14">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -1657,7 +1667,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="14">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -1675,7 +1685,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="14">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -1693,7 +1703,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" ht="14">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -1711,7 +1721,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="14">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -1729,7 +1739,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="14">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -1747,7 +1757,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="14">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -1765,7 +1775,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="14">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -1798,7 +1808,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="14">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -1816,7 +1826,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="14">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -1834,7 +1844,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="14">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -1852,7 +1862,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="14">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -1870,7 +1880,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="14">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -1888,7 +1898,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="14">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -1906,7 +1916,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="14">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -1924,7 +1934,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="14">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -1942,7 +1952,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="14">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -1960,7 +1970,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="14">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -1978,7 +1988,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="14">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -1996,7 +2006,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="14">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -2014,7 +2024,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="14">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -2032,7 +2042,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="14">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -2050,7 +2060,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="14">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -2068,7 +2078,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="14">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -2086,7 +2096,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="14">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -2104,7 +2114,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="14">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -2122,7 +2132,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="14">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -2140,7 +2150,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="14">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -2158,7 +2168,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="14">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -2176,7 +2186,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="14">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -2194,7 +2204,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="14">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -2212,7 +2222,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="14">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -2230,7 +2240,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="14">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -2248,7 +2258,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="14">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -2266,7 +2276,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="14">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -2284,7 +2294,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="14">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -2302,7 +2312,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="14">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -2320,7 +2330,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="14">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -2338,7 +2348,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="14">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -2356,7 +2366,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="14">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -2374,7 +2384,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="14">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -2392,7 +2402,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" ht="14">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -2410,7 +2420,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -2428,7 +2438,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="15" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -2446,7 +2456,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="15" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -2464,7 +2474,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="15" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -2482,7 +2492,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="15" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -2500,7 +2510,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="15" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -2518,7 +2528,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -2536,7 +2546,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="15" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -2554,7 +2564,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -2572,7 +2582,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="15" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -2590,7 +2600,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="15" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -2608,7 +2618,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="15" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -2626,7 +2636,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="15" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -2644,7 +2654,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="15" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -2662,7 +2672,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="15" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -2680,7 +2690,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="15" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -2698,7 +2708,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="15" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -2716,7 +2726,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="15" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -2734,7 +2744,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="15" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -2752,7 +2762,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="15" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -2770,7 +2780,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="15" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -2788,7 +2798,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="15" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -2806,7 +2816,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="15" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -2824,7 +2834,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="15" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -2842,7 +2852,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="15" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -2860,7 +2870,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="15" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -2878,7 +2888,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="15" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -2896,7 +2906,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="15" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -2914,7 +2924,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="15" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -2932,7 +2942,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="15" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -2965,7 +2975,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="15" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -2983,7 +2993,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="15" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -3001,7 +3011,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="15" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -3019,7 +3029,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="15" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -3037,7 +3047,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="15" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -3055,7 +3065,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="15" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -3073,7 +3083,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="15" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -3091,7 +3101,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="15" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -3109,7 +3119,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="15" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -3127,7 +3137,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="15" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -3145,7 +3155,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="15" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -3163,7 +3173,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="15" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -3181,7 +3191,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="15" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -3199,7 +3209,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="15" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -3217,7 +3227,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="15" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -3235,7 +3245,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="15" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -3253,7 +3263,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="15" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -3271,7 +3281,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="15" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -3289,7 +3299,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="15" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -3307,7 +3317,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="15" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -3325,7 +3335,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="15" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -3343,7 +3353,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="15" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -3361,7 +3371,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="15" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -3379,7 +3389,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="15" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -3397,7 +3407,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="15" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -3415,7 +3425,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="15" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -3433,7 +3443,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="15" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -3451,7 +3461,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="15" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -3469,7 +3479,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="15" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -3487,7 +3497,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="15" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -3505,7 +3515,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="15" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -3523,7 +3533,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="15" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -3541,7 +3551,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" ht="15" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -3559,7 +3569,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="15" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -3577,7 +3587,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" ht="15" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -3595,7 +3605,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="15" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -3613,7 +3623,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="15" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -3631,7 +3641,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="15" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -3649,7 +3659,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="15" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -3667,7 +3677,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="15" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -3685,7 +3695,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="15" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -3703,7 +3713,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="15" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -3721,7 +3731,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="15" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -3739,7 +3749,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="15" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -3757,7 +3767,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="15" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -3775,7 +3785,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="15" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -3793,7 +3803,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="15" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -3811,7 +3821,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="15" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -3829,7 +3839,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="15" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -3847,7 +3857,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="15" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -3865,7 +3875,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="15" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -3883,7 +3893,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="15" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -3901,7 +3911,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="15" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -3919,7 +3929,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="15" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -3937,7 +3947,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="15" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -3955,7 +3965,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="15" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -3973,7 +3983,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="15" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -3991,7 +4001,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="15" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -4009,7 +4019,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="15" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -4027,7 +4037,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="15" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -4045,7 +4055,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="15" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -4063,7 +4073,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="15" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -4081,7 +4091,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="15" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -4099,7 +4109,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="15" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -4132,7 +4142,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="15" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -4150,7 +4160,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="15" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -4168,7 +4178,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="15" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -4186,7 +4196,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="15" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -4204,7 +4214,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="15" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -4222,7 +4232,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="15" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -4240,7 +4250,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="15" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -4258,7 +4268,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="15" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -4276,7 +4286,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="15" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -4294,7 +4304,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="15" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -4312,7 +4322,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="15" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -4330,7 +4340,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="15" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -4348,7 +4358,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="15" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -4366,7 +4376,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="15" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -4384,7 +4394,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="15" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -4402,7 +4412,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="15" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -4420,7 +4430,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="15" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -4438,7 +4448,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="15" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -4456,7 +4466,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="15" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -4474,7 +4484,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="15" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -4492,7 +4502,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="15" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -4510,7 +4520,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="15" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -4528,7 +4538,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="15" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -4546,7 +4556,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="15" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -4564,7 +4574,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="15" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -4582,7 +4592,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="15" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -4600,7 +4610,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="15" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -4618,7 +4628,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="15" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -4636,7 +4646,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="15" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -4654,7 +4664,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="15" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -4672,7 +4682,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="15" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -4690,7 +4700,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="15" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -4708,7 +4718,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="15" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -4726,7 +4736,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="15" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -4744,7 +4754,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="15" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -4762,7 +4772,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="15" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -4780,7 +4790,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="15" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -4798,7 +4808,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="15" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -4816,7 +4826,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="15" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -4834,7 +4844,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="15" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -4852,7 +4862,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="15" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -4870,7 +4880,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="15" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -4888,7 +4898,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="15" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -4906,7 +4916,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="15" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -4924,7 +4934,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="15" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -4942,7 +4952,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="15" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -4960,7 +4970,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="15" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -4978,7 +4988,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="15" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -4996,7 +5006,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="15" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -5014,7 +5024,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="15" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -5032,7 +5042,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="15" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -5050,7 +5060,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="15" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -5068,7 +5078,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="15" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -5086,7 +5096,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="15" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -5104,7 +5114,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="15" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -5122,7 +5132,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="15" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -5140,7 +5150,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="15" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -5158,7 +5168,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="15" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -5176,7 +5186,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="15" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -5194,7 +5204,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="15" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -5212,7 +5222,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="15" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -5230,7 +5240,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="15" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -5248,7 +5258,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="15" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -5266,7 +5276,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="15" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -5299,7 +5309,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="15" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -5317,7 +5327,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="15" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -5335,7 +5345,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="15" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -5353,7 +5363,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="15" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -5371,7 +5381,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="15" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -5389,7 +5399,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="15" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -5407,7 +5417,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="15" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -5425,7 +5435,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="15" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -5443,7 +5453,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="15" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -5461,7 +5471,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="15" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -5479,7 +5489,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="15" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -5497,7 +5507,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="15" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -5515,7 +5525,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="15" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -5533,7 +5543,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="15" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -5551,7 +5561,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="15" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -5569,7 +5579,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="15" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -5587,7 +5597,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="15" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -5605,7 +5615,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="15" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -5623,7 +5633,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="15" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -5641,7 +5651,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="15" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -5659,7 +5669,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="15" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -5677,7 +5687,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="15" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -5695,7 +5705,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="15" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -5713,7 +5723,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="15" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -5731,7 +5741,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="15" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -5749,7 +5759,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="15" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -5767,7 +5777,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="15" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -5785,7 +5795,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="15" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -5803,7 +5813,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="15" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -5821,7 +5831,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="15" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -5839,7 +5849,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="15" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -5857,7 +5867,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="15" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -5875,7 +5885,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="15" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -5893,7 +5903,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="15" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -5911,7 +5921,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="15" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -5929,7 +5939,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="15" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -5947,7 +5957,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="15" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -5965,7 +5975,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="15" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -5983,7 +5993,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="15" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -6001,7 +6011,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="15" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -6019,7 +6029,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="15" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -6037,7 +6047,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="15" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -6055,7 +6065,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="15" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -6073,7 +6083,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="15" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -6091,7 +6101,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="15" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -6109,7 +6119,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="15" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -6127,7 +6137,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="15" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -6145,7 +6155,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="15" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -6163,7 +6173,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="15" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -6181,7 +6191,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="15" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -6199,7 +6209,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="15" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -6217,7 +6227,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="15" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -6235,7 +6245,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="15" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -6253,7 +6263,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="15" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -6271,7 +6281,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="15" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -6289,7 +6299,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="15" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -6307,7 +6317,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="15" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -6325,7 +6335,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="15" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -6343,7 +6353,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="15" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -6361,7 +6371,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="15" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -6379,7 +6389,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="15" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -6397,7 +6407,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="15" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -6415,7 +6425,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="15" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -6433,7 +6443,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="15" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -6466,7 +6476,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="15" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -6484,7 +6494,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="15" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -6502,7 +6512,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="15" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -6520,7 +6530,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="15" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -6538,7 +6548,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="15" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -6556,7 +6566,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="15" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -6574,7 +6584,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="15" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -6592,7 +6602,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="15" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -6610,7 +6620,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="15" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -6628,7 +6638,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="15" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -6646,7 +6656,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="15" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -6664,7 +6674,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="15" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -6682,7 +6692,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="15" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -6700,7 +6710,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="15" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -6718,7 +6728,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="15" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -6736,7 +6746,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="15" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -6754,7 +6764,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="15" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -6772,7 +6782,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="15" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -6790,7 +6800,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="15" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -6808,7 +6818,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="15" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -6826,7 +6836,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="15" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -6844,7 +6854,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="15" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -6862,7 +6872,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="15" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -6880,7 +6890,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="15" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -6898,7 +6908,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="15" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -6916,7 +6926,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="15" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -6934,7 +6944,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="15" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -6952,7 +6962,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="15" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -6970,7 +6980,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="15" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -6988,7 +6998,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="15" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -7006,7 +7016,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="15" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -7024,7 +7034,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="15" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -7042,7 +7052,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="15" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -7060,7 +7070,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="15" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -7078,7 +7088,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="15" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -7096,7 +7106,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="15" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -7114,7 +7124,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="15" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -7132,7 +7142,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="15" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -7150,7 +7160,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="15" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -7168,7 +7178,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="15" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -7186,7 +7196,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="15" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -7204,7 +7214,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="15" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -7222,7 +7232,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="15" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -7240,7 +7250,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="15" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -7258,7 +7268,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="15" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -7276,7 +7286,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="15" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -7294,7 +7304,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="15" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -7312,7 +7322,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="15" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -7330,7 +7340,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="15" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -7348,7 +7358,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="15" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -7366,7 +7376,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="15" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -7384,7 +7394,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="15" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -7402,7 +7412,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="15" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -7420,7 +7430,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="15" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -7438,7 +7448,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="15" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -7456,7 +7466,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="15" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -7474,7 +7484,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="15" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -7492,7 +7502,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="15" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -7510,7 +7520,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="15" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -7528,7 +7538,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="15" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -7546,7 +7556,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="15" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -7564,7 +7574,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="15" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -7582,7 +7592,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="15" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -7600,7 +7610,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="15" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -7633,7 +7643,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="15" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -7651,7 +7661,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="15" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -7669,7 +7679,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="15" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -7687,7 +7697,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="15" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -7705,7 +7715,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="15" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -7723,7 +7733,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="15" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -7741,7 +7751,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="15" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -7759,7 +7769,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="15" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -7777,7 +7787,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="15" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -7795,7 +7805,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="15" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -7813,7 +7823,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="15" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -7831,7 +7841,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="15" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -7849,7 +7859,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="15" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -7867,7 +7877,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="15" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -7885,7 +7895,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="15" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -7903,7 +7913,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="15" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -7921,7 +7931,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="15" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -7939,7 +7949,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="15" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -7957,7 +7967,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="15" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -7975,7 +7985,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="15" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -7993,7 +8003,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="15" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -8011,7 +8021,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="15" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -8029,7 +8039,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="15" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -8047,7 +8057,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="15" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -8065,7 +8075,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="15" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -8083,7 +8093,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="15" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -8101,7 +8111,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="15" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -8119,7 +8129,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="15" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -8137,7 +8147,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="15" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -8155,7 +8165,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="15" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -8173,7 +8183,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="15" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -8191,7 +8201,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="15" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -8209,7 +8219,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="15" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -8227,7 +8237,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="15" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -8245,7 +8255,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="15" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -8263,7 +8273,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="15" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -8281,7 +8291,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="15" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -8299,7 +8309,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="15" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -8317,7 +8327,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="15" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -8335,7 +8345,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="15" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -8353,7 +8363,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="15" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -8371,7 +8381,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="15" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -8389,7 +8399,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="15" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -8407,7 +8417,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="15" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -8425,7 +8435,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="15" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -8443,7 +8453,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="15" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -8461,7 +8471,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="15" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -8479,7 +8489,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="15" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -8497,7 +8507,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="15" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -8515,7 +8525,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="15" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -8533,7 +8543,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="15" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -8551,7 +8561,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="15" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -8569,7 +8579,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="15" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -8587,7 +8597,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="15" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -8605,7 +8615,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="15" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -8623,7 +8633,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="15" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -8641,7 +8651,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="15" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -8659,7 +8669,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="15" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -8677,7 +8687,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="15" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -8695,7 +8705,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="15" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -8713,7 +8723,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="15" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -8731,7 +8741,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="15" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -8749,7 +8759,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="15" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -8767,7 +8777,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="15" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -8800,7 +8810,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="15" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -8818,7 +8828,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="15" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -8836,7 +8846,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="15" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -8854,7 +8864,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="15" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -8872,7 +8882,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="15" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -8890,7 +8900,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="15" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -8908,7 +8918,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="15" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -8926,7 +8936,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="15" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -8944,7 +8954,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="15" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -8962,7 +8972,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="15" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -8980,7 +8990,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="15" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -8998,7 +9008,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="15" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -9016,7 +9026,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="15" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -9034,7 +9044,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="15" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -9052,7 +9062,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="15" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -9070,7 +9080,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="15" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -9088,7 +9098,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="15" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -9106,7 +9116,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="15" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -9124,7 +9134,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="15" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -9142,7 +9152,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="15" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -9160,7 +9170,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="15" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -9178,7 +9188,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="15" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -9196,7 +9206,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="15" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -9214,7 +9224,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="15" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -9232,7 +9242,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="15" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -9250,7 +9260,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="15" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -9268,7 +9278,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="15" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -9286,7 +9296,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="15" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -9304,7 +9314,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="15" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -9322,7 +9332,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="15" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -9340,7 +9350,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="15" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -9358,7 +9368,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="15" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -9376,7 +9386,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="15" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -9394,7 +9404,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="15" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -9412,7 +9422,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="15" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -9430,7 +9440,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="15" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -9448,7 +9458,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="15" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -9466,7 +9476,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="15" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -9484,7 +9494,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="15" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -9502,7 +9512,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="15" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -9520,7 +9530,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="15" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -9538,7 +9548,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="15" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -9556,7 +9566,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="15" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -9574,7 +9584,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="15" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -9592,7 +9602,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="15" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -9610,7 +9620,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="15" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -9628,7 +9638,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="15" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -9646,7 +9656,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="15" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -9664,7 +9674,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="15" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -9682,7 +9692,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="15" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -9700,7 +9710,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="15" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -9718,7 +9728,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="15" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -9736,7 +9746,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="15" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -9754,7 +9764,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="15" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -9772,7 +9782,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="15" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -9790,7 +9800,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="15" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -9808,7 +9818,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="15" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -9826,7 +9836,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="15" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -9844,7 +9854,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="15" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -9862,7 +9872,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="15" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -9880,7 +9890,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="15" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -9898,7 +9908,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="15" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -9916,7 +9926,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="15" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -9934,7 +9944,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="15" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -9967,7 +9977,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="15" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -9985,7 +9995,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="15" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -10003,7 +10013,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="15" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -10021,7 +10031,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="15" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -10039,7 +10049,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="15" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -10057,7 +10067,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="15" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -10075,7 +10085,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="15" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -10093,7 +10103,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="15" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -10111,7 +10121,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="15" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -10129,7 +10139,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="15" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -10147,7 +10157,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="15" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -10165,7 +10175,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="15" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -10183,7 +10193,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="15" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -10201,7 +10211,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="15" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -10219,7 +10229,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="15" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -10237,7 +10247,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="15" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -10255,7 +10265,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="15" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -10273,7 +10283,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="15" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -10291,7 +10301,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="15" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -10309,7 +10319,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="15" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -10327,7 +10337,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="15" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -10345,7 +10355,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="15" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -10363,7 +10373,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="15" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -10381,7 +10391,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="15" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -10399,7 +10409,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="15" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -10417,7 +10427,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="15" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -10435,7 +10445,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="15" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -10453,7 +10463,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="15" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -10471,7 +10481,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="15" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -10489,7 +10499,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="15" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -10507,7 +10517,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="15" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -10525,7 +10535,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="15" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -10543,7 +10553,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="15" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -10561,7 +10571,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="15" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -10579,7 +10589,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="15" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -10597,7 +10607,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="15" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -10615,7 +10625,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="15" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -10633,7 +10643,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="15" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -10651,7 +10661,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="15" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -10669,7 +10679,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="15" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -10687,7 +10697,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="15" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -10705,7 +10715,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="15" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -10723,7 +10733,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="15" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -10741,7 +10751,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="15" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -10759,7 +10769,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="15" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -10777,7 +10787,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="15" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -10795,7 +10805,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="15" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -10813,7 +10823,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="15" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -10831,7 +10841,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="15" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -10849,7 +10859,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="15" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -10867,7 +10877,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="15" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -10885,7 +10895,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="15" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -10903,7 +10913,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="15" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -10921,7 +10931,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="15" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -10939,7 +10949,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="15" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -10957,7 +10967,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="15" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -10975,7 +10985,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="15" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -10993,7 +11003,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="15" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -11011,7 +11021,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="15" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -11029,7 +11039,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="15" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -11047,7 +11057,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="15" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -11065,7 +11075,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="15" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -11083,7 +11093,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="15" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -11101,7 +11111,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="15" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -11134,7 +11144,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="15" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -11152,7 +11162,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="15" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -11170,7 +11180,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="15" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -11188,7 +11198,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="15" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -11206,7 +11216,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="15" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -11224,7 +11234,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="15" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -11242,7 +11252,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="15" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -11260,7 +11270,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="15" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -11278,7 +11288,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="15" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -11296,7 +11306,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="15" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -11314,7 +11324,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="15" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -11332,7 +11342,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="15" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -11350,7 +11360,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="15" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -11368,7 +11378,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="15" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -11386,7 +11396,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="15" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -11404,7 +11414,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="15" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -11422,7 +11432,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="15" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -11440,7 +11450,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="15" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -11458,7 +11468,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="15" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -11476,7 +11486,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="15" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -11494,7 +11504,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="15" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -11512,7 +11522,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="15" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -11530,7 +11540,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="15" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -11548,7 +11558,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="15" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -11566,7 +11576,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="15" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -11584,7 +11594,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="15" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -11602,7 +11612,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="15" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -11620,7 +11630,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="15" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -11638,7 +11648,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="15" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -11656,7 +11666,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="15" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -11674,7 +11684,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="15" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -11692,7 +11702,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="15" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -11710,7 +11720,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="15" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -11728,7 +11738,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="15" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -11746,7 +11756,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="15" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -11764,7 +11774,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="15" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -11782,7 +11792,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="15" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -11800,7 +11810,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="15" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -11818,7 +11828,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="15" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -11836,7 +11846,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="15" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -11854,7 +11864,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="15" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -11872,7 +11882,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="15" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -11890,7 +11900,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="15" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -11908,7 +11918,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="15" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -11926,7 +11936,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="15" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -11944,7 +11954,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="15" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -11962,7 +11972,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="15" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -11980,7 +11990,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="15" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -11998,7 +12008,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="15" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -12016,7 +12026,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="15" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -12034,7 +12044,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="15" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -12052,7 +12062,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="15" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -12070,7 +12080,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="15" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -12088,7 +12098,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="15" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -12106,7 +12116,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="15" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -12124,7 +12134,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="15" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -12142,7 +12152,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="15" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -12160,7 +12170,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="15" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -12178,7 +12188,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="15" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -12196,7 +12206,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="15" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -12214,7 +12224,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="15" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -12232,7 +12242,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="15" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -12250,7 +12260,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="15" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -12268,7 +12278,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="15" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -12301,7 +12311,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="15" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -12319,7 +12329,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="15" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -12337,7 +12347,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="15" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -12355,7 +12365,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="15" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -12373,7 +12383,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="15" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -12391,7 +12401,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="15" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -12409,7 +12419,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="15" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -12427,7 +12437,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="15" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -12445,7 +12455,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="15" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -12463,7 +12473,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="15" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -12481,7 +12491,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="15" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -12499,7 +12509,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="15" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -12517,7 +12527,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="15" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -12535,7 +12545,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="15" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -12553,7 +12563,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="15" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -12571,7 +12581,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="15" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -12589,7 +12599,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="15" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -12607,7 +12617,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="15" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -12625,7 +12635,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="15" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -12643,7 +12653,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="15" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -12661,7 +12671,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="15" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -12679,7 +12689,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="15" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -12697,7 +12707,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="15" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -12715,7 +12725,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="15" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -12733,7 +12743,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="15" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -12751,7 +12761,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="15" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -12769,7 +12779,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="15" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -12787,7 +12797,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="15" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -12805,7 +12815,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="15" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -12823,7 +12833,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="15" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -12841,7 +12851,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="15" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -12859,7 +12869,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="15" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -12877,7 +12887,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="15" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -12895,7 +12905,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="15" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -12913,7 +12923,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="15" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -12931,7 +12941,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="15" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -12949,7 +12959,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="15" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -12967,7 +12977,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="15" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -12985,7 +12995,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="15" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -13003,7 +13013,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="15" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -13021,7 +13031,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="15" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -13039,7 +13049,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="15" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -13057,7 +13067,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="15" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -13075,7 +13085,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="15" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -13093,7 +13103,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="15" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -13111,7 +13121,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="15" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -13129,7 +13139,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="15" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -13147,7 +13157,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="15" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -13165,7 +13175,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="15" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -13183,7 +13193,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="15" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -13201,7 +13211,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="15" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -13219,7 +13229,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="15" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -13237,7 +13247,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="15" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -13255,7 +13265,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="15" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -13273,7 +13283,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="15" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -13291,7 +13301,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="15" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -13309,7 +13319,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="15" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -13327,7 +13337,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="15" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -13345,7 +13355,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="15" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -13363,7 +13373,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="15" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -13381,7 +13391,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="15" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -13399,7 +13409,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="15" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -13417,7 +13427,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="15" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -13435,7 +13445,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="15" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -13468,7 +13478,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="15" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -13486,7 +13496,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="15" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -13504,7 +13514,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="15" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -13522,7 +13532,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="15" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -13540,7 +13550,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="15" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -13558,7 +13568,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="15" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -13576,7 +13586,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="15" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -13594,7 +13604,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="15" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -13612,7 +13622,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="15" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -13630,7 +13640,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="15" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -13648,7 +13658,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="15" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -13666,7 +13676,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="15" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -13684,7 +13694,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="15" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -13702,7 +13712,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="15" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -13720,7 +13730,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="15" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -13738,7 +13748,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="15" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -13756,7 +13766,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="15" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -13774,7 +13784,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="15" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -13792,7 +13802,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="15" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -13810,7 +13820,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" ht="15" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -13828,7 +13838,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" ht="15" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -13846,7 +13856,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" ht="15" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -13864,7 +13874,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" ht="15" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -13882,7 +13892,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5" ht="15" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -13900,7 +13910,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" ht="15" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -13918,7 +13928,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" ht="15" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -13936,7 +13946,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" ht="15" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -13954,7 +13964,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" ht="15" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -13972,7 +13982,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" ht="15" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -13990,7 +14000,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" ht="15" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -14008,7 +14018,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5" ht="15" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -14026,7 +14036,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5" ht="15" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -14044,7 +14054,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5" ht="15" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -14062,7 +14072,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5" ht="15" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -14080,7 +14090,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5" ht="15" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -14098,7 +14108,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5" ht="15" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -14116,7 +14126,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5" ht="15" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -14134,7 +14144,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5" ht="15" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -14152,7 +14162,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5" ht="15" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -14170,7 +14180,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5" ht="15" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -14188,7 +14198,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5" ht="15" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -14206,7 +14216,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5" ht="15" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -14224,7 +14234,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5" ht="15" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -14242,7 +14252,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5" ht="15" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -14260,7 +14270,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5" ht="15" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -14278,7 +14288,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5" ht="15" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -14296,7 +14306,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:5" ht="15" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -14314,7 +14324,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:5" ht="15" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -14332,7 +14342,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:5" ht="15" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -14350,7 +14360,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:5" ht="15" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -14368,7 +14378,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:5" ht="15" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -14386,7 +14396,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:5" ht="15" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -14404,7 +14414,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5" ht="15" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -14422,7 +14432,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:5" ht="15" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -14440,7 +14450,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:5" ht="15" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -14458,7 +14468,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5" ht="15" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -14476,7 +14486,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5" ht="15" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -14494,7 +14504,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:5" ht="15" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -14512,7 +14522,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5" ht="15" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -14530,7 +14540,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5" ht="15" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -14548,7 +14558,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5" ht="15" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -14566,7 +14576,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:5" ht="15" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -14584,7 +14594,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" ht="15" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -14602,7 +14612,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" ht="15" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -14635,7 +14645,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" ht="15" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -14653,7 +14663,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" ht="15" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -14671,7 +14681,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" ht="15" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -14689,7 +14699,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" ht="15" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -14707,7 +14717,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" ht="15" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -14725,7 +14735,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" ht="15" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -14743,7 +14753,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" ht="15" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -14761,7 +14771,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" ht="15" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -14779,7 +14789,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" ht="15" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -14797,7 +14807,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" ht="15" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -14815,7 +14825,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" ht="15" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -14833,7 +14843,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" ht="15" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -14851,7 +14861,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" ht="15" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -14869,7 +14879,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" ht="15" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -14887,7 +14897,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5" ht="15" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -14905,7 +14915,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:5" ht="15" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -14923,7 +14933,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:5" ht="15" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -14941,7 +14951,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:5" ht="15" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -14959,7 +14969,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:5" ht="15" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -14977,7 +14987,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:5" ht="15" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -14995,7 +15005,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5" ht="15" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -15013,7 +15023,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:5" ht="15" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -15031,7 +15041,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5" ht="15" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -15049,7 +15059,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:5" ht="15" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -15067,7 +15077,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:5" ht="15" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -15085,7 +15095,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:5" ht="15" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -15103,7 +15113,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:5" ht="15" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -15121,7 +15131,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:5" ht="15" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -15139,7 +15149,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:5" ht="15" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -15157,7 +15167,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5" ht="15" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -15175,7 +15185,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5" ht="15" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -15193,7 +15203,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:5" ht="15" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -15211,7 +15221,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:5" ht="15" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -15229,7 +15239,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:5" ht="15" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -15247,7 +15257,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:5" ht="15" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -15265,7 +15275,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:5" ht="15" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -15283,7 +15293,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5" ht="15" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -15301,7 +15311,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:5" ht="15" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -15319,7 +15329,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:5" ht="15" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -15337,7 +15347,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:5" ht="15" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -15355,7 +15365,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5" ht="15" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -15373,7 +15383,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:5" ht="15" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -15391,7 +15401,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:5" ht="15" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -15409,7 +15419,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5" ht="15" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -15427,7 +15437,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:5" ht="15" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -15445,7 +15455,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:5" ht="15" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -15463,7 +15473,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:5" ht="15" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -15481,7 +15491,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:5" ht="15" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -15499,7 +15509,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:5" ht="15" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -15517,7 +15527,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:5" ht="15" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -15535,7 +15545,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:5" ht="15" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -15553,7 +15563,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5" ht="15" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -15571,7 +15581,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:5" ht="15" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -15589,7 +15599,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:5" ht="15" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -15607,7 +15617,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5" ht="15" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -15625,7 +15635,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:5" ht="15" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -15643,7 +15653,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:5" ht="15" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -15661,7 +15671,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:5" ht="15" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -15679,7 +15689,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:5" ht="15" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -15697,7 +15707,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:5" ht="15" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -15715,7 +15725,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5" ht="15" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -15733,7 +15743,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:5" ht="15" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -15751,7 +15761,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:5" ht="15" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -15769,7 +15779,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:5" ht="15" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -15802,7 +15812,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:5" ht="15" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -15820,7 +15830,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:5" ht="15" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -15838,7 +15848,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:5" ht="15" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -15856,7 +15866,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:5" ht="15" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -15874,7 +15884,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" ht="15" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -15892,7 +15902,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:5" ht="15" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -15910,7 +15920,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:5" ht="15" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -15928,7 +15938,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:5" ht="15" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -15946,7 +15956,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:5" ht="15" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -15964,7 +15974,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:5" ht="15" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -15982,7 +15992,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:5" ht="15" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -16000,7 +16010,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:5" ht="15" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -16018,7 +16028,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:5" ht="15" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -16036,7 +16046,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:5" ht="15" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -16054,7 +16064,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:5" ht="15" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -16072,7 +16082,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:5" ht="15" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -16090,7 +16100,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:5" ht="15" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -16108,7 +16118,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:5" ht="15" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -16126,7 +16136,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:5" ht="15" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -16144,7 +16154,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:5" ht="15" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -16162,7 +16172,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:5" ht="15" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -16180,7 +16190,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:5" ht="15" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -16198,7 +16208,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:5" ht="15" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -16216,7 +16226,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5" ht="15" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -16234,7 +16244,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5" ht="15" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -16252,7 +16262,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:5" ht="15" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -16270,7 +16280,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:5" ht="15" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -16288,7 +16298,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:5" ht="15" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -16306,7 +16316,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5" ht="15" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -16324,7 +16334,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:5" ht="15" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -16342,7 +16352,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:5" ht="15" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -16360,7 +16370,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:5" ht="15" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -16378,7 +16388,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:5" ht="15" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -16396,7 +16406,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:5" ht="15" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -16414,7 +16424,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:5" ht="15" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -16432,7 +16442,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:5" ht="15" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -16450,7 +16460,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:5" ht="15" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -16468,7 +16478,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:5" ht="15" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -16486,7 +16496,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:5" ht="15" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -16504,7 +16514,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:5" ht="15" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -16522,7 +16532,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5" ht="15" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -16540,7 +16550,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5" ht="15" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -16558,7 +16568,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:5" ht="15" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -16576,7 +16586,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:5" ht="15" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -16609,7 +16619,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:5" ht="15" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -16642,7 +16652,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:5" ht="15" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -16675,7 +16685,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5" ht="15" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -16693,7 +16703,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:5" ht="15" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -16726,7 +16736,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:5" ht="15" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -16737,7 +16747,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="D883" s="7" t="str">
-        <f t="shared" ref="D883" si="15">IF(
+        <f t="shared" ref="D883:D884" si="15">IF(
  AND(
   A883 &gt;= IF(
          YEAR(A883)&gt;=2007,
@@ -16759,16 +16769,26 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:5" ht="14">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
       <c r="B884" s="8">
         <v>46085</v>
       </c>
+      <c r="C884" s="21">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="D884" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>UTC-5</v>
+      </c>
+      <c r="E884" s="20">
+        <v>516729</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:E876">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -16780,12 +16800,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -16793,7 +16813,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -16801,7 +16821,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C6326F-6BAC-4D71-B0C5-D9375E83DA0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BB45D8-8B9E-410D-A0A3-BBB9F3D8864F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -5656,6 +5656,9 @@
                 </c:pt>
                 <c:pt idx="882">
                   <c:v>516729</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>514996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22949,7 +22952,7 @@
         <v>46092</v>
       </c>
       <c r="C885" s="21">
-        <v>1.0006944444444399</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="D885" s="7" t="str">
         <f t="shared" ref="D885" si="16">IF(
@@ -22969,6 +22972,9 @@
  "UTC-5"
 )</f>
         <v>UTC-5</v>
+      </c>
+      <c r="E885" s="20">
+        <v>514996</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BB45D8-8B9E-410D-A0A3-BBB9F3D8864F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF73BE11-12F3-421D-B575-DED1317229A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -6737,7 +6737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E885"/>
+  <dimension ref="A1:E886"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="8" bestFit="1" customWidth="1"/>
@@ -22955,7 +22955,7 @@
         <v>0.51388888888888895</v>
       </c>
       <c r="D885" s="7" t="str">
-        <f t="shared" ref="D885" si="16">IF(
+        <f t="shared" ref="D885:D886" si="16">IF(
  AND(
   A885 &gt;= IF(
          YEAR(A885)&gt;=2007,
@@ -22975,6 +22975,21 @@
       </c>
       <c r="E885" s="20">
         <v>514996</v>
+      </c>
+    </row>
+    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A886" s="8">
+        <v>46095</v>
+      </c>
+      <c r="B886" s="8">
+        <v>46099</v>
+      </c>
+      <c r="C886" s="21">
+        <v>0.52569444444444502</v>
+      </c>
+      <c r="D886" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF73BE11-12F3-421D-B575-DED1317229A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92087D6C-5594-4638-ABFE-B3DA89D21473}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -22985,7 +22985,7 @@
         <v>46099</v>
       </c>
       <c r="C886" s="21">
-        <v>0.52569444444444502</v>
+        <v>0.5</v>
       </c>
       <c r="D886" s="7" t="str">
         <f t="shared" si="16"/>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92087D6C-5594-4638-ABFE-B3DA89D21473}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E83C6F-7467-41D5-8F45-C43D530130DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -22955,7 +22955,7 @@
         <v>0.51388888888888895</v>
       </c>
       <c r="D885" s="7" t="str">
-        <f t="shared" ref="D885:D886" si="16">IF(
+        <f t="shared" ref="D885" si="16">IF(
  AND(
   A885 &gt;= IF(
          YEAR(A885)&gt;=2007,
@@ -22979,17 +22979,35 @@
     </row>
     <row r="886" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A886" s="8">
-        <v>46095</v>
+        <v>46102</v>
       </c>
       <c r="B886" s="8">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="C886" s="21">
-        <v>0.5</v>
+        <v>0.50069444444444444</v>
       </c>
       <c r="D886" s="7" t="str">
-        <f t="shared" si="16"/>
-        <v>UTC-4</v>
+        <f>IF(
+ AND(
+  A886 &gt;= IF(
+         YEAR(A886)&gt;=2007,
+         DATE(YEAR(A886),3,14)-WEEKDAY(DATE(YEAR(A886),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A886),4,7)-WEEKDAY(DATE(YEAR(A886),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A886 &lt;  IF(
+         YEAR(A886)&gt;=2007,
+         DATE(YEAR(A886),11,7)-WEEKDAY(DATE(YEAR(A886),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A886),10,31)-WEEKDAY(DATE(YEAR(A886),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E886" s="20">
+        <v>502252</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E83C6F-7467-41D5-8F45-C43D530130DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8830D25B-97AE-43FE-A4F2-181830B6ED36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="6495" windowWidth="28800" windowHeight="12120" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -78,12 +89,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -181,7 +192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -198,68 +209,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -277,7 +288,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5804,6 +5815,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5811,7 +5823,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6441,9 +6452,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6481,7 +6492,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6587,7 +6598,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6729,7 +6740,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6737,18 +6748,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E886"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E887"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="5" max="5" width="12.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6765,7 +6776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6798,7 +6809,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6816,7 +6827,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6834,7 +6845,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6852,7 +6863,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6870,7 +6881,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6888,7 +6899,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -6906,7 +6917,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -6924,7 +6935,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -6942,7 +6953,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -6960,7 +6971,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -6978,7 +6989,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -6996,7 +7007,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7014,7 +7025,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7032,7 +7043,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7050,7 +7061,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7068,7 +7079,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7086,7 +7097,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7104,7 +7115,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7122,7 +7133,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7140,7 +7151,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7158,7 +7169,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7176,7 +7187,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7194,7 +7205,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7212,7 +7223,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7230,7 +7241,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7248,7 +7259,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7266,7 +7277,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7284,7 +7295,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7302,7 +7313,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7320,7 +7331,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7338,7 +7349,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7356,7 +7367,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7374,7 +7385,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7392,7 +7403,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7410,7 +7421,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7428,7 +7439,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7446,7 +7457,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7464,7 +7475,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7482,7 +7493,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7500,7 +7511,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7518,7 +7529,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7536,7 +7547,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7554,7 +7565,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7572,7 +7583,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7590,7 +7601,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7608,7 +7619,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7626,7 +7637,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7644,7 +7655,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7662,7 +7673,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7680,7 +7691,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7698,7 +7709,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7716,7 +7727,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7734,7 +7745,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7752,7 +7763,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7770,7 +7781,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7788,7 +7799,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7806,7 +7817,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7824,7 +7835,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7842,7 +7853,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7860,7 +7871,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7878,7 +7889,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -7896,7 +7907,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -7914,7 +7925,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -7932,7 +7943,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -7965,7 +7976,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -7983,7 +7994,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8001,7 +8012,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8019,7 +8030,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8037,7 +8048,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8055,7 +8066,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8073,7 +8084,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8091,7 +8102,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8109,7 +8120,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8127,7 +8138,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8145,7 +8156,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8163,7 +8174,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8181,7 +8192,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8199,7 +8210,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8217,7 +8228,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8235,7 +8246,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8253,7 +8264,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8271,7 +8282,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8289,7 +8300,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8307,7 +8318,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8325,7 +8336,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8343,7 +8354,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8361,7 +8372,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8379,7 +8390,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8397,7 +8408,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8415,7 +8426,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8433,7 +8444,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8451,7 +8462,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8469,7 +8480,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8487,7 +8498,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8505,7 +8516,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8523,7 +8534,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8541,7 +8552,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8559,7 +8570,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8577,7 +8588,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="14" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8595,7 +8606,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="14" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8613,7 +8624,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="14" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8631,7 +8642,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="14" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8649,7 +8660,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="14" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8667,7 +8678,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="14" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8685,7 +8696,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="14" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8703,7 +8714,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="14" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8721,7 +8732,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="14" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8739,7 +8750,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="14" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8757,7 +8768,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="14" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8775,7 +8786,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="14" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8793,7 +8804,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="14" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8811,7 +8822,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="14" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8829,7 +8840,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="14" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8847,7 +8858,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="14" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8865,7 +8876,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="14" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8883,7 +8894,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="14" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -8901,7 +8912,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="14" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -8919,7 +8930,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="14" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -8937,7 +8948,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="14" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -8955,7 +8966,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="14" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -8973,7 +8984,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="14" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -8991,7 +9002,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="14" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9009,7 +9020,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="14" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9027,7 +9038,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="14" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9045,7 +9056,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="14" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9063,7 +9074,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="14" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9081,7 +9092,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="14" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9099,7 +9110,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="14" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9132,7 +9143,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="14" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9150,7 +9161,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="14" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9168,7 +9179,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="14" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9186,7 +9197,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="14" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9204,7 +9215,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="14" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9222,7 +9233,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="14" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9240,7 +9251,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="14" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9258,7 +9269,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="14" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9276,7 +9287,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="14" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9294,7 +9305,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="14" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9312,7 +9323,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="14" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9330,7 +9341,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="14" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9348,7 +9359,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="14" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9366,7 +9377,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="14" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9384,7 +9395,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="14" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9402,7 +9413,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="14" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9420,7 +9431,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="14" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9438,7 +9449,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="14" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9456,7 +9467,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="14" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9474,7 +9485,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="14" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9492,7 +9503,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="14" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9510,7 +9521,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="14" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9528,7 +9539,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="14" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9546,7 +9557,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="14" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9564,7 +9575,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="14" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9582,7 +9593,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="14" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9600,7 +9611,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="14" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9618,7 +9629,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="14" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9636,7 +9647,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="14" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9654,7 +9665,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="14" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9672,7 +9683,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="14" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9690,7 +9701,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="14" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9708,7 +9719,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" ht="14" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9726,7 +9737,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="14" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9744,7 +9755,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" ht="14" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9762,7 +9773,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="14" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9780,7 +9791,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="14" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9798,7 +9809,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="14" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9816,7 +9827,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="14" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9834,7 +9845,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="14" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9852,7 +9863,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="14" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9870,7 +9881,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="14" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9888,7 +9899,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="14" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -9906,7 +9917,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="14" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -9924,7 +9935,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="14" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -9942,7 +9953,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="14" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -9960,7 +9971,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="14" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -9978,7 +9989,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="14" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -9996,7 +10007,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="14" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10014,7 +10025,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="14" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10032,7 +10043,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="14" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10050,7 +10061,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="14" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10068,7 +10079,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="14" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10086,7 +10097,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="14" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10104,7 +10115,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="14" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10122,7 +10133,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="14" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10140,7 +10151,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="14" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10158,7 +10169,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="14" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10176,7 +10187,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="14" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10194,7 +10205,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="14" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10212,7 +10223,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="14" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10230,7 +10241,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="14" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10248,7 +10259,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="14" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10266,7 +10277,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="14" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10299,7 +10310,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="14" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10317,7 +10328,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="14" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10335,7 +10346,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="14" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10353,7 +10364,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="14" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10371,7 +10382,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="14" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10389,7 +10400,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="14" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10407,7 +10418,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="14" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10425,7 +10436,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="14" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10443,7 +10454,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="14" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10461,7 +10472,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="14" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10479,7 +10490,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="14" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10497,7 +10508,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="14" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10515,7 +10526,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="14" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10533,7 +10544,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="14" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10551,7 +10562,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="14" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10569,7 +10580,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="14" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10587,7 +10598,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="14" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10605,7 +10616,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="14" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10623,7 +10634,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="14" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10641,7 +10652,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="14" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10659,7 +10670,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="14" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10677,7 +10688,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="14" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10695,7 +10706,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="14" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10713,7 +10724,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="14" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10731,7 +10742,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="14" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10749,7 +10760,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="14" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10767,7 +10778,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="14" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10785,7 +10796,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="14" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10803,7 +10814,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="14" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10821,7 +10832,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="14" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10839,7 +10850,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="14" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10857,7 +10868,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="14" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10875,7 +10886,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="14" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -10893,7 +10904,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="14" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -10911,7 +10922,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="14" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -10929,7 +10940,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="14" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -10947,7 +10958,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="14" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -10965,7 +10976,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="14" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -10983,7 +10994,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="14" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11001,7 +11012,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="14" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11019,7 +11030,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="14" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11037,7 +11048,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="14" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11055,7 +11066,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="14" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11073,7 +11084,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="14" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11091,7 +11102,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="14" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11109,7 +11120,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="14" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11127,7 +11138,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="14" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11145,7 +11156,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="14" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11163,7 +11174,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="14" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11181,7 +11192,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="14" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11199,7 +11210,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="14" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11217,7 +11228,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="14" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11235,7 +11246,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="14" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11253,7 +11264,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="14" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11271,7 +11282,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="14" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11289,7 +11300,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="14" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11307,7 +11318,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="14" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11325,7 +11336,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="14" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11343,7 +11354,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="14" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11361,7 +11372,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="14" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11379,7 +11390,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="14" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11397,7 +11408,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="14" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11415,7 +11426,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="14" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11433,7 +11444,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="14" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11466,7 +11477,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="14" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11484,7 +11495,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="14" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11502,7 +11513,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="14" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11520,7 +11531,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="14" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11538,7 +11549,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="14" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11556,7 +11567,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="14" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11574,7 +11585,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="14" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11592,7 +11603,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="14" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11610,7 +11621,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="14" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11628,7 +11639,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="14" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11646,7 +11657,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="14" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11664,7 +11675,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="14" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11682,7 +11693,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="14" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11700,7 +11711,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="14" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11718,7 +11729,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="14" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11736,7 +11747,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="14" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11754,7 +11765,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="14" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11772,7 +11783,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="14" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11790,7 +11801,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="14" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11808,7 +11819,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="14" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11826,7 +11837,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="14" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11844,7 +11855,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="14" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11862,7 +11873,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="14" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11880,7 +11891,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="14" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -11898,7 +11909,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="14" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -11916,7 +11927,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="14" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -11934,7 +11945,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="14" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -11952,7 +11963,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="14" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -11970,7 +11981,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="14" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -11988,7 +11999,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="14" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12006,7 +12017,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="14" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12024,7 +12035,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="14" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12042,7 +12053,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="14" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12060,7 +12071,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="14" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12078,7 +12089,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="14" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12096,7 +12107,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="14" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12114,7 +12125,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="14" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12132,7 +12143,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="14" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12150,7 +12161,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="14" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12168,7 +12179,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="14" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12186,7 +12197,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="14" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12204,7 +12215,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="14" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12222,7 +12233,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="14" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12240,7 +12251,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="14" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12258,7 +12269,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="14" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12276,7 +12287,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="14" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12294,7 +12305,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="14" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12312,7 +12323,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="14" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12330,7 +12341,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="14" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12348,7 +12359,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="14" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12366,7 +12377,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="14" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12384,7 +12395,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="14" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12402,7 +12413,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="14" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12420,7 +12431,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="14" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12438,7 +12449,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="14" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12456,7 +12467,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="14" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12474,7 +12485,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="14" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12492,7 +12503,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="14" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12510,7 +12521,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="14" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12528,7 +12539,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="14" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12546,7 +12557,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="14" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12564,7 +12575,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="14" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12582,7 +12593,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="14" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12600,7 +12611,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="14" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12633,7 +12644,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="14" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12651,7 +12662,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="14" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12669,7 +12680,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="14" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12687,7 +12698,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="14" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12705,7 +12716,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="14" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12723,7 +12734,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="14" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12741,7 +12752,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="14" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12759,7 +12770,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="14" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12777,7 +12788,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="14" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12795,7 +12806,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="14" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12813,7 +12824,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="14" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12831,7 +12842,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="14" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12849,7 +12860,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="14" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12867,7 +12878,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="14" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12885,7 +12896,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="14" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -12903,7 +12914,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="14" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -12921,7 +12932,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="14" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -12939,7 +12950,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="14" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -12957,7 +12968,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="14" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -12975,7 +12986,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="14" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -12993,7 +13004,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="14" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13011,7 +13022,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="14" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13029,7 +13040,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="14" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13047,7 +13058,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="14" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13065,7 +13076,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="14" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13083,7 +13094,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="14" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13101,7 +13112,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="14" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13119,7 +13130,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="14" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13137,7 +13148,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="14" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13155,7 +13166,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="14" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13173,7 +13184,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="14" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13191,7 +13202,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="14" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13209,7 +13220,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="14" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13227,7 +13238,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="14" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13245,7 +13256,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="14" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13263,7 +13274,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="14" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13281,7 +13292,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="14" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13299,7 +13310,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="14" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13317,7 +13328,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="14" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13335,7 +13346,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="14" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13353,7 +13364,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="14" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13371,7 +13382,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="14" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13389,7 +13400,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="14" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13407,7 +13418,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="14" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13425,7 +13436,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="14" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13443,7 +13454,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="14" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13461,7 +13472,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="14" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13479,7 +13490,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="14" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13497,7 +13508,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="14" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13515,7 +13526,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="14" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13533,7 +13544,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="14" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13551,7 +13562,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="14" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13569,7 +13580,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="14" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13587,7 +13598,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="14" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13605,7 +13616,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="14" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13623,7 +13634,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="14" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13641,7 +13652,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="14" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13659,7 +13670,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="14" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13677,7 +13688,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="14" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13695,7 +13706,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="14" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13713,7 +13724,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="14" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13731,7 +13742,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="14" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13749,7 +13760,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="14" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13767,7 +13778,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="14" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13800,7 +13811,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="14" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13818,7 +13829,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="14" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13836,7 +13847,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="14" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13854,7 +13865,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="14" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13872,7 +13883,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="14" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13890,7 +13901,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="14" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -13908,7 +13919,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="14" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -13926,7 +13937,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="14" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -13944,7 +13955,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="14" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -13962,7 +13973,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="14" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -13980,7 +13991,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="14" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -13998,7 +14009,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="14" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14016,7 +14027,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="14" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14034,7 +14045,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="14" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14052,7 +14063,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="14" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14070,7 +14081,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="14" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14088,7 +14099,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="14" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14106,7 +14117,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="14" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14124,7 +14135,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="14" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14142,7 +14153,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="14" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14160,7 +14171,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="14" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14178,7 +14189,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="14" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14196,7 +14207,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="14" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14214,7 +14225,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="14" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14232,7 +14243,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="14" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14250,7 +14261,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="14" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14268,7 +14279,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="14" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14286,7 +14297,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="14" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14304,7 +14315,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="14" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14322,7 +14333,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="14" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14340,7 +14351,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="14" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14358,7 +14369,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="14" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14376,7 +14387,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="14" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14394,7 +14405,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="14" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14412,7 +14423,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="14" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14430,7 +14441,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="14" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14448,7 +14459,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="14" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14466,7 +14477,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="14" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14484,7 +14495,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="14" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14502,7 +14513,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="14" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14520,7 +14531,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="14" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14538,7 +14549,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="14" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14556,7 +14567,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="14" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14574,7 +14585,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="14" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14592,7 +14603,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="14" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14610,7 +14621,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="14" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14628,7 +14639,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="14" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14646,7 +14657,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="14" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14664,7 +14675,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="14" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14682,7 +14693,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="14" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14700,7 +14711,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="14" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14718,7 +14729,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="14" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14736,7 +14747,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="14" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14754,7 +14765,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="14" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14772,7 +14783,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="14" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14790,7 +14801,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="14" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14808,7 +14819,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="14" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14826,7 +14837,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="14" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14844,7 +14855,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="14" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14862,7 +14873,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="14" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14880,7 +14891,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="14" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -14898,7 +14909,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="14" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -14916,7 +14927,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="14" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -14934,7 +14945,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="14" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -14967,7 +14978,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="14" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -14985,7 +14996,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="14" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15003,7 +15014,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="14" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15021,7 +15032,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="14" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15039,7 +15050,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="14" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15057,7 +15068,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="14" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15075,7 +15086,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="14" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15093,7 +15104,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="14" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15111,7 +15122,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="14" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15129,7 +15140,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="14" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15147,7 +15158,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="14" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15165,7 +15176,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="14" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15183,7 +15194,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="14" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15201,7 +15212,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="14" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15219,7 +15230,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="14" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15237,7 +15248,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="14" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15255,7 +15266,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="14" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15273,7 +15284,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="14" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15291,7 +15302,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="14" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15309,7 +15320,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="14" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15327,7 +15338,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="14" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15345,7 +15356,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="14" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15363,7 +15374,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="14" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15381,7 +15392,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="14" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15399,7 +15410,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="14" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15417,7 +15428,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="14" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15435,7 +15446,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="14" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15453,7 +15464,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="14" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15471,7 +15482,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="14" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15489,7 +15500,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="14" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15507,7 +15518,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="14" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15525,7 +15536,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="14" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15543,7 +15554,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="14" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15561,7 +15572,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="14" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15579,7 +15590,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="14" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15597,7 +15608,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="14" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15615,7 +15626,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="14" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15633,7 +15644,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="14" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15651,7 +15662,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="14" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15669,7 +15680,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="14" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15687,7 +15698,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="14" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15705,7 +15716,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="14" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15723,7 +15734,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="14" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15741,7 +15752,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="14" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15759,7 +15770,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="14" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15777,7 +15788,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="14" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15795,7 +15806,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="14" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15813,7 +15824,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="14" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15831,7 +15842,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="14" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15849,7 +15860,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="14" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15867,7 +15878,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="14" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15885,7 +15896,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="14" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -15903,7 +15914,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="14" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -15921,7 +15932,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="14" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -15939,7 +15950,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="14" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -15957,7 +15968,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="14" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -15975,7 +15986,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="14" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -15993,7 +16004,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="14" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16011,7 +16022,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="14" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16029,7 +16040,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="14" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16047,7 +16058,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="14" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16065,7 +16076,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="14" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16083,7 +16094,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="14" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16101,7 +16112,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="14" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16134,7 +16145,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="14" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16152,7 +16163,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="14" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16170,7 +16181,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="14" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16188,7 +16199,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="14" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16206,7 +16217,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="14" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16224,7 +16235,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="14" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16242,7 +16253,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="14" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16260,7 +16271,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="14" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16278,7 +16289,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="14" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16296,7 +16307,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="14" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16314,7 +16325,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="14" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16332,7 +16343,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="14" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16350,7 +16361,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="14" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16368,7 +16379,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="14" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16386,7 +16397,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="14" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16404,7 +16415,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="14" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16422,7 +16433,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="14" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16440,7 +16451,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="14" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16458,7 +16469,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="14" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16476,7 +16487,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="14" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16494,7 +16505,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="14" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16512,7 +16523,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="14" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16530,7 +16541,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="14" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16548,7 +16559,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="14" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16566,7 +16577,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="14" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16584,7 +16595,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="14" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16602,7 +16613,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="14" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16620,7 +16631,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="14" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16638,7 +16649,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="14" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16656,7 +16667,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="14" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16674,7 +16685,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="14" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16692,7 +16703,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="14" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16710,7 +16721,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="14" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16728,7 +16739,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="14" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16746,7 +16757,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="14" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16764,7 +16775,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="14" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16782,7 +16793,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="14" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16800,7 +16811,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="14" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16818,7 +16829,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="14" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16836,7 +16847,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="14" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16854,7 +16865,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="14" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16872,7 +16883,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="14" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16890,7 +16901,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="14" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -16908,7 +16919,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="14" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -16926,7 +16937,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="14" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -16944,7 +16955,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="14" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -16962,7 +16973,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="14" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -16980,7 +16991,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="14" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -16998,7 +17009,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="14" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17016,7 +17027,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="14" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17034,7 +17045,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="14" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17052,7 +17063,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="14" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17070,7 +17081,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="14" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17088,7 +17099,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="14" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17106,7 +17117,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="14" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17124,7 +17135,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="14" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17142,7 +17153,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="14" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17160,7 +17171,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="14" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17178,7 +17189,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="14" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17196,7 +17207,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="14" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17214,7 +17225,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="14" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17232,7 +17243,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="14" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17250,7 +17261,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="14" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17268,7 +17279,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="14" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17301,7 +17312,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="14" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17319,7 +17330,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="14" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17337,7 +17348,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="14" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17355,7 +17366,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="14" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17373,7 +17384,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="14" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17391,7 +17402,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="14" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17409,7 +17420,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="14" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17427,7 +17438,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="14" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17445,7 +17456,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="14" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17463,7 +17474,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="14" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17481,7 +17492,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="14" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17499,7 +17510,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="14" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17517,7 +17528,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="14" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17535,7 +17546,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="14" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17553,7 +17564,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="14" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17571,7 +17582,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="14" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17589,7 +17600,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="14" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17607,7 +17618,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="14" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17625,7 +17636,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="14" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17643,7 +17654,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="14" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17661,7 +17672,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="14" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17679,7 +17690,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="14" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17697,7 +17708,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="14" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17715,7 +17726,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="14" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17733,7 +17744,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="14" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17751,7 +17762,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="14" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17769,7 +17780,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="14" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17787,7 +17798,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="14" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17805,7 +17816,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="14" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17823,7 +17834,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="14" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17841,7 +17852,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="14" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17859,7 +17870,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="14" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17877,7 +17888,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="14" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -17895,7 +17906,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="14" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -17913,7 +17924,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="14" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -17931,7 +17942,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="14" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -17949,7 +17960,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="14" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -17967,7 +17978,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="14" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -17985,7 +17996,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="14" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18003,7 +18014,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="14" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18021,7 +18032,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="14" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18039,7 +18050,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="14" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18057,7 +18068,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="14" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18075,7 +18086,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="14" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18093,7 +18104,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="14" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18111,7 +18122,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="14" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18129,7 +18140,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="14" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18147,7 +18158,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="14" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18165,7 +18176,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="14" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18183,7 +18194,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="14" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18201,7 +18212,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="14" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18219,7 +18230,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="14" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18237,7 +18248,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="14" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18255,7 +18266,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="14" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18273,7 +18284,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="14" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18291,7 +18302,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="14" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18309,7 +18320,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="14" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18327,7 +18338,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="14" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18345,7 +18356,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="14" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18363,7 +18374,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="14" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18381,7 +18392,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="14" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18399,7 +18410,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="14" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18417,7 +18428,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="14" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18435,7 +18446,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="14" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18468,7 +18479,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="14" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18486,7 +18497,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="14" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18504,7 +18515,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="14" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18522,7 +18533,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="14" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18540,7 +18551,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="14" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18558,7 +18569,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="14" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18576,7 +18587,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="14" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18594,7 +18605,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="14" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18612,7 +18623,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="14" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18630,7 +18641,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="14" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18648,7 +18659,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="14" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18666,7 +18677,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="14" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18684,7 +18695,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="14" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18702,7 +18713,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="14" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18720,7 +18731,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="14" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18738,7 +18749,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="14" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18756,7 +18767,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="14" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18774,7 +18785,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="14" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18792,7 +18803,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="14" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18810,7 +18821,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="14" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18828,7 +18839,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="14" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18846,7 +18857,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="14" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18864,7 +18875,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="14" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18882,7 +18893,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="14" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -18900,7 +18911,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="14" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -18918,7 +18929,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="14" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -18936,7 +18947,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="14" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -18954,7 +18965,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="14" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -18972,7 +18983,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="14" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -18990,7 +19001,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="14" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19008,7 +19019,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="14" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19026,7 +19037,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="14" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19044,7 +19055,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="14" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19062,7 +19073,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="14" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19080,7 +19091,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="14" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19098,7 +19109,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="14" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19116,7 +19127,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="14" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19134,7 +19145,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="14" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19152,7 +19163,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="14" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19170,7 +19181,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="14" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19188,7 +19199,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="14" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19206,7 +19217,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="14" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19224,7 +19235,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="14" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19242,7 +19253,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="14" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19260,7 +19271,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="14" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19278,7 +19289,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="14" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19296,7 +19307,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="14" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19314,7 +19325,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="14" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19332,7 +19343,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="14" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19350,7 +19361,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="14" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19368,7 +19379,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="14" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19386,7 +19397,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="14" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19404,7 +19415,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="14" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19422,7 +19433,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="14" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19440,7 +19451,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="14" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19458,7 +19469,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="14" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19476,7 +19487,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="14" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19494,7 +19505,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="14" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19512,7 +19523,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="14" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19530,7 +19541,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="14" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19548,7 +19559,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="14" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19566,7 +19577,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="14" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19584,7 +19595,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="14" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19602,7 +19613,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="14" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19635,7 +19646,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="14" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19653,7 +19664,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="14" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19671,7 +19682,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="14" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19689,7 +19700,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="14" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19707,7 +19718,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="14" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19725,7 +19736,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="14" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19743,7 +19754,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="14" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19761,7 +19772,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="14" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19779,7 +19790,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="14" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19797,7 +19808,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="14" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19815,7 +19826,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="14" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19833,7 +19844,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="14" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19851,7 +19862,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="14" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19869,7 +19880,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="14" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19887,7 +19898,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="14" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -19905,7 +19916,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="14" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -19923,7 +19934,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="14" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -19941,7 +19952,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="14" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -19959,7 +19970,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="14" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -19977,7 +19988,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" ht="14" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -19995,7 +20006,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" ht="14" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20013,7 +20024,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" ht="14" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20031,7 +20042,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" ht="14" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20049,7 +20060,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5" ht="14" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20067,7 +20078,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" ht="14" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20085,7 +20096,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" ht="14" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20103,7 +20114,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" ht="14" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20121,7 +20132,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" ht="14" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20139,7 +20150,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" ht="14" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20157,7 +20168,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" ht="14" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20175,7 +20186,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5" ht="14" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20193,7 +20204,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5" ht="14" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20211,7 +20222,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5" ht="14" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20229,7 +20240,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5" ht="14" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20247,7 +20258,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5" ht="14" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20265,7 +20276,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5" ht="14" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20283,7 +20294,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5" ht="14" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20301,7 +20312,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5" ht="14" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20319,7 +20330,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5" ht="14" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20337,7 +20348,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5" ht="14" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20355,7 +20366,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5" ht="14" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20373,7 +20384,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5" ht="14" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20391,7 +20402,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5" ht="14" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20409,7 +20420,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5" ht="14" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20427,7 +20438,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5" ht="14" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20445,7 +20456,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5" ht="14" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20463,7 +20474,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:5" ht="14" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20481,7 +20492,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:5" ht="14" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20499,7 +20510,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:5" ht="14" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20517,7 +20528,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:5" ht="14" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20535,7 +20546,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:5" ht="14" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20553,7 +20564,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:5" ht="14" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20571,7 +20582,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5" ht="14" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20589,7 +20600,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:5" ht="14" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20607,7 +20618,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:5" ht="14" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20625,7 +20636,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5" ht="14" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20643,7 +20654,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5" ht="14" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20661,7 +20672,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:5" ht="14" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20679,7 +20690,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5" ht="14" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20697,7 +20708,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5" ht="14" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20715,7 +20726,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5" ht="14" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20733,7 +20744,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:5" ht="14" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20751,7 +20762,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" ht="14" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20769,7 +20780,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" ht="14" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20802,7 +20813,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" ht="14" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20820,7 +20831,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" ht="14" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20838,7 +20849,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" ht="14" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20856,7 +20867,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" ht="14" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20874,7 +20885,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" ht="14" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -20892,7 +20903,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" ht="14" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -20910,7 +20921,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" ht="14" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -20928,7 +20939,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" ht="14" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -20946,7 +20957,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" ht="14" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -20964,7 +20975,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" ht="14" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -20982,7 +20993,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" ht="14" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21000,7 +21011,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" ht="14" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21018,7 +21029,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" ht="14" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21036,7 +21047,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" ht="14" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21054,7 +21065,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5" ht="14" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21072,7 +21083,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:5" ht="14" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21090,7 +21101,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:5" ht="14" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21108,7 +21119,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:5" ht="14" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21126,7 +21137,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:5" ht="14" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21144,7 +21155,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:5" ht="14" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21162,7 +21173,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5" ht="14" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21180,7 +21191,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:5" ht="14" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21198,7 +21209,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5" ht="14" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21216,7 +21227,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:5" ht="14" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21234,7 +21245,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:5" ht="14" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21252,7 +21263,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:5" ht="14" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21270,7 +21281,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:5" ht="14" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21288,7 +21299,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:5" ht="14" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21306,7 +21317,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:5" ht="14" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21324,7 +21335,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5" ht="14" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21342,7 +21353,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5" ht="14" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21360,7 +21371,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:5" ht="14" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21378,7 +21389,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:5" ht="14" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21396,7 +21407,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:5" ht="14" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21414,7 +21425,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:5" ht="14" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21432,7 +21443,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:5" ht="14" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21450,7 +21461,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5" ht="14" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21468,7 +21479,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:5" ht="14" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21486,7 +21497,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:5" ht="14" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21504,7 +21515,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:5" ht="14" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21522,7 +21533,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5" ht="14" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21540,7 +21551,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:5" ht="14" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21558,7 +21569,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:5" ht="14" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21576,7 +21587,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5" ht="14" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21594,7 +21605,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:5" ht="14" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21612,7 +21623,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:5" ht="14" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21630,7 +21641,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:5" ht="14" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21648,7 +21659,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:5" ht="14" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21666,7 +21677,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:5" ht="14" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21684,7 +21695,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:5" ht="14" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21702,7 +21713,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:5" ht="14" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21720,7 +21731,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5" ht="14" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21738,7 +21749,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:5" ht="14" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21756,7 +21767,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:5" ht="14" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21774,7 +21785,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5" ht="14" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21792,7 +21803,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:5" ht="14" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21810,7 +21821,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:5" ht="14" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21828,7 +21839,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:5" ht="14" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21846,7 +21857,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:5" ht="14" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21864,7 +21875,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:5" ht="14" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21882,7 +21893,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5" ht="14" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -21900,7 +21911,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:5" ht="14" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -21918,7 +21929,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:5" ht="14" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -21936,7 +21947,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:5" ht="14" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -21969,7 +21980,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:5" ht="14" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -21987,7 +21998,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:5" ht="14" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22005,7 +22016,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:5" ht="14" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22023,7 +22034,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:5" ht="14" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22041,7 +22052,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" ht="14" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22059,7 +22070,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:5" ht="14" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22077,7 +22088,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:5" ht="14" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22095,7 +22106,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:5" ht="14" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22113,7 +22124,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:5" ht="14" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22131,7 +22142,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:5" ht="14" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22149,7 +22160,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:5" ht="14" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22167,7 +22178,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:5" ht="14" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22185,7 +22196,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:5" ht="14" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22203,7 +22214,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:5" ht="14" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22221,7 +22232,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:5" ht="14" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22239,7 +22250,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:5" ht="14" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22257,7 +22268,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:5" ht="14" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22275,7 +22286,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:5" ht="14" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22293,7 +22304,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:5" ht="14" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22311,7 +22322,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:5" ht="14" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22329,7 +22340,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:5" ht="14" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22347,7 +22358,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:5" ht="14" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22365,7 +22376,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:5" ht="14" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22383,7 +22394,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5" ht="14" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22401,7 +22412,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5" ht="14" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22419,7 +22430,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:5" ht="14" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22437,7 +22448,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:5" ht="14" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22455,7 +22466,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:5" ht="14" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22473,7 +22484,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5" ht="14" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22491,7 +22502,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:5" ht="14" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22509,7 +22520,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:5" ht="14" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22527,7 +22538,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:5" ht="14" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22545,7 +22556,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:5" ht="14" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22563,7 +22574,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:5" ht="14" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22581,7 +22592,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:5" ht="14" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22599,7 +22610,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:5" ht="14" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22617,7 +22628,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:5" ht="14" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22635,7 +22646,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:5" ht="14" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22653,7 +22664,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:5" ht="14" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22671,7 +22682,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:5" ht="14" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22689,7 +22700,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5" ht="14" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22707,7 +22718,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5" ht="14" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22725,7 +22736,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:5" ht="14" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22743,7 +22754,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:5" ht="14" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22776,7 +22787,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:5" ht="14" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22809,7 +22820,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:5" ht="14" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22842,7 +22853,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5" ht="14" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22860,7 +22871,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:5" ht="14" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -22893,7 +22904,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:5" ht="14" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -22926,7 +22937,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:5" ht="14" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -22944,7 +22955,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:5" ht="14" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -22977,7 +22988,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:5">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23010,8 +23021,38 @@
         <v>502252</v>
       </c>
     </row>
+    <row r="887" spans="1:5">
+      <c r="A887" s="8">
+        <v>46109</v>
+      </c>
+      <c r="B887" s="8">
+        <v>46113</v>
+      </c>
+      <c r="C887" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="D887" s="8" t="str">
+        <f>IF(
+ AND(
+  A887 &gt;= IF(
+         YEAR(A887)&gt;=2007,
+         DATE(YEAR(A887),3,14)-WEEKDAY(DATE(YEAR(A887),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A887),4,7)-WEEKDAY(DATE(YEAR(A887),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A887 &lt;  IF(
+         YEAR(A887)&gt;=2007,
+         DATE(YEAR(A887),11,7)-WEEKDAY(DATE(YEAR(A887),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A887),10,31)-WEEKDAY(DATE(YEAR(A887),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:E876">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -23023,7 +23064,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23034,12 +23075,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23047,7 +23088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23055,7 +23096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8830D25B-97AE-43FE-A4F2-181830B6ED36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884EB1EA-C12B-475E-A03C-DC49E47E03B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -89,12 +90,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -192,7 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -209,68 +210,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,7 +289,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5815,7 +5816,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5823,6 +5823,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6452,9 +6453,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6492,7 +6493,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6598,7 +6599,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6740,7 +6741,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6749,17 +6750,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E887"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="6"/>
+    <col min="5" max="5" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6776,7 +6777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6809,7 +6810,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6827,7 +6828,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6845,7 +6846,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6863,7 +6864,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6881,7 +6882,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6899,7 +6900,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -6917,7 +6918,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -6935,7 +6936,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -6971,7 +6972,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -6989,7 +6990,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7007,7 +7008,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7025,7 +7026,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7043,7 +7044,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7061,7 +7062,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7079,7 +7080,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7097,7 +7098,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7115,7 +7116,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7133,7 +7134,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7151,7 +7152,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7169,7 +7170,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7187,7 +7188,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7205,7 +7206,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7223,7 +7224,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7241,7 +7242,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7259,7 +7260,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7277,7 +7278,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7295,7 +7296,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7313,7 +7314,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7331,7 +7332,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7349,7 +7350,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7367,7 +7368,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7385,7 +7386,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7403,7 +7404,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7421,7 +7422,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7439,7 +7440,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7457,7 +7458,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7475,7 +7476,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7493,7 +7494,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7511,7 +7512,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7529,7 +7530,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7565,7 +7566,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7583,7 +7584,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7601,7 +7602,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7619,7 +7620,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7637,7 +7638,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7655,7 +7656,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7673,7 +7674,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7691,7 +7692,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7709,7 +7710,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7727,7 +7728,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7745,7 +7746,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7763,7 +7764,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7781,7 +7782,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7799,7 +7800,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7817,7 +7818,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7835,7 +7836,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7853,7 +7854,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7871,7 +7872,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -7907,7 +7908,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -7925,7 +7926,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -7943,7 +7944,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -7976,7 +7977,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -7994,7 +7995,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8012,7 +8013,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8030,7 +8031,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8048,7 +8049,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8066,7 +8067,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8084,7 +8085,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8102,7 +8103,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8120,7 +8121,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8138,7 +8139,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8156,7 +8157,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8174,7 +8175,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8192,7 +8193,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8210,7 +8211,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8228,7 +8229,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8246,7 +8247,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8264,7 +8265,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8282,7 +8283,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8300,7 +8301,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8318,7 +8319,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8336,7 +8337,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8354,7 +8355,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8372,7 +8373,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8390,7 +8391,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8408,7 +8409,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8426,7 +8427,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8444,7 +8445,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8462,7 +8463,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8480,7 +8481,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8498,7 +8499,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8516,7 +8517,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8534,7 +8535,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8552,7 +8553,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8570,7 +8571,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8588,7 +8589,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="14" thickBot="1">
+    <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8606,7 +8607,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="14" thickBot="1">
+    <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8624,7 +8625,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="14" thickBot="1">
+    <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8642,7 +8643,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="14" thickBot="1">
+    <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8660,7 +8661,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="14" thickBot="1">
+    <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="14" thickBot="1">
+    <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8696,7 +8697,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="14" thickBot="1">
+    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8714,7 +8715,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="14" thickBot="1">
+    <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8732,7 +8733,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="14" thickBot="1">
+    <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8750,7 +8751,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="14" thickBot="1">
+    <row r="110" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8768,7 +8769,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="14" thickBot="1">
+    <row r="111" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8786,7 +8787,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="14" thickBot="1">
+    <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8804,7 +8805,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="14" thickBot="1">
+    <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8822,7 +8823,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="14" thickBot="1">
+    <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8840,7 +8841,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="14" thickBot="1">
+    <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8858,7 +8859,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="14" thickBot="1">
+    <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8876,7 +8877,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="14" thickBot="1">
+    <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8894,7 +8895,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="14" thickBot="1">
+    <row r="118" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -8912,7 +8913,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="14" thickBot="1">
+    <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -8930,7 +8931,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="14" thickBot="1">
+    <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -8948,7 +8949,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="14" thickBot="1">
+    <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -8966,7 +8967,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="14" thickBot="1">
+    <row r="122" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -8984,7 +8985,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="14" thickBot="1">
+    <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9002,7 +9003,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14" thickBot="1">
+    <row r="124" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9020,7 +9021,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="14" thickBot="1">
+    <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9038,7 +9039,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="14" thickBot="1">
+    <row r="126" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9056,7 +9057,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="14" thickBot="1">
+    <row r="127" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9074,7 +9075,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="14" thickBot="1">
+    <row r="128" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9092,7 +9093,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="14" thickBot="1">
+    <row r="129" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9110,7 +9111,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="14" thickBot="1">
+    <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9143,7 +9144,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="14" thickBot="1">
+    <row r="131" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9161,7 +9162,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14" thickBot="1">
+    <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9179,7 +9180,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="14" thickBot="1">
+    <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9197,7 +9198,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="14" thickBot="1">
+    <row r="134" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9215,7 +9216,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="14" thickBot="1">
+    <row r="135" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9233,7 +9234,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="14" thickBot="1">
+    <row r="136" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9251,7 +9252,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="14" thickBot="1">
+    <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9269,7 +9270,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="14" thickBot="1">
+    <row r="138" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9287,7 +9288,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="14" thickBot="1">
+    <row r="139" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9305,7 +9306,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="14" thickBot="1">
+    <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14" thickBot="1">
+    <row r="141" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9341,7 +9342,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="14" thickBot="1">
+    <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9359,7 +9360,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="14" thickBot="1">
+    <row r="143" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9377,7 +9378,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14" thickBot="1">
+    <row r="144" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9395,7 +9396,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14" thickBot="1">
+    <row r="145" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9413,7 +9414,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14" thickBot="1">
+    <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9431,7 +9432,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="14" thickBot="1">
+    <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9449,7 +9450,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="14" thickBot="1">
+    <row r="148" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9467,7 +9468,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="14" thickBot="1">
+    <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9485,7 +9486,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="14" thickBot="1">
+    <row r="150" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9503,7 +9504,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="14" thickBot="1">
+    <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9521,7 +9522,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="14" thickBot="1">
+    <row r="152" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9539,7 +9540,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="14" thickBot="1">
+    <row r="153" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9557,7 +9558,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="14" thickBot="1">
+    <row r="154" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9575,7 +9576,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="14" thickBot="1">
+    <row r="155" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9593,7 +9594,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="14" thickBot="1">
+    <row r="156" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9611,7 +9612,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="14" thickBot="1">
+    <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9629,7 +9630,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="14" thickBot="1">
+    <row r="158" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9647,7 +9648,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="14" thickBot="1">
+    <row r="159" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9665,7 +9666,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14" thickBot="1">
+    <row r="160" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9683,7 +9684,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="14" thickBot="1">
+    <row r="161" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9701,7 +9702,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="14" thickBot="1">
+    <row r="162" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9719,7 +9720,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="14" thickBot="1">
+    <row r="163" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9737,7 +9738,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="14" thickBot="1">
+    <row r="164" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9755,7 +9756,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="14" thickBot="1">
+    <row r="165" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9773,7 +9774,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="14" thickBot="1">
+    <row r="166" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9791,7 +9792,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="14" thickBot="1">
+    <row r="167" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9809,7 +9810,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="14" thickBot="1">
+    <row r="168" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9827,7 +9828,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="14" thickBot="1">
+    <row r="169" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9845,7 +9846,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="14" thickBot="1">
+    <row r="170" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9863,7 +9864,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="14" thickBot="1">
+    <row r="171" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9881,7 +9882,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="14" thickBot="1">
+    <row r="172" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9899,7 +9900,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="14" thickBot="1">
+    <row r="173" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -9917,7 +9918,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="14" thickBot="1">
+    <row r="174" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -9935,7 +9936,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="14" thickBot="1">
+    <row r="175" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -9953,7 +9954,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="14" thickBot="1">
+    <row r="176" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -9971,7 +9972,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="14" thickBot="1">
+    <row r="177" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -9989,7 +9990,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="14" thickBot="1">
+    <row r="178" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10007,7 +10008,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="14" thickBot="1">
+    <row r="179" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10025,7 +10026,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="14" thickBot="1">
+    <row r="180" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10043,7 +10044,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="14" thickBot="1">
+    <row r="181" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10061,7 +10062,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="14" thickBot="1">
+    <row r="182" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10079,7 +10080,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="14" thickBot="1">
+    <row r="183" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10097,7 +10098,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="14" thickBot="1">
+    <row r="184" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10115,7 +10116,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="14" thickBot="1">
+    <row r="185" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10133,7 +10134,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="14" thickBot="1">
+    <row r="186" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10151,7 +10152,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="14" thickBot="1">
+    <row r="187" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10169,7 +10170,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="14" thickBot="1">
+    <row r="188" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10187,7 +10188,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="14" thickBot="1">
+    <row r="189" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10205,7 +10206,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="14" thickBot="1">
+    <row r="190" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10223,7 +10224,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="14" thickBot="1">
+    <row r="191" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10241,7 +10242,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="14" thickBot="1">
+    <row r="192" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10259,7 +10260,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="14" thickBot="1">
+    <row r="193" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10277,7 +10278,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="14" thickBot="1">
+    <row r="194" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10310,7 +10311,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="14" thickBot="1">
+    <row r="195" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10328,7 +10329,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="14" thickBot="1">
+    <row r="196" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10346,7 +10347,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="14" thickBot="1">
+    <row r="197" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10364,7 +10365,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="14" thickBot="1">
+    <row r="198" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10382,7 +10383,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="14" thickBot="1">
+    <row r="199" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10400,7 +10401,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="14" thickBot="1">
+    <row r="200" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10418,7 +10419,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="14" thickBot="1">
+    <row r="201" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="14" thickBot="1">
+    <row r="202" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10454,7 +10455,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="14" thickBot="1">
+    <row r="203" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10472,7 +10473,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="14" thickBot="1">
+    <row r="204" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10490,7 +10491,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="14" thickBot="1">
+    <row r="205" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="14" thickBot="1">
+    <row r="206" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10526,7 +10527,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="14" thickBot="1">
+    <row r="207" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10544,7 +10545,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="14" thickBot="1">
+    <row r="208" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10562,7 +10563,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="14" thickBot="1">
+    <row r="209" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10580,7 +10581,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="14" thickBot="1">
+    <row r="210" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10598,7 +10599,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="14" thickBot="1">
+    <row r="211" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10616,7 +10617,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="14" thickBot="1">
+    <row r="212" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10634,7 +10635,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="14" thickBot="1">
+    <row r="213" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10652,7 +10653,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="14" thickBot="1">
+    <row r="214" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10670,7 +10671,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="14" thickBot="1">
+    <row r="215" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10688,7 +10689,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="14" thickBot="1">
+    <row r="216" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10706,7 +10707,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="14" thickBot="1">
+    <row r="217" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10724,7 +10725,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="14" thickBot="1">
+    <row r="218" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10742,7 +10743,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="14" thickBot="1">
+    <row r="219" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10760,7 +10761,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="14" thickBot="1">
+    <row r="220" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10778,7 +10779,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="14" thickBot="1">
+    <row r="221" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="14" thickBot="1">
+    <row r="222" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10814,7 +10815,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="14" thickBot="1">
+    <row r="223" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10832,7 +10833,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="14" thickBot="1">
+    <row r="224" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10850,7 +10851,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="14" thickBot="1">
+    <row r="225" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10868,7 +10869,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="14" thickBot="1">
+    <row r="226" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10886,7 +10887,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="14" thickBot="1">
+    <row r="227" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -10904,7 +10905,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="14" thickBot="1">
+    <row r="228" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -10922,7 +10923,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="14" thickBot="1">
+    <row r="229" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -10940,7 +10941,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="14" thickBot="1">
+    <row r="230" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="14" thickBot="1">
+    <row r="231" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="14" thickBot="1">
+    <row r="232" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -10994,7 +10995,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="14" thickBot="1">
+    <row r="233" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11012,7 +11013,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="14" thickBot="1">
+    <row r="234" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11030,7 +11031,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="14" thickBot="1">
+    <row r="235" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11048,7 +11049,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="14" thickBot="1">
+    <row r="236" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11066,7 +11067,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="14" thickBot="1">
+    <row r="237" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11084,7 +11085,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="14" thickBot="1">
+    <row r="238" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11102,7 +11103,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="14" thickBot="1">
+    <row r="239" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11120,7 +11121,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="14" thickBot="1">
+    <row r="240" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11138,7 +11139,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="14" thickBot="1">
+    <row r="241" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11156,7 +11157,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="14" thickBot="1">
+    <row r="242" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11174,7 +11175,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="14" thickBot="1">
+    <row r="243" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11192,7 +11193,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="14" thickBot="1">
+    <row r="244" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="14" thickBot="1">
+    <row r="245" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11228,7 +11229,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="14" thickBot="1">
+    <row r="246" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11246,7 +11247,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="14" thickBot="1">
+    <row r="247" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11264,7 +11265,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="14" thickBot="1">
+    <row r="248" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11282,7 +11283,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="14" thickBot="1">
+    <row r="249" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11300,7 +11301,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="14" thickBot="1">
+    <row r="250" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11318,7 +11319,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="14" thickBot="1">
+    <row r="251" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="14" thickBot="1">
+    <row r="252" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11354,7 +11355,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="14" thickBot="1">
+    <row r="253" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11372,7 +11373,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="14" thickBot="1">
+    <row r="254" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11390,7 +11391,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="14" thickBot="1">
+    <row r="255" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11408,7 +11409,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="14" thickBot="1">
+    <row r="256" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11426,7 +11427,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="14" thickBot="1">
+    <row r="257" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11444,7 +11445,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="14" thickBot="1">
+    <row r="258" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11477,7 +11478,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="14" thickBot="1">
+    <row r="259" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11495,7 +11496,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="14" thickBot="1">
+    <row r="260" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11513,7 +11514,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="14" thickBot="1">
+    <row r="261" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11531,7 +11532,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="14" thickBot="1">
+    <row r="262" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11549,7 +11550,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="14" thickBot="1">
+    <row r="263" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11567,7 +11568,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="14" thickBot="1">
+    <row r="264" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11585,7 +11586,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="14" thickBot="1">
+    <row r="265" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11603,7 +11604,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="14" thickBot="1">
+    <row r="266" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11621,7 +11622,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="14" thickBot="1">
+    <row r="267" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11639,7 +11640,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="14" thickBot="1">
+    <row r="268" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11657,7 +11658,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="14" thickBot="1">
+    <row r="269" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11675,7 +11676,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="14" thickBot="1">
+    <row r="270" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11693,7 +11694,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="14" thickBot="1">
+    <row r="271" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11711,7 +11712,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="14" thickBot="1">
+    <row r="272" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11729,7 +11730,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="14" thickBot="1">
+    <row r="273" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11747,7 +11748,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="14" thickBot="1">
+    <row r="274" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11765,7 +11766,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="14" thickBot="1">
+    <row r="275" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11783,7 +11784,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="14" thickBot="1">
+    <row r="276" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11801,7 +11802,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14" thickBot="1">
+    <row r="277" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11819,7 +11820,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14" thickBot="1">
+    <row r="278" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11837,7 +11838,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="14" thickBot="1">
+    <row r="279" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11855,7 +11856,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="14" thickBot="1">
+    <row r="280" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11873,7 +11874,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="14" thickBot="1">
+    <row r="281" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11891,7 +11892,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="14" thickBot="1">
+    <row r="282" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -11909,7 +11910,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="14" thickBot="1">
+    <row r="283" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -11927,7 +11928,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="14" thickBot="1">
+    <row r="284" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -11945,7 +11946,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="14" thickBot="1">
+    <row r="285" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -11963,7 +11964,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="14" thickBot="1">
+    <row r="286" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -11981,7 +11982,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="14" thickBot="1">
+    <row r="287" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -11999,7 +12000,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="14" thickBot="1">
+    <row r="288" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12017,7 +12018,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="14" thickBot="1">
+    <row r="289" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12035,7 +12036,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="14" thickBot="1">
+    <row r="290" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12053,7 +12054,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="14" thickBot="1">
+    <row r="291" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12071,7 +12072,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="14" thickBot="1">
+    <row r="292" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12089,7 +12090,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="14" thickBot="1">
+    <row r="293" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12107,7 +12108,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="14" thickBot="1">
+    <row r="294" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12125,7 +12126,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="14" thickBot="1">
+    <row r="295" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12143,7 +12144,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="14" thickBot="1">
+    <row r="296" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12161,7 +12162,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="14" thickBot="1">
+    <row r="297" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12179,7 +12180,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="14" thickBot="1">
+    <row r="298" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12197,7 +12198,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="14" thickBot="1">
+    <row r="299" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12215,7 +12216,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="14" thickBot="1">
+    <row r="300" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12233,7 +12234,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="14" thickBot="1">
+    <row r="301" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12251,7 +12252,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="14" thickBot="1">
+    <row r="302" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12269,7 +12270,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="14" thickBot="1">
+    <row r="303" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12287,7 +12288,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="14" thickBot="1">
+    <row r="304" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12305,7 +12306,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="14" thickBot="1">
+    <row r="305" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12323,7 +12324,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="14" thickBot="1">
+    <row r="306" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12341,7 +12342,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="14" thickBot="1">
+    <row r="307" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12359,7 +12360,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="14" thickBot="1">
+    <row r="308" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12377,7 +12378,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="14" thickBot="1">
+    <row r="309" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12395,7 +12396,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="14" thickBot="1">
+    <row r="310" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12413,7 +12414,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="14" thickBot="1">
+    <row r="311" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12431,7 +12432,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="14" thickBot="1">
+    <row r="312" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12449,7 +12450,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="14" thickBot="1">
+    <row r="313" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12467,7 +12468,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="14" thickBot="1">
+    <row r="314" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12485,7 +12486,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="14" thickBot="1">
+    <row r="315" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12503,7 +12504,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="14" thickBot="1">
+    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12521,7 +12522,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="14" thickBot="1">
+    <row r="317" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12539,7 +12540,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="14" thickBot="1">
+    <row r="318" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12557,7 +12558,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="14" thickBot="1">
+    <row r="319" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12575,7 +12576,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="14" thickBot="1">
+    <row r="320" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12593,7 +12594,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="14" thickBot="1">
+    <row r="321" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12611,7 +12612,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="14" thickBot="1">
+    <row r="322" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12644,7 +12645,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="14" thickBot="1">
+    <row r="323" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12662,7 +12663,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="14" thickBot="1">
+    <row r="324" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12680,7 +12681,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="14" thickBot="1">
+    <row r="325" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12698,7 +12699,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="14" thickBot="1">
+    <row r="326" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12716,7 +12717,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="14" thickBot="1">
+    <row r="327" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12734,7 +12735,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="14" thickBot="1">
+    <row r="328" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12752,7 +12753,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="14" thickBot="1">
+    <row r="329" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12770,7 +12771,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="14" thickBot="1">
+    <row r="330" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12788,7 +12789,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="14" thickBot="1">
+    <row r="331" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12806,7 +12807,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="14" thickBot="1">
+    <row r="332" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12824,7 +12825,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="14" thickBot="1">
+    <row r="333" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12842,7 +12843,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="14" thickBot="1">
+    <row r="334" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12860,7 +12861,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="14" thickBot="1">
+    <row r="335" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12878,7 +12879,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="14" thickBot="1">
+    <row r="336" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12896,7 +12897,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="14" thickBot="1">
+    <row r="337" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -12914,7 +12915,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="14" thickBot="1">
+    <row r="338" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -12932,7 +12933,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="14" thickBot="1">
+    <row r="339" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -12950,7 +12951,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="14" thickBot="1">
+    <row r="340" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -12968,7 +12969,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="14" thickBot="1">
+    <row r="341" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="14" thickBot="1">
+    <row r="342" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13004,7 +13005,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="14" thickBot="1">
+    <row r="343" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13022,7 +13023,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="14" thickBot="1">
+    <row r="344" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13040,7 +13041,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="14" thickBot="1">
+    <row r="345" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13058,7 +13059,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="14" thickBot="1">
+    <row r="346" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13076,7 +13077,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="14" thickBot="1">
+    <row r="347" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13094,7 +13095,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="14" thickBot="1">
+    <row r="348" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13112,7 +13113,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="14" thickBot="1">
+    <row r="349" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13130,7 +13131,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="14" thickBot="1">
+    <row r="350" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13148,7 +13149,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="14" thickBot="1">
+    <row r="351" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13166,7 +13167,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="14" thickBot="1">
+    <row r="352" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13184,7 +13185,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="14" thickBot="1">
+    <row r="353" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13202,7 +13203,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="14" thickBot="1">
+    <row r="354" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13220,7 +13221,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="14" thickBot="1">
+    <row r="355" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13238,7 +13239,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="14" thickBot="1">
+    <row r="356" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13256,7 +13257,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="14" thickBot="1">
+    <row r="357" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13274,7 +13275,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="14" thickBot="1">
+    <row r="358" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13292,7 +13293,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="14" thickBot="1">
+    <row r="359" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13310,7 +13311,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="14" thickBot="1">
+    <row r="360" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13328,7 +13329,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="14" thickBot="1">
+    <row r="361" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13346,7 +13347,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="14" thickBot="1">
+    <row r="362" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13364,7 +13365,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="14" thickBot="1">
+    <row r="363" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13382,7 +13383,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="14" thickBot="1">
+    <row r="364" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13400,7 +13401,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="14" thickBot="1">
+    <row r="365" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13418,7 +13419,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="14" thickBot="1">
+    <row r="366" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13436,7 +13437,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="14" thickBot="1">
+    <row r="367" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13454,7 +13455,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="14" thickBot="1">
+    <row r="368" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13472,7 +13473,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="14" thickBot="1">
+    <row r="369" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="14" thickBot="1">
+    <row r="370" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13508,7 +13509,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="14" thickBot="1">
+    <row r="371" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13526,7 +13527,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="14" thickBot="1">
+    <row r="372" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13544,7 +13545,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="14" thickBot="1">
+    <row r="373" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13562,7 +13563,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="14" thickBot="1">
+    <row r="374" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13580,7 +13581,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="14" thickBot="1">
+    <row r="375" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13598,7 +13599,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="14" thickBot="1">
+    <row r="376" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13616,7 +13617,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="14" thickBot="1">
+    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13634,7 +13635,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="14" thickBot="1">
+    <row r="378" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13652,7 +13653,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="14" thickBot="1">
+    <row r="379" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13670,7 +13671,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="14" thickBot="1">
+    <row r="380" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13688,7 +13689,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="14" thickBot="1">
+    <row r="381" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13706,7 +13707,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="14" thickBot="1">
+    <row r="382" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13724,7 +13725,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="14" thickBot="1">
+    <row r="383" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13742,7 +13743,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="14" thickBot="1">
+    <row r="384" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13760,7 +13761,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="14" thickBot="1">
+    <row r="385" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13778,7 +13779,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="14" thickBot="1">
+    <row r="386" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13811,7 +13812,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="14" thickBot="1">
+    <row r="387" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13829,7 +13830,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="14" thickBot="1">
+    <row r="388" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13847,7 +13848,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="14" thickBot="1">
+    <row r="389" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13865,7 +13866,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="14" thickBot="1">
+    <row r="390" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13883,7 +13884,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="14" thickBot="1">
+    <row r="391" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13901,7 +13902,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="14" thickBot="1">
+    <row r="392" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -13919,7 +13920,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="14" thickBot="1">
+    <row r="393" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -13937,7 +13938,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="14" thickBot="1">
+    <row r="394" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -13955,7 +13956,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="14" thickBot="1">
+    <row r="395" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -13973,7 +13974,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="14" thickBot="1">
+    <row r="396" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -13991,7 +13992,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="14" thickBot="1">
+    <row r="397" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14009,7 +14010,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="14" thickBot="1">
+    <row r="398" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14027,7 +14028,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="14" thickBot="1">
+    <row r="399" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14045,7 +14046,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="14" thickBot="1">
+    <row r="400" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14063,7 +14064,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="14" thickBot="1">
+    <row r="401" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14081,7 +14082,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="14" thickBot="1">
+    <row r="402" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14099,7 +14100,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="14" thickBot="1">
+    <row r="403" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14117,7 +14118,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="14" thickBot="1">
+    <row r="404" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14135,7 +14136,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="14" thickBot="1">
+    <row r="405" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14153,7 +14154,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="14" thickBot="1">
+    <row r="406" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14171,7 +14172,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="14" thickBot="1">
+    <row r="407" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14189,7 +14190,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="14" thickBot="1">
+    <row r="408" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14207,7 +14208,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="14" thickBot="1">
+    <row r="409" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14225,7 +14226,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="14" thickBot="1">
+    <row r="410" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14243,7 +14244,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="14" thickBot="1">
+    <row r="411" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14261,7 +14262,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="14" thickBot="1">
+    <row r="412" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14279,7 +14280,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="14" thickBot="1">
+    <row r="413" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14297,7 +14298,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="14" thickBot="1">
+    <row r="414" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14315,7 +14316,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="14" thickBot="1">
+    <row r="415" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14333,7 +14334,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="14" thickBot="1">
+    <row r="416" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14351,7 +14352,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="14" thickBot="1">
+    <row r="417" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14369,7 +14370,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="14" thickBot="1">
+    <row r="418" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14387,7 +14388,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="14" thickBot="1">
+    <row r="419" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14405,7 +14406,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="14" thickBot="1">
+    <row r="420" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14423,7 +14424,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="14" thickBot="1">
+    <row r="421" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14441,7 +14442,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="14" thickBot="1">
+    <row r="422" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14459,7 +14460,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="14" thickBot="1">
+    <row r="423" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14477,7 +14478,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="14" thickBot="1">
+    <row r="424" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14495,7 +14496,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="14" thickBot="1">
+    <row r="425" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14513,7 +14514,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="14" thickBot="1">
+    <row r="426" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14531,7 +14532,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="14" thickBot="1">
+    <row r="427" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14549,7 +14550,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="14" thickBot="1">
+    <row r="428" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14567,7 +14568,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="14" thickBot="1">
+    <row r="429" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14585,7 +14586,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="14" thickBot="1">
+    <row r="430" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14603,7 +14604,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="14" thickBot="1">
+    <row r="431" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14621,7 +14622,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="14" thickBot="1">
+    <row r="432" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14639,7 +14640,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="14" thickBot="1">
+    <row r="433" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14657,7 +14658,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="14" thickBot="1">
+    <row r="434" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14675,7 +14676,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="14" thickBot="1">
+    <row r="435" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14693,7 +14694,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="14" thickBot="1">
+    <row r="436" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14711,7 +14712,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="14" thickBot="1">
+    <row r="437" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14729,7 +14730,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="14" thickBot="1">
+    <row r="438" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14747,7 +14748,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="14" thickBot="1">
+    <row r="439" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14765,7 +14766,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="14" thickBot="1">
+    <row r="440" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14783,7 +14784,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="14" thickBot="1">
+    <row r="441" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14801,7 +14802,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="14" thickBot="1">
+    <row r="442" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14819,7 +14820,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="14" thickBot="1">
+    <row r="443" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14837,7 +14838,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="14" thickBot="1">
+    <row r="444" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14855,7 +14856,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="14" thickBot="1">
+    <row r="445" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14873,7 +14874,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="14" thickBot="1">
+    <row r="446" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14891,7 +14892,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="14" thickBot="1">
+    <row r="447" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -14909,7 +14910,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="14" thickBot="1">
+    <row r="448" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -14927,7 +14928,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="14" thickBot="1">
+    <row r="449" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -14945,7 +14946,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="14" thickBot="1">
+    <row r="450" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -14978,7 +14979,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="14" thickBot="1">
+    <row r="451" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -14996,7 +14997,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="14" thickBot="1">
+    <row r="452" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15014,7 +15015,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="14" thickBot="1">
+    <row r="453" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15032,7 +15033,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="14" thickBot="1">
+    <row r="454" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15050,7 +15051,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="14" thickBot="1">
+    <row r="455" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15068,7 +15069,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="14" thickBot="1">
+    <row r="456" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15086,7 +15087,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="14" thickBot="1">
+    <row r="457" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15104,7 +15105,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="14" thickBot="1">
+    <row r="458" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15122,7 +15123,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="14" thickBot="1">
+    <row r="459" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15140,7 +15141,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="14" thickBot="1">
+    <row r="460" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15158,7 +15159,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="14" thickBot="1">
+    <row r="461" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15176,7 +15177,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="14" thickBot="1">
+    <row r="462" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15194,7 +15195,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="14" thickBot="1">
+    <row r="463" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15212,7 +15213,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="14" thickBot="1">
+    <row r="464" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15230,7 +15231,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="14" thickBot="1">
+    <row r="465" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15248,7 +15249,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="14" thickBot="1">
+    <row r="466" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15266,7 +15267,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="14" thickBot="1">
+    <row r="467" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15284,7 +15285,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="14" thickBot="1">
+    <row r="468" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15302,7 +15303,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="14" thickBot="1">
+    <row r="469" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15320,7 +15321,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="14" thickBot="1">
+    <row r="470" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15338,7 +15339,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="14" thickBot="1">
+    <row r="471" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15356,7 +15357,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="14" thickBot="1">
+    <row r="472" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15374,7 +15375,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="14" thickBot="1">
+    <row r="473" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15392,7 +15393,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="14" thickBot="1">
+    <row r="474" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15410,7 +15411,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="14" thickBot="1">
+    <row r="475" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15428,7 +15429,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="14" thickBot="1">
+    <row r="476" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15446,7 +15447,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="14" thickBot="1">
+    <row r="477" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15464,7 +15465,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="14" thickBot="1">
+    <row r="478" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15482,7 +15483,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="14" thickBot="1">
+    <row r="479" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15500,7 +15501,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="14" thickBot="1">
+    <row r="480" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15518,7 +15519,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="14" thickBot="1">
+    <row r="481" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15536,7 +15537,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="14" thickBot="1">
+    <row r="482" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15554,7 +15555,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="14" thickBot="1">
+    <row r="483" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15572,7 +15573,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="14" thickBot="1">
+    <row r="484" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15590,7 +15591,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="14" thickBot="1">
+    <row r="485" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15608,7 +15609,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="14" thickBot="1">
+    <row r="486" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15626,7 +15627,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="14" thickBot="1">
+    <row r="487" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15644,7 +15645,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="14" thickBot="1">
+    <row r="488" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15662,7 +15663,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="14" thickBot="1">
+    <row r="489" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15680,7 +15681,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="14" thickBot="1">
+    <row r="490" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15698,7 +15699,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="14" thickBot="1">
+    <row r="491" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15716,7 +15717,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="14" thickBot="1">
+    <row r="492" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15734,7 +15735,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="14" thickBot="1">
+    <row r="493" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15752,7 +15753,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="14" thickBot="1">
+    <row r="494" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15770,7 +15771,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="14" thickBot="1">
+    <row r="495" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15788,7 +15789,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="14" thickBot="1">
+    <row r="496" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15806,7 +15807,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="14" thickBot="1">
+    <row r="497" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15824,7 +15825,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="14" thickBot="1">
+    <row r="498" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15842,7 +15843,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="14" thickBot="1">
+    <row r="499" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15860,7 +15861,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="14" thickBot="1">
+    <row r="500" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15878,7 +15879,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="14" thickBot="1">
+    <row r="501" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15896,7 +15897,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="14" thickBot="1">
+    <row r="502" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -15914,7 +15915,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="14" thickBot="1">
+    <row r="503" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -15932,7 +15933,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="14" thickBot="1">
+    <row r="504" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -15950,7 +15951,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="14" thickBot="1">
+    <row r="505" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -15968,7 +15969,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="14" thickBot="1">
+    <row r="506" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -15986,7 +15987,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="14" thickBot="1">
+    <row r="507" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16004,7 +16005,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="14" thickBot="1">
+    <row r="508" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16022,7 +16023,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="14" thickBot="1">
+    <row r="509" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16040,7 +16041,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="14" thickBot="1">
+    <row r="510" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16058,7 +16059,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="14" thickBot="1">
+    <row r="511" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16076,7 +16077,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="14" thickBot="1">
+    <row r="512" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16094,7 +16095,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="14" thickBot="1">
+    <row r="513" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16112,7 +16113,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="14" thickBot="1">
+    <row r="514" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16145,7 +16146,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="14" thickBot="1">
+    <row r="515" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16163,7 +16164,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="14" thickBot="1">
+    <row r="516" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16181,7 +16182,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="14" thickBot="1">
+    <row r="517" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16199,7 +16200,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="14" thickBot="1">
+    <row r="518" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16217,7 +16218,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="14" thickBot="1">
+    <row r="519" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16235,7 +16236,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="14" thickBot="1">
+    <row r="520" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16253,7 +16254,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="14" thickBot="1">
+    <row r="521" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16271,7 +16272,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="14" thickBot="1">
+    <row r="522" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16289,7 +16290,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="14" thickBot="1">
+    <row r="523" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16307,7 +16308,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="14" thickBot="1">
+    <row r="524" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16325,7 +16326,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="14" thickBot="1">
+    <row r="525" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16343,7 +16344,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="14" thickBot="1">
+    <row r="526" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16361,7 +16362,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="14" thickBot="1">
+    <row r="527" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16379,7 +16380,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="14" thickBot="1">
+    <row r="528" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16397,7 +16398,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="14" thickBot="1">
+    <row r="529" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16415,7 +16416,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="14" thickBot="1">
+    <row r="530" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16433,7 +16434,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="14" thickBot="1">
+    <row r="531" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16451,7 +16452,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="14" thickBot="1">
+    <row r="532" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16469,7 +16470,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="14" thickBot="1">
+    <row r="533" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16487,7 +16488,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="14" thickBot="1">
+    <row r="534" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16505,7 +16506,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="14" thickBot="1">
+    <row r="535" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16523,7 +16524,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="14" thickBot="1">
+    <row r="536" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16541,7 +16542,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="14" thickBot="1">
+    <row r="537" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16559,7 +16560,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="14" thickBot="1">
+    <row r="538" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16577,7 +16578,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="14" thickBot="1">
+    <row r="539" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16595,7 +16596,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="14" thickBot="1">
+    <row r="540" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16613,7 +16614,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="14" thickBot="1">
+    <row r="541" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16631,7 +16632,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="14" thickBot="1">
+    <row r="542" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16649,7 +16650,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="14" thickBot="1">
+    <row r="543" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16667,7 +16668,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="14" thickBot="1">
+    <row r="544" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16685,7 +16686,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="14" thickBot="1">
+    <row r="545" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16703,7 +16704,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="14" thickBot="1">
+    <row r="546" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16721,7 +16722,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="14" thickBot="1">
+    <row r="547" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16739,7 +16740,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="14" thickBot="1">
+    <row r="548" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16757,7 +16758,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="14" thickBot="1">
+    <row r="549" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16775,7 +16776,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="14" thickBot="1">
+    <row r="550" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16793,7 +16794,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="14" thickBot="1">
+    <row r="551" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16811,7 +16812,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="14" thickBot="1">
+    <row r="552" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16829,7 +16830,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="14" thickBot="1">
+    <row r="553" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16847,7 +16848,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="14" thickBot="1">
+    <row r="554" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16865,7 +16866,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="14" thickBot="1">
+    <row r="555" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16883,7 +16884,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="14" thickBot="1">
+    <row r="556" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16901,7 +16902,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="14" thickBot="1">
+    <row r="557" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -16919,7 +16920,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="14" thickBot="1">
+    <row r="558" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -16937,7 +16938,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="14" thickBot="1">
+    <row r="559" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -16955,7 +16956,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="14" thickBot="1">
+    <row r="560" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -16973,7 +16974,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="14" thickBot="1">
+    <row r="561" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -16991,7 +16992,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="14" thickBot="1">
+    <row r="562" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17009,7 +17010,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="14" thickBot="1">
+    <row r="563" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17027,7 +17028,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="14" thickBot="1">
+    <row r="564" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17045,7 +17046,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="14" thickBot="1">
+    <row r="565" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17063,7 +17064,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="14" thickBot="1">
+    <row r="566" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17081,7 +17082,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="14" thickBot="1">
+    <row r="567" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17099,7 +17100,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="14" thickBot="1">
+    <row r="568" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17117,7 +17118,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="14" thickBot="1">
+    <row r="569" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17135,7 +17136,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="14" thickBot="1">
+    <row r="570" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17153,7 +17154,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="14" thickBot="1">
+    <row r="571" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17171,7 +17172,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="14" thickBot="1">
+    <row r="572" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17189,7 +17190,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="14" thickBot="1">
+    <row r="573" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17207,7 +17208,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="14" thickBot="1">
+    <row r="574" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17225,7 +17226,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="14" thickBot="1">
+    <row r="575" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17243,7 +17244,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="14" thickBot="1">
+    <row r="576" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17261,7 +17262,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="14" thickBot="1">
+    <row r="577" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17279,7 +17280,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="14" thickBot="1">
+    <row r="578" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17312,7 +17313,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="14" thickBot="1">
+    <row r="579" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17330,7 +17331,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="14" thickBot="1">
+    <row r="580" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17348,7 +17349,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="14" thickBot="1">
+    <row r="581" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17366,7 +17367,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="14" thickBot="1">
+    <row r="582" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17384,7 +17385,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="14" thickBot="1">
+    <row r="583" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17402,7 +17403,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="14" thickBot="1">
+    <row r="584" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17420,7 +17421,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="14" thickBot="1">
+    <row r="585" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17438,7 +17439,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="14" thickBot="1">
+    <row r="586" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17456,7 +17457,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="14" thickBot="1">
+    <row r="587" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17474,7 +17475,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="14" thickBot="1">
+    <row r="588" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17492,7 +17493,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="14" thickBot="1">
+    <row r="589" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17510,7 +17511,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="14" thickBot="1">
+    <row r="590" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17528,7 +17529,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="14" thickBot="1">
+    <row r="591" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17546,7 +17547,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="14" thickBot="1">
+    <row r="592" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17564,7 +17565,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="14" thickBot="1">
+    <row r="593" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17582,7 +17583,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="14" thickBot="1">
+    <row r="594" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17600,7 +17601,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="14" thickBot="1">
+    <row r="595" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17618,7 +17619,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="14" thickBot="1">
+    <row r="596" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17636,7 +17637,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="14" thickBot="1">
+    <row r="597" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17654,7 +17655,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="14" thickBot="1">
+    <row r="598" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17672,7 +17673,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="14" thickBot="1">
+    <row r="599" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17690,7 +17691,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="14" thickBot="1">
+    <row r="600" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17708,7 +17709,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="14" thickBot="1">
+    <row r="601" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17726,7 +17727,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="14" thickBot="1">
+    <row r="602" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17744,7 +17745,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="14" thickBot="1">
+    <row r="603" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17762,7 +17763,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="14" thickBot="1">
+    <row r="604" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17780,7 +17781,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="14" thickBot="1">
+    <row r="605" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17798,7 +17799,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="14" thickBot="1">
+    <row r="606" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17816,7 +17817,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="14" thickBot="1">
+    <row r="607" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17834,7 +17835,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="14" thickBot="1">
+    <row r="608" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17852,7 +17853,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="14" thickBot="1">
+    <row r="609" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17870,7 +17871,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="14" thickBot="1">
+    <row r="610" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17888,7 +17889,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="14" thickBot="1">
+    <row r="611" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -17906,7 +17907,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="14" thickBot="1">
+    <row r="612" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -17924,7 +17925,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="14" thickBot="1">
+    <row r="613" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -17942,7 +17943,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="14" thickBot="1">
+    <row r="614" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -17960,7 +17961,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="14" thickBot="1">
+    <row r="615" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -17978,7 +17979,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="14" thickBot="1">
+    <row r="616" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -17996,7 +17997,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="14" thickBot="1">
+    <row r="617" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18014,7 +18015,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="14" thickBot="1">
+    <row r="618" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18032,7 +18033,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="14" thickBot="1">
+    <row r="619" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18050,7 +18051,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="14" thickBot="1">
+    <row r="620" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18068,7 +18069,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="14" thickBot="1">
+    <row r="621" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18086,7 +18087,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="14" thickBot="1">
+    <row r="622" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18104,7 +18105,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="14" thickBot="1">
+    <row r="623" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18122,7 +18123,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="14" thickBot="1">
+    <row r="624" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18140,7 +18141,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="14" thickBot="1">
+    <row r="625" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18158,7 +18159,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="14" thickBot="1">
+    <row r="626" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18176,7 +18177,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="14" thickBot="1">
+    <row r="627" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18194,7 +18195,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="14" thickBot="1">
+    <row r="628" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18212,7 +18213,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="14" thickBot="1">
+    <row r="629" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18230,7 +18231,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="14" thickBot="1">
+    <row r="630" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18248,7 +18249,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="14" thickBot="1">
+    <row r="631" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18266,7 +18267,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="14" thickBot="1">
+    <row r="632" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18284,7 +18285,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="14" thickBot="1">
+    <row r="633" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18302,7 +18303,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="14" thickBot="1">
+    <row r="634" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18320,7 +18321,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="14" thickBot="1">
+    <row r="635" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18338,7 +18339,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="14" thickBot="1">
+    <row r="636" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18356,7 +18357,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="14" thickBot="1">
+    <row r="637" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18374,7 +18375,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="14" thickBot="1">
+    <row r="638" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18392,7 +18393,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="14" thickBot="1">
+    <row r="639" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18410,7 +18411,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="14" thickBot="1">
+    <row r="640" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18428,7 +18429,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="14" thickBot="1">
+    <row r="641" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18446,7 +18447,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="14" thickBot="1">
+    <row r="642" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18479,7 +18480,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="14" thickBot="1">
+    <row r="643" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18497,7 +18498,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="14" thickBot="1">
+    <row r="644" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18515,7 +18516,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="14" thickBot="1">
+    <row r="645" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18533,7 +18534,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="14" thickBot="1">
+    <row r="646" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18551,7 +18552,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="14" thickBot="1">
+    <row r="647" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18569,7 +18570,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="14" thickBot="1">
+    <row r="648" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18587,7 +18588,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="14" thickBot="1">
+    <row r="649" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18605,7 +18606,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="14" thickBot="1">
+    <row r="650" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18623,7 +18624,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="14" thickBot="1">
+    <row r="651" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18641,7 +18642,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="14" thickBot="1">
+    <row r="652" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18659,7 +18660,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="14" thickBot="1">
+    <row r="653" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18677,7 +18678,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="14" thickBot="1">
+    <row r="654" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18695,7 +18696,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="14" thickBot="1">
+    <row r="655" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18713,7 +18714,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="14" thickBot="1">
+    <row r="656" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18731,7 +18732,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="14" thickBot="1">
+    <row r="657" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18749,7 +18750,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="14" thickBot="1">
+    <row r="658" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18767,7 +18768,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="14" thickBot="1">
+    <row r="659" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18785,7 +18786,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="14" thickBot="1">
+    <row r="660" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18803,7 +18804,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="14" thickBot="1">
+    <row r="661" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18821,7 +18822,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="14" thickBot="1">
+    <row r="662" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18839,7 +18840,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="14" thickBot="1">
+    <row r="663" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18857,7 +18858,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="14" thickBot="1">
+    <row r="664" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18875,7 +18876,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="14" thickBot="1">
+    <row r="665" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18893,7 +18894,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="14" thickBot="1">
+    <row r="666" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -18911,7 +18912,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="14" thickBot="1">
+    <row r="667" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -18929,7 +18930,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="14" thickBot="1">
+    <row r="668" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -18947,7 +18948,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="14" thickBot="1">
+    <row r="669" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -18965,7 +18966,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="14" thickBot="1">
+    <row r="670" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -18983,7 +18984,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="14" thickBot="1">
+    <row r="671" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19001,7 +19002,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="14" thickBot="1">
+    <row r="672" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19019,7 +19020,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="14" thickBot="1">
+    <row r="673" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19037,7 +19038,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="14" thickBot="1">
+    <row r="674" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19055,7 +19056,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="14" thickBot="1">
+    <row r="675" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19073,7 +19074,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="14" thickBot="1">
+    <row r="676" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19091,7 +19092,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="14" thickBot="1">
+    <row r="677" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19109,7 +19110,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="14" thickBot="1">
+    <row r="678" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19127,7 +19128,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="14" thickBot="1">
+    <row r="679" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19145,7 +19146,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="14" thickBot="1">
+    <row r="680" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19163,7 +19164,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="14" thickBot="1">
+    <row r="681" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19181,7 +19182,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="14" thickBot="1">
+    <row r="682" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19199,7 +19200,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="14" thickBot="1">
+    <row r="683" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19217,7 +19218,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="14" thickBot="1">
+    <row r="684" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19235,7 +19236,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="14" thickBot="1">
+    <row r="685" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19253,7 +19254,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="14" thickBot="1">
+    <row r="686" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19271,7 +19272,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="14" thickBot="1">
+    <row r="687" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19289,7 +19290,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="14" thickBot="1">
+    <row r="688" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19307,7 +19308,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="14" thickBot="1">
+    <row r="689" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19325,7 +19326,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="14" thickBot="1">
+    <row r="690" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19343,7 +19344,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="14" thickBot="1">
+    <row r="691" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19361,7 +19362,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="14" thickBot="1">
+    <row r="692" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19379,7 +19380,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="14" thickBot="1">
+    <row r="693" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19397,7 +19398,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="14" thickBot="1">
+    <row r="694" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19415,7 +19416,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="14" thickBot="1">
+    <row r="695" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19433,7 +19434,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="14" thickBot="1">
+    <row r="696" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19451,7 +19452,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="14" thickBot="1">
+    <row r="697" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19469,7 +19470,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="14" thickBot="1">
+    <row r="698" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19487,7 +19488,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="14" thickBot="1">
+    <row r="699" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19505,7 +19506,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="14" thickBot="1">
+    <row r="700" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19523,7 +19524,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="14" thickBot="1">
+    <row r="701" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19541,7 +19542,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="14" thickBot="1">
+    <row r="702" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19559,7 +19560,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="14" thickBot="1">
+    <row r="703" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19577,7 +19578,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="14" thickBot="1">
+    <row r="704" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19595,7 +19596,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="14" thickBot="1">
+    <row r="705" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19613,7 +19614,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="14" thickBot="1">
+    <row r="706" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19646,7 +19647,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="14" thickBot="1">
+    <row r="707" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19664,7 +19665,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="14" thickBot="1">
+    <row r="708" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19682,7 +19683,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="14" thickBot="1">
+    <row r="709" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19700,7 +19701,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="14" thickBot="1">
+    <row r="710" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19718,7 +19719,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="14" thickBot="1">
+    <row r="711" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19736,7 +19737,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="14" thickBot="1">
+    <row r="712" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19754,7 +19755,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="14" thickBot="1">
+    <row r="713" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19772,7 +19773,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="14" thickBot="1">
+    <row r="714" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19790,7 +19791,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="14" thickBot="1">
+    <row r="715" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19808,7 +19809,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="14" thickBot="1">
+    <row r="716" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19826,7 +19827,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="14" thickBot="1">
+    <row r="717" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19844,7 +19845,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="14" thickBot="1">
+    <row r="718" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19862,7 +19863,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="14" thickBot="1">
+    <row r="719" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19880,7 +19881,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="14" thickBot="1">
+    <row r="720" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19898,7 +19899,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="14" thickBot="1">
+    <row r="721" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -19916,7 +19917,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="14" thickBot="1">
+    <row r="722" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -19934,7 +19935,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="14" thickBot="1">
+    <row r="723" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -19952,7 +19953,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="14" thickBot="1">
+    <row r="724" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -19970,7 +19971,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="14" thickBot="1">
+    <row r="725" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -19988,7 +19989,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="14" thickBot="1">
+    <row r="726" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20006,7 +20007,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="14" thickBot="1">
+    <row r="727" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20024,7 +20025,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="14" thickBot="1">
+    <row r="728" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20042,7 +20043,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="14" thickBot="1">
+    <row r="729" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20060,7 +20061,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="14" thickBot="1">
+    <row r="730" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20078,7 +20079,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="14" thickBot="1">
+    <row r="731" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20096,7 +20097,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="14" thickBot="1">
+    <row r="732" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20114,7 +20115,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="14" thickBot="1">
+    <row r="733" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20132,7 +20133,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="14" thickBot="1">
+    <row r="734" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20150,7 +20151,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="14" thickBot="1">
+    <row r="735" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20168,7 +20169,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="14" thickBot="1">
+    <row r="736" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20186,7 +20187,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="14" thickBot="1">
+    <row r="737" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20204,7 +20205,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="14" thickBot="1">
+    <row r="738" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20222,7 +20223,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="14" thickBot="1">
+    <row r="739" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20240,7 +20241,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="14" thickBot="1">
+    <row r="740" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20258,7 +20259,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="14" thickBot="1">
+    <row r="741" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20276,7 +20277,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="14" thickBot="1">
+    <row r="742" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20294,7 +20295,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="14" thickBot="1">
+    <row r="743" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20312,7 +20313,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="14" thickBot="1">
+    <row r="744" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20330,7 +20331,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="14" thickBot="1">
+    <row r="745" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20348,7 +20349,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="14" thickBot="1">
+    <row r="746" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20366,7 +20367,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="14" thickBot="1">
+    <row r="747" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20384,7 +20385,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="14" thickBot="1">
+    <row r="748" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20402,7 +20403,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="14" thickBot="1">
+    <row r="749" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20420,7 +20421,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="14" thickBot="1">
+    <row r="750" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20438,7 +20439,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="14" thickBot="1">
+    <row r="751" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20456,7 +20457,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="14" thickBot="1">
+    <row r="752" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20474,7 +20475,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="14" thickBot="1">
+    <row r="753" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20492,7 +20493,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="14" thickBot="1">
+    <row r="754" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20510,7 +20511,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="14" thickBot="1">
+    <row r="755" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20528,7 +20529,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="14" thickBot="1">
+    <row r="756" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20546,7 +20547,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="14" thickBot="1">
+    <row r="757" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20564,7 +20565,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="14" thickBot="1">
+    <row r="758" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20582,7 +20583,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="14" thickBot="1">
+    <row r="759" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20600,7 +20601,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="14" thickBot="1">
+    <row r="760" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20618,7 +20619,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="14" thickBot="1">
+    <row r="761" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20636,7 +20637,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="14" thickBot="1">
+    <row r="762" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20654,7 +20655,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="14" thickBot="1">
+    <row r="763" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20672,7 +20673,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="14" thickBot="1">
+    <row r="764" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20690,7 +20691,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="14" thickBot="1">
+    <row r="765" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20708,7 +20709,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="14" thickBot="1">
+    <row r="766" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20726,7 +20727,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="14" thickBot="1">
+    <row r="767" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20744,7 +20745,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="14" thickBot="1">
+    <row r="768" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20762,7 +20763,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="14" thickBot="1">
+    <row r="769" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20780,7 +20781,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="14" thickBot="1">
+    <row r="770" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20813,7 +20814,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="14" thickBot="1">
+    <row r="771" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20831,7 +20832,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="14" thickBot="1">
+    <row r="772" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20849,7 +20850,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="14" thickBot="1">
+    <row r="773" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20867,7 +20868,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="14" thickBot="1">
+    <row r="774" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20885,7 +20886,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="14" thickBot="1">
+    <row r="775" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -20903,7 +20904,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="14" thickBot="1">
+    <row r="776" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -20921,7 +20922,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="14" thickBot="1">
+    <row r="777" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -20939,7 +20940,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="14" thickBot="1">
+    <row r="778" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -20957,7 +20958,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="14" thickBot="1">
+    <row r="779" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -20975,7 +20976,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="14" thickBot="1">
+    <row r="780" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -20993,7 +20994,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="14" thickBot="1">
+    <row r="781" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21011,7 +21012,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="14" thickBot="1">
+    <row r="782" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21029,7 +21030,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="14" thickBot="1">
+    <row r="783" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21047,7 +21048,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="14" thickBot="1">
+    <row r="784" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21065,7 +21066,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="14" thickBot="1">
+    <row r="785" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21083,7 +21084,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="14" thickBot="1">
+    <row r="786" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21101,7 +21102,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="14" thickBot="1">
+    <row r="787" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21119,7 +21120,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="14" thickBot="1">
+    <row r="788" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21137,7 +21138,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="14" thickBot="1">
+    <row r="789" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21155,7 +21156,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="14" thickBot="1">
+    <row r="790" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21173,7 +21174,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="14" thickBot="1">
+    <row r="791" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21191,7 +21192,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="14" thickBot="1">
+    <row r="792" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21209,7 +21210,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="14" thickBot="1">
+    <row r="793" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21227,7 +21228,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="14" thickBot="1">
+    <row r="794" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21245,7 +21246,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="14" thickBot="1">
+    <row r="795" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21263,7 +21264,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="14" thickBot="1">
+    <row r="796" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21281,7 +21282,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="14" thickBot="1">
+    <row r="797" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21299,7 +21300,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="14" thickBot="1">
+    <row r="798" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21317,7 +21318,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="14" thickBot="1">
+    <row r="799" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21335,7 +21336,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="14" thickBot="1">
+    <row r="800" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21353,7 +21354,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="14" thickBot="1">
+    <row r="801" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21371,7 +21372,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="14" thickBot="1">
+    <row r="802" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21389,7 +21390,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="14" thickBot="1">
+    <row r="803" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21407,7 +21408,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="14" thickBot="1">
+    <row r="804" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21425,7 +21426,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="14" thickBot="1">
+    <row r="805" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21443,7 +21444,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="14" thickBot="1">
+    <row r="806" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21461,7 +21462,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="14" thickBot="1">
+    <row r="807" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21479,7 +21480,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="14" thickBot="1">
+    <row r="808" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21497,7 +21498,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="14" thickBot="1">
+    <row r="809" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21515,7 +21516,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="14" thickBot="1">
+    <row r="810" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21533,7 +21534,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="14" thickBot="1">
+    <row r="811" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21551,7 +21552,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="14" thickBot="1">
+    <row r="812" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21569,7 +21570,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="14" thickBot="1">
+    <row r="813" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21587,7 +21588,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="14" thickBot="1">
+    <row r="814" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21605,7 +21606,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="14" thickBot="1">
+    <row r="815" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21623,7 +21624,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="14" thickBot="1">
+    <row r="816" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21641,7 +21642,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="14" thickBot="1">
+    <row r="817" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21659,7 +21660,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="14" thickBot="1">
+    <row r="818" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21677,7 +21678,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="14" thickBot="1">
+    <row r="819" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21695,7 +21696,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="14" thickBot="1">
+    <row r="820" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21713,7 +21714,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="14" thickBot="1">
+    <row r="821" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21731,7 +21732,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="14" thickBot="1">
+    <row r="822" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21749,7 +21750,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="14" thickBot="1">
+    <row r="823" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21767,7 +21768,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="14" thickBot="1">
+    <row r="824" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21785,7 +21786,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="14" thickBot="1">
+    <row r="825" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21803,7 +21804,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="14" thickBot="1">
+    <row r="826" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21821,7 +21822,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="14" thickBot="1">
+    <row r="827" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21839,7 +21840,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="14" thickBot="1">
+    <row r="828" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21857,7 +21858,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="14" thickBot="1">
+    <row r="829" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21875,7 +21876,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="14" thickBot="1">
+    <row r="830" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21893,7 +21894,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="14" thickBot="1">
+    <row r="831" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -21911,7 +21912,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="14" thickBot="1">
+    <row r="832" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -21929,7 +21930,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="14" thickBot="1">
+    <row r="833" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -21947,7 +21948,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="14" thickBot="1">
+    <row r="834" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -21980,7 +21981,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="14" thickBot="1">
+    <row r="835" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -21998,7 +21999,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="14" thickBot="1">
+    <row r="836" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22016,7 +22017,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="14" thickBot="1">
+    <row r="837" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22034,7 +22035,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="14" thickBot="1">
+    <row r="838" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22052,7 +22053,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="14" thickBot="1">
+    <row r="839" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22070,7 +22071,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="14" thickBot="1">
+    <row r="840" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22088,7 +22089,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="14" thickBot="1">
+    <row r="841" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22106,7 +22107,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="14" thickBot="1">
+    <row r="842" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22124,7 +22125,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="14" thickBot="1">
+    <row r="843" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22142,7 +22143,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="14" thickBot="1">
+    <row r="844" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22160,7 +22161,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="14" thickBot="1">
+    <row r="845" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22178,7 +22179,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="14" thickBot="1">
+    <row r="846" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22196,7 +22197,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="14" thickBot="1">
+    <row r="847" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22214,7 +22215,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="14" thickBot="1">
+    <row r="848" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22232,7 +22233,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="14" thickBot="1">
+    <row r="849" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22250,7 +22251,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="14" thickBot="1">
+    <row r="850" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22268,7 +22269,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="14" thickBot="1">
+    <row r="851" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22286,7 +22287,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="14" thickBot="1">
+    <row r="852" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22304,7 +22305,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="14" thickBot="1">
+    <row r="853" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22322,7 +22323,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="14" thickBot="1">
+    <row r="854" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22340,7 +22341,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="14" thickBot="1">
+    <row r="855" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22358,7 +22359,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="14" thickBot="1">
+    <row r="856" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22376,7 +22377,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="14" thickBot="1">
+    <row r="857" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22394,7 +22395,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="14" thickBot="1">
+    <row r="858" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22412,7 +22413,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="14" thickBot="1">
+    <row r="859" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22430,7 +22431,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="14" thickBot="1">
+    <row r="860" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22448,7 +22449,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="14" thickBot="1">
+    <row r="861" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22466,7 +22467,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="14" thickBot="1">
+    <row r="862" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22484,7 +22485,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="14" thickBot="1">
+    <row r="863" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22502,7 +22503,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="14" thickBot="1">
+    <row r="864" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22520,7 +22521,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="14" thickBot="1">
+    <row r="865" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22538,7 +22539,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="14" thickBot="1">
+    <row r="866" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22556,7 +22557,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="14" thickBot="1">
+    <row r="867" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22574,7 +22575,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="14" thickBot="1">
+    <row r="868" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22592,7 +22593,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="14" thickBot="1">
+    <row r="869" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22610,7 +22611,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="14" thickBot="1">
+    <row r="870" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22628,7 +22629,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="14" thickBot="1">
+    <row r="871" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22646,7 +22647,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="14" thickBot="1">
+    <row r="872" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22664,7 +22665,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="14" thickBot="1">
+    <row r="873" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22682,7 +22683,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="14" thickBot="1">
+    <row r="874" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22700,7 +22701,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="14" thickBot="1">
+    <row r="875" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22718,7 +22719,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="14" thickBot="1">
+    <row r="876" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22736,7 +22737,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="14" thickBot="1">
+    <row r="877" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22754,7 +22755,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="14" thickBot="1">
+    <row r="878" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22787,7 +22788,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="14" thickBot="1">
+    <row r="879" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22820,7 +22821,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="14" thickBot="1">
+    <row r="880" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22853,7 +22854,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="14" thickBot="1">
+    <row r="881" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22871,7 +22872,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="14" thickBot="1">
+    <row r="882" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -22904,7 +22905,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="14" thickBot="1">
+    <row r="883" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -22937,7 +22938,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="14" thickBot="1">
+    <row r="884" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -22955,7 +22956,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="14" thickBot="1">
+    <row r="885" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -22988,7 +22989,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23021,7 +23022,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23029,7 +23030,7 @@
         <v>46113</v>
       </c>
       <c r="C887" s="21">
-        <v>0.5</v>
+        <v>0.50069444444444444</v>
       </c>
       <c r="D887" s="8" t="str">
         <f>IF(
@@ -23050,6 +23051,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E887" s="20">
+        <v>515921</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
@@ -23064,7 +23068,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23075,12 +23079,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23088,7 +23092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23096,7 +23100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884EB1EA-C12B-475E-A03C-DC49E47E03B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838696B5-7C0E-431F-A76F-DCA90A74C36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -90,12 +87,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -193,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -210,68 +207,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -289,7 +286,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5816,6 +5813,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5823,7 +5821,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6453,9 +6450,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6493,7 +6490,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6599,7 +6596,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6741,7 +6738,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6749,18 +6746,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E887"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E888"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="5" max="5" width="12.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6777,7 +6774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="7">
         <v>39823</v>
       </c>
@@ -6810,7 +6807,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="7">
         <v>39830</v>
       </c>
@@ -6828,7 +6825,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="7">
         <v>39837</v>
       </c>
@@ -6846,7 +6843,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="7">
         <v>39844</v>
       </c>
@@ -6864,7 +6861,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="7">
         <v>39851</v>
       </c>
@@ -6882,7 +6879,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="7">
         <v>39858</v>
       </c>
@@ -6900,7 +6897,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="7">
         <v>39865</v>
       </c>
@@ -6918,7 +6915,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="7">
         <v>39872</v>
       </c>
@@ -6936,7 +6933,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="7">
         <v>39879</v>
       </c>
@@ -6954,7 +6951,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="7">
         <v>39886</v>
       </c>
@@ -6972,7 +6969,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="7">
         <v>39893</v>
       </c>
@@ -6990,7 +6987,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="7">
         <v>39900</v>
       </c>
@@ -7008,7 +7005,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="7">
         <v>39907</v>
       </c>
@@ -7026,7 +7023,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="7">
         <v>39914</v>
       </c>
@@ -7044,7 +7041,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="7">
         <v>39921</v>
       </c>
@@ -7062,7 +7059,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="7">
         <v>39928</v>
       </c>
@@ -7080,7 +7077,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="7">
         <v>39935</v>
       </c>
@@ -7098,7 +7095,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="7">
         <v>39942</v>
       </c>
@@ -7116,7 +7113,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="7">
         <v>39949</v>
       </c>
@@ -7134,7 +7131,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="7">
         <v>39956</v>
       </c>
@@ -7152,7 +7149,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="7">
         <v>39963</v>
       </c>
@@ -7170,7 +7167,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="7">
         <v>39970</v>
       </c>
@@ -7188,7 +7185,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="7">
         <v>39977</v>
       </c>
@@ -7206,7 +7203,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="7">
         <v>39984</v>
       </c>
@@ -7224,7 +7221,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="7">
         <v>39991</v>
       </c>
@@ -7242,7 +7239,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="7">
         <v>39998</v>
       </c>
@@ -7260,7 +7257,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="7">
         <v>40005</v>
       </c>
@@ -7278,7 +7275,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="7">
         <v>40012</v>
       </c>
@@ -7296,7 +7293,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="7">
         <v>40019</v>
       </c>
@@ -7314,7 +7311,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="7">
         <v>40026</v>
       </c>
@@ -7332,7 +7329,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="7">
         <v>40033</v>
       </c>
@@ -7350,7 +7347,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="7">
         <v>40040</v>
       </c>
@@ -7368,7 +7365,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="7">
         <v>40047</v>
       </c>
@@ -7386,7 +7383,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="7">
         <v>40054</v>
       </c>
@@ -7404,7 +7401,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="7">
         <v>40061</v>
       </c>
@@ -7422,7 +7419,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="7">
         <v>40068</v>
       </c>
@@ -7440,7 +7437,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="7">
         <v>40075</v>
       </c>
@@ -7458,7 +7455,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="7">
         <v>40082</v>
       </c>
@@ -7476,7 +7473,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="7">
         <v>40089</v>
       </c>
@@ -7494,7 +7491,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="7">
         <v>40096</v>
       </c>
@@ -7512,7 +7509,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="7">
         <v>40103</v>
       </c>
@@ -7530,7 +7527,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="7">
         <v>40110</v>
       </c>
@@ -7548,7 +7545,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="7">
         <v>40117</v>
       </c>
@@ -7566,7 +7563,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="7">
         <v>40124</v>
       </c>
@@ -7584,7 +7581,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="7">
         <v>40131</v>
       </c>
@@ -7602,7 +7599,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="7">
         <v>40138</v>
       </c>
@@ -7620,7 +7617,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="7">
         <v>40145</v>
       </c>
@@ -7638,7 +7635,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="7">
         <v>40152</v>
       </c>
@@ -7656,7 +7653,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="7">
         <v>40159</v>
       </c>
@@ -7674,7 +7671,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="7">
         <v>40166</v>
       </c>
@@ -7692,7 +7689,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="7">
         <v>40173</v>
       </c>
@@ -7710,7 +7707,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="7">
         <v>40180</v>
       </c>
@@ -7728,7 +7725,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="7">
         <v>40187</v>
       </c>
@@ -7746,7 +7743,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="7">
         <v>40194</v>
       </c>
@@ -7764,7 +7761,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="7">
         <v>40201</v>
       </c>
@@ -7782,7 +7779,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="7">
         <v>40208</v>
       </c>
@@ -7800,7 +7797,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="7">
         <v>40215</v>
       </c>
@@ -7818,7 +7815,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="7">
         <v>40222</v>
       </c>
@@ -7836,7 +7833,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="7">
         <v>40229</v>
       </c>
@@ -7854,7 +7851,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="7">
         <v>40236</v>
       </c>
@@ -7872,7 +7869,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="7">
         <v>40243</v>
       </c>
@@ -7890,7 +7887,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="7">
         <v>40250</v>
       </c>
@@ -7908,7 +7905,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="7">
         <v>40257</v>
       </c>
@@ -7926,7 +7923,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="7">
         <v>40264</v>
       </c>
@@ -7944,7 +7941,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="7">
         <v>40271</v>
       </c>
@@ -7977,7 +7974,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="7">
         <v>40278</v>
       </c>
@@ -7995,7 +7992,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="7">
         <v>40285</v>
       </c>
@@ -8013,7 +8010,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="7">
         <v>40292</v>
       </c>
@@ -8031,7 +8028,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="7">
         <v>40299</v>
       </c>
@@ -8049,7 +8046,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="7">
         <v>40306</v>
       </c>
@@ -8067,7 +8064,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="7">
         <v>40313</v>
       </c>
@@ -8085,7 +8082,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="7">
         <v>40320</v>
       </c>
@@ -8103,7 +8100,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="7">
         <v>40327</v>
       </c>
@@ -8121,7 +8118,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="7">
         <v>40334</v>
       </c>
@@ -8139,7 +8136,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="7">
         <v>40341</v>
       </c>
@@ -8157,7 +8154,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="7">
         <v>40348</v>
       </c>
@@ -8175,7 +8172,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="7">
         <v>40355</v>
       </c>
@@ -8193,7 +8190,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="7">
         <v>40362</v>
       </c>
@@ -8211,7 +8208,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="7">
         <v>40369</v>
       </c>
@@ -8229,7 +8226,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="7">
         <v>40376</v>
       </c>
@@ -8247,7 +8244,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="7">
         <v>40383</v>
       </c>
@@ -8265,7 +8262,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="7">
         <v>40390</v>
       </c>
@@ -8283,7 +8280,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="7">
         <v>40397</v>
       </c>
@@ -8301,7 +8298,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="7">
         <v>40404</v>
       </c>
@@ -8319,7 +8316,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="7">
         <v>40411</v>
       </c>
@@ -8337,7 +8334,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="7">
         <v>40418</v>
       </c>
@@ -8355,7 +8352,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="7">
         <v>40425</v>
       </c>
@@ -8373,7 +8370,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="7">
         <v>40432</v>
       </c>
@@ -8391,7 +8388,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="7">
         <v>40439</v>
       </c>
@@ -8409,7 +8406,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="7">
         <v>40446</v>
       </c>
@@ -8427,7 +8424,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="7">
         <v>40453</v>
       </c>
@@ -8445,7 +8442,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="7">
         <v>40460</v>
       </c>
@@ -8463,7 +8460,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="7">
         <v>40467</v>
       </c>
@@ -8481,7 +8478,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="7">
         <v>40474</v>
       </c>
@@ -8499,7 +8496,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="7">
         <v>40481</v>
       </c>
@@ -8517,7 +8514,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="7">
         <v>40488</v>
       </c>
@@ -8535,7 +8532,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="7">
         <v>40495</v>
       </c>
@@ -8553,7 +8550,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="7">
         <v>40502</v>
       </c>
@@ -8571,7 +8568,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="7">
         <v>40509</v>
       </c>
@@ -8589,7 +8586,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="14" thickBot="1">
       <c r="A101" s="7">
         <v>40516</v>
       </c>
@@ -8607,7 +8604,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="14" thickBot="1">
       <c r="A102" s="11">
         <v>40523</v>
       </c>
@@ -8625,7 +8622,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="14" thickBot="1">
       <c r="A103" s="11">
         <v>40530</v>
       </c>
@@ -8643,7 +8640,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="14" thickBot="1">
       <c r="A104" s="11">
         <v>40537</v>
       </c>
@@ -8661,7 +8658,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="14" thickBot="1">
       <c r="A105" s="11">
         <v>40544</v>
       </c>
@@ -8679,7 +8676,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="14" thickBot="1">
       <c r="A106" s="11">
         <v>40551</v>
       </c>
@@ -8697,7 +8694,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="14" thickBot="1">
       <c r="A107" s="11">
         <v>40558</v>
       </c>
@@ -8715,7 +8712,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="14" thickBot="1">
       <c r="A108" s="11">
         <v>40565</v>
       </c>
@@ -8733,7 +8730,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="14" thickBot="1">
       <c r="A109" s="11">
         <v>40572</v>
       </c>
@@ -8751,7 +8748,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="14" thickBot="1">
       <c r="A110" s="11">
         <v>40579</v>
       </c>
@@ -8769,7 +8766,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="14" thickBot="1">
       <c r="A111" s="11">
         <v>40586</v>
       </c>
@@ -8787,7 +8784,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="14" thickBot="1">
       <c r="A112" s="11">
         <v>40593</v>
       </c>
@@ -8805,7 +8802,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="14" thickBot="1">
       <c r="A113" s="11">
         <v>40600</v>
       </c>
@@ -8823,7 +8820,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="14" thickBot="1">
       <c r="A114" s="11">
         <v>40607</v>
       </c>
@@ -8841,7 +8838,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="14" thickBot="1">
       <c r="A115" s="11">
         <v>40614</v>
       </c>
@@ -8859,7 +8856,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="14" thickBot="1">
       <c r="A116" s="11">
         <v>40621</v>
       </c>
@@ -8877,7 +8874,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="14" thickBot="1">
       <c r="A117" s="11">
         <v>40628</v>
       </c>
@@ -8895,7 +8892,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="14" thickBot="1">
       <c r="A118" s="11">
         <v>40635</v>
       </c>
@@ -8913,7 +8910,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="14" thickBot="1">
       <c r="A119" s="11">
         <v>40642</v>
       </c>
@@ -8931,7 +8928,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="14" thickBot="1">
       <c r="A120" s="11">
         <v>40649</v>
       </c>
@@ -8949,7 +8946,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="14" thickBot="1">
       <c r="A121" s="11">
         <v>40656</v>
       </c>
@@ -8967,7 +8964,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="14" thickBot="1">
       <c r="A122" s="11">
         <v>40663</v>
       </c>
@@ -8985,7 +8982,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="14" thickBot="1">
       <c r="A123" s="11">
         <v>40670</v>
       </c>
@@ -9003,7 +9000,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="14" thickBot="1">
       <c r="A124" s="11">
         <v>40677</v>
       </c>
@@ -9021,7 +9018,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="14" thickBot="1">
       <c r="A125" s="11">
         <v>40684</v>
       </c>
@@ -9039,7 +9036,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="14" thickBot="1">
       <c r="A126" s="13">
         <v>40691</v>
       </c>
@@ -9057,7 +9054,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="14" thickBot="1">
       <c r="A127" s="11">
         <v>40698</v>
       </c>
@@ -9075,7 +9072,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="14" thickBot="1">
       <c r="A128" s="11">
         <v>40705</v>
       </c>
@@ -9093,7 +9090,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="14" thickBot="1">
       <c r="A129" s="11">
         <v>40712</v>
       </c>
@@ -9111,7 +9108,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="14" thickBot="1">
       <c r="A130" s="11">
         <v>40719</v>
       </c>
@@ -9144,7 +9141,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="14" thickBot="1">
       <c r="A131" s="11">
         <v>40726</v>
       </c>
@@ -9162,7 +9159,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="14" thickBot="1">
       <c r="A132" s="11">
         <v>40733</v>
       </c>
@@ -9180,7 +9177,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="14" thickBot="1">
       <c r="A133" s="11">
         <v>40740</v>
       </c>
@@ -9198,7 +9195,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="14" thickBot="1">
       <c r="A134" s="11">
         <v>40747</v>
       </c>
@@ -9216,7 +9213,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="14" thickBot="1">
       <c r="A135" s="11">
         <v>40754</v>
       </c>
@@ -9234,7 +9231,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="14" thickBot="1">
       <c r="A136" s="11">
         <v>40761</v>
       </c>
@@ -9252,7 +9249,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="14" thickBot="1">
       <c r="A137" s="11">
         <v>40768</v>
       </c>
@@ -9270,7 +9267,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="14" thickBot="1">
       <c r="A138" s="11">
         <v>40775</v>
       </c>
@@ -9288,7 +9285,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="14" thickBot="1">
       <c r="A139" s="11">
         <v>40782</v>
       </c>
@@ -9306,7 +9303,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="14" thickBot="1">
       <c r="A140" s="11">
         <v>40789</v>
       </c>
@@ -9324,7 +9321,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="14" thickBot="1">
       <c r="A141" s="11">
         <v>40796</v>
       </c>
@@ -9342,7 +9339,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="14" thickBot="1">
       <c r="A142" s="11">
         <v>40803</v>
       </c>
@@ -9360,7 +9357,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="14" thickBot="1">
       <c r="A143" s="11">
         <v>40810</v>
       </c>
@@ -9378,7 +9375,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="14" thickBot="1">
       <c r="A144" s="11">
         <v>40817</v>
       </c>
@@ -9396,7 +9393,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="14" thickBot="1">
       <c r="A145" s="11">
         <v>40824</v>
       </c>
@@ -9414,7 +9411,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="14" thickBot="1">
       <c r="A146" s="11">
         <v>40831</v>
       </c>
@@ -9432,7 +9429,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="14" thickBot="1">
       <c r="A147" s="11">
         <v>40838</v>
       </c>
@@ -9450,7 +9447,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="14" thickBot="1">
       <c r="A148" s="11">
         <v>40845</v>
       </c>
@@ -9468,7 +9465,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="14" thickBot="1">
       <c r="A149" s="11">
         <v>40852</v>
       </c>
@@ -9486,7 +9483,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="14" thickBot="1">
       <c r="A150" s="11">
         <v>40859</v>
       </c>
@@ -9504,7 +9501,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="14" thickBot="1">
       <c r="A151" s="13">
         <v>40866</v>
       </c>
@@ -9522,7 +9519,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="14" thickBot="1">
       <c r="A152" s="11">
         <v>40873</v>
       </c>
@@ -9540,7 +9537,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="14" thickBot="1">
       <c r="A153" s="11">
         <v>40880</v>
       </c>
@@ -9558,7 +9555,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="14" thickBot="1">
       <c r="A154" s="11">
         <v>40887</v>
       </c>
@@ -9576,7 +9573,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="14" thickBot="1">
       <c r="A155" s="11">
         <v>40894</v>
       </c>
@@ -9594,7 +9591,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="14" thickBot="1">
       <c r="A156" s="11">
         <v>40901</v>
       </c>
@@ -9612,7 +9609,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="14" thickBot="1">
       <c r="A157" s="11">
         <v>40908</v>
       </c>
@@ -9630,7 +9627,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="14" thickBot="1">
       <c r="A158" s="11">
         <v>40915</v>
       </c>
@@ -9648,7 +9645,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="14" thickBot="1">
       <c r="A159" s="11">
         <v>40922</v>
       </c>
@@ -9666,7 +9663,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="14" thickBot="1">
       <c r="A160" s="11">
         <v>40929</v>
       </c>
@@ -9684,7 +9681,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="14" thickBot="1">
       <c r="A161" s="11">
         <v>40936</v>
       </c>
@@ -9702,7 +9699,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="14" thickBot="1">
       <c r="A162" s="11">
         <v>40943</v>
       </c>
@@ -9720,7 +9717,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" ht="14" thickBot="1">
       <c r="A163" s="11">
         <v>40950</v>
       </c>
@@ -9738,7 +9735,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" ht="14" thickBot="1">
       <c r="A164" s="11">
         <v>40957</v>
       </c>
@@ -9756,7 +9753,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" ht="14" thickBot="1">
       <c r="A165" s="11">
         <v>40964</v>
       </c>
@@ -9774,7 +9771,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="14" thickBot="1">
       <c r="A166" s="11">
         <v>40971</v>
       </c>
@@ -9792,7 +9789,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="14" thickBot="1">
       <c r="A167" s="11">
         <v>40978</v>
       </c>
@@ -9810,7 +9807,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="14" thickBot="1">
       <c r="A168" s="11">
         <v>40985</v>
       </c>
@@ -9828,7 +9825,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="14" thickBot="1">
       <c r="A169" s="11">
         <v>40992</v>
       </c>
@@ -9846,7 +9843,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="14" thickBot="1">
       <c r="A170" s="11">
         <v>40999</v>
       </c>
@@ -9864,7 +9861,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="14" thickBot="1">
       <c r="A171" s="11">
         <v>41006</v>
       </c>
@@ -9882,7 +9879,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="14" thickBot="1">
       <c r="A172" s="11">
         <v>41013</v>
       </c>
@@ -9900,7 +9897,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="14" thickBot="1">
       <c r="A173" s="11">
         <v>41020</v>
       </c>
@@ -9918,7 +9915,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="14" thickBot="1">
       <c r="A174" s="11">
         <v>41027</v>
       </c>
@@ -9936,7 +9933,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="14" thickBot="1">
       <c r="A175" s="11">
         <v>41034</v>
       </c>
@@ -9954,7 +9951,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="14" thickBot="1">
       <c r="A176" s="13">
         <v>41041</v>
       </c>
@@ -9972,7 +9969,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="14" thickBot="1">
       <c r="A177" s="11">
         <v>41048</v>
       </c>
@@ -9990,7 +9987,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="14" thickBot="1">
       <c r="A178" s="11">
         <v>41055</v>
       </c>
@@ -10008,7 +10005,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="14" thickBot="1">
       <c r="A179" s="11">
         <v>41062</v>
       </c>
@@ -10026,7 +10023,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="14" thickBot="1">
       <c r="A180" s="11">
         <v>41069</v>
       </c>
@@ -10044,7 +10041,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="14" thickBot="1">
       <c r="A181" s="11">
         <v>41076</v>
       </c>
@@ -10062,7 +10059,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="14" thickBot="1">
       <c r="A182" s="11">
         <v>41083</v>
       </c>
@@ -10080,7 +10077,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="14" thickBot="1">
       <c r="A183" s="11">
         <v>41090</v>
       </c>
@@ -10098,7 +10095,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="14" thickBot="1">
       <c r="A184" s="11">
         <v>41097</v>
       </c>
@@ -10116,7 +10113,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="14" thickBot="1">
       <c r="A185" s="11">
         <v>41104</v>
       </c>
@@ -10134,7 +10131,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="14" thickBot="1">
       <c r="A186" s="11">
         <v>41111</v>
       </c>
@@ -10152,7 +10149,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="14" thickBot="1">
       <c r="A187" s="11">
         <v>41118</v>
       </c>
@@ -10170,7 +10167,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="14" thickBot="1">
       <c r="A188" s="11">
         <v>41125</v>
       </c>
@@ -10188,7 +10185,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="14" thickBot="1">
       <c r="A189" s="11">
         <v>41132</v>
       </c>
@@ -10206,7 +10203,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="14" thickBot="1">
       <c r="A190" s="11">
         <v>41139</v>
       </c>
@@ -10224,7 +10221,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="14" thickBot="1">
       <c r="A191" s="11">
         <v>41146</v>
       </c>
@@ -10242,7 +10239,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="14" thickBot="1">
       <c r="A192" s="11">
         <v>41153</v>
       </c>
@@ -10260,7 +10257,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="14" thickBot="1">
       <c r="A193" s="11">
         <v>41160</v>
       </c>
@@ -10278,7 +10275,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="14" thickBot="1">
       <c r="A194" s="11">
         <v>41167</v>
       </c>
@@ -10311,7 +10308,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="14" thickBot="1">
       <c r="A195" s="11">
         <v>41174</v>
       </c>
@@ -10329,7 +10326,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="14" thickBot="1">
       <c r="A196" s="11">
         <v>41181</v>
       </c>
@@ -10347,7 +10344,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="14" thickBot="1">
       <c r="A197" s="11">
         <v>41188</v>
       </c>
@@ -10365,7 +10362,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="14" thickBot="1">
       <c r="A198" s="11">
         <v>41195</v>
       </c>
@@ -10383,7 +10380,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="14" thickBot="1">
       <c r="A199" s="11">
         <v>41202</v>
       </c>
@@ -10401,7 +10398,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="14" thickBot="1">
       <c r="A200" s="11">
         <v>41209</v>
       </c>
@@ -10419,7 +10416,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="14" thickBot="1">
       <c r="A201" s="13">
         <v>41216</v>
       </c>
@@ -10437,7 +10434,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="14" thickBot="1">
       <c r="A202" s="11">
         <v>41223</v>
       </c>
@@ -10455,7 +10452,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="14" thickBot="1">
       <c r="A203" s="11">
         <v>41230</v>
       </c>
@@ -10473,7 +10470,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="14" thickBot="1">
       <c r="A204" s="11">
         <v>41237</v>
       </c>
@@ -10491,7 +10488,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="14" thickBot="1">
       <c r="A205" s="11">
         <v>41244</v>
       </c>
@@ -10509,7 +10506,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="14" thickBot="1">
       <c r="A206" s="11">
         <v>41251</v>
       </c>
@@ -10527,7 +10524,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="14" thickBot="1">
       <c r="A207" s="11">
         <v>41258</v>
       </c>
@@ -10545,7 +10542,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="14" thickBot="1">
       <c r="A208" s="11">
         <v>41265</v>
       </c>
@@ -10563,7 +10560,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="14" thickBot="1">
       <c r="A209" s="11">
         <v>41272</v>
       </c>
@@ -10581,7 +10578,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="14" thickBot="1">
       <c r="A210" s="11">
         <v>41279</v>
       </c>
@@ -10599,7 +10596,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="14" thickBot="1">
       <c r="A211" s="11">
         <v>41286</v>
       </c>
@@ -10617,7 +10614,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="14" thickBot="1">
       <c r="A212" s="11">
         <v>41293</v>
       </c>
@@ -10635,7 +10632,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="14" thickBot="1">
       <c r="A213" s="11">
         <v>41300</v>
       </c>
@@ -10653,7 +10650,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="14" thickBot="1">
       <c r="A214" s="11">
         <v>41307</v>
       </c>
@@ -10671,7 +10668,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="14" thickBot="1">
       <c r="A215" s="11">
         <v>41314</v>
       </c>
@@ -10689,7 +10686,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="14" thickBot="1">
       <c r="A216" s="11">
         <v>41321</v>
       </c>
@@ -10707,7 +10704,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="14" thickBot="1">
       <c r="A217" s="11">
         <v>41328</v>
       </c>
@@ -10725,7 +10722,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="14" thickBot="1">
       <c r="A218" s="11">
         <v>41335</v>
       </c>
@@ -10743,7 +10740,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="14" thickBot="1">
       <c r="A219" s="11">
         <v>41342</v>
       </c>
@@ -10761,7 +10758,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="14" thickBot="1">
       <c r="A220" s="11">
         <v>41349</v>
       </c>
@@ -10779,7 +10776,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="14" thickBot="1">
       <c r="A221" s="11">
         <v>41356</v>
       </c>
@@ -10797,7 +10794,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="14" thickBot="1">
       <c r="A222" s="11">
         <v>41363</v>
       </c>
@@ -10815,7 +10812,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="14" thickBot="1">
       <c r="A223" s="11">
         <v>41370</v>
       </c>
@@ -10833,7 +10830,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="14" thickBot="1">
       <c r="A224" s="11">
         <v>41377</v>
       </c>
@@ -10851,7 +10848,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="14" thickBot="1">
       <c r="A225" s="11">
         <v>41384</v>
       </c>
@@ -10869,7 +10866,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="14" thickBot="1">
       <c r="A226" s="13">
         <v>41391</v>
       </c>
@@ -10887,7 +10884,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="14" thickBot="1">
       <c r="A227" s="11">
         <v>41398</v>
       </c>
@@ -10905,7 +10902,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="14" thickBot="1">
       <c r="A228" s="11">
         <v>41405</v>
       </c>
@@ -10923,7 +10920,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="14" thickBot="1">
       <c r="A229" s="11">
         <v>41412</v>
       </c>
@@ -10941,7 +10938,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="14" thickBot="1">
       <c r="A230" s="11">
         <v>41419</v>
       </c>
@@ -10959,7 +10956,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="14" thickBot="1">
       <c r="A231" s="11">
         <v>41426</v>
       </c>
@@ -10977,7 +10974,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="14" thickBot="1">
       <c r="A232" s="11">
         <v>41433</v>
       </c>
@@ -10995,7 +10992,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="14" thickBot="1">
       <c r="A233" s="11">
         <v>41440</v>
       </c>
@@ -11013,7 +11010,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="14" thickBot="1">
       <c r="A234" s="11">
         <v>41447</v>
       </c>
@@ -11031,7 +11028,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="14" thickBot="1">
       <c r="A235" s="11">
         <v>41454</v>
       </c>
@@ -11049,7 +11046,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="14" thickBot="1">
       <c r="A236" s="11">
         <v>41461</v>
       </c>
@@ -11067,7 +11064,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="14" thickBot="1">
       <c r="A237" s="11">
         <v>41468</v>
       </c>
@@ -11085,7 +11082,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="14" thickBot="1">
       <c r="A238" s="11">
         <v>41475</v>
       </c>
@@ -11103,7 +11100,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="14" thickBot="1">
       <c r="A239" s="11">
         <v>41482</v>
       </c>
@@ -11121,7 +11118,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="14" thickBot="1">
       <c r="A240" s="11">
         <v>41489</v>
       </c>
@@ -11139,7 +11136,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="14" thickBot="1">
       <c r="A241" s="11">
         <v>41496</v>
       </c>
@@ -11157,7 +11154,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="14" thickBot="1">
       <c r="A242" s="11">
         <v>41503</v>
       </c>
@@ -11175,7 +11172,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="14" thickBot="1">
       <c r="A243" s="11">
         <v>41510</v>
       </c>
@@ -11193,7 +11190,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="14" thickBot="1">
       <c r="A244" s="11">
         <v>41517</v>
       </c>
@@ -11211,7 +11208,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="14" thickBot="1">
       <c r="A245" s="11">
         <v>41524</v>
       </c>
@@ -11229,7 +11226,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="14" thickBot="1">
       <c r="A246" s="11">
         <v>41531</v>
       </c>
@@ -11247,7 +11244,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="14" thickBot="1">
       <c r="A247" s="11">
         <v>41538</v>
       </c>
@@ -11265,7 +11262,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="14" thickBot="1">
       <c r="A248" s="11">
         <v>41545</v>
       </c>
@@ -11283,7 +11280,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="14" thickBot="1">
       <c r="A249" s="11">
         <v>41552</v>
       </c>
@@ -11301,7 +11298,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="14" thickBot="1">
       <c r="A250" s="11">
         <v>41559</v>
       </c>
@@ -11319,7 +11316,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="14" thickBot="1">
       <c r="A251" s="13">
         <v>41566</v>
       </c>
@@ -11337,7 +11334,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="14" thickBot="1">
       <c r="A252" s="11">
         <v>41573</v>
       </c>
@@ -11355,7 +11352,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="14" thickBot="1">
       <c r="A253" s="11">
         <v>41580</v>
       </c>
@@ -11373,7 +11370,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="14" thickBot="1">
       <c r="A254" s="11">
         <v>41587</v>
       </c>
@@ -11391,7 +11388,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="14" thickBot="1">
       <c r="A255" s="11">
         <v>41594</v>
       </c>
@@ -11409,7 +11406,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="14" thickBot="1">
       <c r="A256" s="11">
         <v>41601</v>
       </c>
@@ -11427,7 +11424,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="14" thickBot="1">
       <c r="A257" s="11">
         <v>41608</v>
       </c>
@@ -11445,7 +11442,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="14" thickBot="1">
       <c r="A258" s="11">
         <v>41615</v>
       </c>
@@ -11478,7 +11475,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="14" thickBot="1">
       <c r="A259" s="11">
         <v>41622</v>
       </c>
@@ -11496,7 +11493,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="14" thickBot="1">
       <c r="A260" s="11">
         <v>41629</v>
       </c>
@@ -11514,7 +11511,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="14" thickBot="1">
       <c r="A261" s="11">
         <v>41636</v>
       </c>
@@ -11532,7 +11529,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="14" thickBot="1">
       <c r="A262" s="11">
         <v>41643</v>
       </c>
@@ -11550,7 +11547,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="14" thickBot="1">
       <c r="A263" s="11">
         <v>41650</v>
       </c>
@@ -11568,7 +11565,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="14" thickBot="1">
       <c r="A264" s="11">
         <v>41657</v>
       </c>
@@ -11586,7 +11583,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="14" thickBot="1">
       <c r="A265" s="11">
         <v>41664</v>
       </c>
@@ -11604,7 +11601,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="14" thickBot="1">
       <c r="A266" s="11">
         <v>41671</v>
       </c>
@@ -11622,7 +11619,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="14" thickBot="1">
       <c r="A267" s="11">
         <v>41678</v>
       </c>
@@ -11640,7 +11637,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="14" thickBot="1">
       <c r="A268" s="11">
         <v>41685</v>
       </c>
@@ -11658,7 +11655,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="14" thickBot="1">
       <c r="A269" s="11">
         <v>41692</v>
       </c>
@@ -11676,7 +11673,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="14" thickBot="1">
       <c r="A270" s="11">
         <v>41699</v>
       </c>
@@ -11694,7 +11691,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="14" thickBot="1">
       <c r="A271" s="11">
         <v>41706</v>
       </c>
@@ -11712,7 +11709,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="14" thickBot="1">
       <c r="A272" s="11">
         <v>41713</v>
       </c>
@@ -11730,7 +11727,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="14" thickBot="1">
       <c r="A273" s="11">
         <v>41720</v>
       </c>
@@ -11748,7 +11745,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="14" thickBot="1">
       <c r="A274" s="11">
         <v>41727</v>
       </c>
@@ -11766,7 +11763,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="14" thickBot="1">
       <c r="A275" s="11">
         <v>41734</v>
       </c>
@@ -11784,7 +11781,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="14" thickBot="1">
       <c r="A276" s="13">
         <v>41741</v>
       </c>
@@ -11802,7 +11799,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="14" thickBot="1">
       <c r="A277" s="11">
         <v>41748</v>
       </c>
@@ -11820,7 +11817,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="14" thickBot="1">
       <c r="A278" s="11">
         <v>41755</v>
       </c>
@@ -11838,7 +11835,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="14" thickBot="1">
       <c r="A279" s="11">
         <v>41762</v>
       </c>
@@ -11856,7 +11853,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="14" thickBot="1">
       <c r="A280" s="11">
         <v>41769</v>
       </c>
@@ -11874,7 +11871,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="14" thickBot="1">
       <c r="A281" s="11">
         <v>41783</v>
       </c>
@@ -11892,7 +11889,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="14" thickBot="1">
       <c r="A282" s="11">
         <v>41790</v>
       </c>
@@ -11910,7 +11907,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="14" thickBot="1">
       <c r="A283" s="11">
         <v>41797</v>
       </c>
@@ -11928,7 +11925,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="14" thickBot="1">
       <c r="A284" s="11">
         <v>41804</v>
       </c>
@@ -11946,7 +11943,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="14" thickBot="1">
       <c r="A285" s="11">
         <v>41811</v>
       </c>
@@ -11964,7 +11961,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="14" thickBot="1">
       <c r="A286" s="11">
         <v>41818</v>
       </c>
@@ -11982,7 +11979,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="14" thickBot="1">
       <c r="A287" s="11">
         <v>41825</v>
       </c>
@@ -12000,7 +11997,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="14" thickBot="1">
       <c r="A288" s="11">
         <v>41832</v>
       </c>
@@ -12018,7 +12015,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="14" thickBot="1">
       <c r="A289" s="11">
         <v>41839</v>
       </c>
@@ -12036,7 +12033,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="14" thickBot="1">
       <c r="A290" s="11">
         <v>41846</v>
       </c>
@@ -12054,7 +12051,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="14" thickBot="1">
       <c r="A291" s="11">
         <v>41853</v>
       </c>
@@ -12072,7 +12069,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="14" thickBot="1">
       <c r="A292" s="11">
         <v>41860</v>
       </c>
@@ -12090,7 +12087,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="14" thickBot="1">
       <c r="A293" s="11">
         <v>41867</v>
       </c>
@@ -12108,7 +12105,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="14" thickBot="1">
       <c r="A294" s="11">
         <v>41874</v>
       </c>
@@ -12126,7 +12123,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="14" thickBot="1">
       <c r="A295" s="11">
         <v>41881</v>
       </c>
@@ -12144,7 +12141,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="14" thickBot="1">
       <c r="A296" s="11">
         <v>41888</v>
       </c>
@@ -12162,7 +12159,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="14" thickBot="1">
       <c r="A297" s="11">
         <v>41895</v>
       </c>
@@ -12180,7 +12177,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="14" thickBot="1">
       <c r="A298" s="11">
         <v>41902</v>
       </c>
@@ -12198,7 +12195,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="14" thickBot="1">
       <c r="A299" s="11">
         <v>41909</v>
       </c>
@@ -12216,7 +12213,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="14" thickBot="1">
       <c r="A300" s="11">
         <v>41916</v>
       </c>
@@ -12234,7 +12231,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="14" thickBot="1">
       <c r="A301" s="13">
         <v>41923</v>
       </c>
@@ -12252,7 +12249,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="14" thickBot="1">
       <c r="A302" s="11">
         <v>41930</v>
       </c>
@@ -12270,7 +12267,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="14" thickBot="1">
       <c r="A303" s="11">
         <v>41937</v>
       </c>
@@ -12288,7 +12285,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="14" thickBot="1">
       <c r="A304" s="11">
         <v>41944</v>
       </c>
@@ -12306,7 +12303,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="14" thickBot="1">
       <c r="A305" s="11">
         <v>41951</v>
       </c>
@@ -12324,7 +12321,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="14" thickBot="1">
       <c r="A306" s="11">
         <v>41958</v>
       </c>
@@ -12342,7 +12339,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="14" thickBot="1">
       <c r="A307" s="11">
         <v>41965</v>
       </c>
@@ -12360,7 +12357,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="14" thickBot="1">
       <c r="A308" s="11">
         <v>41972</v>
       </c>
@@ -12378,7 +12375,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="14" thickBot="1">
       <c r="A309" s="11">
         <v>41979</v>
       </c>
@@ -12396,7 +12393,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="14" thickBot="1">
       <c r="A310" s="11">
         <v>41986</v>
       </c>
@@ -12414,7 +12411,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="14" thickBot="1">
       <c r="A311" s="11">
         <v>41993</v>
       </c>
@@ -12432,7 +12429,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="14" thickBot="1">
       <c r="A312" s="11">
         <v>42000</v>
       </c>
@@ -12450,7 +12447,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="14" thickBot="1">
       <c r="A313" s="11">
         <v>42007</v>
       </c>
@@ -12468,7 +12465,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="14" thickBot="1">
       <c r="A314" s="11">
         <v>42014</v>
       </c>
@@ -12486,7 +12483,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="14" thickBot="1">
       <c r="A315" s="11">
         <v>42021</v>
       </c>
@@ -12504,7 +12501,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="14" thickBot="1">
       <c r="A316" s="11">
         <v>42028</v>
       </c>
@@ -12522,7 +12519,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="14" thickBot="1">
       <c r="A317" s="11">
         <v>42035</v>
       </c>
@@ -12540,7 +12537,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="14" thickBot="1">
       <c r="A318" s="11">
         <v>42042</v>
       </c>
@@ -12558,7 +12555,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="14" thickBot="1">
       <c r="A319" s="11">
         <v>42049</v>
       </c>
@@ -12576,7 +12573,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="14" thickBot="1">
       <c r="A320" s="11">
         <v>42056</v>
       </c>
@@ -12594,7 +12591,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="14" thickBot="1">
       <c r="A321" s="11">
         <v>42063</v>
       </c>
@@ -12612,7 +12609,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="14" thickBot="1">
       <c r="A322" s="11">
         <v>42070</v>
       </c>
@@ -12645,7 +12642,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="14" thickBot="1">
       <c r="A323" s="11">
         <v>42077</v>
       </c>
@@ -12663,7 +12660,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="14" thickBot="1">
       <c r="A324" s="11">
         <v>42084</v>
       </c>
@@ -12681,7 +12678,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="14" thickBot="1">
       <c r="A325" s="11">
         <v>42091</v>
       </c>
@@ -12699,7 +12696,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="14" thickBot="1">
       <c r="A326" s="13">
         <v>42098</v>
       </c>
@@ -12717,7 +12714,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="14" thickBot="1">
       <c r="A327" s="11">
         <v>42105</v>
       </c>
@@ -12735,7 +12732,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="14" thickBot="1">
       <c r="A328" s="11">
         <v>42112</v>
       </c>
@@ -12753,7 +12750,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="14" thickBot="1">
       <c r="A329" s="11">
         <v>42119</v>
       </c>
@@ -12771,7 +12768,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="14" thickBot="1">
       <c r="A330" s="11">
         <v>42126</v>
       </c>
@@ -12789,7 +12786,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="14" thickBot="1">
       <c r="A331" s="11">
         <v>42133</v>
       </c>
@@ -12807,7 +12804,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="14" thickBot="1">
       <c r="A332" s="11">
         <v>42140</v>
       </c>
@@ -12825,7 +12822,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="14" thickBot="1">
       <c r="A333" s="11">
         <v>42147</v>
       </c>
@@ -12843,7 +12840,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="14" thickBot="1">
       <c r="A334" s="11">
         <v>42154</v>
       </c>
@@ -12861,7 +12858,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="14" thickBot="1">
       <c r="A335" s="11">
         <v>42161</v>
       </c>
@@ -12879,7 +12876,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="14" thickBot="1">
       <c r="A336" s="11">
         <v>42168</v>
       </c>
@@ -12897,7 +12894,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="14" thickBot="1">
       <c r="A337" s="11">
         <v>42175</v>
       </c>
@@ -12915,7 +12912,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="14" thickBot="1">
       <c r="A338" s="11">
         <v>42182</v>
       </c>
@@ -12933,7 +12930,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="14" thickBot="1">
       <c r="A339" s="11">
         <v>42189</v>
       </c>
@@ -12951,7 +12948,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="14" thickBot="1">
       <c r="A340" s="11">
         <v>42196</v>
       </c>
@@ -12969,7 +12966,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="14" thickBot="1">
       <c r="A341" s="11">
         <v>42203</v>
       </c>
@@ -12987,7 +12984,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="14" thickBot="1">
       <c r="A342" s="11">
         <v>42210</v>
       </c>
@@ -13005,7 +13002,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="14" thickBot="1">
       <c r="A343" s="11">
         <v>42217</v>
       </c>
@@ -13023,7 +13020,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="14" thickBot="1">
       <c r="A344" s="11">
         <v>42224</v>
       </c>
@@ -13041,7 +13038,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="14" thickBot="1">
       <c r="A345" s="11">
         <v>42238</v>
       </c>
@@ -13059,7 +13056,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="14" thickBot="1">
       <c r="A346" s="11">
         <v>42245</v>
       </c>
@@ -13077,7 +13074,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="14" thickBot="1">
       <c r="A347" s="11">
         <v>42252</v>
       </c>
@@ -13095,7 +13092,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="14" thickBot="1">
       <c r="A348" s="11">
         <v>42259</v>
       </c>
@@ -13113,7 +13110,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="14" thickBot="1">
       <c r="A349" s="11">
         <v>42266</v>
       </c>
@@ -13131,7 +13128,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="14" thickBot="1">
       <c r="A350" s="11">
         <v>42273</v>
       </c>
@@ -13149,7 +13146,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="14" thickBot="1">
       <c r="A351" s="13">
         <v>42280</v>
       </c>
@@ -13167,7 +13164,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="14" thickBot="1">
       <c r="A352" s="11">
         <v>42287</v>
       </c>
@@ -13185,7 +13182,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="14" thickBot="1">
       <c r="A353" s="11">
         <v>42294</v>
       </c>
@@ -13203,7 +13200,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="14" thickBot="1">
       <c r="A354" s="11">
         <v>42301</v>
       </c>
@@ -13221,7 +13218,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="14" thickBot="1">
       <c r="A355" s="11">
         <v>42308</v>
       </c>
@@ -13239,7 +13236,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="14" thickBot="1">
       <c r="A356" s="11">
         <v>42315</v>
       </c>
@@ -13257,7 +13254,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="14" thickBot="1">
       <c r="A357" s="11">
         <v>42322</v>
       </c>
@@ -13275,7 +13272,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="14" thickBot="1">
       <c r="A358" s="11">
         <v>42336</v>
       </c>
@@ -13293,7 +13290,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="14" thickBot="1">
       <c r="A359" s="11">
         <v>42343</v>
       </c>
@@ -13311,7 +13308,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="14" thickBot="1">
       <c r="A360" s="11">
         <v>42350</v>
       </c>
@@ -13329,7 +13326,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="14" thickBot="1">
       <c r="A361" s="11">
         <v>42357</v>
       </c>
@@ -13347,7 +13344,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="14" thickBot="1">
       <c r="A362" s="11">
         <v>42364</v>
       </c>
@@ -13365,7 +13362,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="14" thickBot="1">
       <c r="A363" s="11">
         <v>42371</v>
       </c>
@@ -13383,7 +13380,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="14" thickBot="1">
       <c r="A364" s="11">
         <v>42378</v>
       </c>
@@ -13401,7 +13398,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="14" thickBot="1">
       <c r="A365" s="11">
         <v>42385</v>
       </c>
@@ -13419,7 +13416,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="14" thickBot="1">
       <c r="A366" s="11">
         <v>42392</v>
       </c>
@@ -13437,7 +13434,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="14" thickBot="1">
       <c r="A367" s="11">
         <v>42399</v>
       </c>
@@ -13455,7 +13452,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="14" thickBot="1">
       <c r="A368" s="11">
         <v>42406</v>
       </c>
@@ -13473,7 +13470,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="14" thickBot="1">
       <c r="A369" s="11">
         <v>42413</v>
       </c>
@@ -13491,7 +13488,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="14" thickBot="1">
       <c r="A370" s="11">
         <v>42420</v>
       </c>
@@ -13509,7 +13506,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="14" thickBot="1">
       <c r="A371" s="11">
         <v>42427</v>
       </c>
@@ -13527,7 +13524,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="14" thickBot="1">
       <c r="A372" s="11">
         <v>42434</v>
       </c>
@@ -13545,7 +13542,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="14" thickBot="1">
       <c r="A373" s="11">
         <v>42441</v>
       </c>
@@ -13563,7 +13560,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="14" thickBot="1">
       <c r="A374" s="11">
         <v>42448</v>
       </c>
@@ -13581,7 +13578,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="14" thickBot="1">
       <c r="A375" s="11">
         <v>42455</v>
       </c>
@@ -13599,7 +13596,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="14" thickBot="1">
       <c r="A376" s="13">
         <v>42462</v>
       </c>
@@ -13617,7 +13614,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="14" thickBot="1">
       <c r="A377" s="11">
         <v>42469</v>
       </c>
@@ -13635,7 +13632,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="14" thickBot="1">
       <c r="A378" s="11">
         <v>42476</v>
       </c>
@@ -13653,7 +13650,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="14" thickBot="1">
       <c r="A379" s="11">
         <v>42483</v>
       </c>
@@ -13671,7 +13668,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="14" thickBot="1">
       <c r="A380" s="11">
         <v>42490</v>
       </c>
@@ -13689,7 +13686,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="14" thickBot="1">
       <c r="A381" s="11">
         <v>42497</v>
       </c>
@@ -13707,7 +13704,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="14" thickBot="1">
       <c r="A382" s="11">
         <v>42504</v>
       </c>
@@ -13725,7 +13722,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="14" thickBot="1">
       <c r="A383" s="11">
         <v>42511</v>
       </c>
@@ -13743,7 +13740,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="14" thickBot="1">
       <c r="A384" s="11">
         <v>42518</v>
       </c>
@@ -13761,7 +13758,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="14" thickBot="1">
       <c r="A385" s="11">
         <v>42525</v>
       </c>
@@ -13779,7 +13776,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="14" thickBot="1">
       <c r="A386" s="11">
         <v>42532</v>
       </c>
@@ -13812,7 +13809,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="14" thickBot="1">
       <c r="A387" s="11">
         <v>42539</v>
       </c>
@@ -13830,7 +13827,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="14" thickBot="1">
       <c r="A388" s="11">
         <v>42546</v>
       </c>
@@ -13848,7 +13845,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="14" thickBot="1">
       <c r="A389" s="11">
         <v>42553</v>
       </c>
@@ -13866,7 +13863,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="14" thickBot="1">
       <c r="A390" s="11">
         <v>42560</v>
       </c>
@@ -13884,7 +13881,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="14" thickBot="1">
       <c r="A391" s="11">
         <v>42567</v>
       </c>
@@ -13902,7 +13899,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="14" thickBot="1">
       <c r="A392" s="11">
         <v>42574</v>
       </c>
@@ -13920,7 +13917,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="14" thickBot="1">
       <c r="A393" s="11">
         <v>42581</v>
       </c>
@@ -13938,7 +13935,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="14" thickBot="1">
       <c r="A394" s="11">
         <v>42588</v>
       </c>
@@ -13956,7 +13953,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="14" thickBot="1">
       <c r="A395" s="11">
         <v>42595</v>
       </c>
@@ -13974,7 +13971,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="14" thickBot="1">
       <c r="A396" s="11">
         <v>42602</v>
       </c>
@@ -13992,7 +13989,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="14" thickBot="1">
       <c r="A397" s="11">
         <v>42609</v>
       </c>
@@ -14010,7 +14007,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="14" thickBot="1">
       <c r="A398" s="11">
         <v>42616</v>
       </c>
@@ -14028,7 +14025,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="14" thickBot="1">
       <c r="A399" s="11">
         <v>42623</v>
       </c>
@@ -14046,7 +14043,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="14" thickBot="1">
       <c r="A400" s="11">
         <v>42630</v>
       </c>
@@ -14064,7 +14061,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="14" thickBot="1">
       <c r="A401" s="13">
         <v>42637</v>
       </c>
@@ -14082,7 +14079,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="14" thickBot="1">
       <c r="A402" s="11">
         <v>42644</v>
       </c>
@@ -14100,7 +14097,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="14" thickBot="1">
       <c r="A403" s="11">
         <v>42651</v>
       </c>
@@ -14118,7 +14115,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="14" thickBot="1">
       <c r="A404" s="11">
         <v>42658</v>
       </c>
@@ -14136,7 +14133,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="14" thickBot="1">
       <c r="A405" s="11">
         <v>42665</v>
       </c>
@@ -14154,7 +14151,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="14" thickBot="1">
       <c r="A406" s="11">
         <v>42672</v>
       </c>
@@ -14172,7 +14169,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="14" thickBot="1">
       <c r="A407" s="11">
         <v>42679</v>
       </c>
@@ -14190,7 +14187,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="14" thickBot="1">
       <c r="A408" s="11">
         <v>42686</v>
       </c>
@@ -14208,7 +14205,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="14" thickBot="1">
       <c r="A409" s="11">
         <v>42693</v>
       </c>
@@ -14226,7 +14223,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="14" thickBot="1">
       <c r="A410" s="11">
         <v>42700</v>
       </c>
@@ -14244,7 +14241,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="14" thickBot="1">
       <c r="A411" s="11">
         <v>42707</v>
       </c>
@@ -14262,7 +14259,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="14" thickBot="1">
       <c r="A412" s="11">
         <v>42714</v>
       </c>
@@ -14280,7 +14277,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="14" thickBot="1">
       <c r="A413" s="11">
         <v>42721</v>
       </c>
@@ -14298,7 +14295,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="14" thickBot="1">
       <c r="A414" s="11">
         <v>42728</v>
       </c>
@@ -14316,7 +14313,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="14" thickBot="1">
       <c r="A415" s="11">
         <v>42735</v>
       </c>
@@ -14334,7 +14331,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="14" thickBot="1">
       <c r="A416" s="11">
         <v>42742</v>
       </c>
@@ -14352,7 +14349,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="14" thickBot="1">
       <c r="A417" s="11">
         <v>42749</v>
       </c>
@@ -14370,7 +14367,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="14" thickBot="1">
       <c r="A418" s="11">
         <v>42756</v>
       </c>
@@ -14388,7 +14385,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="14" thickBot="1">
       <c r="A419" s="11">
         <v>42763</v>
       </c>
@@ -14406,7 +14403,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="14" thickBot="1">
       <c r="A420" s="11">
         <v>42770</v>
       </c>
@@ -14424,7 +14421,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="14" thickBot="1">
       <c r="A421" s="11">
         <v>42777</v>
       </c>
@@ -14442,7 +14439,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="14" thickBot="1">
       <c r="A422" s="11">
         <v>42784</v>
       </c>
@@ -14460,7 +14457,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="14" thickBot="1">
       <c r="A423" s="11">
         <v>42791</v>
       </c>
@@ -14478,7 +14475,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="14" thickBot="1">
       <c r="A424" s="11">
         <v>42798</v>
       </c>
@@ -14496,7 +14493,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="14" thickBot="1">
       <c r="A425" s="11">
         <v>42805</v>
       </c>
@@ -14514,7 +14511,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="14" thickBot="1">
       <c r="A426" s="13">
         <v>42812</v>
       </c>
@@ -14532,7 +14529,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="14" thickBot="1">
       <c r="A427" s="11">
         <v>42819</v>
       </c>
@@ -14550,7 +14547,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="14" thickBot="1">
       <c r="A428" s="11">
         <v>42826</v>
       </c>
@@ -14568,7 +14565,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="14" thickBot="1">
       <c r="A429" s="11">
         <v>42833</v>
       </c>
@@ -14586,7 +14583,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="14" thickBot="1">
       <c r="A430" s="11">
         <v>42840</v>
       </c>
@@ -14604,7 +14601,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="14" thickBot="1">
       <c r="A431" s="11">
         <v>42847</v>
       </c>
@@ -14622,7 +14619,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="14" thickBot="1">
       <c r="A432" s="11">
         <v>42854</v>
       </c>
@@ -14640,7 +14637,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="14" thickBot="1">
       <c r="A433" s="11">
         <v>42861</v>
       </c>
@@ -14658,7 +14655,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="14" thickBot="1">
       <c r="A434" s="11">
         <v>42868</v>
       </c>
@@ -14676,7 +14673,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="14" thickBot="1">
       <c r="A435" s="11">
         <v>42875</v>
       </c>
@@ -14694,7 +14691,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="14" thickBot="1">
       <c r="A436" s="11">
         <v>42882</v>
       </c>
@@ -14712,7 +14709,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="14" thickBot="1">
       <c r="A437" s="11">
         <v>42889</v>
       </c>
@@ -14730,7 +14727,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="14" thickBot="1">
       <c r="A438" s="11">
         <v>42896</v>
       </c>
@@ -14748,7 +14745,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="14" thickBot="1">
       <c r="A439" s="11">
         <v>42903</v>
       </c>
@@ -14766,7 +14763,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="14" thickBot="1">
       <c r="A440" s="11">
         <v>42910</v>
       </c>
@@ -14784,7 +14781,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="14" thickBot="1">
       <c r="A441" s="11">
         <v>42917</v>
       </c>
@@ -14802,7 +14799,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="14" thickBot="1">
       <c r="A442" s="11">
         <v>42924</v>
       </c>
@@ -14820,7 +14817,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="14" thickBot="1">
       <c r="A443" s="11">
         <v>42931</v>
       </c>
@@ -14838,7 +14835,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="14" thickBot="1">
       <c r="A444" s="11">
         <v>42938</v>
       </c>
@@ -14856,7 +14853,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="14" thickBot="1">
       <c r="A445" s="11">
         <v>42945</v>
       </c>
@@ -14874,7 +14871,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="14" thickBot="1">
       <c r="A446" s="11">
         <v>42952</v>
       </c>
@@ -14892,7 +14889,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="14" thickBot="1">
       <c r="A447" s="11">
         <v>42959</v>
       </c>
@@ -14910,7 +14907,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="14" thickBot="1">
       <c r="A448" s="11">
         <v>42966</v>
       </c>
@@ -14928,7 +14925,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="14" thickBot="1">
       <c r="A449" s="11">
         <v>42973</v>
       </c>
@@ -14946,7 +14943,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="14" thickBot="1">
       <c r="A450" s="11">
         <v>42980</v>
       </c>
@@ -14979,7 +14976,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="14" thickBot="1">
       <c r="A451" s="13">
         <v>42987</v>
       </c>
@@ -14997,7 +14994,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="14" thickBot="1">
       <c r="A452" s="11">
         <v>42994</v>
       </c>
@@ -15015,7 +15012,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="14" thickBot="1">
       <c r="A453" s="11">
         <v>43001</v>
       </c>
@@ -15033,7 +15030,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="14" thickBot="1">
       <c r="A454" s="11">
         <v>43008</v>
       </c>
@@ -15051,7 +15048,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="14" thickBot="1">
       <c r="A455" s="11">
         <v>43015</v>
       </c>
@@ -15069,7 +15066,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="14" thickBot="1">
       <c r="A456" s="11">
         <v>43022</v>
       </c>
@@ -15087,7 +15084,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="14" thickBot="1">
       <c r="A457" s="11">
         <v>43029</v>
       </c>
@@ -15105,7 +15102,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="14" thickBot="1">
       <c r="A458" s="11">
         <v>43036</v>
       </c>
@@ -15123,7 +15120,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="14" thickBot="1">
       <c r="A459" s="11">
         <v>43043</v>
       </c>
@@ -15141,7 +15138,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="14" thickBot="1">
       <c r="A460" s="11">
         <v>43050</v>
       </c>
@@ -15159,7 +15156,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="14" thickBot="1">
       <c r="A461" s="11">
         <v>43057</v>
       </c>
@@ -15177,7 +15174,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="14" thickBot="1">
       <c r="A462" s="11">
         <v>43064</v>
       </c>
@@ -15195,7 +15192,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="14" thickBot="1">
       <c r="A463" s="11">
         <v>43071</v>
       </c>
@@ -15213,7 +15210,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="14" thickBot="1">
       <c r="A464" s="11">
         <v>43078</v>
       </c>
@@ -15231,7 +15228,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="14" thickBot="1">
       <c r="A465" s="11">
         <v>43085</v>
       </c>
@@ -15249,7 +15246,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="14" thickBot="1">
       <c r="A466" s="11">
         <v>43092</v>
       </c>
@@ -15267,7 +15264,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="14" thickBot="1">
       <c r="A467" s="11">
         <v>43099</v>
       </c>
@@ -15285,7 +15282,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="14" thickBot="1">
       <c r="A468" s="11">
         <v>43113</v>
       </c>
@@ -15303,7 +15300,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="14" thickBot="1">
       <c r="A469" s="11">
         <v>43120</v>
       </c>
@@ -15321,7 +15318,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="14" thickBot="1">
       <c r="A470" s="11">
         <v>43127</v>
       </c>
@@ -15339,7 +15336,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="14" thickBot="1">
       <c r="A471" s="11">
         <v>43134</v>
       </c>
@@ -15357,7 +15354,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="14" thickBot="1">
       <c r="A472" s="11">
         <v>43141</v>
       </c>
@@ -15375,7 +15372,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="14" thickBot="1">
       <c r="A473" s="11">
         <v>43148</v>
       </c>
@@ -15393,7 +15390,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="14" thickBot="1">
       <c r="A474" s="11">
         <v>43155</v>
       </c>
@@ -15411,7 +15408,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="14" thickBot="1">
       <c r="A475" s="11">
         <v>43162</v>
       </c>
@@ -15429,7 +15426,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="14" thickBot="1">
       <c r="A476" s="13">
         <v>43169</v>
       </c>
@@ -15447,7 +15444,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="14" thickBot="1">
       <c r="A477" s="11">
         <v>43176</v>
       </c>
@@ -15465,7 +15462,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="14" thickBot="1">
       <c r="A478" s="11">
         <v>43183</v>
       </c>
@@ -15483,7 +15480,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="14" thickBot="1">
       <c r="A479" s="11">
         <v>43190</v>
       </c>
@@ -15501,7 +15498,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="14" thickBot="1">
       <c r="A480" s="11">
         <v>43197</v>
       </c>
@@ -15519,7 +15516,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="14" thickBot="1">
       <c r="A481" s="11">
         <v>43204</v>
       </c>
@@ -15537,7 +15534,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="14" thickBot="1">
       <c r="A482" s="11">
         <v>43211</v>
       </c>
@@ -15555,7 +15552,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="14" thickBot="1">
       <c r="A483" s="11">
         <v>43218</v>
       </c>
@@ -15573,7 +15570,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="14" thickBot="1">
       <c r="A484" s="11">
         <v>43225</v>
       </c>
@@ -15591,7 +15588,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="14" thickBot="1">
       <c r="A485" s="11">
         <v>43232</v>
       </c>
@@ -15609,7 +15606,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="14" thickBot="1">
       <c r="A486" s="11">
         <v>43239</v>
       </c>
@@ -15627,7 +15624,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="14" thickBot="1">
       <c r="A487" s="11">
         <v>43246</v>
       </c>
@@ -15645,7 +15642,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="14" thickBot="1">
       <c r="A488" s="11">
         <v>43253</v>
       </c>
@@ -15663,7 +15660,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="14" thickBot="1">
       <c r="A489" s="11">
         <v>43260</v>
       </c>
@@ -15681,7 +15678,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="14" thickBot="1">
       <c r="A490" s="11">
         <v>43267</v>
       </c>
@@ -15699,7 +15696,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="14" thickBot="1">
       <c r="A491" s="11">
         <v>43274</v>
       </c>
@@ -15717,7 +15714,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="14" thickBot="1">
       <c r="A492" s="11">
         <v>43281</v>
       </c>
@@ -15735,7 +15732,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="14" thickBot="1">
       <c r="A493" s="11">
         <v>43288</v>
       </c>
@@ -15753,7 +15750,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="14" thickBot="1">
       <c r="A494" s="11">
         <v>43295</v>
       </c>
@@ -15771,7 +15768,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="14" thickBot="1">
       <c r="A495" s="11">
         <v>43302</v>
       </c>
@@ -15789,7 +15786,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="14" thickBot="1">
       <c r="A496" s="11">
         <v>43309</v>
       </c>
@@ -15807,7 +15804,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="14" thickBot="1">
       <c r="A497" s="11">
         <v>43316</v>
       </c>
@@ -15825,7 +15822,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="14" thickBot="1">
       <c r="A498" s="11">
         <v>43323</v>
       </c>
@@ -15843,7 +15840,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="14" thickBot="1">
       <c r="A499" s="11">
         <v>43330</v>
       </c>
@@ -15861,7 +15858,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="14" thickBot="1">
       <c r="A500" s="11">
         <v>43337</v>
       </c>
@@ -15879,7 +15876,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="14" thickBot="1">
       <c r="A501" s="13">
         <v>43344</v>
       </c>
@@ -15897,7 +15894,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="14" thickBot="1">
       <c r="A502" s="11">
         <v>43351</v>
       </c>
@@ -15915,7 +15912,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="14" thickBot="1">
       <c r="A503" s="11">
         <v>43358</v>
       </c>
@@ -15933,7 +15930,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="14" thickBot="1">
       <c r="A504" s="11">
         <v>43365</v>
       </c>
@@ -15951,7 +15948,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="14" thickBot="1">
       <c r="A505" s="11">
         <v>43372</v>
       </c>
@@ -15969,7 +15966,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="14" thickBot="1">
       <c r="A506" s="11">
         <v>43379</v>
       </c>
@@ -15987,7 +15984,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="14" thickBot="1">
       <c r="A507" s="11">
         <v>43386</v>
       </c>
@@ -16005,7 +16002,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="14" thickBot="1">
       <c r="A508" s="11">
         <v>43393</v>
       </c>
@@ -16023,7 +16020,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="14" thickBot="1">
       <c r="A509" s="11">
         <v>43400</v>
       </c>
@@ -16041,7 +16038,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="14" thickBot="1">
       <c r="A510" s="11">
         <v>43407</v>
       </c>
@@ -16059,7 +16056,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="14" thickBot="1">
       <c r="A511" s="11">
         <v>43414</v>
       </c>
@@ -16077,7 +16074,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="14" thickBot="1">
       <c r="A512" s="11">
         <v>43421</v>
       </c>
@@ -16095,7 +16092,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="14" thickBot="1">
       <c r="A513" s="11">
         <v>43428</v>
       </c>
@@ -16113,7 +16110,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="14" thickBot="1">
       <c r="A514" s="11">
         <v>43435</v>
       </c>
@@ -16146,7 +16143,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="14" thickBot="1">
       <c r="A515" s="11">
         <v>43442</v>
       </c>
@@ -16164,7 +16161,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="14" thickBot="1">
       <c r="A516" s="11">
         <v>43449</v>
       </c>
@@ -16182,7 +16179,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="14" thickBot="1">
       <c r="A517" s="11">
         <v>43456</v>
       </c>
@@ -16200,7 +16197,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="14" thickBot="1">
       <c r="A518" s="11">
         <v>43463</v>
       </c>
@@ -16218,7 +16215,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="14" thickBot="1">
       <c r="A519" s="11">
         <v>43470</v>
       </c>
@@ -16236,7 +16233,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="14" thickBot="1">
       <c r="A520" s="11">
         <v>43477</v>
       </c>
@@ -16254,7 +16251,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="14" thickBot="1">
       <c r="A521" s="11">
         <v>43484</v>
       </c>
@@ -16272,7 +16269,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="14" thickBot="1">
       <c r="A522" s="11">
         <v>43491</v>
       </c>
@@ -16290,7 +16287,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="14" thickBot="1">
       <c r="A523" s="11">
         <v>43498</v>
       </c>
@@ -16308,7 +16305,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="14" thickBot="1">
       <c r="A524" s="11">
         <v>43505</v>
       </c>
@@ -16326,7 +16323,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="14" thickBot="1">
       <c r="A525" s="11">
         <v>43512</v>
       </c>
@@ -16344,7 +16341,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="14" thickBot="1">
       <c r="A526" s="13">
         <v>43519</v>
       </c>
@@ -16362,7 +16359,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="14" thickBot="1">
       <c r="A527" s="11">
         <v>43526</v>
       </c>
@@ -16380,7 +16377,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="14" thickBot="1">
       <c r="A528" s="11">
         <v>43533</v>
       </c>
@@ -16398,7 +16395,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="14" thickBot="1">
       <c r="A529" s="11">
         <v>43540</v>
       </c>
@@ -16416,7 +16413,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="14" thickBot="1">
       <c r="A530" s="11">
         <v>43547</v>
       </c>
@@ -16434,7 +16431,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="14" thickBot="1">
       <c r="A531" s="11">
         <v>43554</v>
       </c>
@@ -16452,7 +16449,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="14" thickBot="1">
       <c r="A532" s="11">
         <v>43561</v>
       </c>
@@ -16470,7 +16467,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="14" thickBot="1">
       <c r="A533" s="11">
         <v>43568</v>
       </c>
@@ -16488,7 +16485,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="14" thickBot="1">
       <c r="A534" s="11">
         <v>43575</v>
       </c>
@@ -16506,7 +16503,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="14" thickBot="1">
       <c r="A535" s="11">
         <v>43582</v>
       </c>
@@ -16524,7 +16521,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="14" thickBot="1">
       <c r="A536" s="11">
         <v>43589</v>
       </c>
@@ -16542,7 +16539,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="14" thickBot="1">
       <c r="A537" s="11">
         <v>43596</v>
       </c>
@@ -16560,7 +16557,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="14" thickBot="1">
       <c r="A538" s="11">
         <v>43603</v>
       </c>
@@ -16578,7 +16575,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="14" thickBot="1">
       <c r="A539" s="11">
         <v>43610</v>
       </c>
@@ -16596,7 +16593,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="14" thickBot="1">
       <c r="A540" s="11">
         <v>43617</v>
       </c>
@@ -16614,7 +16611,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="14" thickBot="1">
       <c r="A541" s="11">
         <v>43624</v>
       </c>
@@ -16632,7 +16629,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="14" thickBot="1">
       <c r="A542" s="11">
         <v>43631</v>
       </c>
@@ -16650,7 +16647,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="14" thickBot="1">
       <c r="A543" s="11">
         <v>43638</v>
       </c>
@@ -16668,7 +16665,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="14" thickBot="1">
       <c r="A544" s="11">
         <v>43645</v>
       </c>
@@ -16686,7 +16683,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="14" thickBot="1">
       <c r="A545" s="11">
         <v>43652</v>
       </c>
@@ -16704,7 +16701,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="14" thickBot="1">
       <c r="A546" s="11">
         <v>43659</v>
       </c>
@@ -16722,7 +16719,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="14" thickBot="1">
       <c r="A547" s="11">
         <v>43666</v>
       </c>
@@ -16740,7 +16737,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="14" thickBot="1">
       <c r="A548" s="11">
         <v>43673</v>
       </c>
@@ -16758,7 +16755,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="14" thickBot="1">
       <c r="A549" s="11">
         <v>43680</v>
       </c>
@@ -16776,7 +16773,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="14" thickBot="1">
       <c r="A550" s="11">
         <v>43687</v>
       </c>
@@ -16794,7 +16791,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="14" thickBot="1">
       <c r="A551" s="13">
         <v>43694</v>
       </c>
@@ -16812,7 +16809,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="14" thickBot="1">
       <c r="A552" s="11">
         <v>43701</v>
       </c>
@@ -16830,7 +16827,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="14" thickBot="1">
       <c r="A553" s="11">
         <v>43708</v>
       </c>
@@ -16848,7 +16845,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="14" thickBot="1">
       <c r="A554" s="11">
         <v>43715</v>
       </c>
@@ -16866,7 +16863,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="14" thickBot="1">
       <c r="A555" s="11">
         <v>43722</v>
       </c>
@@ -16884,7 +16881,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="14" thickBot="1">
       <c r="A556" s="11">
         <v>43729</v>
       </c>
@@ -16902,7 +16899,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="14" thickBot="1">
       <c r="A557" s="11">
         <v>43736</v>
       </c>
@@ -16920,7 +16917,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="14" thickBot="1">
       <c r="A558" s="11">
         <v>43743</v>
       </c>
@@ -16938,7 +16935,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="14" thickBot="1">
       <c r="A559" s="11">
         <v>43750</v>
       </c>
@@ -16956,7 +16953,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="14" thickBot="1">
       <c r="A560" s="11">
         <v>43757</v>
       </c>
@@ -16974,7 +16971,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="14" thickBot="1">
       <c r="A561" s="11">
         <v>43764</v>
       </c>
@@ -16992,7 +16989,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="14" thickBot="1">
       <c r="A562" s="11">
         <v>43771</v>
       </c>
@@ -17010,7 +17007,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="14" thickBot="1">
       <c r="A563" s="11">
         <v>43778</v>
       </c>
@@ -17028,7 +17025,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="14" thickBot="1">
       <c r="A564" s="11">
         <v>43785</v>
       </c>
@@ -17046,7 +17043,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="14" thickBot="1">
       <c r="A565" s="11">
         <v>43792</v>
       </c>
@@ -17064,7 +17061,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="14" thickBot="1">
       <c r="A566" s="11">
         <v>43813</v>
       </c>
@@ -17082,7 +17079,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="14" thickBot="1">
       <c r="A567" s="11">
         <v>43820</v>
       </c>
@@ -17100,7 +17097,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="14" thickBot="1">
       <c r="A568" s="11">
         <v>43827</v>
       </c>
@@ -17118,7 +17115,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="14" thickBot="1">
       <c r="A569" s="11">
         <v>43834</v>
       </c>
@@ -17136,7 +17133,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="14" thickBot="1">
       <c r="A570" s="11">
         <v>43841</v>
       </c>
@@ -17154,7 +17151,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="14" thickBot="1">
       <c r="A571" s="11">
         <v>43848</v>
       </c>
@@ -17172,7 +17169,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="14" thickBot="1">
       <c r="A572" s="11">
         <v>43855</v>
       </c>
@@ -17190,7 +17187,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="14" thickBot="1">
       <c r="A573" s="11">
         <v>43862</v>
       </c>
@@ -17208,7 +17205,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="14" thickBot="1">
       <c r="A574" s="11">
         <v>43869</v>
       </c>
@@ -17226,7 +17223,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="14" thickBot="1">
       <c r="A575" s="11">
         <v>43876</v>
       </c>
@@ -17244,7 +17241,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="14" thickBot="1">
       <c r="A576" s="13">
         <v>43883</v>
       </c>
@@ -17262,7 +17259,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="14" thickBot="1">
       <c r="A577" s="11">
         <v>43890</v>
       </c>
@@ -17280,7 +17277,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="14" thickBot="1">
       <c r="A578" s="11">
         <v>43897</v>
       </c>
@@ -17313,7 +17310,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="14" thickBot="1">
       <c r="A579" s="11">
         <v>43904</v>
       </c>
@@ -17331,7 +17328,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="14" thickBot="1">
       <c r="A580" s="11">
         <v>43911</v>
       </c>
@@ -17349,7 +17346,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="14" thickBot="1">
       <c r="A581" s="11">
         <v>43918</v>
       </c>
@@ -17367,7 +17364,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="14" thickBot="1">
       <c r="A582" s="11">
         <v>43925</v>
       </c>
@@ -17385,7 +17382,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="14" thickBot="1">
       <c r="A583" s="11">
         <v>43932</v>
       </c>
@@ -17403,7 +17400,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="14" thickBot="1">
       <c r="A584" s="11">
         <v>43939</v>
       </c>
@@ -17421,7 +17418,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="14" thickBot="1">
       <c r="A585" s="11">
         <v>43946</v>
       </c>
@@ -17439,7 +17436,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="14" thickBot="1">
       <c r="A586" s="11">
         <v>43953</v>
       </c>
@@ -17457,7 +17454,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="14" thickBot="1">
       <c r="A587" s="11">
         <v>43960</v>
       </c>
@@ -17475,7 +17472,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="14" thickBot="1">
       <c r="A588" s="11">
         <v>43967</v>
       </c>
@@ -17493,7 +17490,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="14" thickBot="1">
       <c r="A589" s="11">
         <v>43974</v>
       </c>
@@ -17511,7 +17508,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="14" thickBot="1">
       <c r="A590" s="11">
         <v>43981</v>
       </c>
@@ -17529,7 +17526,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="14" thickBot="1">
       <c r="A591" s="11">
         <v>43988</v>
       </c>
@@ -17547,7 +17544,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="14" thickBot="1">
       <c r="A592" s="11">
         <v>43995</v>
       </c>
@@ -17565,7 +17562,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="14" thickBot="1">
       <c r="A593" s="11">
         <v>44002</v>
       </c>
@@ -17583,7 +17580,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="14" thickBot="1">
       <c r="A594" s="11">
         <v>44009</v>
       </c>
@@ -17601,7 +17598,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="14" thickBot="1">
       <c r="A595" s="11">
         <v>44016</v>
       </c>
@@ -17619,7 +17616,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="14" thickBot="1">
       <c r="A596" s="11">
         <v>44023</v>
       </c>
@@ -17637,7 +17634,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="14" thickBot="1">
       <c r="A597" s="11">
         <v>44030</v>
       </c>
@@ -17655,7 +17652,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="14" thickBot="1">
       <c r="A598" s="11">
         <v>44037</v>
       </c>
@@ -17673,7 +17670,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="14" thickBot="1">
       <c r="A599" s="11">
         <v>44044</v>
       </c>
@@ -17691,7 +17688,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="14" thickBot="1">
       <c r="A600" s="11">
         <v>44051</v>
       </c>
@@ -17709,7 +17706,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="14" thickBot="1">
       <c r="A601" s="13">
         <v>44058</v>
       </c>
@@ -17727,7 +17724,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="14" thickBot="1">
       <c r="A602" s="11">
         <v>44072</v>
       </c>
@@ -17745,7 +17742,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="14" thickBot="1">
       <c r="A603" s="11">
         <v>44079</v>
       </c>
@@ -17763,7 +17760,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="14" thickBot="1">
       <c r="A604" s="11">
         <v>44086</v>
       </c>
@@ -17781,7 +17778,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="14" thickBot="1">
       <c r="A605" s="11">
         <v>44093</v>
       </c>
@@ -17799,7 +17796,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="14" thickBot="1">
       <c r="A606" s="11">
         <v>44100</v>
       </c>
@@ -17817,7 +17814,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="14" thickBot="1">
       <c r="A607" s="11">
         <v>44107</v>
       </c>
@@ -17835,7 +17832,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="14" thickBot="1">
       <c r="A608" s="11">
         <v>44114</v>
       </c>
@@ -17853,7 +17850,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="14" thickBot="1">
       <c r="A609" s="11">
         <v>44121</v>
       </c>
@@ -17871,7 +17868,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="14" thickBot="1">
       <c r="A610" s="11">
         <v>44128</v>
       </c>
@@ -17889,7 +17886,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="14" thickBot="1">
       <c r="A611" s="11">
         <v>44135</v>
       </c>
@@ -17907,7 +17904,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="14" thickBot="1">
       <c r="A612" s="11">
         <v>44142</v>
       </c>
@@ -17925,7 +17922,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="14" thickBot="1">
       <c r="A613" s="11">
         <v>44149</v>
       </c>
@@ -17943,7 +17940,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="14" thickBot="1">
       <c r="A614" s="11">
         <v>44156</v>
       </c>
@@ -17961,7 +17958,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="14" thickBot="1">
       <c r="A615" s="11">
         <v>44163</v>
       </c>
@@ -17979,7 +17976,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="14" thickBot="1">
       <c r="A616" s="11">
         <v>44170</v>
       </c>
@@ -17997,7 +17994,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="14" thickBot="1">
       <c r="A617" s="11">
         <v>44177</v>
       </c>
@@ -18015,7 +18012,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="14" thickBot="1">
       <c r="A618" s="11">
         <v>44191</v>
       </c>
@@ -18033,7 +18030,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="14" thickBot="1">
       <c r="A619" s="11">
         <v>44198</v>
       </c>
@@ -18051,7 +18048,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="14" thickBot="1">
       <c r="A620" s="11">
         <v>44205</v>
       </c>
@@ -18069,7 +18066,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="14" thickBot="1">
       <c r="A621" s="11">
         <v>44212</v>
       </c>
@@ -18087,7 +18084,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="14" thickBot="1">
       <c r="A622" s="11">
         <v>44219</v>
       </c>
@@ -18105,7 +18102,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="14" thickBot="1">
       <c r="A623" s="11">
         <v>44226</v>
       </c>
@@ -18123,7 +18120,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="14" thickBot="1">
       <c r="A624" s="11">
         <v>44233</v>
       </c>
@@ -18141,7 +18138,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="14" thickBot="1">
       <c r="A625" s="11">
         <v>44240</v>
       </c>
@@ -18159,7 +18156,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="14" thickBot="1">
       <c r="A626" s="13">
         <v>44247</v>
       </c>
@@ -18177,7 +18174,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="14" thickBot="1">
       <c r="A627" s="11">
         <v>44254</v>
       </c>
@@ -18195,7 +18192,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="14" thickBot="1">
       <c r="A628" s="11">
         <v>44261</v>
       </c>
@@ -18213,7 +18210,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="14" thickBot="1">
       <c r="A629" s="11">
         <v>44268</v>
       </c>
@@ -18231,7 +18228,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="14" thickBot="1">
       <c r="A630" s="11">
         <v>44275</v>
       </c>
@@ -18249,7 +18246,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="14" thickBot="1">
       <c r="A631" s="11">
         <v>44282</v>
       </c>
@@ -18267,7 +18264,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="14" thickBot="1">
       <c r="A632" s="11">
         <v>44289</v>
       </c>
@@ -18285,7 +18282,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="14" thickBot="1">
       <c r="A633" s="11">
         <v>44296</v>
       </c>
@@ -18303,7 +18300,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="14" thickBot="1">
       <c r="A634" s="11">
         <v>44303</v>
       </c>
@@ -18321,7 +18318,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="14" thickBot="1">
       <c r="A635" s="11">
         <v>44310</v>
       </c>
@@ -18339,7 +18336,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="14" thickBot="1">
       <c r="A636" s="11">
         <v>44317</v>
       </c>
@@ -18357,7 +18354,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="14" thickBot="1">
       <c r="A637" s="11">
         <v>44324</v>
       </c>
@@ -18375,7 +18372,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="14" thickBot="1">
       <c r="A638" s="11">
         <v>44331</v>
       </c>
@@ -18393,7 +18390,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="14" thickBot="1">
       <c r="A639" s="11">
         <v>44338</v>
       </c>
@@ -18411,7 +18408,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="14" thickBot="1">
       <c r="A640" s="11">
         <v>44345</v>
       </c>
@@ -18429,7 +18426,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="14" thickBot="1">
       <c r="A641" s="11">
         <v>44352</v>
       </c>
@@ -18447,7 +18444,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="14" thickBot="1">
       <c r="A642" s="11">
         <v>44359</v>
       </c>
@@ -18480,7 +18477,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="14" thickBot="1">
       <c r="A643" s="11">
         <v>44366</v>
       </c>
@@ -18498,7 +18495,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="14" thickBot="1">
       <c r="A644" s="11">
         <v>44373</v>
       </c>
@@ -18516,7 +18513,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="14" thickBot="1">
       <c r="A645" s="11">
         <v>44380</v>
       </c>
@@ -18534,7 +18531,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="14" thickBot="1">
       <c r="A646" s="11">
         <v>44387</v>
       </c>
@@ -18552,7 +18549,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="14" thickBot="1">
       <c r="A647" s="11">
         <v>44394</v>
       </c>
@@ -18570,7 +18567,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="14" thickBot="1">
       <c r="A648" s="11">
         <v>44401</v>
       </c>
@@ -18588,7 +18585,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="14" thickBot="1">
       <c r="A649" s="11">
         <v>44408</v>
       </c>
@@ -18606,7 +18603,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="14" thickBot="1">
       <c r="A650" s="11">
         <v>44415</v>
       </c>
@@ -18624,7 +18621,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="14" thickBot="1">
       <c r="A651" s="13">
         <v>44422</v>
       </c>
@@ -18642,7 +18639,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="14" thickBot="1">
       <c r="A652" s="11">
         <v>44429</v>
       </c>
@@ -18660,7 +18657,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="14" thickBot="1">
       <c r="A653" s="11">
         <v>44436</v>
       </c>
@@ -18678,7 +18675,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="14" thickBot="1">
       <c r="A654" s="11">
         <v>44443</v>
       </c>
@@ -18696,7 +18693,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="14" thickBot="1">
       <c r="A655" s="11">
         <v>44450</v>
       </c>
@@ -18714,7 +18711,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="14" thickBot="1">
       <c r="A656" s="11">
         <v>44457</v>
       </c>
@@ -18732,7 +18729,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="14" thickBot="1">
       <c r="A657" s="11">
         <v>44464</v>
       </c>
@@ -18750,7 +18747,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="14" thickBot="1">
       <c r="A658" s="11">
         <v>44471</v>
       </c>
@@ -18768,7 +18765,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="14" thickBot="1">
       <c r="A659" s="11">
         <v>44478</v>
       </c>
@@ -18786,7 +18783,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="14" thickBot="1">
       <c r="A660" s="11">
         <v>44485</v>
       </c>
@@ -18804,7 +18801,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="14" thickBot="1">
       <c r="A661" s="11">
         <v>44492</v>
       </c>
@@ -18822,7 +18819,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="14" thickBot="1">
       <c r="A662" s="11">
         <v>44499</v>
       </c>
@@ -18840,7 +18837,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="14" thickBot="1">
       <c r="A663" s="11">
         <v>44506</v>
       </c>
@@ -18858,7 +18855,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="14" thickBot="1">
       <c r="A664" s="11">
         <v>44513</v>
       </c>
@@ -18876,7 +18873,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="14" thickBot="1">
       <c r="A665" s="11">
         <v>44520</v>
       </c>
@@ -18894,7 +18891,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="14" thickBot="1">
       <c r="A666" s="11">
         <v>44527</v>
       </c>
@@ -18912,7 +18909,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="14" thickBot="1">
       <c r="A667" s="11">
         <v>44534</v>
       </c>
@@ -18930,7 +18927,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="14" thickBot="1">
       <c r="A668" s="11">
         <v>44541</v>
       </c>
@@ -18948,7 +18945,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="14" thickBot="1">
       <c r="A669" s="11">
         <v>44548</v>
       </c>
@@ -18966,7 +18963,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="14" thickBot="1">
       <c r="A670" s="11">
         <v>44555</v>
       </c>
@@ -18984,7 +18981,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="14" thickBot="1">
       <c r="A671" s="11">
         <v>44562</v>
       </c>
@@ -19002,7 +18999,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="14" thickBot="1">
       <c r="A672" s="11">
         <v>44569</v>
       </c>
@@ -19020,7 +19017,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="14" thickBot="1">
       <c r="A673" s="11">
         <v>44576</v>
       </c>
@@ -19038,7 +19035,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="14" thickBot="1">
       <c r="A674" s="11">
         <v>44583</v>
       </c>
@@ -19056,7 +19053,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="14" thickBot="1">
       <c r="A675" s="11">
         <v>44590</v>
       </c>
@@ -19074,7 +19071,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="14" thickBot="1">
       <c r="A676" s="13">
         <v>44597</v>
       </c>
@@ -19092,7 +19089,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="14" thickBot="1">
       <c r="A677" s="11">
         <v>44604</v>
       </c>
@@ -19110,7 +19107,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="14" thickBot="1">
       <c r="A678" s="11">
         <v>44611</v>
       </c>
@@ -19128,7 +19125,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="14" thickBot="1">
       <c r="A679" s="11">
         <v>44625</v>
       </c>
@@ -19146,7 +19143,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="14" thickBot="1">
       <c r="A680" s="11">
         <v>44632</v>
       </c>
@@ -19164,7 +19161,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="14" thickBot="1">
       <c r="A681" s="11">
         <v>44639</v>
       </c>
@@ -19182,7 +19179,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="14" thickBot="1">
       <c r="A682" s="11">
         <v>44646</v>
       </c>
@@ -19200,7 +19197,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="14" thickBot="1">
       <c r="A683" s="11">
         <v>44653</v>
       </c>
@@ -19218,7 +19215,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="14" thickBot="1">
       <c r="A684" s="11">
         <v>44660</v>
       </c>
@@ -19236,7 +19233,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="14" thickBot="1">
       <c r="A685" s="11">
         <v>44667</v>
       </c>
@@ -19254,7 +19251,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="14" thickBot="1">
       <c r="A686" s="11">
         <v>44674</v>
       </c>
@@ -19272,7 +19269,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="14" thickBot="1">
       <c r="A687" s="11">
         <v>44681</v>
       </c>
@@ -19290,7 +19287,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="14" thickBot="1">
       <c r="A688" s="11">
         <v>44688</v>
       </c>
@@ -19308,7 +19305,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="14" thickBot="1">
       <c r="A689" s="11">
         <v>44695</v>
       </c>
@@ -19326,7 +19323,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="14" thickBot="1">
       <c r="A690" s="11">
         <v>44702</v>
       </c>
@@ -19344,7 +19341,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="14" thickBot="1">
       <c r="A691" s="11">
         <v>44709</v>
       </c>
@@ -19362,7 +19359,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="14" thickBot="1">
       <c r="A692" s="11">
         <v>44716</v>
       </c>
@@ -19380,7 +19377,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="14" thickBot="1">
       <c r="A693" s="11">
         <v>44723</v>
       </c>
@@ -19398,7 +19395,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="14" thickBot="1">
       <c r="A694" s="11">
         <v>44730</v>
       </c>
@@ -19416,7 +19413,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="14" thickBot="1">
       <c r="A695" s="11">
         <v>44737</v>
       </c>
@@ -19434,7 +19431,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="14" thickBot="1">
       <c r="A696" s="11">
         <v>44744</v>
       </c>
@@ -19452,7 +19449,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="14" thickBot="1">
       <c r="A697" s="11">
         <v>44751</v>
       </c>
@@ -19470,7 +19467,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="14" thickBot="1">
       <c r="A698" s="11">
         <v>44758</v>
       </c>
@@ -19488,7 +19485,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="14" thickBot="1">
       <c r="A699" s="11">
         <v>44765</v>
       </c>
@@ -19506,7 +19503,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="14" thickBot="1">
       <c r="A700" s="11">
         <v>44772</v>
       </c>
@@ -19524,7 +19521,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="14" thickBot="1">
       <c r="A701" s="13">
         <v>44779</v>
       </c>
@@ -19542,7 +19539,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="14" thickBot="1">
       <c r="A702" s="11">
         <v>44786</v>
       </c>
@@ -19560,7 +19557,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="14" thickBot="1">
       <c r="A703" s="11">
         <v>44793</v>
       </c>
@@ -19578,7 +19575,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="14" thickBot="1">
       <c r="A704" s="11">
         <v>44800</v>
       </c>
@@ -19596,7 +19593,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="14" thickBot="1">
       <c r="A705" s="11">
         <v>44807</v>
       </c>
@@ -19614,7 +19611,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="14" thickBot="1">
       <c r="A706" s="11">
         <v>44814</v>
       </c>
@@ -19647,7 +19644,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="14" thickBot="1">
       <c r="A707" s="11">
         <v>44821</v>
       </c>
@@ -19665,7 +19662,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="14" thickBot="1">
       <c r="A708" s="11">
         <v>44828</v>
       </c>
@@ -19683,7 +19680,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="14" thickBot="1">
       <c r="A709" s="11">
         <v>44835</v>
       </c>
@@ -19701,7 +19698,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="14" thickBot="1">
       <c r="A710" s="11">
         <v>44842</v>
       </c>
@@ -19719,7 +19716,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="14" thickBot="1">
       <c r="A711" s="11">
         <v>44849</v>
       </c>
@@ -19737,7 +19734,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="14" thickBot="1">
       <c r="A712" s="11">
         <v>44856</v>
       </c>
@@ -19755,7 +19752,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="14" thickBot="1">
       <c r="A713" s="11">
         <v>44863</v>
       </c>
@@ -19773,7 +19770,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="14" thickBot="1">
       <c r="A714" s="11">
         <v>44870</v>
       </c>
@@ -19791,7 +19788,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="14" thickBot="1">
       <c r="A715" s="11">
         <v>44877</v>
       </c>
@@ -19809,7 +19806,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="14" thickBot="1">
       <c r="A716" s="11">
         <v>44884</v>
       </c>
@@ -19827,7 +19824,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="14" thickBot="1">
       <c r="A717" s="11">
         <v>44891</v>
       </c>
@@ -19845,7 +19842,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="14" thickBot="1">
       <c r="A718" s="11">
         <v>44898</v>
       </c>
@@ -19863,7 +19860,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="14" thickBot="1">
       <c r="A719" s="11">
         <v>44905</v>
       </c>
@@ -19881,7 +19878,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="14" thickBot="1">
       <c r="A720" s="11">
         <v>44912</v>
       </c>
@@ -19899,7 +19896,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="14" thickBot="1">
       <c r="A721" s="11">
         <v>44919</v>
       </c>
@@ -19917,7 +19914,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="14" thickBot="1">
       <c r="A722" s="11">
         <v>44926</v>
       </c>
@@ -19935,7 +19932,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="14" thickBot="1">
       <c r="A723" s="11">
         <v>44933</v>
       </c>
@@ -19953,7 +19950,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="14" thickBot="1">
       <c r="A724" s="11">
         <v>44940</v>
       </c>
@@ -19971,7 +19968,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="14" thickBot="1">
       <c r="A725" s="11">
         <v>44947</v>
       </c>
@@ -19989,7 +19986,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" ht="14" thickBot="1">
       <c r="A726" s="13">
         <v>44954</v>
       </c>
@@ -20007,7 +20004,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" ht="14" thickBot="1">
       <c r="A727" s="11">
         <v>44961</v>
       </c>
@@ -20025,7 +20022,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" ht="14" thickBot="1">
       <c r="A728" s="11">
         <v>44968</v>
       </c>
@@ -20043,7 +20040,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" ht="14" thickBot="1">
       <c r="A729" s="11">
         <v>44975</v>
       </c>
@@ -20061,7 +20058,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:5" ht="14" thickBot="1">
       <c r="A730" s="11">
         <v>44982</v>
       </c>
@@ -20079,7 +20076,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" ht="14" thickBot="1">
       <c r="A731" s="11">
         <v>44989</v>
       </c>
@@ -20097,7 +20094,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" ht="14" thickBot="1">
       <c r="A732" s="11">
         <v>44996</v>
       </c>
@@ -20115,7 +20112,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" ht="14" thickBot="1">
       <c r="A733" s="11">
         <v>45003</v>
       </c>
@@ -20133,7 +20130,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" ht="14" thickBot="1">
       <c r="A734" s="11">
         <v>45010</v>
       </c>
@@ -20151,7 +20148,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" ht="14" thickBot="1">
       <c r="A735" s="11">
         <v>45017</v>
       </c>
@@ -20169,7 +20166,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" ht="14" thickBot="1">
       <c r="A736" s="11">
         <v>45024</v>
       </c>
@@ -20187,7 +20184,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:5" ht="14" thickBot="1">
       <c r="A737" s="11">
         <v>45031</v>
       </c>
@@ -20205,7 +20202,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:5" ht="14" thickBot="1">
       <c r="A738" s="11">
         <v>45038</v>
       </c>
@@ -20223,7 +20220,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:5" ht="14" thickBot="1">
       <c r="A739" s="11">
         <v>45045</v>
       </c>
@@ -20241,7 +20238,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:5" ht="14" thickBot="1">
       <c r="A740" s="11">
         <v>45052</v>
       </c>
@@ -20259,7 +20256,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:5" ht="14" thickBot="1">
       <c r="A741" s="11">
         <v>45059</v>
       </c>
@@ -20277,7 +20274,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:5" ht="14" thickBot="1">
       <c r="A742" s="11">
         <v>45066</v>
       </c>
@@ -20295,7 +20292,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:5" ht="14" thickBot="1">
       <c r="A743" s="11">
         <v>45073</v>
       </c>
@@ -20313,7 +20310,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:5" ht="14" thickBot="1">
       <c r="A744" s="11">
         <v>45080</v>
       </c>
@@ -20331,7 +20328,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:5" ht="14" thickBot="1">
       <c r="A745" s="11">
         <v>45087</v>
       </c>
@@ -20349,7 +20346,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:5" ht="14" thickBot="1">
       <c r="A746" s="11">
         <v>45094</v>
       </c>
@@ -20367,7 +20364,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:5" ht="14" thickBot="1">
       <c r="A747" s="11">
         <v>45101</v>
       </c>
@@ -20385,7 +20382,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:5" ht="14" thickBot="1">
       <c r="A748" s="11">
         <v>45108</v>
       </c>
@@ -20403,7 +20400,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:5" ht="14" thickBot="1">
       <c r="A749" s="11">
         <v>45115</v>
       </c>
@@ -20421,7 +20418,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:5" ht="14" thickBot="1">
       <c r="A750" s="11">
         <v>45122</v>
       </c>
@@ -20439,7 +20436,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:5" ht="14" thickBot="1">
       <c r="A751" s="13">
         <v>45129</v>
       </c>
@@ -20457,7 +20454,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:5" ht="14" thickBot="1">
       <c r="A752" s="11">
         <v>45136</v>
       </c>
@@ -20475,7 +20472,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:5" ht="14" thickBot="1">
       <c r="A753" s="11">
         <v>45143</v>
       </c>
@@ -20493,7 +20490,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:5" ht="14" thickBot="1">
       <c r="A754" s="11">
         <v>45150</v>
       </c>
@@ -20511,7 +20508,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:5" ht="14" thickBot="1">
       <c r="A755" s="11">
         <v>45157</v>
       </c>
@@ -20529,7 +20526,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:5" ht="14" thickBot="1">
       <c r="A756" s="11">
         <v>45164</v>
       </c>
@@ -20547,7 +20544,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:5" ht="14" thickBot="1">
       <c r="A757" s="11">
         <v>45171</v>
       </c>
@@ -20565,7 +20562,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:5" ht="14" thickBot="1">
       <c r="A758" s="11">
         <v>45178</v>
       </c>
@@ -20583,7 +20580,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:5" ht="14" thickBot="1">
       <c r="A759" s="11">
         <v>45185</v>
       </c>
@@ -20601,7 +20598,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:5" ht="14" thickBot="1">
       <c r="A760" s="11">
         <v>45192</v>
       </c>
@@ -20619,7 +20616,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:5" ht="14" thickBot="1">
       <c r="A761" s="11">
         <v>45199</v>
       </c>
@@ -20637,7 +20634,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:5" ht="14" thickBot="1">
       <c r="A762" s="11">
         <v>45206</v>
       </c>
@@ -20655,7 +20652,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:5" ht="14" thickBot="1">
       <c r="A763" s="11">
         <v>45213</v>
       </c>
@@ -20673,7 +20670,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:5" ht="14" thickBot="1">
       <c r="A764" s="11">
         <v>45220</v>
       </c>
@@ -20691,7 +20688,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:5" ht="14" thickBot="1">
       <c r="A765" s="11">
         <v>45227</v>
       </c>
@@ -20709,7 +20706,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:5" ht="14" thickBot="1">
       <c r="A766" s="11">
         <v>45234</v>
       </c>
@@ -20727,7 +20724,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:5" ht="14" thickBot="1">
       <c r="A767" s="11">
         <v>45241</v>
       </c>
@@ -20745,7 +20742,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:5" ht="14" thickBot="1">
       <c r="A768" s="11">
         <v>45248</v>
       </c>
@@ -20763,7 +20760,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" ht="14" thickBot="1">
       <c r="A769" s="11">
         <v>45255</v>
       </c>
@@ -20781,7 +20778,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" ht="14" thickBot="1">
       <c r="A770" s="11">
         <v>45262</v>
       </c>
@@ -20814,7 +20811,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" ht="14" thickBot="1">
       <c r="A771" s="11">
         <v>45269</v>
       </c>
@@ -20832,7 +20829,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" ht="14" thickBot="1">
       <c r="A772" s="11">
         <v>45276</v>
       </c>
@@ -20850,7 +20847,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" ht="14" thickBot="1">
       <c r="A773" s="11">
         <v>45283</v>
       </c>
@@ -20868,7 +20865,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" ht="14" thickBot="1">
       <c r="A774" s="11">
         <v>45297</v>
       </c>
@@ -20886,7 +20883,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" ht="14" thickBot="1">
       <c r="A775" s="11">
         <v>45304</v>
       </c>
@@ -20904,7 +20901,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" ht="14" thickBot="1">
       <c r="A776" s="15">
         <v>45311</v>
       </c>
@@ -20922,7 +20919,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" ht="14" thickBot="1">
       <c r="A777" s="17">
         <v>45318</v>
       </c>
@@ -20940,7 +20937,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" ht="14" thickBot="1">
       <c r="A778" s="17">
         <v>45325</v>
       </c>
@@ -20958,7 +20955,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" ht="14" thickBot="1">
       <c r="A779" s="17">
         <v>45332</v>
       </c>
@@ -20976,7 +20973,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" ht="14" thickBot="1">
       <c r="A780" s="17">
         <v>45339</v>
       </c>
@@ -20994,7 +20991,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" ht="14" thickBot="1">
       <c r="A781" s="17">
         <v>45346</v>
       </c>
@@ -21012,7 +21009,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" ht="14" thickBot="1">
       <c r="A782" s="17">
         <v>45353</v>
       </c>
@@ -21030,7 +21027,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" ht="14" thickBot="1">
       <c r="A783" s="17">
         <v>45360</v>
       </c>
@@ -21048,7 +21045,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" ht="14" thickBot="1">
       <c r="A784" s="17">
         <v>45367</v>
       </c>
@@ -21066,7 +21063,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:5" ht="14" thickBot="1">
       <c r="A785" s="17">
         <v>45374</v>
       </c>
@@ -21084,7 +21081,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:5" ht="14" thickBot="1">
       <c r="A786" s="17">
         <v>45381</v>
       </c>
@@ -21102,7 +21099,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:5" ht="14" thickBot="1">
       <c r="A787" s="17">
         <v>45388</v>
       </c>
@@ -21120,7 +21117,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:5" ht="14" thickBot="1">
       <c r="A788" s="17">
         <v>45395</v>
       </c>
@@ -21138,7 +21135,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:5" ht="14" thickBot="1">
       <c r="A789" s="17">
         <v>45402</v>
       </c>
@@ -21156,7 +21153,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:5" ht="14" thickBot="1">
       <c r="A790" s="17">
         <v>45409</v>
       </c>
@@ -21174,7 +21171,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:5" ht="14" thickBot="1">
       <c r="A791" s="17">
         <v>45416</v>
       </c>
@@ -21192,7 +21189,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:5" ht="14" thickBot="1">
       <c r="A792" s="17">
         <v>45423</v>
       </c>
@@ -21210,7 +21207,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:5" ht="14" thickBot="1">
       <c r="A793" s="17">
         <v>45430</v>
       </c>
@@ -21228,7 +21225,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:5" ht="14" thickBot="1">
       <c r="A794" s="17">
         <v>45437</v>
       </c>
@@ -21246,7 +21243,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:5" ht="14" thickBot="1">
       <c r="A795" s="17">
         <v>45444</v>
       </c>
@@ -21264,7 +21261,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:5" ht="14" thickBot="1">
       <c r="A796" s="17">
         <v>45451</v>
       </c>
@@ -21282,7 +21279,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:5" ht="14" thickBot="1">
       <c r="A797" s="17">
         <v>45458</v>
       </c>
@@ -21300,7 +21297,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:5" ht="14" thickBot="1">
       <c r="A798" s="17">
         <v>45465</v>
       </c>
@@ -21318,7 +21315,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:5" ht="14" thickBot="1">
       <c r="A799" s="17">
         <v>45472</v>
       </c>
@@ -21336,7 +21333,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:5" ht="14" thickBot="1">
       <c r="A800" s="17">
         <v>45479</v>
       </c>
@@ -21354,7 +21351,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:5" ht="14" thickBot="1">
       <c r="A801" s="15">
         <v>45486</v>
       </c>
@@ -21372,7 +21369,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:5" ht="14" thickBot="1">
       <c r="A802" s="17">
         <v>45493</v>
       </c>
@@ -21390,7 +21387,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:5" ht="14" thickBot="1">
       <c r="A803" s="17">
         <v>45500</v>
       </c>
@@ -21408,7 +21405,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:5" ht="14" thickBot="1">
       <c r="A804" s="17">
         <v>45507</v>
       </c>
@@ -21426,7 +21423,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:5" ht="14" thickBot="1">
       <c r="A805" s="17">
         <v>45514</v>
       </c>
@@ -21444,7 +21441,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:5" ht="14" thickBot="1">
       <c r="A806" s="17">
         <v>45521</v>
       </c>
@@ -21462,7 +21459,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:5" ht="14" thickBot="1">
       <c r="A807" s="17">
         <v>45528</v>
       </c>
@@ -21480,7 +21477,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:5" ht="14" thickBot="1">
       <c r="A808" s="17">
         <v>45535</v>
       </c>
@@ -21498,7 +21495,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:5" ht="14" thickBot="1">
       <c r="A809" s="17">
         <v>45542</v>
       </c>
@@ -21516,7 +21513,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:5" ht="14" thickBot="1">
       <c r="A810" s="17">
         <v>45549</v>
       </c>
@@ -21534,7 +21531,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:5" ht="14" thickBot="1">
       <c r="A811" s="17">
         <v>45556</v>
       </c>
@@ -21552,7 +21549,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:5" ht="14" thickBot="1">
       <c r="A812" s="17">
         <v>45563</v>
       </c>
@@ -21570,7 +21567,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:5" ht="14" thickBot="1">
       <c r="A813" s="17">
         <v>45570</v>
       </c>
@@ -21588,7 +21585,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:5" ht="14" thickBot="1">
       <c r="A814" s="17">
         <v>45577</v>
       </c>
@@ -21606,7 +21603,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:5" ht="14" thickBot="1">
       <c r="A815" s="17">
         <v>45584</v>
       </c>
@@ -21624,7 +21621,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:5" ht="14" thickBot="1">
       <c r="A816" s="17">
         <v>45591</v>
       </c>
@@ -21642,7 +21639,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:5" ht="14" thickBot="1">
       <c r="A817" s="17">
         <v>45598</v>
       </c>
@@ -21660,7 +21657,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:5" ht="14" thickBot="1">
       <c r="A818" s="17">
         <v>45612</v>
       </c>
@@ -21678,7 +21675,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:5" ht="14" thickBot="1">
       <c r="A819" s="17">
         <v>45619</v>
       </c>
@@ -21696,7 +21693,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:5" ht="14" thickBot="1">
       <c r="A820" s="17">
         <v>45626</v>
       </c>
@@ -21714,7 +21711,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:5" ht="14" thickBot="1">
       <c r="A821" s="17">
         <v>45633</v>
       </c>
@@ -21732,7 +21729,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:5" ht="14" thickBot="1">
       <c r="A822" s="17">
         <v>45640</v>
       </c>
@@ -21750,7 +21747,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:5" ht="14" thickBot="1">
       <c r="A823" s="17">
         <v>45647</v>
       </c>
@@ -21768,7 +21765,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:5" ht="14" thickBot="1">
       <c r="A824" s="17">
         <v>45654</v>
       </c>
@@ -21786,7 +21783,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:5" ht="14" thickBot="1">
       <c r="A825" s="17">
         <v>45661</v>
       </c>
@@ -21804,7 +21801,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:5" ht="14" thickBot="1">
       <c r="A826" s="15">
         <v>45668</v>
       </c>
@@ -21822,7 +21819,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:5" ht="14" thickBot="1">
       <c r="A827" s="17">
         <v>45675</v>
       </c>
@@ -21840,7 +21837,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:5" ht="14" thickBot="1">
       <c r="A828" s="17">
         <v>45682</v>
       </c>
@@ -21858,7 +21855,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:5" ht="14" thickBot="1">
       <c r="A829" s="17">
         <v>45689</v>
       </c>
@@ -21876,7 +21873,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:5" ht="14" thickBot="1">
       <c r="A830" s="17">
         <v>45696</v>
       </c>
@@ -21894,7 +21891,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:5" ht="14" thickBot="1">
       <c r="A831" s="17">
         <v>45703</v>
       </c>
@@ -21912,7 +21909,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:5" ht="14" thickBot="1">
       <c r="A832" s="17">
         <v>45710</v>
       </c>
@@ -21930,7 +21927,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:5" ht="14" thickBot="1">
       <c r="A833" s="17">
         <v>45717</v>
       </c>
@@ -21948,7 +21945,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:5" ht="14" thickBot="1">
       <c r="A834" s="17">
         <v>45724</v>
       </c>
@@ -21981,7 +21978,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:5" ht="14" thickBot="1">
       <c r="A835" s="17">
         <v>45731</v>
       </c>
@@ -21999,7 +21996,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:5" ht="14" thickBot="1">
       <c r="A836" s="17">
         <v>45738</v>
       </c>
@@ -22017,7 +22014,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:5" ht="14" thickBot="1">
       <c r="A837" s="17">
         <v>45745</v>
       </c>
@@ -22035,7 +22032,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:5" ht="14" thickBot="1">
       <c r="A838" s="17">
         <v>45752</v>
       </c>
@@ -22053,7 +22050,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:5" ht="14" thickBot="1">
       <c r="A839" s="17">
         <v>45759</v>
       </c>
@@ -22071,7 +22068,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:5" ht="14" thickBot="1">
       <c r="A840" s="17">
         <v>45766</v>
       </c>
@@ -22089,7 +22086,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:5" ht="14" thickBot="1">
       <c r="A841" s="17">
         <v>45773</v>
       </c>
@@ -22107,7 +22104,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:5" ht="14" thickBot="1">
       <c r="A842" s="17">
         <v>45780</v>
       </c>
@@ -22125,7 +22122,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:5" ht="14" thickBot="1">
       <c r="A843" s="17">
         <v>45787</v>
       </c>
@@ -22143,7 +22140,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:5" ht="14" thickBot="1">
       <c r="A844" s="17">
         <v>45794</v>
       </c>
@@ -22161,7 +22158,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:5" ht="14" thickBot="1">
       <c r="A845" s="17">
         <v>45801</v>
       </c>
@@ -22179,7 +22176,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:5" ht="14" thickBot="1">
       <c r="A846" s="17">
         <v>45808</v>
       </c>
@@ -22197,7 +22194,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:5" ht="14" thickBot="1">
       <c r="A847" s="17">
         <v>45815</v>
       </c>
@@ -22215,7 +22212,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:5" ht="14" thickBot="1">
       <c r="A848" s="17">
         <v>45822</v>
       </c>
@@ -22233,7 +22230,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:5" ht="14" thickBot="1">
       <c r="A849" s="17">
         <v>45829</v>
       </c>
@@ -22251,7 +22248,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:5" ht="14" thickBot="1">
       <c r="A850" s="17">
         <v>45836</v>
       </c>
@@ -22269,7 +22266,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:5" ht="14" thickBot="1">
       <c r="A851" s="15">
         <v>45843</v>
       </c>
@@ -22287,7 +22284,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:5" ht="14" thickBot="1">
       <c r="A852" s="17">
         <v>45850</v>
       </c>
@@ -22305,7 +22302,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:5" ht="14" thickBot="1">
       <c r="A853" s="17">
         <v>45857</v>
       </c>
@@ -22323,7 +22320,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:5" ht="14" thickBot="1">
       <c r="A854" s="17">
         <v>45864</v>
       </c>
@@ -22341,7 +22338,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:5" ht="14" thickBot="1">
       <c r="A855" s="17">
         <v>45871</v>
       </c>
@@ -22359,7 +22356,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:5" ht="14" thickBot="1">
       <c r="A856" s="17">
         <v>45878</v>
       </c>
@@ -22377,7 +22374,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:5" ht="14" thickBot="1">
       <c r="A857" s="17">
         <v>45885</v>
       </c>
@@ -22395,7 +22392,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:5" ht="14" thickBot="1">
       <c r="A858" s="17">
         <v>45892</v>
       </c>
@@ -22413,7 +22410,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:5" ht="14" thickBot="1">
       <c r="A859" s="17">
         <v>45899</v>
       </c>
@@ -22431,7 +22428,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:5" ht="14" thickBot="1">
       <c r="A860" s="17">
         <v>45906</v>
       </c>
@@ -22449,7 +22446,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:5" ht="14" thickBot="1">
       <c r="A861" s="17">
         <v>45913</v>
       </c>
@@ -22467,7 +22464,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:5" ht="14" thickBot="1">
       <c r="A862" s="17">
         <v>45920</v>
       </c>
@@ -22485,7 +22482,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:5" ht="14" thickBot="1">
       <c r="A863" s="15">
         <v>45927</v>
       </c>
@@ -22503,7 +22500,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:5" ht="14" thickBot="1">
       <c r="A864" s="17">
         <v>45934</v>
       </c>
@@ -22521,7 +22518,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:5" ht="14" thickBot="1">
       <c r="A865" s="17">
         <v>45941</v>
       </c>
@@ -22539,7 +22536,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:5" ht="14" thickBot="1">
       <c r="A866" s="17">
         <v>45948</v>
       </c>
@@ -22557,7 +22554,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:5" ht="14" thickBot="1">
       <c r="A867" s="17">
         <v>45955</v>
       </c>
@@ -22575,7 +22572,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:5" ht="14" thickBot="1">
       <c r="A868" s="17">
         <v>45962</v>
       </c>
@@ -22593,7 +22590,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:5" ht="14" thickBot="1">
       <c r="A869" s="17">
         <v>45969</v>
       </c>
@@ -22611,7 +22608,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:5" ht="14" thickBot="1">
       <c r="A870" s="17">
         <v>45976</v>
       </c>
@@ -22629,7 +22626,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:5" ht="14" thickBot="1">
       <c r="A871" s="17">
         <v>45983</v>
       </c>
@@ -22647,7 +22644,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:5" ht="14" thickBot="1">
       <c r="A872" s="17">
         <v>45990</v>
       </c>
@@ -22665,7 +22662,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:5" ht="14" thickBot="1">
       <c r="A873" s="17">
         <v>45997</v>
       </c>
@@ -22683,7 +22680,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:5" ht="14" thickBot="1">
       <c r="A874" s="17">
         <v>46004</v>
       </c>
@@ -22701,7 +22698,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:5" ht="14" thickBot="1">
       <c r="A875" s="15">
         <v>46018</v>
       </c>
@@ -22719,7 +22716,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:5" ht="14" thickBot="1">
       <c r="A876" s="8">
         <v>46025</v>
       </c>
@@ -22737,7 +22734,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:5" ht="14" thickBot="1">
       <c r="A877" s="15">
         <v>46032</v>
       </c>
@@ -22755,7 +22752,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:5" ht="14" thickBot="1">
       <c r="A878" s="8">
         <v>46039</v>
       </c>
@@ -22788,7 +22785,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:5" ht="14" thickBot="1">
       <c r="A879" s="15">
         <v>46046</v>
       </c>
@@ -22821,7 +22818,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:5" ht="14" thickBot="1">
       <c r="A880" s="15">
         <v>46053</v>
       </c>
@@ -22854,7 +22851,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:5" ht="14" thickBot="1">
       <c r="A881" s="15">
         <v>46060</v>
       </c>
@@ -22872,7 +22869,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:5" ht="14" thickBot="1">
       <c r="A882" s="8">
         <v>46067</v>
       </c>
@@ -22905,7 +22902,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:5" ht="14" thickBot="1">
       <c r="A883" s="15">
         <v>46074</v>
       </c>
@@ -22938,7 +22935,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:5" ht="14" thickBot="1">
       <c r="A884" s="8">
         <v>46081</v>
       </c>
@@ -22956,7 +22953,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:5" ht="14" thickBot="1">
       <c r="A885" s="15">
         <v>46088</v>
       </c>
@@ -22989,7 +22986,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:5">
       <c r="A886" s="8">
         <v>46102</v>
       </c>
@@ -23022,7 +23019,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:5">
       <c r="A887" s="8">
         <v>46109</v>
       </c>
@@ -23055,6 +23052,36 @@
         <v>515921</v>
       </c>
     </row>
+    <row r="888" spans="1:5">
+      <c r="A888" s="8">
+        <v>46116</v>
+      </c>
+      <c r="B888" s="8">
+        <v>46120</v>
+      </c>
+      <c r="C888" s="21">
+        <v>0.500694444444444</v>
+      </c>
+      <c r="D888" s="7" t="str">
+        <f>IF(
+ AND(
+  A888 &gt;= IF(
+         YEAR(A888)&gt;=2007,
+         DATE(YEAR(A888),3,14)-WEEKDAY(DATE(YEAR(A888),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A888),4,7)-WEEKDAY(DATE(YEAR(A888),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A888 &lt;  IF(
+         YEAR(A888)&gt;=2007,
+         DATE(YEAR(A888),11,7)-WEEKDAY(DATE(YEAR(A888),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A888),10,31)-WEEKDAY(DATE(YEAR(A888),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
@@ -23068,7 +23095,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23079,12 +23106,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23092,7 +23119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23100,7 +23127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951197DF-26FF-4E53-B6D9-FFB5794A92CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9DA03C-B90A-4C2B-AA78-0FC960228101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,6 @@
   </si>
   <si>
     <t>https://ycharts.com/indicators/us_weekly_rail_traffic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -87,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -190,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -207,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -286,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5711,6 +5710,9 @@
                 </c:pt>
                 <c:pt idx="886">
                   <c:v>501328</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>500040</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6496,9 +6498,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6536,7 +6538,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6642,7 +6644,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6784,7 +6786,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6793,17 +6795,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E889"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="5"/>
+    <col min="5" max="5" width="12.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.08984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6820,7 +6822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="6">
         <v>39823</v>
       </c>
@@ -6853,7 +6855,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" s="6">
         <v>39830</v>
       </c>
@@ -6871,7 +6873,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" s="6">
         <v>39837</v>
       </c>
@@ -6889,7 +6891,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="6">
         <v>39844</v>
       </c>
@@ -6907,7 +6909,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="6">
         <v>39851</v>
       </c>
@@ -6925,7 +6927,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" s="6">
         <v>39858</v>
       </c>
@@ -6943,7 +6945,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="6">
         <v>39865</v>
       </c>
@@ -6961,7 +6963,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" s="6">
         <v>39872</v>
       </c>
@@ -6979,7 +6981,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="6">
         <v>39879</v>
       </c>
@@ -6997,7 +6999,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" s="6">
         <v>39886</v>
       </c>
@@ -7015,7 +7017,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" s="6">
         <v>39893</v>
       </c>
@@ -7033,7 +7035,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" s="6">
         <v>39900</v>
       </c>
@@ -7051,7 +7053,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" s="6">
         <v>39907</v>
       </c>
@@ -7069,7 +7071,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" s="6">
         <v>39914</v>
       </c>
@@ -7087,7 +7089,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16" s="6">
         <v>39921</v>
       </c>
@@ -7105,7 +7107,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" s="6">
         <v>39928</v>
       </c>
@@ -7123,7 +7125,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" s="6">
         <v>39935</v>
       </c>
@@ -7141,7 +7143,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" s="6">
         <v>39942</v>
       </c>
@@ -7159,7 +7161,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" s="6">
         <v>39949</v>
       </c>
@@ -7177,7 +7179,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" s="6">
         <v>39956</v>
       </c>
@@ -7195,7 +7197,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22" s="6">
         <v>39963</v>
       </c>
@@ -7213,7 +7215,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" s="6">
         <v>39970</v>
       </c>
@@ -7231,7 +7233,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24" s="6">
         <v>39977</v>
       </c>
@@ -7249,7 +7251,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25" s="6">
         <v>39984</v>
       </c>
@@ -7267,7 +7269,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26" s="6">
         <v>39991</v>
       </c>
@@ -7285,7 +7287,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" s="6">
         <v>39998</v>
       </c>
@@ -7303,7 +7305,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28" s="6">
         <v>40005</v>
       </c>
@@ -7321,7 +7323,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" s="6">
         <v>40012</v>
       </c>
@@ -7339,7 +7341,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5">
       <c r="A30" s="6">
         <v>40019</v>
       </c>
@@ -7357,7 +7359,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5">
       <c r="A31" s="6">
         <v>40026</v>
       </c>
@@ -7375,7 +7377,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32" s="6">
         <v>40033</v>
       </c>
@@ -7393,7 +7395,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" s="6">
         <v>40040</v>
       </c>
@@ -7411,7 +7413,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="6">
         <v>40047</v>
       </c>
@@ -7429,7 +7431,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="6">
         <v>40054</v>
       </c>
@@ -7447,7 +7449,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" s="6">
         <v>40061</v>
       </c>
@@ -7465,7 +7467,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" s="6">
         <v>40068</v>
       </c>
@@ -7483,7 +7485,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" s="6">
         <v>40075</v>
       </c>
@@ -7501,7 +7503,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" s="6">
         <v>40082</v>
       </c>
@@ -7519,7 +7521,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" s="6">
         <v>40089</v>
       </c>
@@ -7537,7 +7539,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" s="6">
         <v>40096</v>
       </c>
@@ -7555,7 +7557,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42" s="6">
         <v>40103</v>
       </c>
@@ -7573,7 +7575,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" s="6">
         <v>40110</v>
       </c>
@@ -7591,7 +7593,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" s="6">
         <v>40117</v>
       </c>
@@ -7609,7 +7611,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" s="6">
         <v>40124</v>
       </c>
@@ -7627,7 +7629,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" s="6">
         <v>40131</v>
       </c>
@@ -7645,7 +7647,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" s="6">
         <v>40138</v>
       </c>
@@ -7663,7 +7665,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" s="6">
         <v>40145</v>
       </c>
@@ -7681,7 +7683,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5">
       <c r="A49" s="6">
         <v>40152</v>
       </c>
@@ -7699,7 +7701,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5">
       <c r="A50" s="6">
         <v>40159</v>
       </c>
@@ -7717,7 +7719,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5">
       <c r="A51" s="6">
         <v>40166</v>
       </c>
@@ -7735,7 +7737,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52" s="6">
         <v>40173</v>
       </c>
@@ -7753,7 +7755,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5">
       <c r="A53" s="6">
         <v>40180</v>
       </c>
@@ -7771,7 +7773,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5">
       <c r="A54" s="6">
         <v>40187</v>
       </c>
@@ -7789,7 +7791,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5">
       <c r="A55" s="6">
         <v>40194</v>
       </c>
@@ -7807,7 +7809,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5">
       <c r="A56" s="6">
         <v>40201</v>
       </c>
@@ -7825,7 +7827,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5">
       <c r="A57" s="6">
         <v>40208</v>
       </c>
@@ -7843,7 +7845,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5">
       <c r="A58" s="6">
         <v>40215</v>
       </c>
@@ -7861,7 +7863,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5">
       <c r="A59" s="6">
         <v>40222</v>
       </c>
@@ -7879,7 +7881,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5">
       <c r="A60" s="6">
         <v>40229</v>
       </c>
@@ -7897,7 +7899,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5">
       <c r="A61" s="6">
         <v>40236</v>
       </c>
@@ -7915,7 +7917,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5">
       <c r="A62" s="6">
         <v>40243</v>
       </c>
@@ -7933,7 +7935,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5">
       <c r="A63" s="6">
         <v>40250</v>
       </c>
@@ -7951,7 +7953,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5">
       <c r="A64" s="6">
         <v>40257</v>
       </c>
@@ -7969,7 +7971,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5">
       <c r="A65" s="6">
         <v>40264</v>
       </c>
@@ -7987,7 +7989,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5">
       <c r="A66" s="6">
         <v>40271</v>
       </c>
@@ -8020,7 +8022,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5">
       <c r="A67" s="6">
         <v>40278</v>
       </c>
@@ -8038,7 +8040,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5">
       <c r="A68" s="6">
         <v>40285</v>
       </c>
@@ -8056,7 +8058,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5">
       <c r="A69" s="6">
         <v>40292</v>
       </c>
@@ -8074,7 +8076,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5">
       <c r="A70" s="6">
         <v>40299</v>
       </c>
@@ -8092,7 +8094,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5">
       <c r="A71" s="6">
         <v>40306</v>
       </c>
@@ -8110,7 +8112,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5">
       <c r="A72" s="6">
         <v>40313</v>
       </c>
@@ -8128,7 +8130,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5">
       <c r="A73" s="6">
         <v>40320</v>
       </c>
@@ -8146,7 +8148,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5">
       <c r="A74" s="6">
         <v>40327</v>
       </c>
@@ -8164,7 +8166,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5">
       <c r="A75" s="6">
         <v>40334</v>
       </c>
@@ -8182,7 +8184,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5">
       <c r="A76" s="6">
         <v>40341</v>
       </c>
@@ -8200,7 +8202,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5">
       <c r="A77" s="6">
         <v>40348</v>
       </c>
@@ -8218,7 +8220,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5">
       <c r="A78" s="6">
         <v>40355</v>
       </c>
@@ -8236,7 +8238,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5">
       <c r="A79" s="6">
         <v>40362</v>
       </c>
@@ -8254,7 +8256,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5">
       <c r="A80" s="6">
         <v>40369</v>
       </c>
@@ -8272,7 +8274,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5">
       <c r="A81" s="6">
         <v>40376</v>
       </c>
@@ -8290,7 +8292,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5">
       <c r="A82" s="6">
         <v>40383</v>
       </c>
@@ -8308,7 +8310,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5">
       <c r="A83" s="6">
         <v>40390</v>
       </c>
@@ -8326,7 +8328,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5">
       <c r="A84" s="6">
         <v>40397</v>
       </c>
@@ -8344,7 +8346,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5">
       <c r="A85" s="6">
         <v>40404</v>
       </c>
@@ -8362,7 +8364,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5">
       <c r="A86" s="6">
         <v>40411</v>
       </c>
@@ -8380,7 +8382,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5">
       <c r="A87" s="6">
         <v>40418</v>
       </c>
@@ -8398,7 +8400,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5">
       <c r="A88" s="6">
         <v>40425</v>
       </c>
@@ -8416,7 +8418,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5">
       <c r="A89" s="6">
         <v>40432</v>
       </c>
@@ -8434,7 +8436,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5">
       <c r="A90" s="6">
         <v>40439</v>
       </c>
@@ -8452,7 +8454,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5">
       <c r="A91" s="6">
         <v>40446</v>
       </c>
@@ -8470,7 +8472,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5">
       <c r="A92" s="6">
         <v>40453</v>
       </c>
@@ -8488,7 +8490,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5">
       <c r="A93" s="6">
         <v>40460</v>
       </c>
@@ -8506,7 +8508,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5">
       <c r="A94" s="6">
         <v>40467</v>
       </c>
@@ -8524,7 +8526,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5">
       <c r="A95" s="6">
         <v>40474</v>
       </c>
@@ -8542,7 +8544,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5">
       <c r="A96" s="6">
         <v>40481</v>
       </c>
@@ -8560,7 +8562,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5">
       <c r="A97" s="6">
         <v>40488</v>
       </c>
@@ -8578,7 +8580,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5">
       <c r="A98" s="6">
         <v>40495</v>
       </c>
@@ -8596,7 +8598,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5">
       <c r="A99" s="6">
         <v>40502</v>
       </c>
@@ -8614,7 +8616,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5">
       <c r="A100" s="6">
         <v>40509</v>
       </c>
@@ -8632,7 +8634,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="14" thickBot="1">
       <c r="A101" s="6">
         <v>40516</v>
       </c>
@@ -8650,7 +8652,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="14" thickBot="1">
       <c r="A102" s="9">
         <v>40523</v>
       </c>
@@ -8668,7 +8670,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="14" thickBot="1">
       <c r="A103" s="9">
         <v>40530</v>
       </c>
@@ -8686,7 +8688,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="14" thickBot="1">
       <c r="A104" s="9">
         <v>40537</v>
       </c>
@@ -8704,7 +8706,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="14" thickBot="1">
       <c r="A105" s="9">
         <v>40544</v>
       </c>
@@ -8722,7 +8724,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="14" thickBot="1">
       <c r="A106" s="9">
         <v>40551</v>
       </c>
@@ -8740,7 +8742,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="14" thickBot="1">
       <c r="A107" s="9">
         <v>40558</v>
       </c>
@@ -8758,7 +8760,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="14" thickBot="1">
       <c r="A108" s="9">
         <v>40565</v>
       </c>
@@ -8776,7 +8778,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="14" thickBot="1">
       <c r="A109" s="9">
         <v>40572</v>
       </c>
@@ -8794,7 +8796,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="14" thickBot="1">
       <c r="A110" s="9">
         <v>40579</v>
       </c>
@@ -8812,7 +8814,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="14" thickBot="1">
       <c r="A111" s="9">
         <v>40586</v>
       </c>
@@ -8830,7 +8832,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="14" thickBot="1">
       <c r="A112" s="9">
         <v>40593</v>
       </c>
@@ -8848,7 +8850,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="14" thickBot="1">
       <c r="A113" s="9">
         <v>40600</v>
       </c>
@@ -8866,7 +8868,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="14" thickBot="1">
       <c r="A114" s="9">
         <v>40607</v>
       </c>
@@ -8884,7 +8886,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="14" thickBot="1">
       <c r="A115" s="9">
         <v>40614</v>
       </c>
@@ -8902,7 +8904,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="14" thickBot="1">
       <c r="A116" s="9">
         <v>40621</v>
       </c>
@@ -8920,7 +8922,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="14" thickBot="1">
       <c r="A117" s="9">
         <v>40628</v>
       </c>
@@ -8938,7 +8940,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="14" thickBot="1">
       <c r="A118" s="9">
         <v>40635</v>
       </c>
@@ -8956,7 +8958,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="14" thickBot="1">
       <c r="A119" s="9">
         <v>40642</v>
       </c>
@@ -8974,7 +8976,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="14" thickBot="1">
       <c r="A120" s="9">
         <v>40649</v>
       </c>
@@ -8992,7 +8994,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="14" thickBot="1">
       <c r="A121" s="9">
         <v>40656</v>
       </c>
@@ -9010,7 +9012,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="14" thickBot="1">
       <c r="A122" s="9">
         <v>40663</v>
       </c>
@@ -9028,7 +9030,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="14" thickBot="1">
       <c r="A123" s="9">
         <v>40670</v>
       </c>
@@ -9046,7 +9048,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="14" thickBot="1">
       <c r="A124" s="9">
         <v>40677</v>
       </c>
@@ -9064,7 +9066,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="14" thickBot="1">
       <c r="A125" s="9">
         <v>40684</v>
       </c>
@@ -9082,7 +9084,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="14" thickBot="1">
       <c r="A126" s="11">
         <v>40691</v>
       </c>
@@ -9100,7 +9102,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="14" thickBot="1">
       <c r="A127" s="9">
         <v>40698</v>
       </c>
@@ -9118,7 +9120,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="14" thickBot="1">
       <c r="A128" s="9">
         <v>40705</v>
       </c>
@@ -9136,7 +9138,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="14" thickBot="1">
       <c r="A129" s="9">
         <v>40712</v>
       </c>
@@ -9154,7 +9156,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="14" thickBot="1">
       <c r="A130" s="9">
         <v>40719</v>
       </c>
@@ -9187,7 +9189,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="14" thickBot="1">
       <c r="A131" s="9">
         <v>40726</v>
       </c>
@@ -9205,7 +9207,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="14" thickBot="1">
       <c r="A132" s="9">
         <v>40733</v>
       </c>
@@ -9223,7 +9225,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="14" thickBot="1">
       <c r="A133" s="9">
         <v>40740</v>
       </c>
@@ -9241,7 +9243,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="14" thickBot="1">
       <c r="A134" s="9">
         <v>40747</v>
       </c>
@@ -9259,7 +9261,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="14" thickBot="1">
       <c r="A135" s="9">
         <v>40754</v>
       </c>
@@ -9277,7 +9279,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="14" thickBot="1">
       <c r="A136" s="9">
         <v>40761</v>
       </c>
@@ -9295,7 +9297,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="14" thickBot="1">
       <c r="A137" s="9">
         <v>40768</v>
       </c>
@@ -9313,7 +9315,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="14" thickBot="1">
       <c r="A138" s="9">
         <v>40775</v>
       </c>
@@ -9331,7 +9333,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="14" thickBot="1">
       <c r="A139" s="9">
         <v>40782</v>
       </c>
@@ -9349,7 +9351,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="14" thickBot="1">
       <c r="A140" s="9">
         <v>40789</v>
       </c>
@@ -9367,7 +9369,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="14" thickBot="1">
       <c r="A141" s="9">
         <v>40796</v>
       </c>
@@ -9385,7 +9387,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="14" thickBot="1">
       <c r="A142" s="9">
         <v>40803</v>
       </c>
@@ -9403,7 +9405,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="14" thickBot="1">
       <c r="A143" s="9">
         <v>40810</v>
       </c>
@@ -9421,7 +9423,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="14" thickBot="1">
       <c r="A144" s="9">
         <v>40817</v>
       </c>
@@ -9439,7 +9441,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="14" thickBot="1">
       <c r="A145" s="9">
         <v>40824</v>
       </c>
@@ -9457,7 +9459,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="14" thickBot="1">
       <c r="A146" s="9">
         <v>40831</v>
       </c>
@@ -9475,7 +9477,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="14" thickBot="1">
       <c r="A147" s="9">
         <v>40838</v>
       </c>
@@ -9493,7 +9495,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="14" thickBot="1">
       <c r="A148" s="9">
         <v>40845</v>
       </c>
@@ -9511,7 +9513,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="14" thickBot="1">
       <c r="A149" s="9">
         <v>40852</v>
       </c>
@@ -9529,7 +9531,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="14" thickBot="1">
       <c r="A150" s="9">
         <v>40859</v>
       </c>
@@ -9547,7 +9549,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="14" thickBot="1">
       <c r="A151" s="11">
         <v>40866</v>
       </c>
@@ -9565,7 +9567,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="14" thickBot="1">
       <c r="A152" s="9">
         <v>40873</v>
       </c>
@@ -9583,7 +9585,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="14" thickBot="1">
       <c r="A153" s="9">
         <v>40880</v>
       </c>
@@ -9601,7 +9603,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="14" thickBot="1">
       <c r="A154" s="9">
         <v>40887</v>
       </c>
@@ -9619,7 +9621,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="14" thickBot="1">
       <c r="A155" s="9">
         <v>40894</v>
       </c>
@@ -9637,7 +9639,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="14" thickBot="1">
       <c r="A156" s="9">
         <v>40901</v>
       </c>
@@ -9655,7 +9657,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="14" thickBot="1">
       <c r="A157" s="9">
         <v>40908</v>
       </c>
@@ -9673,7 +9675,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="14" thickBot="1">
       <c r="A158" s="9">
         <v>40915</v>
       </c>
@@ -9691,7 +9693,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="14" thickBot="1">
       <c r="A159" s="9">
         <v>40922</v>
       </c>
@@ -9709,7 +9711,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="14" thickBot="1">
       <c r="A160" s="9">
         <v>40929</v>
       </c>
@@ -9727,7 +9729,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="14" thickBot="1">
       <c r="A161" s="9">
         <v>40936</v>
       </c>
@@ -9745,7 +9747,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="14" thickBot="1">
       <c r="A162" s="9">
         <v>40943</v>
       </c>
@@ -9763,7 +9765,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="14" thickBot="1">
       <c r="A163" s="9">
         <v>40950</v>
       </c>
@@ -9781,7 +9783,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="14" thickBot="1">
       <c r="A164" s="9">
         <v>40957</v>
       </c>
@@ -9799,7 +9801,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="14" thickBot="1">
       <c r="A165" s="9">
         <v>40964</v>
       </c>
@@ -9817,7 +9819,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="14" thickBot="1">
       <c r="A166" s="9">
         <v>40971</v>
       </c>
@@ -9835,7 +9837,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="14" thickBot="1">
       <c r="A167" s="9">
         <v>40978</v>
       </c>
@@ -9853,7 +9855,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="14" thickBot="1">
       <c r="A168" s="9">
         <v>40985</v>
       </c>
@@ -9871,7 +9873,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="14" thickBot="1">
       <c r="A169" s="9">
         <v>40992</v>
       </c>
@@ -9889,7 +9891,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="14" thickBot="1">
       <c r="A170" s="9">
         <v>40999</v>
       </c>
@@ -9907,7 +9909,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="14" thickBot="1">
       <c r="A171" s="9">
         <v>41006</v>
       </c>
@@ -9925,7 +9927,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="14" thickBot="1">
       <c r="A172" s="9">
         <v>41013</v>
       </c>
@@ -9943,7 +9945,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="14" thickBot="1">
       <c r="A173" s="9">
         <v>41020</v>
       </c>
@@ -9961,7 +9963,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="14" thickBot="1">
       <c r="A174" s="9">
         <v>41027</v>
       </c>
@@ -9979,7 +9981,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="14" thickBot="1">
       <c r="A175" s="9">
         <v>41034</v>
       </c>
@@ -9997,7 +9999,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="14" thickBot="1">
       <c r="A176" s="11">
         <v>41041</v>
       </c>
@@ -10015,7 +10017,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="14" thickBot="1">
       <c r="A177" s="9">
         <v>41048</v>
       </c>
@@ -10033,7 +10035,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="14" thickBot="1">
       <c r="A178" s="9">
         <v>41055</v>
       </c>
@@ -10051,7 +10053,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="14" thickBot="1">
       <c r="A179" s="9">
         <v>41062</v>
       </c>
@@ -10069,7 +10071,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="14" thickBot="1">
       <c r="A180" s="9">
         <v>41069</v>
       </c>
@@ -10087,7 +10089,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="14" thickBot="1">
       <c r="A181" s="9">
         <v>41076</v>
       </c>
@@ -10105,7 +10107,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="14" thickBot="1">
       <c r="A182" s="9">
         <v>41083</v>
       </c>
@@ -10123,7 +10125,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="14" thickBot="1">
       <c r="A183" s="9">
         <v>41090</v>
       </c>
@@ -10141,7 +10143,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="14" thickBot="1">
       <c r="A184" s="9">
         <v>41097</v>
       </c>
@@ -10159,7 +10161,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="14" thickBot="1">
       <c r="A185" s="9">
         <v>41104</v>
       </c>
@@ -10177,7 +10179,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="14" thickBot="1">
       <c r="A186" s="9">
         <v>41111</v>
       </c>
@@ -10195,7 +10197,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="14" thickBot="1">
       <c r="A187" s="9">
         <v>41118</v>
       </c>
@@ -10213,7 +10215,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="14" thickBot="1">
       <c r="A188" s="9">
         <v>41125</v>
       </c>
@@ -10231,7 +10233,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="14" thickBot="1">
       <c r="A189" s="9">
         <v>41132</v>
       </c>
@@ -10249,7 +10251,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="14" thickBot="1">
       <c r="A190" s="9">
         <v>41139</v>
       </c>
@@ -10267,7 +10269,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="14" thickBot="1">
       <c r="A191" s="9">
         <v>41146</v>
       </c>
@@ -10285,7 +10287,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="14" thickBot="1">
       <c r="A192" s="9">
         <v>41153</v>
       </c>
@@ -10303,7 +10305,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="14" thickBot="1">
       <c r="A193" s="9">
         <v>41160</v>
       </c>
@@ -10321,7 +10323,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="14" thickBot="1">
       <c r="A194" s="9">
         <v>41167</v>
       </c>
@@ -10354,7 +10356,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="14" thickBot="1">
       <c r="A195" s="9">
         <v>41174</v>
       </c>
@@ -10372,7 +10374,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="14" thickBot="1">
       <c r="A196" s="9">
         <v>41181</v>
       </c>
@@ -10390,7 +10392,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="14" thickBot="1">
       <c r="A197" s="9">
         <v>41188</v>
       </c>
@@ -10408,7 +10410,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="14" thickBot="1">
       <c r="A198" s="9">
         <v>41195</v>
       </c>
@@ -10426,7 +10428,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="14" thickBot="1">
       <c r="A199" s="9">
         <v>41202</v>
       </c>
@@ -10444,7 +10446,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="14" thickBot="1">
       <c r="A200" s="9">
         <v>41209</v>
       </c>
@@ -10462,7 +10464,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="14" thickBot="1">
       <c r="A201" s="11">
         <v>41216</v>
       </c>
@@ -10480,7 +10482,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="14" thickBot="1">
       <c r="A202" s="9">
         <v>41223</v>
       </c>
@@ -10498,7 +10500,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="14" thickBot="1">
       <c r="A203" s="9">
         <v>41230</v>
       </c>
@@ -10516,7 +10518,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="14" thickBot="1">
       <c r="A204" s="9">
         <v>41237</v>
       </c>
@@ -10534,7 +10536,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="14" thickBot="1">
       <c r="A205" s="9">
         <v>41244</v>
       </c>
@@ -10552,7 +10554,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="14" thickBot="1">
       <c r="A206" s="9">
         <v>41251</v>
       </c>
@@ -10570,7 +10572,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="14" thickBot="1">
       <c r="A207" s="9">
         <v>41258</v>
       </c>
@@ -10588,7 +10590,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="14" thickBot="1">
       <c r="A208" s="9">
         <v>41265</v>
       </c>
@@ -10606,7 +10608,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="14" thickBot="1">
       <c r="A209" s="9">
         <v>41272</v>
       </c>
@@ -10624,7 +10626,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="14" thickBot="1">
       <c r="A210" s="9">
         <v>41279</v>
       </c>
@@ -10642,7 +10644,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="14" thickBot="1">
       <c r="A211" s="9">
         <v>41286</v>
       </c>
@@ -10660,7 +10662,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="14" thickBot="1">
       <c r="A212" s="9">
         <v>41293</v>
       </c>
@@ -10678,7 +10680,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="14" thickBot="1">
       <c r="A213" s="9">
         <v>41300</v>
       </c>
@@ -10696,7 +10698,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="14" thickBot="1">
       <c r="A214" s="9">
         <v>41307</v>
       </c>
@@ -10714,7 +10716,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="14" thickBot="1">
       <c r="A215" s="9">
         <v>41314</v>
       </c>
@@ -10732,7 +10734,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="14" thickBot="1">
       <c r="A216" s="9">
         <v>41321</v>
       </c>
@@ -10750,7 +10752,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="14" thickBot="1">
       <c r="A217" s="9">
         <v>41328</v>
       </c>
@@ -10768,7 +10770,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="14" thickBot="1">
       <c r="A218" s="9">
         <v>41335</v>
       </c>
@@ -10786,7 +10788,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="14" thickBot="1">
       <c r="A219" s="9">
         <v>41342</v>
       </c>
@@ -10804,7 +10806,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="14" thickBot="1">
       <c r="A220" s="9">
         <v>41349</v>
       </c>
@@ -10822,7 +10824,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="14" thickBot="1">
       <c r="A221" s="9">
         <v>41356</v>
       </c>
@@ -10840,7 +10842,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="14" thickBot="1">
       <c r="A222" s="9">
         <v>41363</v>
       </c>
@@ -10858,7 +10860,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="14" thickBot="1">
       <c r="A223" s="9">
         <v>41370</v>
       </c>
@@ -10876,7 +10878,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="14" thickBot="1">
       <c r="A224" s="9">
         <v>41377</v>
       </c>
@@ -10894,7 +10896,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="14" thickBot="1">
       <c r="A225" s="9">
         <v>41384</v>
       </c>
@@ -10912,7 +10914,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="14" thickBot="1">
       <c r="A226" s="11">
         <v>41391</v>
       </c>
@@ -10930,7 +10932,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="14" thickBot="1">
       <c r="A227" s="9">
         <v>41398</v>
       </c>
@@ -10948,7 +10950,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="14" thickBot="1">
       <c r="A228" s="9">
         <v>41405</v>
       </c>
@@ -10966,7 +10968,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="14" thickBot="1">
       <c r="A229" s="9">
         <v>41412</v>
       </c>
@@ -10984,7 +10986,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="14" thickBot="1">
       <c r="A230" s="9">
         <v>41419</v>
       </c>
@@ -11002,7 +11004,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="14" thickBot="1">
       <c r="A231" s="9">
         <v>41426</v>
       </c>
@@ -11020,7 +11022,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="14" thickBot="1">
       <c r="A232" s="9">
         <v>41433</v>
       </c>
@@ -11038,7 +11040,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="14" thickBot="1">
       <c r="A233" s="9">
         <v>41440</v>
       </c>
@@ -11056,7 +11058,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="14" thickBot="1">
       <c r="A234" s="9">
         <v>41447</v>
       </c>
@@ -11074,7 +11076,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="14" thickBot="1">
       <c r="A235" s="9">
         <v>41454</v>
       </c>
@@ -11092,7 +11094,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="14" thickBot="1">
       <c r="A236" s="9">
         <v>41461</v>
       </c>
@@ -11110,7 +11112,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="14" thickBot="1">
       <c r="A237" s="9">
         <v>41468</v>
       </c>
@@ -11128,7 +11130,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="14" thickBot="1">
       <c r="A238" s="9">
         <v>41475</v>
       </c>
@@ -11146,7 +11148,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="14" thickBot="1">
       <c r="A239" s="9">
         <v>41482</v>
       </c>
@@ -11164,7 +11166,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="14" thickBot="1">
       <c r="A240" s="9">
         <v>41489</v>
       </c>
@@ -11182,7 +11184,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="14" thickBot="1">
       <c r="A241" s="9">
         <v>41496</v>
       </c>
@@ -11200,7 +11202,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="14" thickBot="1">
       <c r="A242" s="9">
         <v>41503</v>
       </c>
@@ -11218,7 +11220,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="14" thickBot="1">
       <c r="A243" s="9">
         <v>41510</v>
       </c>
@@ -11236,7 +11238,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="14" thickBot="1">
       <c r="A244" s="9">
         <v>41517</v>
       </c>
@@ -11254,7 +11256,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="14" thickBot="1">
       <c r="A245" s="9">
         <v>41524</v>
       </c>
@@ -11272,7 +11274,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="14" thickBot="1">
       <c r="A246" s="9">
         <v>41531</v>
       </c>
@@ -11290,7 +11292,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="14" thickBot="1">
       <c r="A247" s="9">
         <v>41538</v>
       </c>
@@ -11308,7 +11310,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="14" thickBot="1">
       <c r="A248" s="9">
         <v>41545</v>
       </c>
@@ -11326,7 +11328,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="14" thickBot="1">
       <c r="A249" s="9">
         <v>41552</v>
       </c>
@@ -11344,7 +11346,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="14" thickBot="1">
       <c r="A250" s="9">
         <v>41559</v>
       </c>
@@ -11362,7 +11364,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="14" thickBot="1">
       <c r="A251" s="11">
         <v>41566</v>
       </c>
@@ -11380,7 +11382,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="14" thickBot="1">
       <c r="A252" s="9">
         <v>41573</v>
       </c>
@@ -11398,7 +11400,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="14" thickBot="1">
       <c r="A253" s="9">
         <v>41580</v>
       </c>
@@ -11416,7 +11418,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="14" thickBot="1">
       <c r="A254" s="9">
         <v>41587</v>
       </c>
@@ -11434,7 +11436,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="14" thickBot="1">
       <c r="A255" s="9">
         <v>41594</v>
       </c>
@@ -11452,7 +11454,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="14" thickBot="1">
       <c r="A256" s="9">
         <v>41601</v>
       </c>
@@ -11470,7 +11472,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="14" thickBot="1">
       <c r="A257" s="9">
         <v>41608</v>
       </c>
@@ -11488,7 +11490,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="14" thickBot="1">
       <c r="A258" s="9">
         <v>41615</v>
       </c>
@@ -11521,7 +11523,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="14" thickBot="1">
       <c r="A259" s="9">
         <v>41622</v>
       </c>
@@ -11539,7 +11541,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="14" thickBot="1">
       <c r="A260" s="9">
         <v>41629</v>
       </c>
@@ -11557,7 +11559,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="14" thickBot="1">
       <c r="A261" s="9">
         <v>41636</v>
       </c>
@@ -11575,7 +11577,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="14" thickBot="1">
       <c r="A262" s="9">
         <v>41643</v>
       </c>
@@ -11593,7 +11595,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="14" thickBot="1">
       <c r="A263" s="9">
         <v>41650</v>
       </c>
@@ -11611,7 +11613,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="14" thickBot="1">
       <c r="A264" s="9">
         <v>41657</v>
       </c>
@@ -11629,7 +11631,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="14" thickBot="1">
       <c r="A265" s="9">
         <v>41664</v>
       </c>
@@ -11647,7 +11649,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="14" thickBot="1">
       <c r="A266" s="9">
         <v>41671</v>
       </c>
@@ -11665,7 +11667,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="14" thickBot="1">
       <c r="A267" s="9">
         <v>41678</v>
       </c>
@@ -11683,7 +11685,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="14" thickBot="1">
       <c r="A268" s="9">
         <v>41685</v>
       </c>
@@ -11701,7 +11703,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="14" thickBot="1">
       <c r="A269" s="9">
         <v>41692</v>
       </c>
@@ -11719,7 +11721,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="14" thickBot="1">
       <c r="A270" s="9">
         <v>41699</v>
       </c>
@@ -11737,7 +11739,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="14" thickBot="1">
       <c r="A271" s="9">
         <v>41706</v>
       </c>
@@ -11755,7 +11757,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="14" thickBot="1">
       <c r="A272" s="9">
         <v>41713</v>
       </c>
@@ -11773,7 +11775,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="14" thickBot="1">
       <c r="A273" s="9">
         <v>41720</v>
       </c>
@@ -11791,7 +11793,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="14" thickBot="1">
       <c r="A274" s="9">
         <v>41727</v>
       </c>
@@ -11809,7 +11811,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="14" thickBot="1">
       <c r="A275" s="9">
         <v>41734</v>
       </c>
@@ -11827,7 +11829,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="14" thickBot="1">
       <c r="A276" s="11">
         <v>41741</v>
       </c>
@@ -11845,7 +11847,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="14" thickBot="1">
       <c r="A277" s="9">
         <v>41748</v>
       </c>
@@ -11863,7 +11865,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="14" thickBot="1">
       <c r="A278" s="9">
         <v>41755</v>
       </c>
@@ -11881,7 +11883,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="14" thickBot="1">
       <c r="A279" s="9">
         <v>41762</v>
       </c>
@@ -11899,7 +11901,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="14" thickBot="1">
       <c r="A280" s="9">
         <v>41769</v>
       </c>
@@ -11917,7 +11919,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="14" thickBot="1">
       <c r="A281" s="9">
         <v>41783</v>
       </c>
@@ -11935,7 +11937,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="14" thickBot="1">
       <c r="A282" s="9">
         <v>41790</v>
       </c>
@@ -11953,7 +11955,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="14" thickBot="1">
       <c r="A283" s="9">
         <v>41797</v>
       </c>
@@ -11971,7 +11973,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="14" thickBot="1">
       <c r="A284" s="9">
         <v>41804</v>
       </c>
@@ -11989,7 +11991,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="14" thickBot="1">
       <c r="A285" s="9">
         <v>41811</v>
       </c>
@@ -12007,7 +12009,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="14" thickBot="1">
       <c r="A286" s="9">
         <v>41818</v>
       </c>
@@ -12025,7 +12027,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="14" thickBot="1">
       <c r="A287" s="9">
         <v>41825</v>
       </c>
@@ -12043,7 +12045,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="14" thickBot="1">
       <c r="A288" s="9">
         <v>41832</v>
       </c>
@@ -12061,7 +12063,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="14" thickBot="1">
       <c r="A289" s="9">
         <v>41839</v>
       </c>
@@ -12079,7 +12081,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="14" thickBot="1">
       <c r="A290" s="9">
         <v>41846</v>
       </c>
@@ -12097,7 +12099,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="14" thickBot="1">
       <c r="A291" s="9">
         <v>41853</v>
       </c>
@@ -12115,7 +12117,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="14" thickBot="1">
       <c r="A292" s="9">
         <v>41860</v>
       </c>
@@ -12133,7 +12135,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="14" thickBot="1">
       <c r="A293" s="9">
         <v>41867</v>
       </c>
@@ -12151,7 +12153,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="14" thickBot="1">
       <c r="A294" s="9">
         <v>41874</v>
       </c>
@@ -12169,7 +12171,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="14" thickBot="1">
       <c r="A295" s="9">
         <v>41881</v>
       </c>
@@ -12187,7 +12189,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="14" thickBot="1">
       <c r="A296" s="9">
         <v>41888</v>
       </c>
@@ -12205,7 +12207,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="14" thickBot="1">
       <c r="A297" s="9">
         <v>41895</v>
       </c>
@@ -12223,7 +12225,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="14" thickBot="1">
       <c r="A298" s="9">
         <v>41902</v>
       </c>
@@ -12241,7 +12243,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="14" thickBot="1">
       <c r="A299" s="9">
         <v>41909</v>
       </c>
@@ -12259,7 +12261,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="14" thickBot="1">
       <c r="A300" s="9">
         <v>41916</v>
       </c>
@@ -12277,7 +12279,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="14" thickBot="1">
       <c r="A301" s="11">
         <v>41923</v>
       </c>
@@ -12295,7 +12297,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="14" thickBot="1">
       <c r="A302" s="9">
         <v>41930</v>
       </c>
@@ -12313,7 +12315,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="14" thickBot="1">
       <c r="A303" s="9">
         <v>41937</v>
       </c>
@@ -12331,7 +12333,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="14" thickBot="1">
       <c r="A304" s="9">
         <v>41944</v>
       </c>
@@ -12349,7 +12351,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="14" thickBot="1">
       <c r="A305" s="9">
         <v>41951</v>
       </c>
@@ -12367,7 +12369,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="14" thickBot="1">
       <c r="A306" s="9">
         <v>41958</v>
       </c>
@@ -12385,7 +12387,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="14" thickBot="1">
       <c r="A307" s="9">
         <v>41965</v>
       </c>
@@ -12403,7 +12405,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="14" thickBot="1">
       <c r="A308" s="9">
         <v>41972</v>
       </c>
@@ -12421,7 +12423,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="14" thickBot="1">
       <c r="A309" s="9">
         <v>41979</v>
       </c>
@@ -12439,7 +12441,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="14" thickBot="1">
       <c r="A310" s="9">
         <v>41986</v>
       </c>
@@ -12457,7 +12459,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="14" thickBot="1">
       <c r="A311" s="9">
         <v>41993</v>
       </c>
@@ -12475,7 +12477,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="14" thickBot="1">
       <c r="A312" s="9">
         <v>42000</v>
       </c>
@@ -12493,7 +12495,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="14" thickBot="1">
       <c r="A313" s="9">
         <v>42007</v>
       </c>
@@ -12511,7 +12513,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="14" thickBot="1">
       <c r="A314" s="9">
         <v>42014</v>
       </c>
@@ -12529,7 +12531,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="14" thickBot="1">
       <c r="A315" s="9">
         <v>42021</v>
       </c>
@@ -12547,7 +12549,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="14" thickBot="1">
       <c r="A316" s="9">
         <v>42028</v>
       </c>
@@ -12565,7 +12567,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="14" thickBot="1">
       <c r="A317" s="9">
         <v>42035</v>
       </c>
@@ -12583,7 +12585,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="14" thickBot="1">
       <c r="A318" s="9">
         <v>42042</v>
       </c>
@@ -12601,7 +12603,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="14" thickBot="1">
       <c r="A319" s="9">
         <v>42049</v>
       </c>
@@ -12619,7 +12621,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="14" thickBot="1">
       <c r="A320" s="9">
         <v>42056</v>
       </c>
@@ -12637,7 +12639,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="14" thickBot="1">
       <c r="A321" s="9">
         <v>42063</v>
       </c>
@@ -12655,7 +12657,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="14" thickBot="1">
       <c r="A322" s="9">
         <v>42070</v>
       </c>
@@ -12688,7 +12690,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="14" thickBot="1">
       <c r="A323" s="9">
         <v>42077</v>
       </c>
@@ -12706,7 +12708,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="14" thickBot="1">
       <c r="A324" s="9">
         <v>42084</v>
       </c>
@@ -12724,7 +12726,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="14" thickBot="1">
       <c r="A325" s="9">
         <v>42091</v>
       </c>
@@ -12742,7 +12744,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="14" thickBot="1">
       <c r="A326" s="11">
         <v>42098</v>
       </c>
@@ -12760,7 +12762,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="14" thickBot="1">
       <c r="A327" s="9">
         <v>42105</v>
       </c>
@@ -12778,7 +12780,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="14" thickBot="1">
       <c r="A328" s="9">
         <v>42112</v>
       </c>
@@ -12796,7 +12798,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="14" thickBot="1">
       <c r="A329" s="9">
         <v>42119</v>
       </c>
@@ -12814,7 +12816,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="14" thickBot="1">
       <c r="A330" s="9">
         <v>42126</v>
       </c>
@@ -12832,7 +12834,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="14" thickBot="1">
       <c r="A331" s="9">
         <v>42133</v>
       </c>
@@ -12850,7 +12852,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="14" thickBot="1">
       <c r="A332" s="9">
         <v>42140</v>
       </c>
@@ -12868,7 +12870,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="14" thickBot="1">
       <c r="A333" s="9">
         <v>42147</v>
       </c>
@@ -12886,7 +12888,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="14" thickBot="1">
       <c r="A334" s="9">
         <v>42154</v>
       </c>
@@ -12904,7 +12906,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="14" thickBot="1">
       <c r="A335" s="9">
         <v>42161</v>
       </c>
@@ -12922,7 +12924,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="14" thickBot="1">
       <c r="A336" s="9">
         <v>42168</v>
       </c>
@@ -12940,7 +12942,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="14" thickBot="1">
       <c r="A337" s="9">
         <v>42175</v>
       </c>
@@ -12958,7 +12960,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="14" thickBot="1">
       <c r="A338" s="9">
         <v>42182</v>
       </c>
@@ -12976,7 +12978,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="14" thickBot="1">
       <c r="A339" s="9">
         <v>42189</v>
       </c>
@@ -12994,7 +12996,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="14" thickBot="1">
       <c r="A340" s="9">
         <v>42196</v>
       </c>
@@ -13012,7 +13014,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="14" thickBot="1">
       <c r="A341" s="9">
         <v>42203</v>
       </c>
@@ -13030,7 +13032,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="14" thickBot="1">
       <c r="A342" s="9">
         <v>42210</v>
       </c>
@@ -13048,7 +13050,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="14" thickBot="1">
       <c r="A343" s="9">
         <v>42217</v>
       </c>
@@ -13066,7 +13068,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="14" thickBot="1">
       <c r="A344" s="9">
         <v>42224</v>
       </c>
@@ -13084,7 +13086,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="14" thickBot="1">
       <c r="A345" s="9">
         <v>42238</v>
       </c>
@@ -13102,7 +13104,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="14" thickBot="1">
       <c r="A346" s="9">
         <v>42245</v>
       </c>
@@ -13120,7 +13122,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="14" thickBot="1">
       <c r="A347" s="9">
         <v>42252</v>
       </c>
@@ -13138,7 +13140,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="14" thickBot="1">
       <c r="A348" s="9">
         <v>42259</v>
       </c>
@@ -13156,7 +13158,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="14" thickBot="1">
       <c r="A349" s="9">
         <v>42266</v>
       </c>
@@ -13174,7 +13176,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="14" thickBot="1">
       <c r="A350" s="9">
         <v>42273</v>
       </c>
@@ -13192,7 +13194,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="14" thickBot="1">
       <c r="A351" s="11">
         <v>42280</v>
       </c>
@@ -13210,7 +13212,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="14" thickBot="1">
       <c r="A352" s="9">
         <v>42287</v>
       </c>
@@ -13228,7 +13230,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="14" thickBot="1">
       <c r="A353" s="9">
         <v>42294</v>
       </c>
@@ -13246,7 +13248,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="14" thickBot="1">
       <c r="A354" s="9">
         <v>42301</v>
       </c>
@@ -13264,7 +13266,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="14" thickBot="1">
       <c r="A355" s="9">
         <v>42308</v>
       </c>
@@ -13282,7 +13284,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="14" thickBot="1">
       <c r="A356" s="9">
         <v>42315</v>
       </c>
@@ -13300,7 +13302,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="14" thickBot="1">
       <c r="A357" s="9">
         <v>42322</v>
       </c>
@@ -13318,7 +13320,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="14" thickBot="1">
       <c r="A358" s="9">
         <v>42336</v>
       </c>
@@ -13336,7 +13338,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="14" thickBot="1">
       <c r="A359" s="9">
         <v>42343</v>
       </c>
@@ -13354,7 +13356,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="14" thickBot="1">
       <c r="A360" s="9">
         <v>42350</v>
       </c>
@@ -13372,7 +13374,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="14" thickBot="1">
       <c r="A361" s="9">
         <v>42357</v>
       </c>
@@ -13390,7 +13392,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="14" thickBot="1">
       <c r="A362" s="9">
         <v>42364</v>
       </c>
@@ -13408,7 +13410,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="14" thickBot="1">
       <c r="A363" s="9">
         <v>42371</v>
       </c>
@@ -13426,7 +13428,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="14" thickBot="1">
       <c r="A364" s="9">
         <v>42378</v>
       </c>
@@ -13444,7 +13446,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="14" thickBot="1">
       <c r="A365" s="9">
         <v>42385</v>
       </c>
@@ -13462,7 +13464,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="14" thickBot="1">
       <c r="A366" s="9">
         <v>42392</v>
       </c>
@@ -13480,7 +13482,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="14" thickBot="1">
       <c r="A367" s="9">
         <v>42399</v>
       </c>
@@ -13498,7 +13500,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="14" thickBot="1">
       <c r="A368" s="9">
         <v>42406</v>
       </c>
@@ -13516,7 +13518,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="14" thickBot="1">
       <c r="A369" s="9">
         <v>42413</v>
       </c>
@@ -13534,7 +13536,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="14" thickBot="1">
       <c r="A370" s="9">
         <v>42420</v>
       </c>
@@ -13552,7 +13554,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="14" thickBot="1">
       <c r="A371" s="9">
         <v>42427</v>
       </c>
@@ -13570,7 +13572,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="14" thickBot="1">
       <c r="A372" s="9">
         <v>42434</v>
       </c>
@@ -13588,7 +13590,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="14" thickBot="1">
       <c r="A373" s="9">
         <v>42441</v>
       </c>
@@ -13606,7 +13608,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="14" thickBot="1">
       <c r="A374" s="9">
         <v>42448</v>
       </c>
@@ -13624,7 +13626,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="14" thickBot="1">
       <c r="A375" s="9">
         <v>42455</v>
       </c>
@@ -13642,7 +13644,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="14" thickBot="1">
       <c r="A376" s="11">
         <v>42462</v>
       </c>
@@ -13660,7 +13662,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="14" thickBot="1">
       <c r="A377" s="9">
         <v>42469</v>
       </c>
@@ -13678,7 +13680,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="14" thickBot="1">
       <c r="A378" s="9">
         <v>42476</v>
       </c>
@@ -13696,7 +13698,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="14" thickBot="1">
       <c r="A379" s="9">
         <v>42483</v>
       </c>
@@ -13714,7 +13716,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="14" thickBot="1">
       <c r="A380" s="9">
         <v>42490</v>
       </c>
@@ -13732,7 +13734,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="14" thickBot="1">
       <c r="A381" s="9">
         <v>42497</v>
       </c>
@@ -13750,7 +13752,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="14" thickBot="1">
       <c r="A382" s="9">
         <v>42504</v>
       </c>
@@ -13768,7 +13770,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="14" thickBot="1">
       <c r="A383" s="9">
         <v>42511</v>
       </c>
@@ -13786,7 +13788,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="14" thickBot="1">
       <c r="A384" s="9">
         <v>42518</v>
       </c>
@@ -13804,7 +13806,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="14" thickBot="1">
       <c r="A385" s="9">
         <v>42525</v>
       </c>
@@ -13822,7 +13824,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="14" thickBot="1">
       <c r="A386" s="9">
         <v>42532</v>
       </c>
@@ -13855,7 +13857,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="14" thickBot="1">
       <c r="A387" s="9">
         <v>42539</v>
       </c>
@@ -13873,7 +13875,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="14" thickBot="1">
       <c r="A388" s="9">
         <v>42546</v>
       </c>
@@ -13891,7 +13893,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="14" thickBot="1">
       <c r="A389" s="9">
         <v>42553</v>
       </c>
@@ -13909,7 +13911,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="14" thickBot="1">
       <c r="A390" s="9">
         <v>42560</v>
       </c>
@@ -13927,7 +13929,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="14" thickBot="1">
       <c r="A391" s="9">
         <v>42567</v>
       </c>
@@ -13945,7 +13947,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="14" thickBot="1">
       <c r="A392" s="9">
         <v>42574</v>
       </c>
@@ -13963,7 +13965,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="14" thickBot="1">
       <c r="A393" s="9">
         <v>42581</v>
       </c>
@@ -13981,7 +13983,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="14" thickBot="1">
       <c r="A394" s="9">
         <v>42588</v>
       </c>
@@ -13999,7 +14001,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="14" thickBot="1">
       <c r="A395" s="9">
         <v>42595</v>
       </c>
@@ -14017,7 +14019,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="14" thickBot="1">
       <c r="A396" s="9">
         <v>42602</v>
       </c>
@@ -14035,7 +14037,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="14" thickBot="1">
       <c r="A397" s="9">
         <v>42609</v>
       </c>
@@ -14053,7 +14055,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="14" thickBot="1">
       <c r="A398" s="9">
         <v>42616</v>
       </c>
@@ -14071,7 +14073,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="14" thickBot="1">
       <c r="A399" s="9">
         <v>42623</v>
       </c>
@@ -14089,7 +14091,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="14" thickBot="1">
       <c r="A400" s="9">
         <v>42630</v>
       </c>
@@ -14107,7 +14109,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="14" thickBot="1">
       <c r="A401" s="11">
         <v>42637</v>
       </c>
@@ -14125,7 +14127,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="14" thickBot="1">
       <c r="A402" s="9">
         <v>42644</v>
       </c>
@@ -14143,7 +14145,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="14" thickBot="1">
       <c r="A403" s="9">
         <v>42651</v>
       </c>
@@ -14161,7 +14163,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="14" thickBot="1">
       <c r="A404" s="9">
         <v>42658</v>
       </c>
@@ -14179,7 +14181,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="14" thickBot="1">
       <c r="A405" s="9">
         <v>42665</v>
       </c>
@@ -14197,7 +14199,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="14" thickBot="1">
       <c r="A406" s="9">
         <v>42672</v>
       </c>
@@ -14215,7 +14217,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="14" thickBot="1">
       <c r="A407" s="9">
         <v>42679</v>
       </c>
@@ -14233,7 +14235,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="14" thickBot="1">
       <c r="A408" s="9">
         <v>42686</v>
       </c>
@@ -14251,7 +14253,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="14" thickBot="1">
       <c r="A409" s="9">
         <v>42693</v>
       </c>
@@ -14269,7 +14271,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="14" thickBot="1">
       <c r="A410" s="9">
         <v>42700</v>
       </c>
@@ -14287,7 +14289,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="14" thickBot="1">
       <c r="A411" s="9">
         <v>42707</v>
       </c>
@@ -14305,7 +14307,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="14" thickBot="1">
       <c r="A412" s="9">
         <v>42714</v>
       </c>
@@ -14323,7 +14325,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="14" thickBot="1">
       <c r="A413" s="9">
         <v>42721</v>
       </c>
@@ -14341,7 +14343,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="14" thickBot="1">
       <c r="A414" s="9">
         <v>42728</v>
       </c>
@@ -14359,7 +14361,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="14" thickBot="1">
       <c r="A415" s="9">
         <v>42735</v>
       </c>
@@ -14377,7 +14379,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="14" thickBot="1">
       <c r="A416" s="9">
         <v>42742</v>
       </c>
@@ -14395,7 +14397,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="14" thickBot="1">
       <c r="A417" s="9">
         <v>42749</v>
       </c>
@@ -14413,7 +14415,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="14" thickBot="1">
       <c r="A418" s="9">
         <v>42756</v>
       </c>
@@ -14431,7 +14433,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="14" thickBot="1">
       <c r="A419" s="9">
         <v>42763</v>
       </c>
@@ -14449,7 +14451,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="14" thickBot="1">
       <c r="A420" s="9">
         <v>42770</v>
       </c>
@@ -14467,7 +14469,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="14" thickBot="1">
       <c r="A421" s="9">
         <v>42777</v>
       </c>
@@ -14485,7 +14487,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="14" thickBot="1">
       <c r="A422" s="9">
         <v>42784</v>
       </c>
@@ -14503,7 +14505,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="14" thickBot="1">
       <c r="A423" s="9">
         <v>42791</v>
       </c>
@@ -14521,7 +14523,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="14" thickBot="1">
       <c r="A424" s="9">
         <v>42798</v>
       </c>
@@ -14539,7 +14541,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="14" thickBot="1">
       <c r="A425" s="9">
         <v>42805</v>
       </c>
@@ -14557,7 +14559,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="14" thickBot="1">
       <c r="A426" s="11">
         <v>42812</v>
       </c>
@@ -14575,7 +14577,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="14" thickBot="1">
       <c r="A427" s="9">
         <v>42819</v>
       </c>
@@ -14593,7 +14595,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="14" thickBot="1">
       <c r="A428" s="9">
         <v>42826</v>
       </c>
@@ -14611,7 +14613,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="14" thickBot="1">
       <c r="A429" s="9">
         <v>42833</v>
       </c>
@@ -14629,7 +14631,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="14" thickBot="1">
       <c r="A430" s="9">
         <v>42840</v>
       </c>
@@ -14647,7 +14649,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="14" thickBot="1">
       <c r="A431" s="9">
         <v>42847</v>
       </c>
@@ -14665,7 +14667,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="14" thickBot="1">
       <c r="A432" s="9">
         <v>42854</v>
       </c>
@@ -14683,7 +14685,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="14" thickBot="1">
       <c r="A433" s="9">
         <v>42861</v>
       </c>
@@ -14701,7 +14703,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="14" thickBot="1">
       <c r="A434" s="9">
         <v>42868</v>
       </c>
@@ -14719,7 +14721,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="14" thickBot="1">
       <c r="A435" s="9">
         <v>42875</v>
       </c>
@@ -14737,7 +14739,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="14" thickBot="1">
       <c r="A436" s="9">
         <v>42882</v>
       </c>
@@ -14755,7 +14757,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="14" thickBot="1">
       <c r="A437" s="9">
         <v>42889</v>
       </c>
@@ -14773,7 +14775,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="14" thickBot="1">
       <c r="A438" s="9">
         <v>42896</v>
       </c>
@@ -14791,7 +14793,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="14" thickBot="1">
       <c r="A439" s="9">
         <v>42903</v>
       </c>
@@ -14809,7 +14811,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="14" thickBot="1">
       <c r="A440" s="9">
         <v>42910</v>
       </c>
@@ -14827,7 +14829,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="14" thickBot="1">
       <c r="A441" s="9">
         <v>42917</v>
       </c>
@@ -14845,7 +14847,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="14" thickBot="1">
       <c r="A442" s="9">
         <v>42924</v>
       </c>
@@ -14863,7 +14865,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="14" thickBot="1">
       <c r="A443" s="9">
         <v>42931</v>
       </c>
@@ -14881,7 +14883,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="14" thickBot="1">
       <c r="A444" s="9">
         <v>42938</v>
       </c>
@@ -14899,7 +14901,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="14" thickBot="1">
       <c r="A445" s="9">
         <v>42945</v>
       </c>
@@ -14917,7 +14919,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="14" thickBot="1">
       <c r="A446" s="9">
         <v>42952</v>
       </c>
@@ -14935,7 +14937,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="14" thickBot="1">
       <c r="A447" s="9">
         <v>42959</v>
       </c>
@@ -14953,7 +14955,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="14" thickBot="1">
       <c r="A448" s="9">
         <v>42966</v>
       </c>
@@ -14971,7 +14973,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="14" thickBot="1">
       <c r="A449" s="9">
         <v>42973</v>
       </c>
@@ -14989,7 +14991,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="14" thickBot="1">
       <c r="A450" s="9">
         <v>42980</v>
       </c>
@@ -15022,7 +15024,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="14" thickBot="1">
       <c r="A451" s="11">
         <v>42987</v>
       </c>
@@ -15040,7 +15042,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="14" thickBot="1">
       <c r="A452" s="9">
         <v>42994</v>
       </c>
@@ -15058,7 +15060,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="14" thickBot="1">
       <c r="A453" s="9">
         <v>43001</v>
       </c>
@@ -15076,7 +15078,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="14" thickBot="1">
       <c r="A454" s="9">
         <v>43008</v>
       </c>
@@ -15094,7 +15096,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="14" thickBot="1">
       <c r="A455" s="9">
         <v>43015</v>
       </c>
@@ -15112,7 +15114,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="14" thickBot="1">
       <c r="A456" s="9">
         <v>43022</v>
       </c>
@@ -15130,7 +15132,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="14" thickBot="1">
       <c r="A457" s="9">
         <v>43029</v>
       </c>
@@ -15148,7 +15150,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="14" thickBot="1">
       <c r="A458" s="9">
         <v>43036</v>
       </c>
@@ -15166,7 +15168,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="14" thickBot="1">
       <c r="A459" s="9">
         <v>43043</v>
       </c>
@@ -15184,7 +15186,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="14" thickBot="1">
       <c r="A460" s="9">
         <v>43050</v>
       </c>
@@ -15202,7 +15204,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="14" thickBot="1">
       <c r="A461" s="9">
         <v>43057</v>
       </c>
@@ -15220,7 +15222,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="14" thickBot="1">
       <c r="A462" s="9">
         <v>43064</v>
       </c>
@@ -15238,7 +15240,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="14" thickBot="1">
       <c r="A463" s="9">
         <v>43071</v>
       </c>
@@ -15256,7 +15258,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="14" thickBot="1">
       <c r="A464" s="9">
         <v>43078</v>
       </c>
@@ -15274,7 +15276,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="14" thickBot="1">
       <c r="A465" s="9">
         <v>43085</v>
       </c>
@@ -15292,7 +15294,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="14" thickBot="1">
       <c r="A466" s="9">
         <v>43092</v>
       </c>
@@ -15310,7 +15312,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="14" thickBot="1">
       <c r="A467" s="9">
         <v>43099</v>
       </c>
@@ -15328,7 +15330,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="14" thickBot="1">
       <c r="A468" s="9">
         <v>43113</v>
       </c>
@@ -15346,7 +15348,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="14" thickBot="1">
       <c r="A469" s="9">
         <v>43120</v>
       </c>
@@ -15364,7 +15366,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="14" thickBot="1">
       <c r="A470" s="9">
         <v>43127</v>
       </c>
@@ -15382,7 +15384,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="14" thickBot="1">
       <c r="A471" s="9">
         <v>43134</v>
       </c>
@@ -15400,7 +15402,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="14" thickBot="1">
       <c r="A472" s="9">
         <v>43141</v>
       </c>
@@ -15418,7 +15420,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="14" thickBot="1">
       <c r="A473" s="9">
         <v>43148</v>
       </c>
@@ -15436,7 +15438,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="14" thickBot="1">
       <c r="A474" s="9">
         <v>43155</v>
       </c>
@@ -15454,7 +15456,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="14" thickBot="1">
       <c r="A475" s="9">
         <v>43162</v>
       </c>
@@ -15472,7 +15474,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="14" thickBot="1">
       <c r="A476" s="11">
         <v>43169</v>
       </c>
@@ -15490,7 +15492,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="14" thickBot="1">
       <c r="A477" s="9">
         <v>43176</v>
       </c>
@@ -15508,7 +15510,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="14" thickBot="1">
       <c r="A478" s="9">
         <v>43183</v>
       </c>
@@ -15526,7 +15528,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="14" thickBot="1">
       <c r="A479" s="9">
         <v>43190</v>
       </c>
@@ -15544,7 +15546,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="14" thickBot="1">
       <c r="A480" s="9">
         <v>43197</v>
       </c>
@@ -15562,7 +15564,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="14" thickBot="1">
       <c r="A481" s="9">
         <v>43204</v>
       </c>
@@ -15580,7 +15582,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="14" thickBot="1">
       <c r="A482" s="9">
         <v>43211</v>
       </c>
@@ -15598,7 +15600,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="14" thickBot="1">
       <c r="A483" s="9">
         <v>43218</v>
       </c>
@@ -15616,7 +15618,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="14" thickBot="1">
       <c r="A484" s="9">
         <v>43225</v>
       </c>
@@ -15634,7 +15636,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="14" thickBot="1">
       <c r="A485" s="9">
         <v>43232</v>
       </c>
@@ -15652,7 +15654,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="14" thickBot="1">
       <c r="A486" s="9">
         <v>43239</v>
       </c>
@@ -15670,7 +15672,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="14" thickBot="1">
       <c r="A487" s="9">
         <v>43246</v>
       </c>
@@ -15688,7 +15690,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="14" thickBot="1">
       <c r="A488" s="9">
         <v>43253</v>
       </c>
@@ -15706,7 +15708,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="14" thickBot="1">
       <c r="A489" s="9">
         <v>43260</v>
       </c>
@@ -15724,7 +15726,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="14" thickBot="1">
       <c r="A490" s="9">
         <v>43267</v>
       </c>
@@ -15742,7 +15744,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="14" thickBot="1">
       <c r="A491" s="9">
         <v>43274</v>
       </c>
@@ -15760,7 +15762,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="14" thickBot="1">
       <c r="A492" s="9">
         <v>43281</v>
       </c>
@@ -15778,7 +15780,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="14" thickBot="1">
       <c r="A493" s="9">
         <v>43288</v>
       </c>
@@ -15796,7 +15798,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="14" thickBot="1">
       <c r="A494" s="9">
         <v>43295</v>
       </c>
@@ -15814,7 +15816,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="14" thickBot="1">
       <c r="A495" s="9">
         <v>43302</v>
       </c>
@@ -15832,7 +15834,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="14" thickBot="1">
       <c r="A496" s="9">
         <v>43309</v>
       </c>
@@ -15850,7 +15852,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="14" thickBot="1">
       <c r="A497" s="9">
         <v>43316</v>
       </c>
@@ -15868,7 +15870,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="14" thickBot="1">
       <c r="A498" s="9">
         <v>43323</v>
       </c>
@@ -15886,7 +15888,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="14" thickBot="1">
       <c r="A499" s="9">
         <v>43330</v>
       </c>
@@ -15904,7 +15906,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="14" thickBot="1">
       <c r="A500" s="9">
         <v>43337</v>
       </c>
@@ -15922,7 +15924,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="14" thickBot="1">
       <c r="A501" s="11">
         <v>43344</v>
       </c>
@@ -15940,7 +15942,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="14" thickBot="1">
       <c r="A502" s="9">
         <v>43351</v>
       </c>
@@ -15958,7 +15960,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="14" thickBot="1">
       <c r="A503" s="9">
         <v>43358</v>
       </c>
@@ -15976,7 +15978,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="14" thickBot="1">
       <c r="A504" s="9">
         <v>43365</v>
       </c>
@@ -15994,7 +15996,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="14" thickBot="1">
       <c r="A505" s="9">
         <v>43372</v>
       </c>
@@ -16012,7 +16014,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="14" thickBot="1">
       <c r="A506" s="9">
         <v>43379</v>
       </c>
@@ -16030,7 +16032,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="14" thickBot="1">
       <c r="A507" s="9">
         <v>43386</v>
       </c>
@@ -16048,7 +16050,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="14" thickBot="1">
       <c r="A508" s="9">
         <v>43393</v>
       </c>
@@ -16066,7 +16068,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="14" thickBot="1">
       <c r="A509" s="9">
         <v>43400</v>
       </c>
@@ -16084,7 +16086,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="14" thickBot="1">
       <c r="A510" s="9">
         <v>43407</v>
       </c>
@@ -16102,7 +16104,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="14" thickBot="1">
       <c r="A511" s="9">
         <v>43414</v>
       </c>
@@ -16120,7 +16122,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="14" thickBot="1">
       <c r="A512" s="9">
         <v>43421</v>
       </c>
@@ -16138,7 +16140,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="14" thickBot="1">
       <c r="A513" s="9">
         <v>43428</v>
       </c>
@@ -16156,7 +16158,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="14" thickBot="1">
       <c r="A514" s="9">
         <v>43435</v>
       </c>
@@ -16189,7 +16191,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="14" thickBot="1">
       <c r="A515" s="9">
         <v>43442</v>
       </c>
@@ -16207,7 +16209,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="14" thickBot="1">
       <c r="A516" s="9">
         <v>43449</v>
       </c>
@@ -16225,7 +16227,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="14" thickBot="1">
       <c r="A517" s="9">
         <v>43456</v>
       </c>
@@ -16243,7 +16245,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="14" thickBot="1">
       <c r="A518" s="9">
         <v>43463</v>
       </c>
@@ -16261,7 +16263,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="14" thickBot="1">
       <c r="A519" s="9">
         <v>43470</v>
       </c>
@@ -16279,7 +16281,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="14" thickBot="1">
       <c r="A520" s="9">
         <v>43477</v>
       </c>
@@ -16297,7 +16299,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="14" thickBot="1">
       <c r="A521" s="9">
         <v>43484</v>
       </c>
@@ -16315,7 +16317,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="14" thickBot="1">
       <c r="A522" s="9">
         <v>43491</v>
       </c>
@@ -16333,7 +16335,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="14" thickBot="1">
       <c r="A523" s="9">
         <v>43498</v>
       </c>
@@ -16351,7 +16353,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="14" thickBot="1">
       <c r="A524" s="9">
         <v>43505</v>
       </c>
@@ -16369,7 +16371,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="14" thickBot="1">
       <c r="A525" s="9">
         <v>43512</v>
       </c>
@@ -16387,7 +16389,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="14" thickBot="1">
       <c r="A526" s="11">
         <v>43519</v>
       </c>
@@ -16405,7 +16407,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="14" thickBot="1">
       <c r="A527" s="9">
         <v>43526</v>
       </c>
@@ -16423,7 +16425,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="14" thickBot="1">
       <c r="A528" s="9">
         <v>43533</v>
       </c>
@@ -16441,7 +16443,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="14" thickBot="1">
       <c r="A529" s="9">
         <v>43540</v>
       </c>
@@ -16459,7 +16461,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="14" thickBot="1">
       <c r="A530" s="9">
         <v>43547</v>
       </c>
@@ -16477,7 +16479,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="14" thickBot="1">
       <c r="A531" s="9">
         <v>43554</v>
       </c>
@@ -16495,7 +16497,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="14" thickBot="1">
       <c r="A532" s="9">
         <v>43561</v>
       </c>
@@ -16513,7 +16515,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="14" thickBot="1">
       <c r="A533" s="9">
         <v>43568</v>
       </c>
@@ -16531,7 +16533,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="14" thickBot="1">
       <c r="A534" s="9">
         <v>43575</v>
       </c>
@@ -16549,7 +16551,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="14" thickBot="1">
       <c r="A535" s="9">
         <v>43582</v>
       </c>
@@ -16567,7 +16569,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="14" thickBot="1">
       <c r="A536" s="9">
         <v>43589</v>
       </c>
@@ -16585,7 +16587,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="14" thickBot="1">
       <c r="A537" s="9">
         <v>43596</v>
       </c>
@@ -16603,7 +16605,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="14" thickBot="1">
       <c r="A538" s="9">
         <v>43603</v>
       </c>
@@ -16621,7 +16623,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="14" thickBot="1">
       <c r="A539" s="9">
         <v>43610</v>
       </c>
@@ -16639,7 +16641,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="14" thickBot="1">
       <c r="A540" s="9">
         <v>43617</v>
       </c>
@@ -16657,7 +16659,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="14" thickBot="1">
       <c r="A541" s="9">
         <v>43624</v>
       </c>
@@ -16675,7 +16677,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="14" thickBot="1">
       <c r="A542" s="9">
         <v>43631</v>
       </c>
@@ -16693,7 +16695,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="14" thickBot="1">
       <c r="A543" s="9">
         <v>43638</v>
       </c>
@@ -16711,7 +16713,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="14" thickBot="1">
       <c r="A544" s="9">
         <v>43645</v>
       </c>
@@ -16729,7 +16731,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="14" thickBot="1">
       <c r="A545" s="9">
         <v>43652</v>
       </c>
@@ -16747,7 +16749,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="14" thickBot="1">
       <c r="A546" s="9">
         <v>43659</v>
       </c>
@@ -16765,7 +16767,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="14" thickBot="1">
       <c r="A547" s="9">
         <v>43666</v>
       </c>
@@ -16783,7 +16785,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="14" thickBot="1">
       <c r="A548" s="9">
         <v>43673</v>
       </c>
@@ -16801,7 +16803,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="14" thickBot="1">
       <c r="A549" s="9">
         <v>43680</v>
       </c>
@@ -16819,7 +16821,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="14" thickBot="1">
       <c r="A550" s="9">
         <v>43687</v>
       </c>
@@ -16837,7 +16839,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="14" thickBot="1">
       <c r="A551" s="11">
         <v>43694</v>
       </c>
@@ -16855,7 +16857,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="14" thickBot="1">
       <c r="A552" s="9">
         <v>43701</v>
       </c>
@@ -16873,7 +16875,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="14" thickBot="1">
       <c r="A553" s="9">
         <v>43708</v>
       </c>
@@ -16891,7 +16893,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="14" thickBot="1">
       <c r="A554" s="9">
         <v>43715</v>
       </c>
@@ -16909,7 +16911,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="14" thickBot="1">
       <c r="A555" s="9">
         <v>43722</v>
       </c>
@@ -16927,7 +16929,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="14" thickBot="1">
       <c r="A556" s="9">
         <v>43729</v>
       </c>
@@ -16945,7 +16947,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="14" thickBot="1">
       <c r="A557" s="9">
         <v>43736</v>
       </c>
@@ -16963,7 +16965,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="14" thickBot="1">
       <c r="A558" s="9">
         <v>43743</v>
       </c>
@@ -16981,7 +16983,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="14" thickBot="1">
       <c r="A559" s="9">
         <v>43750</v>
       </c>
@@ -16999,7 +17001,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="14" thickBot="1">
       <c r="A560" s="9">
         <v>43757</v>
       </c>
@@ -17017,7 +17019,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="14" thickBot="1">
       <c r="A561" s="9">
         <v>43764</v>
       </c>
@@ -17035,7 +17037,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="14" thickBot="1">
       <c r="A562" s="9">
         <v>43771</v>
       </c>
@@ -17053,7 +17055,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="14" thickBot="1">
       <c r="A563" s="9">
         <v>43778</v>
       </c>
@@ -17071,7 +17073,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="14" thickBot="1">
       <c r="A564" s="9">
         <v>43785</v>
       </c>
@@ -17089,7 +17091,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="14" thickBot="1">
       <c r="A565" s="9">
         <v>43792</v>
       </c>
@@ -17107,7 +17109,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="14" thickBot="1">
       <c r="A566" s="9">
         <v>43813</v>
       </c>
@@ -17125,7 +17127,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="14" thickBot="1">
       <c r="A567" s="9">
         <v>43820</v>
       </c>
@@ -17143,7 +17145,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="14" thickBot="1">
       <c r="A568" s="9">
         <v>43827</v>
       </c>
@@ -17161,7 +17163,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="14" thickBot="1">
       <c r="A569" s="9">
         <v>43834</v>
       </c>
@@ -17179,7 +17181,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="14" thickBot="1">
       <c r="A570" s="9">
         <v>43841</v>
       </c>
@@ -17197,7 +17199,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="14" thickBot="1">
       <c r="A571" s="9">
         <v>43848</v>
       </c>
@@ -17215,7 +17217,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="14" thickBot="1">
       <c r="A572" s="9">
         <v>43855</v>
       </c>
@@ -17233,7 +17235,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="14" thickBot="1">
       <c r="A573" s="9">
         <v>43862</v>
       </c>
@@ -17251,7 +17253,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="14" thickBot="1">
       <c r="A574" s="9">
         <v>43869</v>
       </c>
@@ -17269,7 +17271,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="14" thickBot="1">
       <c r="A575" s="9">
         <v>43876</v>
       </c>
@@ -17287,7 +17289,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="14" thickBot="1">
       <c r="A576" s="11">
         <v>43883</v>
       </c>
@@ -17305,7 +17307,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="14" thickBot="1">
       <c r="A577" s="9">
         <v>43890</v>
       </c>
@@ -17323,7 +17325,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="14" thickBot="1">
       <c r="A578" s="9">
         <v>43897</v>
       </c>
@@ -17356,7 +17358,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="14" thickBot="1">
       <c r="A579" s="9">
         <v>43904</v>
       </c>
@@ -17374,7 +17376,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="14" thickBot="1">
       <c r="A580" s="9">
         <v>43911</v>
       </c>
@@ -17392,7 +17394,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="14" thickBot="1">
       <c r="A581" s="9">
         <v>43918</v>
       </c>
@@ -17410,7 +17412,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="14" thickBot="1">
       <c r="A582" s="9">
         <v>43925</v>
       </c>
@@ -17428,7 +17430,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="14" thickBot="1">
       <c r="A583" s="9">
         <v>43932</v>
       </c>
@@ -17446,7 +17448,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="14" thickBot="1">
       <c r="A584" s="9">
         <v>43939</v>
       </c>
@@ -17464,7 +17466,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="14" thickBot="1">
       <c r="A585" s="9">
         <v>43946</v>
       </c>
@@ -17482,7 +17484,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="14" thickBot="1">
       <c r="A586" s="9">
         <v>43953</v>
       </c>
@@ -17500,7 +17502,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="14" thickBot="1">
       <c r="A587" s="9">
         <v>43960</v>
       </c>
@@ -17518,7 +17520,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="14" thickBot="1">
       <c r="A588" s="9">
         <v>43967</v>
       </c>
@@ -17536,7 +17538,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="14" thickBot="1">
       <c r="A589" s="9">
         <v>43974</v>
       </c>
@@ -17554,7 +17556,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="14" thickBot="1">
       <c r="A590" s="9">
         <v>43981</v>
       </c>
@@ -17572,7 +17574,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="14" thickBot="1">
       <c r="A591" s="9">
         <v>43988</v>
       </c>
@@ -17590,7 +17592,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="14" thickBot="1">
       <c r="A592" s="9">
         <v>43995</v>
       </c>
@@ -17608,7 +17610,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="14" thickBot="1">
       <c r="A593" s="9">
         <v>44002</v>
       </c>
@@ -17626,7 +17628,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="14" thickBot="1">
       <c r="A594" s="9">
         <v>44009</v>
       </c>
@@ -17644,7 +17646,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="14" thickBot="1">
       <c r="A595" s="9">
         <v>44016</v>
       </c>
@@ -17662,7 +17664,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="14" thickBot="1">
       <c r="A596" s="9">
         <v>44023</v>
       </c>
@@ -17680,7 +17682,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="14" thickBot="1">
       <c r="A597" s="9">
         <v>44030</v>
       </c>
@@ -17698,7 +17700,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="14" thickBot="1">
       <c r="A598" s="9">
         <v>44037</v>
       </c>
@@ -17716,7 +17718,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="14" thickBot="1">
       <c r="A599" s="9">
         <v>44044</v>
       </c>
@@ -17734,7 +17736,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="14" thickBot="1">
       <c r="A600" s="9">
         <v>44051</v>
       </c>
@@ -17752,7 +17754,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="14" thickBot="1">
       <c r="A601" s="11">
         <v>44058</v>
       </c>
@@ -17770,7 +17772,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="14" thickBot="1">
       <c r="A602" s="9">
         <v>44072</v>
       </c>
@@ -17788,7 +17790,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="14" thickBot="1">
       <c r="A603" s="9">
         <v>44079</v>
       </c>
@@ -17806,7 +17808,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="14" thickBot="1">
       <c r="A604" s="9">
         <v>44086</v>
       </c>
@@ -17824,7 +17826,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="14" thickBot="1">
       <c r="A605" s="9">
         <v>44093</v>
       </c>
@@ -17842,7 +17844,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="14" thickBot="1">
       <c r="A606" s="9">
         <v>44100</v>
       </c>
@@ -17860,7 +17862,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="14" thickBot="1">
       <c r="A607" s="9">
         <v>44107</v>
       </c>
@@ -17878,7 +17880,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="14" thickBot="1">
       <c r="A608" s="9">
         <v>44114</v>
       </c>
@@ -17896,7 +17898,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="14" thickBot="1">
       <c r="A609" s="9">
         <v>44121</v>
       </c>
@@ -17914,7 +17916,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="14" thickBot="1">
       <c r="A610" s="9">
         <v>44128</v>
       </c>
@@ -17932,7 +17934,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="14" thickBot="1">
       <c r="A611" s="9">
         <v>44135</v>
       </c>
@@ -17950,7 +17952,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="14" thickBot="1">
       <c r="A612" s="9">
         <v>44142</v>
       </c>
@@ -17968,7 +17970,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="14" thickBot="1">
       <c r="A613" s="9">
         <v>44149</v>
       </c>
@@ -17986,7 +17988,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="14" thickBot="1">
       <c r="A614" s="9">
         <v>44156</v>
       </c>
@@ -18004,7 +18006,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="14" thickBot="1">
       <c r="A615" s="9">
         <v>44163</v>
       </c>
@@ -18022,7 +18024,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="14" thickBot="1">
       <c r="A616" s="9">
         <v>44170</v>
       </c>
@@ -18040,7 +18042,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="14" thickBot="1">
       <c r="A617" s="9">
         <v>44177</v>
       </c>
@@ -18058,7 +18060,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="14" thickBot="1">
       <c r="A618" s="9">
         <v>44191</v>
       </c>
@@ -18076,7 +18078,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="14" thickBot="1">
       <c r="A619" s="9">
         <v>44198</v>
       </c>
@@ -18094,7 +18096,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="14" thickBot="1">
       <c r="A620" s="9">
         <v>44205</v>
       </c>
@@ -18112,7 +18114,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="14" thickBot="1">
       <c r="A621" s="9">
         <v>44212</v>
       </c>
@@ -18130,7 +18132,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="14" thickBot="1">
       <c r="A622" s="9">
         <v>44219</v>
       </c>
@@ -18148,7 +18150,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="14" thickBot="1">
       <c r="A623" s="9">
         <v>44226</v>
       </c>
@@ -18166,7 +18168,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="14" thickBot="1">
       <c r="A624" s="9">
         <v>44233</v>
       </c>
@@ -18184,7 +18186,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="14" thickBot="1">
       <c r="A625" s="9">
         <v>44240</v>
       </c>
@@ -18202,7 +18204,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="14" thickBot="1">
       <c r="A626" s="11">
         <v>44247</v>
       </c>
@@ -18220,7 +18222,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="14" thickBot="1">
       <c r="A627" s="9">
         <v>44254</v>
       </c>
@@ -18238,7 +18240,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="14" thickBot="1">
       <c r="A628" s="9">
         <v>44261</v>
       </c>
@@ -18256,7 +18258,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="14" thickBot="1">
       <c r="A629" s="9">
         <v>44268</v>
       </c>
@@ -18274,7 +18276,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="14" thickBot="1">
       <c r="A630" s="9">
         <v>44275</v>
       </c>
@@ -18292,7 +18294,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="14" thickBot="1">
       <c r="A631" s="9">
         <v>44282</v>
       </c>
@@ -18310,7 +18312,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="14" thickBot="1">
       <c r="A632" s="9">
         <v>44289</v>
       </c>
@@ -18328,7 +18330,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="14" thickBot="1">
       <c r="A633" s="9">
         <v>44296</v>
       </c>
@@ -18346,7 +18348,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="14" thickBot="1">
       <c r="A634" s="9">
         <v>44303</v>
       </c>
@@ -18364,7 +18366,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="14" thickBot="1">
       <c r="A635" s="9">
         <v>44310</v>
       </c>
@@ -18382,7 +18384,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="14" thickBot="1">
       <c r="A636" s="9">
         <v>44317</v>
       </c>
@@ -18400,7 +18402,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="14" thickBot="1">
       <c r="A637" s="9">
         <v>44324</v>
       </c>
@@ -18418,7 +18420,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="14" thickBot="1">
       <c r="A638" s="9">
         <v>44331</v>
       </c>
@@ -18436,7 +18438,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="14" thickBot="1">
       <c r="A639" s="9">
         <v>44338</v>
       </c>
@@ -18454,7 +18456,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="14" thickBot="1">
       <c r="A640" s="9">
         <v>44345</v>
       </c>
@@ -18472,7 +18474,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="14" thickBot="1">
       <c r="A641" s="9">
         <v>44352</v>
       </c>
@@ -18490,7 +18492,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="14" thickBot="1">
       <c r="A642" s="9">
         <v>44359</v>
       </c>
@@ -18523,7 +18525,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="14" thickBot="1">
       <c r="A643" s="9">
         <v>44366</v>
       </c>
@@ -18541,7 +18543,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="14" thickBot="1">
       <c r="A644" s="9">
         <v>44373</v>
       </c>
@@ -18559,7 +18561,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="14" thickBot="1">
       <c r="A645" s="9">
         <v>44380</v>
       </c>
@@ -18577,7 +18579,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="14" thickBot="1">
       <c r="A646" s="9">
         <v>44387</v>
       </c>
@@ -18595,7 +18597,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="14" thickBot="1">
       <c r="A647" s="9">
         <v>44394</v>
       </c>
@@ -18613,7 +18615,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="14" thickBot="1">
       <c r="A648" s="9">
         <v>44401</v>
       </c>
@@ -18631,7 +18633,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="14" thickBot="1">
       <c r="A649" s="9">
         <v>44408</v>
       </c>
@@ -18649,7 +18651,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="14" thickBot="1">
       <c r="A650" s="9">
         <v>44415</v>
       </c>
@@ -18667,7 +18669,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="14" thickBot="1">
       <c r="A651" s="11">
         <v>44422</v>
       </c>
@@ -18685,7 +18687,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="14" thickBot="1">
       <c r="A652" s="9">
         <v>44429</v>
       </c>
@@ -18703,7 +18705,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="14" thickBot="1">
       <c r="A653" s="9">
         <v>44436</v>
       </c>
@@ -18721,7 +18723,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="14" thickBot="1">
       <c r="A654" s="9">
         <v>44443</v>
       </c>
@@ -18739,7 +18741,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="14" thickBot="1">
       <c r="A655" s="9">
         <v>44450</v>
       </c>
@@ -18757,7 +18759,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="14" thickBot="1">
       <c r="A656" s="9">
         <v>44457</v>
       </c>
@@ -18775,7 +18777,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="14" thickBot="1">
       <c r="A657" s="9">
         <v>44464</v>
       </c>
@@ -18793,7 +18795,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="14" thickBot="1">
       <c r="A658" s="9">
         <v>44471</v>
       </c>
@@ -18811,7 +18813,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="14" thickBot="1">
       <c r="A659" s="9">
         <v>44478</v>
       </c>
@@ -18829,7 +18831,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="14" thickBot="1">
       <c r="A660" s="9">
         <v>44485</v>
       </c>
@@ -18847,7 +18849,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="14" thickBot="1">
       <c r="A661" s="9">
         <v>44492</v>
       </c>
@@ -18865,7 +18867,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="14" thickBot="1">
       <c r="A662" s="9">
         <v>44499</v>
       </c>
@@ -18883,7 +18885,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="14" thickBot="1">
       <c r="A663" s="9">
         <v>44506</v>
       </c>
@@ -18901,7 +18903,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="14" thickBot="1">
       <c r="A664" s="9">
         <v>44513</v>
       </c>
@@ -18919,7 +18921,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="14" thickBot="1">
       <c r="A665" s="9">
         <v>44520</v>
       </c>
@@ -18937,7 +18939,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="14" thickBot="1">
       <c r="A666" s="9">
         <v>44527</v>
       </c>
@@ -18955,7 +18957,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="14" thickBot="1">
       <c r="A667" s="9">
         <v>44534</v>
       </c>
@@ -18973,7 +18975,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="14" thickBot="1">
       <c r="A668" s="9">
         <v>44541</v>
       </c>
@@ -18991,7 +18993,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="14" thickBot="1">
       <c r="A669" s="9">
         <v>44548</v>
       </c>
@@ -19009,7 +19011,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="14" thickBot="1">
       <c r="A670" s="9">
         <v>44555</v>
       </c>
@@ -19027,7 +19029,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="14" thickBot="1">
       <c r="A671" s="9">
         <v>44562</v>
       </c>
@@ -19045,7 +19047,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="14" thickBot="1">
       <c r="A672" s="9">
         <v>44569</v>
       </c>
@@ -19063,7 +19065,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="14" thickBot="1">
       <c r="A673" s="9">
         <v>44576</v>
       </c>
@@ -19081,7 +19083,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="14" thickBot="1">
       <c r="A674" s="9">
         <v>44583</v>
       </c>
@@ -19099,7 +19101,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="14" thickBot="1">
       <c r="A675" s="9">
         <v>44590</v>
       </c>
@@ -19117,7 +19119,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="14" thickBot="1">
       <c r="A676" s="11">
         <v>44597</v>
       </c>
@@ -19135,7 +19137,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="14" thickBot="1">
       <c r="A677" s="9">
         <v>44604</v>
       </c>
@@ -19153,7 +19155,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="14" thickBot="1">
       <c r="A678" s="9">
         <v>44611</v>
       </c>
@@ -19171,7 +19173,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="14" thickBot="1">
       <c r="A679" s="9">
         <v>44625</v>
       </c>
@@ -19189,7 +19191,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="14" thickBot="1">
       <c r="A680" s="9">
         <v>44632</v>
       </c>
@@ -19207,7 +19209,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="14" thickBot="1">
       <c r="A681" s="9">
         <v>44639</v>
       </c>
@@ -19225,7 +19227,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="14" thickBot="1">
       <c r="A682" s="9">
         <v>44646</v>
       </c>
@@ -19243,7 +19245,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="14" thickBot="1">
       <c r="A683" s="9">
         <v>44653</v>
       </c>
@@ -19261,7 +19263,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="14" thickBot="1">
       <c r="A684" s="9">
         <v>44660</v>
       </c>
@@ -19279,7 +19281,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="14" thickBot="1">
       <c r="A685" s="9">
         <v>44667</v>
       </c>
@@ -19297,7 +19299,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="14" thickBot="1">
       <c r="A686" s="9">
         <v>44674</v>
       </c>
@@ -19315,7 +19317,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="14" thickBot="1">
       <c r="A687" s="9">
         <v>44681</v>
       </c>
@@ -19333,7 +19335,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="14" thickBot="1">
       <c r="A688" s="9">
         <v>44688</v>
       </c>
@@ -19351,7 +19353,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="14" thickBot="1">
       <c r="A689" s="9">
         <v>44695</v>
       </c>
@@ -19369,7 +19371,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="14" thickBot="1">
       <c r="A690" s="9">
         <v>44702</v>
       </c>
@@ -19387,7 +19389,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="14" thickBot="1">
       <c r="A691" s="9">
         <v>44709</v>
       </c>
@@ -19405,7 +19407,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="14" thickBot="1">
       <c r="A692" s="9">
         <v>44716</v>
       </c>
@@ -19423,7 +19425,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="14" thickBot="1">
       <c r="A693" s="9">
         <v>44723</v>
       </c>
@@ -19441,7 +19443,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="14" thickBot="1">
       <c r="A694" s="9">
         <v>44730</v>
       </c>
@@ -19459,7 +19461,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="14" thickBot="1">
       <c r="A695" s="9">
         <v>44737</v>
       </c>
@@ -19477,7 +19479,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="14" thickBot="1">
       <c r="A696" s="9">
         <v>44744</v>
       </c>
@@ -19495,7 +19497,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="14" thickBot="1">
       <c r="A697" s="9">
         <v>44751</v>
       </c>
@@ -19513,7 +19515,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="14" thickBot="1">
       <c r="A698" s="9">
         <v>44758</v>
       </c>
@@ -19531,7 +19533,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="14" thickBot="1">
       <c r="A699" s="9">
         <v>44765</v>
       </c>
@@ -19549,7 +19551,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="14" thickBot="1">
       <c r="A700" s="9">
         <v>44772</v>
       </c>
@@ -19567,7 +19569,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="14" thickBot="1">
       <c r="A701" s="11">
         <v>44779</v>
       </c>
@@ -19585,7 +19587,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="14" thickBot="1">
       <c r="A702" s="9">
         <v>44786</v>
       </c>
@@ -19603,7 +19605,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="14" thickBot="1">
       <c r="A703" s="9">
         <v>44793</v>
       </c>
@@ -19621,7 +19623,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="14" thickBot="1">
       <c r="A704" s="9">
         <v>44800</v>
       </c>
@@ -19639,7 +19641,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="14" thickBot="1">
       <c r="A705" s="9">
         <v>44807</v>
       </c>
@@ -19657,7 +19659,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="14" thickBot="1">
       <c r="A706" s="9">
         <v>44814</v>
       </c>
@@ -19690,7 +19692,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="14" thickBot="1">
       <c r="A707" s="9">
         <v>44821</v>
       </c>
@@ -19708,7 +19710,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="14" thickBot="1">
       <c r="A708" s="9">
         <v>44828</v>
       </c>
@@ -19726,7 +19728,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="14" thickBot="1">
       <c r="A709" s="9">
         <v>44835</v>
       </c>
@@ -19744,7 +19746,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="14" thickBot="1">
       <c r="A710" s="9">
         <v>44842</v>
       </c>
@@ -19762,7 +19764,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="14" thickBot="1">
       <c r="A711" s="9">
         <v>44849</v>
       </c>
@@ -19780,7 +19782,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="14" thickBot="1">
       <c r="A712" s="9">
         <v>44856</v>
       </c>
@@ -19798,7 +19800,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="14" thickBot="1">
       <c r="A713" s="9">
         <v>44863</v>
       </c>
@@ -19816,7 +19818,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="14" thickBot="1">
       <c r="A714" s="9">
         <v>44870</v>
       </c>
@@ -19834,7 +19836,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="14" thickBot="1">
       <c r="A715" s="9">
         <v>44877</v>
       </c>
@@ -19852,7 +19854,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="14" thickBot="1">
       <c r="A716" s="9">
         <v>44884</v>
       </c>
@@ -19870,7 +19872,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="14" thickBot="1">
       <c r="A717" s="9">
         <v>44891</v>
       </c>
@@ -19888,7 +19890,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="14" thickBot="1">
       <c r="A718" s="9">
         <v>44898</v>
       </c>
@@ -19906,7 +19908,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="14" thickBot="1">
       <c r="A719" s="9">
         <v>44905</v>
       </c>
@@ -19924,7 +19926,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="14" thickBot="1">
       <c r="A720" s="9">
         <v>44912</v>
       </c>
@@ -19942,7 +19944,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="14" thickBot="1">
       <c r="A721" s="9">
         <v>44919</v>
       </c>
@@ -19960,7 +19962,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="14" thickBot="1">
       <c r="A722" s="9">
         <v>44926</v>
       </c>
@@ -19978,7 +19980,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="14" thickBot="1">
       <c r="A723" s="9">
         <v>44933</v>
       </c>
@@ -19996,7 +19998,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="14" thickBot="1">
       <c r="A724" s="9">
         <v>44940</v>
       </c>
@@ -20014,7 +20016,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="14" thickBot="1">
       <c r="A725" s="9">
         <v>44947</v>
       </c>
@@ -20032,7 +20034,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="14" thickBot="1">
       <c r="A726" s="11">
         <v>44954</v>
       </c>
@@ -20050,7 +20052,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="14" thickBot="1">
       <c r="A727" s="9">
         <v>44961</v>
       </c>
@@ -20068,7 +20070,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="14" thickBot="1">
       <c r="A728" s="9">
         <v>44968</v>
       </c>
@@ -20086,7 +20088,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="14" thickBot="1">
       <c r="A729" s="9">
         <v>44975</v>
       </c>
@@ -20104,7 +20106,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="14" thickBot="1">
       <c r="A730" s="9">
         <v>44982</v>
       </c>
@@ -20122,7 +20124,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="14" thickBot="1">
       <c r="A731" s="9">
         <v>44989</v>
       </c>
@@ -20140,7 +20142,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="14" thickBot="1">
       <c r="A732" s="9">
         <v>44996</v>
       </c>
@@ -20158,7 +20160,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="14" thickBot="1">
       <c r="A733" s="9">
         <v>45003</v>
       </c>
@@ -20176,7 +20178,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="14" thickBot="1">
       <c r="A734" s="9">
         <v>45010</v>
       </c>
@@ -20194,7 +20196,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="14" thickBot="1">
       <c r="A735" s="9">
         <v>45017</v>
       </c>
@@ -20212,7 +20214,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="14" thickBot="1">
       <c r="A736" s="9">
         <v>45024</v>
       </c>
@@ -20230,7 +20232,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="14" thickBot="1">
       <c r="A737" s="9">
         <v>45031</v>
       </c>
@@ -20248,7 +20250,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="14" thickBot="1">
       <c r="A738" s="9">
         <v>45038</v>
       </c>
@@ -20266,7 +20268,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="14" thickBot="1">
       <c r="A739" s="9">
         <v>45045</v>
       </c>
@@ -20284,7 +20286,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="14" thickBot="1">
       <c r="A740" s="9">
         <v>45052</v>
       </c>
@@ -20302,7 +20304,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="14" thickBot="1">
       <c r="A741" s="9">
         <v>45059</v>
       </c>
@@ -20320,7 +20322,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="14" thickBot="1">
       <c r="A742" s="9">
         <v>45066</v>
       </c>
@@ -20338,7 +20340,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="14" thickBot="1">
       <c r="A743" s="9">
         <v>45073</v>
       </c>
@@ -20356,7 +20358,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="14" thickBot="1">
       <c r="A744" s="9">
         <v>45080</v>
       </c>
@@ -20374,7 +20376,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="14" thickBot="1">
       <c r="A745" s="9">
         <v>45087</v>
       </c>
@@ -20392,7 +20394,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="14" thickBot="1">
       <c r="A746" s="9">
         <v>45094</v>
       </c>
@@ -20410,7 +20412,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="14" thickBot="1">
       <c r="A747" s="9">
         <v>45101</v>
       </c>
@@ -20428,7 +20430,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="14" thickBot="1">
       <c r="A748" s="9">
         <v>45108</v>
       </c>
@@ -20446,7 +20448,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="14" thickBot="1">
       <c r="A749" s="9">
         <v>45115</v>
       </c>
@@ -20464,7 +20466,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="14" thickBot="1">
       <c r="A750" s="9">
         <v>45122</v>
       </c>
@@ -20482,7 +20484,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="14" thickBot="1">
       <c r="A751" s="11">
         <v>45129</v>
       </c>
@@ -20500,7 +20502,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="14" thickBot="1">
       <c r="A752" s="9">
         <v>45136</v>
       </c>
@@ -20518,7 +20520,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="14" thickBot="1">
       <c r="A753" s="9">
         <v>45143</v>
       </c>
@@ -20536,7 +20538,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="14" thickBot="1">
       <c r="A754" s="9">
         <v>45150</v>
       </c>
@@ -20554,7 +20556,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="14" thickBot="1">
       <c r="A755" s="9">
         <v>45157</v>
       </c>
@@ -20572,7 +20574,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="14" thickBot="1">
       <c r="A756" s="9">
         <v>45164</v>
       </c>
@@ -20590,7 +20592,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="14" thickBot="1">
       <c r="A757" s="9">
         <v>45171</v>
       </c>
@@ -20608,7 +20610,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="14" thickBot="1">
       <c r="A758" s="9">
         <v>45178</v>
       </c>
@@ -20626,7 +20628,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="14" thickBot="1">
       <c r="A759" s="9">
         <v>45185</v>
       </c>
@@ -20644,7 +20646,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="14" thickBot="1">
       <c r="A760" s="9">
         <v>45192</v>
       </c>
@@ -20662,7 +20664,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="14" thickBot="1">
       <c r="A761" s="9">
         <v>45199</v>
       </c>
@@ -20680,7 +20682,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="14" thickBot="1">
       <c r="A762" s="9">
         <v>45206</v>
       </c>
@@ -20698,7 +20700,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="14" thickBot="1">
       <c r="A763" s="9">
         <v>45213</v>
       </c>
@@ -20716,7 +20718,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="14" thickBot="1">
       <c r="A764" s="9">
         <v>45220</v>
       </c>
@@ -20734,7 +20736,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="14" thickBot="1">
       <c r="A765" s="9">
         <v>45227</v>
       </c>
@@ -20752,7 +20754,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="14" thickBot="1">
       <c r="A766" s="9">
         <v>45234</v>
       </c>
@@ -20770,7 +20772,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="14" thickBot="1">
       <c r="A767" s="9">
         <v>45241</v>
       </c>
@@ -20788,7 +20790,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="14" thickBot="1">
       <c r="A768" s="9">
         <v>45248</v>
       </c>
@@ -20806,7 +20808,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="14" thickBot="1">
       <c r="A769" s="9">
         <v>45255</v>
       </c>
@@ -20824,7 +20826,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="14" thickBot="1">
       <c r="A770" s="9">
         <v>45262</v>
       </c>
@@ -20857,7 +20859,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="14" thickBot="1">
       <c r="A771" s="9">
         <v>45269</v>
       </c>
@@ -20875,7 +20877,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="14" thickBot="1">
       <c r="A772" s="9">
         <v>45276</v>
       </c>
@@ -20893,7 +20895,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="14" thickBot="1">
       <c r="A773" s="9">
         <v>45283</v>
       </c>
@@ -20911,7 +20913,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="14" thickBot="1">
       <c r="A774" s="9">
         <v>45297</v>
       </c>
@@ -20929,7 +20931,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="14" thickBot="1">
       <c r="A775" s="9">
         <v>45304</v>
       </c>
@@ -20947,7 +20949,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="14" thickBot="1">
       <c r="A776" s="13">
         <v>45311</v>
       </c>
@@ -20965,7 +20967,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="14" thickBot="1">
       <c r="A777" s="15">
         <v>45318</v>
       </c>
@@ -20983,7 +20985,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="14" thickBot="1">
       <c r="A778" s="15">
         <v>45325</v>
       </c>
@@ -21001,7 +21003,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="14" thickBot="1">
       <c r="A779" s="15">
         <v>45332</v>
       </c>
@@ -21019,7 +21021,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="14" thickBot="1">
       <c r="A780" s="15">
         <v>45339</v>
       </c>
@@ -21037,7 +21039,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="14" thickBot="1">
       <c r="A781" s="15">
         <v>45346</v>
       </c>
@@ -21055,7 +21057,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="14" thickBot="1">
       <c r="A782" s="15">
         <v>45353</v>
       </c>
@@ -21073,7 +21075,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="14" thickBot="1">
       <c r="A783" s="15">
         <v>45360</v>
       </c>
@@ -21091,7 +21093,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="14" thickBot="1">
       <c r="A784" s="15">
         <v>45367</v>
       </c>
@@ -21109,7 +21111,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="14" thickBot="1">
       <c r="A785" s="15">
         <v>45374</v>
       </c>
@@ -21127,7 +21129,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="14" thickBot="1">
       <c r="A786" s="15">
         <v>45381</v>
       </c>
@@ -21145,7 +21147,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="14" thickBot="1">
       <c r="A787" s="15">
         <v>45388</v>
       </c>
@@ -21163,7 +21165,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="14" thickBot="1">
       <c r="A788" s="15">
         <v>45395</v>
       </c>
@@ -21181,7 +21183,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="14" thickBot="1">
       <c r="A789" s="15">
         <v>45402</v>
       </c>
@@ -21199,7 +21201,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="14" thickBot="1">
       <c r="A790" s="15">
         <v>45409</v>
       </c>
@@ -21217,7 +21219,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="14" thickBot="1">
       <c r="A791" s="15">
         <v>45416</v>
       </c>
@@ -21235,7 +21237,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="14" thickBot="1">
       <c r="A792" s="15">
         <v>45423</v>
       </c>
@@ -21253,7 +21255,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="14" thickBot="1">
       <c r="A793" s="15">
         <v>45430</v>
       </c>
@@ -21271,7 +21273,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="14" thickBot="1">
       <c r="A794" s="15">
         <v>45437</v>
       </c>
@@ -21289,7 +21291,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="14" thickBot="1">
       <c r="A795" s="15">
         <v>45444</v>
       </c>
@@ -21307,7 +21309,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="14" thickBot="1">
       <c r="A796" s="15">
         <v>45451</v>
       </c>
@@ -21325,7 +21327,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="14" thickBot="1">
       <c r="A797" s="15">
         <v>45458</v>
       </c>
@@ -21343,7 +21345,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="14" thickBot="1">
       <c r="A798" s="15">
         <v>45465</v>
       </c>
@@ -21361,7 +21363,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="14" thickBot="1">
       <c r="A799" s="15">
         <v>45472</v>
       </c>
@@ -21379,7 +21381,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="14" thickBot="1">
       <c r="A800" s="15">
         <v>45479</v>
       </c>
@@ -21397,7 +21399,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="14" thickBot="1">
       <c r="A801" s="13">
         <v>45486</v>
       </c>
@@ -21415,7 +21417,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="14" thickBot="1">
       <c r="A802" s="15">
         <v>45493</v>
       </c>
@@ -21433,7 +21435,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="14" thickBot="1">
       <c r="A803" s="15">
         <v>45500</v>
       </c>
@@ -21451,7 +21453,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="14" thickBot="1">
       <c r="A804" s="15">
         <v>45507</v>
       </c>
@@ -21469,7 +21471,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="14" thickBot="1">
       <c r="A805" s="15">
         <v>45514</v>
       </c>
@@ -21487,7 +21489,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="14" thickBot="1">
       <c r="A806" s="15">
         <v>45521</v>
       </c>
@@ -21505,7 +21507,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="14" thickBot="1">
       <c r="A807" s="15">
         <v>45528</v>
       </c>
@@ -21523,7 +21525,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="14" thickBot="1">
       <c r="A808" s="15">
         <v>45535</v>
       </c>
@@ -21541,7 +21543,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="14" thickBot="1">
       <c r="A809" s="15">
         <v>45542</v>
       </c>
@@ -21559,7 +21561,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="14" thickBot="1">
       <c r="A810" s="15">
         <v>45549</v>
       </c>
@@ -21577,7 +21579,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="14" thickBot="1">
       <c r="A811" s="15">
         <v>45556</v>
       </c>
@@ -21595,7 +21597,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="14" thickBot="1">
       <c r="A812" s="15">
         <v>45563</v>
       </c>
@@ -21613,7 +21615,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="14" thickBot="1">
       <c r="A813" s="15">
         <v>45570</v>
       </c>
@@ -21631,7 +21633,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="14" thickBot="1">
       <c r="A814" s="15">
         <v>45577</v>
       </c>
@@ -21649,7 +21651,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="14" thickBot="1">
       <c r="A815" s="15">
         <v>45584</v>
       </c>
@@ -21667,7 +21669,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="14" thickBot="1">
       <c r="A816" s="15">
         <v>45591</v>
       </c>
@@ -21685,7 +21687,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="14" thickBot="1">
       <c r="A817" s="15">
         <v>45598</v>
       </c>
@@ -21703,7 +21705,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="14" thickBot="1">
       <c r="A818" s="15">
         <v>45612</v>
       </c>
@@ -21721,7 +21723,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="14" thickBot="1">
       <c r="A819" s="15">
         <v>45619</v>
       </c>
@@ -21739,7 +21741,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="14" thickBot="1">
       <c r="A820" s="15">
         <v>45626</v>
       </c>
@@ -21757,7 +21759,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="14" thickBot="1">
       <c r="A821" s="15">
         <v>45633</v>
       </c>
@@ -21775,7 +21777,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="14" thickBot="1">
       <c r="A822" s="15">
         <v>45640</v>
       </c>
@@ -21793,7 +21795,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="14" thickBot="1">
       <c r="A823" s="15">
         <v>45647</v>
       </c>
@@ -21811,7 +21813,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="14" thickBot="1">
       <c r="A824" s="15">
         <v>45654</v>
       </c>
@@ -21829,7 +21831,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="14" thickBot="1">
       <c r="A825" s="15">
         <v>45661</v>
       </c>
@@ -21847,7 +21849,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="14" thickBot="1">
       <c r="A826" s="13">
         <v>45668</v>
       </c>
@@ -21865,7 +21867,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="14" thickBot="1">
       <c r="A827" s="15">
         <v>45675</v>
       </c>
@@ -21883,7 +21885,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="14" thickBot="1">
       <c r="A828" s="15">
         <v>45682</v>
       </c>
@@ -21901,7 +21903,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="14" thickBot="1">
       <c r="A829" s="15">
         <v>45689</v>
       </c>
@@ -21919,7 +21921,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="14" thickBot="1">
       <c r="A830" s="15">
         <v>45696</v>
       </c>
@@ -21937,7 +21939,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="14" thickBot="1">
       <c r="A831" s="15">
         <v>45703</v>
       </c>
@@ -21955,7 +21957,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="14" thickBot="1">
       <c r="A832" s="15">
         <v>45710</v>
       </c>
@@ -21973,7 +21975,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="14" thickBot="1">
       <c r="A833" s="15">
         <v>45717</v>
       </c>
@@ -21991,7 +21993,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="14" thickBot="1">
       <c r="A834" s="15">
         <v>45724</v>
       </c>
@@ -22024,7 +22026,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="14" thickBot="1">
       <c r="A835" s="15">
         <v>45731</v>
       </c>
@@ -22042,7 +22044,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="14" thickBot="1">
       <c r="A836" s="15">
         <v>45738</v>
       </c>
@@ -22060,7 +22062,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="14" thickBot="1">
       <c r="A837" s="15">
         <v>45745</v>
       </c>
@@ -22078,7 +22080,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="14" thickBot="1">
       <c r="A838" s="15">
         <v>45752</v>
       </c>
@@ -22096,7 +22098,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="14" thickBot="1">
       <c r="A839" s="15">
         <v>45759</v>
       </c>
@@ -22114,7 +22116,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="14" thickBot="1">
       <c r="A840" s="15">
         <v>45766</v>
       </c>
@@ -22132,7 +22134,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="14" thickBot="1">
       <c r="A841" s="15">
         <v>45773</v>
       </c>
@@ -22150,7 +22152,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="14" thickBot="1">
       <c r="A842" s="15">
         <v>45780</v>
       </c>
@@ -22168,7 +22170,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="14" thickBot="1">
       <c r="A843" s="15">
         <v>45787</v>
       </c>
@@ -22186,7 +22188,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="14" thickBot="1">
       <c r="A844" s="15">
         <v>45794</v>
       </c>
@@ -22204,7 +22206,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="14" thickBot="1">
       <c r="A845" s="15">
         <v>45801</v>
       </c>
@@ -22222,7 +22224,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="14" thickBot="1">
       <c r="A846" s="15">
         <v>45808</v>
       </c>
@@ -22240,7 +22242,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="14" thickBot="1">
       <c r="A847" s="15">
         <v>45815</v>
       </c>
@@ -22258,7 +22260,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="14" thickBot="1">
       <c r="A848" s="15">
         <v>45822</v>
       </c>
@@ -22276,7 +22278,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="14" thickBot="1">
       <c r="A849" s="15">
         <v>45829</v>
       </c>
@@ -22294,7 +22296,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="14" thickBot="1">
       <c r="A850" s="15">
         <v>45836</v>
       </c>
@@ -22312,7 +22314,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="14" thickBot="1">
       <c r="A851" s="13">
         <v>45843</v>
       </c>
@@ -22330,7 +22332,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="14" thickBot="1">
       <c r="A852" s="15">
         <v>45850</v>
       </c>
@@ -22348,7 +22350,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="14" thickBot="1">
       <c r="A853" s="15">
         <v>45857</v>
       </c>
@@ -22366,7 +22368,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="14" thickBot="1">
       <c r="A854" s="15">
         <v>45864</v>
       </c>
@@ -22384,7 +22386,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="14" thickBot="1">
       <c r="A855" s="15">
         <v>45871</v>
       </c>
@@ -22402,7 +22404,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="14" thickBot="1">
       <c r="A856" s="15">
         <v>45878</v>
       </c>
@@ -22420,7 +22422,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="14" thickBot="1">
       <c r="A857" s="15">
         <v>45885</v>
       </c>
@@ -22438,7 +22440,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="14" thickBot="1">
       <c r="A858" s="15">
         <v>45892</v>
       </c>
@@ -22456,7 +22458,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="14" thickBot="1">
       <c r="A859" s="15">
         <v>45899</v>
       </c>
@@ -22474,7 +22476,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="14" thickBot="1">
       <c r="A860" s="15">
         <v>45906</v>
       </c>
@@ -22492,7 +22494,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="14" thickBot="1">
       <c r="A861" s="15">
         <v>45913</v>
       </c>
@@ -22510,7 +22512,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="14" thickBot="1">
       <c r="A862" s="15">
         <v>45920</v>
       </c>
@@ -22528,7 +22530,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="14" thickBot="1">
       <c r="A863" s="13">
         <v>45927</v>
       </c>
@@ -22546,7 +22548,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="14" thickBot="1">
       <c r="A864" s="15">
         <v>45934</v>
       </c>
@@ -22564,7 +22566,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="14" thickBot="1">
       <c r="A865" s="15">
         <v>45941</v>
       </c>
@@ -22582,7 +22584,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="14" thickBot="1">
       <c r="A866" s="15">
         <v>45948</v>
       </c>
@@ -22600,7 +22602,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="14" thickBot="1">
       <c r="A867" s="15">
         <v>45955</v>
       </c>
@@ -22618,7 +22620,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="14" thickBot="1">
       <c r="A868" s="15">
         <v>45962</v>
       </c>
@@ -22636,7 +22638,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="14" thickBot="1">
       <c r="A869" s="15">
         <v>45969</v>
       </c>
@@ -22654,7 +22656,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="14" thickBot="1">
       <c r="A870" s="15">
         <v>45976</v>
       </c>
@@ -22672,7 +22674,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="14" thickBot="1">
       <c r="A871" s="15">
         <v>45983</v>
       </c>
@@ -22690,7 +22692,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="14" thickBot="1">
       <c r="A872" s="15">
         <v>45990</v>
       </c>
@@ -22708,7 +22710,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="14" thickBot="1">
       <c r="A873" s="15">
         <v>45997</v>
       </c>
@@ -22726,7 +22728,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="14" thickBot="1">
       <c r="A874" s="15">
         <v>46004</v>
       </c>
@@ -22744,7 +22746,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="14" thickBot="1">
       <c r="A875" s="13">
         <v>46018</v>
       </c>
@@ -22762,7 +22764,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="14" thickBot="1">
       <c r="A876" s="7">
         <v>46025</v>
       </c>
@@ -22780,7 +22782,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="14" thickBot="1">
       <c r="A877" s="13">
         <v>46032</v>
       </c>
@@ -22798,7 +22800,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="14" thickBot="1">
       <c r="A878" s="7">
         <v>46039</v>
       </c>
@@ -22831,7 +22833,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="14" thickBot="1">
       <c r="A879" s="13">
         <v>46046</v>
       </c>
@@ -22864,7 +22866,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="14" thickBot="1">
       <c r="A880" s="13">
         <v>46053</v>
       </c>
@@ -22897,7 +22899,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="14" thickBot="1">
       <c r="A881" s="13">
         <v>46060</v>
       </c>
@@ -22915,7 +22917,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="14" thickBot="1">
       <c r="A882" s="7">
         <v>46067</v>
       </c>
@@ -22948,7 +22950,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="14" thickBot="1">
       <c r="A883" s="13">
         <v>46074</v>
       </c>
@@ -22981,7 +22983,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="14" thickBot="1">
       <c r="A884" s="7">
         <v>46081</v>
       </c>
@@ -22999,7 +23001,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="14" thickBot="1">
       <c r="A885" s="13">
         <v>46088</v>
       </c>
@@ -23032,7 +23034,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5">
       <c r="A886" s="7">
         <v>46102</v>
       </c>
@@ -23065,7 +23067,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5">
       <c r="A887" s="7">
         <v>46109</v>
       </c>
@@ -23098,7 +23100,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5">
       <c r="A888" s="7">
         <v>46116</v>
       </c>
@@ -23131,7 +23133,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5">
       <c r="A889" s="7">
         <v>46123</v>
       </c>
@@ -23160,6 +23162,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E889" s="17">
+        <v>500040</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
@@ -23174,7 +23179,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23185,12 +23190,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23198,7 +23203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23206,7 +23211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9DA03C-B90A-4C2B-AA78-0FC960228101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39E3E47-BC69-43F6-893C-5D7FEE03549C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -189,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -206,68 +206,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3041,6 +3041,9 @@
                 <c:pt idx="887">
                   <c:v>46127</c:v>
                 </c:pt>
+                <c:pt idx="888">
+                  <c:v>46134</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5713,6 +5716,9 @@
                 </c:pt>
                 <c:pt idx="887">
                   <c:v>500040</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>508303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6498,9 +6504,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6538,7 +6544,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6644,7 +6650,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6786,7 +6792,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6794,18 +6800,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E889"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5"/>
+  <dimension ref="A1:E890"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.08984375" style="5"/>
+    <col min="5" max="5" width="12.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6822,7 +6828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>39823</v>
       </c>
@@ -6855,7 +6861,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>39830</v>
       </c>
@@ -6873,7 +6879,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>39837</v>
       </c>
@@ -6891,7 +6897,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>39844</v>
       </c>
@@ -6909,7 +6915,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>39851</v>
       </c>
@@ -6927,7 +6933,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>39858</v>
       </c>
@@ -6945,7 +6951,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>39865</v>
       </c>
@@ -6963,7 +6969,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>39872</v>
       </c>
@@ -6981,7 +6987,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>39879</v>
       </c>
@@ -6999,7 +7005,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>39886</v>
       </c>
@@ -7017,7 +7023,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>39893</v>
       </c>
@@ -7035,7 +7041,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>39900</v>
       </c>
@@ -7053,7 +7059,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>39907</v>
       </c>
@@ -7071,7 +7077,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>39914</v>
       </c>
@@ -7089,7 +7095,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>39921</v>
       </c>
@@ -7107,7 +7113,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>39928</v>
       </c>
@@ -7125,7 +7131,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>39935</v>
       </c>
@@ -7143,7 +7149,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>39942</v>
       </c>
@@ -7161,7 +7167,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>39949</v>
       </c>
@@ -7179,7 +7185,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>39956</v>
       </c>
@@ -7197,7 +7203,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>39963</v>
       </c>
@@ -7215,7 +7221,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>39970</v>
       </c>
@@ -7233,7 +7239,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>39977</v>
       </c>
@@ -7251,7 +7257,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39984</v>
       </c>
@@ -7269,7 +7275,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>39991</v>
       </c>
@@ -7287,7 +7293,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>39998</v>
       </c>
@@ -7305,7 +7311,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>40005</v>
       </c>
@@ -7323,7 +7329,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>40012</v>
       </c>
@@ -7341,7 +7347,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>40019</v>
       </c>
@@ -7359,7 +7365,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>40026</v>
       </c>
@@ -7377,7 +7383,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>40033</v>
       </c>
@@ -7395,7 +7401,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>40040</v>
       </c>
@@ -7413,7 +7419,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>40047</v>
       </c>
@@ -7431,7 +7437,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>40054</v>
       </c>
@@ -7449,7 +7455,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>40061</v>
       </c>
@@ -7467,7 +7473,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>40068</v>
       </c>
@@ -7485,7 +7491,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>40075</v>
       </c>
@@ -7503,7 +7509,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>40082</v>
       </c>
@@ -7521,7 +7527,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>40089</v>
       </c>
@@ -7539,7 +7545,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>40096</v>
       </c>
@@ -7557,7 +7563,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>40103</v>
       </c>
@@ -7575,7 +7581,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>40110</v>
       </c>
@@ -7593,7 +7599,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>40117</v>
       </c>
@@ -7611,7 +7617,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>40124</v>
       </c>
@@ -7629,7 +7635,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>40131</v>
       </c>
@@ -7647,7 +7653,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>40138</v>
       </c>
@@ -7665,7 +7671,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>40145</v>
       </c>
@@ -7683,7 +7689,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>40152</v>
       </c>
@@ -7701,7 +7707,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>40159</v>
       </c>
@@ -7719,7 +7725,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>40166</v>
       </c>
@@ -7737,7 +7743,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>40173</v>
       </c>
@@ -7755,7 +7761,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>40180</v>
       </c>
@@ -7773,7 +7779,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>40187</v>
       </c>
@@ -7791,7 +7797,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>40194</v>
       </c>
@@ -7809,7 +7815,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>40201</v>
       </c>
@@ -7827,7 +7833,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>40208</v>
       </c>
@@ -7845,7 +7851,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>40215</v>
       </c>
@@ -7863,7 +7869,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>40222</v>
       </c>
@@ -7881,7 +7887,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>40229</v>
       </c>
@@ -7899,7 +7905,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>40236</v>
       </c>
@@ -7917,7 +7923,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>40243</v>
       </c>
@@ -7935,7 +7941,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>40250</v>
       </c>
@@ -7953,7 +7959,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>40257</v>
       </c>
@@ -7971,7 +7977,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>40264</v>
       </c>
@@ -7989,7 +7995,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>40271</v>
       </c>
@@ -8022,7 +8028,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>40278</v>
       </c>
@@ -8040,7 +8046,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>40285</v>
       </c>
@@ -8058,7 +8064,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>40292</v>
       </c>
@@ -8076,7 +8082,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>40299</v>
       </c>
@@ -8094,7 +8100,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>40306</v>
       </c>
@@ -8112,7 +8118,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>40313</v>
       </c>
@@ -8130,7 +8136,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>40320</v>
       </c>
@@ -8148,7 +8154,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>40327</v>
       </c>
@@ -8166,7 +8172,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>40334</v>
       </c>
@@ -8184,7 +8190,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>40341</v>
       </c>
@@ -8202,7 +8208,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>40348</v>
       </c>
@@ -8220,7 +8226,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>40355</v>
       </c>
@@ -8238,7 +8244,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>40362</v>
       </c>
@@ -8256,7 +8262,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>40369</v>
       </c>
@@ -8274,7 +8280,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>40376</v>
       </c>
@@ -8292,7 +8298,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>40383</v>
       </c>
@@ -8310,7 +8316,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>40390</v>
       </c>
@@ -8328,7 +8334,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>40397</v>
       </c>
@@ -8346,7 +8352,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>40404</v>
       </c>
@@ -8364,7 +8370,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>40411</v>
       </c>
@@ -8382,7 +8388,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>40418</v>
       </c>
@@ -8400,7 +8406,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>40425</v>
       </c>
@@ -8418,7 +8424,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>40432</v>
       </c>
@@ -8436,7 +8442,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>40439</v>
       </c>
@@ -8454,7 +8460,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>40446</v>
       </c>
@@ -8472,7 +8478,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>40453</v>
       </c>
@@ -8490,7 +8496,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>40460</v>
       </c>
@@ -8508,7 +8514,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="6">
         <v>40467</v>
       </c>
@@ -8526,7 +8532,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="6">
         <v>40474</v>
       </c>
@@ -8544,7 +8550,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="6">
         <v>40481</v>
       </c>
@@ -8562,7 +8568,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>40488</v>
       </c>
@@ -8580,7 +8586,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="6">
         <v>40495</v>
       </c>
@@ -8598,7 +8604,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>40502</v>
       </c>
@@ -8616,7 +8622,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="6">
         <v>40509</v>
       </c>
@@ -8634,7 +8640,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="14" thickBot="1">
+    <row r="101" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6">
         <v>40516</v>
       </c>
@@ -8652,7 +8658,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="14" thickBot="1">
+    <row r="102" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="9">
         <v>40523</v>
       </c>
@@ -8670,7 +8676,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="14" thickBot="1">
+    <row r="103" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="9">
         <v>40530</v>
       </c>
@@ -8688,7 +8694,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="14" thickBot="1">
+    <row r="104" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="9">
         <v>40537</v>
       </c>
@@ -8706,7 +8712,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="14" thickBot="1">
+    <row r="105" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="9">
         <v>40544</v>
       </c>
@@ -8724,7 +8730,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="14" thickBot="1">
+    <row r="106" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="9">
         <v>40551</v>
       </c>
@@ -8742,7 +8748,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="14" thickBot="1">
+    <row r="107" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="9">
         <v>40558</v>
       </c>
@@ -8760,7 +8766,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="14" thickBot="1">
+    <row r="108" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="9">
         <v>40565</v>
       </c>
@@ -8778,7 +8784,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="14" thickBot="1">
+    <row r="109" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="9">
         <v>40572</v>
       </c>
@@ -8796,7 +8802,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="14" thickBot="1">
+    <row r="110" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="9">
         <v>40579</v>
       </c>
@@ -8814,7 +8820,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="14" thickBot="1">
+    <row r="111" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="9">
         <v>40586</v>
       </c>
@@ -8832,7 +8838,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="14" thickBot="1">
+    <row r="112" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="9">
         <v>40593</v>
       </c>
@@ -8850,7 +8856,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="14" thickBot="1">
+    <row r="113" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="9">
         <v>40600</v>
       </c>
@@ -8868,7 +8874,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="14" thickBot="1">
+    <row r="114" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="9">
         <v>40607</v>
       </c>
@@ -8886,7 +8892,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="14" thickBot="1">
+    <row r="115" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="9">
         <v>40614</v>
       </c>
@@ -8904,7 +8910,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="14" thickBot="1">
+    <row r="116" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="9">
         <v>40621</v>
       </c>
@@ -8922,7 +8928,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="14" thickBot="1">
+    <row r="117" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="9">
         <v>40628</v>
       </c>
@@ -8940,7 +8946,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="14" thickBot="1">
+    <row r="118" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="9">
         <v>40635</v>
       </c>
@@ -8958,7 +8964,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="14" thickBot="1">
+    <row r="119" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="9">
         <v>40642</v>
       </c>
@@ -8976,7 +8982,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="14" thickBot="1">
+    <row r="120" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="9">
         <v>40649</v>
       </c>
@@ -8994,7 +9000,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="14" thickBot="1">
+    <row r="121" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="9">
         <v>40656</v>
       </c>
@@ -9012,7 +9018,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="14" thickBot="1">
+    <row r="122" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="9">
         <v>40663</v>
       </c>
@@ -9030,7 +9036,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="14" thickBot="1">
+    <row r="123" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="9">
         <v>40670</v>
       </c>
@@ -9048,7 +9054,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14" thickBot="1">
+    <row r="124" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="9">
         <v>40677</v>
       </c>
@@ -9066,7 +9072,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="14" thickBot="1">
+    <row r="125" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="9">
         <v>40684</v>
       </c>
@@ -9084,7 +9090,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="14" thickBot="1">
+    <row r="126" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>40691</v>
       </c>
@@ -9102,7 +9108,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="14" thickBot="1">
+    <row r="127" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="9">
         <v>40698</v>
       </c>
@@ -9120,7 +9126,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="14" thickBot="1">
+    <row r="128" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="9">
         <v>40705</v>
       </c>
@@ -9138,7 +9144,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="14" thickBot="1">
+    <row r="129" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="9">
         <v>40712</v>
       </c>
@@ -9156,7 +9162,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="14" thickBot="1">
+    <row r="130" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="9">
         <v>40719</v>
       </c>
@@ -9189,7 +9195,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="14" thickBot="1">
+    <row r="131" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="9">
         <v>40726</v>
       </c>
@@ -9207,7 +9213,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14" thickBot="1">
+    <row r="132" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="9">
         <v>40733</v>
       </c>
@@ -9225,7 +9231,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="14" thickBot="1">
+    <row r="133" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="9">
         <v>40740</v>
       </c>
@@ -9243,7 +9249,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="14" thickBot="1">
+    <row r="134" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="9">
         <v>40747</v>
       </c>
@@ -9261,7 +9267,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="14" thickBot="1">
+    <row r="135" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="9">
         <v>40754</v>
       </c>
@@ -9279,7 +9285,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="14" thickBot="1">
+    <row r="136" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="9">
         <v>40761</v>
       </c>
@@ -9297,7 +9303,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="14" thickBot="1">
+    <row r="137" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="9">
         <v>40768</v>
       </c>
@@ -9315,7 +9321,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="14" thickBot="1">
+    <row r="138" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="9">
         <v>40775</v>
       </c>
@@ -9333,7 +9339,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="14" thickBot="1">
+    <row r="139" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="9">
         <v>40782</v>
       </c>
@@ -9351,7 +9357,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="14" thickBot="1">
+    <row r="140" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="9">
         <v>40789</v>
       </c>
@@ -9369,7 +9375,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14" thickBot="1">
+    <row r="141" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="9">
         <v>40796</v>
       </c>
@@ -9387,7 +9393,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="14" thickBot="1">
+    <row r="142" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="9">
         <v>40803</v>
       </c>
@@ -9405,7 +9411,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="14" thickBot="1">
+    <row r="143" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="9">
         <v>40810</v>
       </c>
@@ -9423,7 +9429,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14" thickBot="1">
+    <row r="144" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="9">
         <v>40817</v>
       </c>
@@ -9441,7 +9447,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14" thickBot="1">
+    <row r="145" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="9">
         <v>40824</v>
       </c>
@@ -9459,7 +9465,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14" thickBot="1">
+    <row r="146" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="9">
         <v>40831</v>
       </c>
@@ -9477,7 +9483,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="14" thickBot="1">
+    <row r="147" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="9">
         <v>40838</v>
       </c>
@@ -9495,7 +9501,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="14" thickBot="1">
+    <row r="148" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="9">
         <v>40845</v>
       </c>
@@ -9513,7 +9519,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="14" thickBot="1">
+    <row r="149" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="9">
         <v>40852</v>
       </c>
@@ -9531,7 +9537,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="14" thickBot="1">
+    <row r="150" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="9">
         <v>40859</v>
       </c>
@@ -9549,7 +9555,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="14" thickBot="1">
+    <row r="151" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="11">
         <v>40866</v>
       </c>
@@ -9567,7 +9573,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="14" thickBot="1">
+    <row r="152" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="9">
         <v>40873</v>
       </c>
@@ -9585,7 +9591,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="14" thickBot="1">
+    <row r="153" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="9">
         <v>40880</v>
       </c>
@@ -9603,7 +9609,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="14" thickBot="1">
+    <row r="154" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="9">
         <v>40887</v>
       </c>
@@ -9621,7 +9627,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="14" thickBot="1">
+    <row r="155" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="9">
         <v>40894</v>
       </c>
@@ -9639,7 +9645,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="14" thickBot="1">
+    <row r="156" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="9">
         <v>40901</v>
       </c>
@@ -9657,7 +9663,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="14" thickBot="1">
+    <row r="157" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="9">
         <v>40908</v>
       </c>
@@ -9675,7 +9681,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="14" thickBot="1">
+    <row r="158" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9">
         <v>40915</v>
       </c>
@@ -9693,7 +9699,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="14" thickBot="1">
+    <row r="159" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="9">
         <v>40922</v>
       </c>
@@ -9711,7 +9717,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14" thickBot="1">
+    <row r="160" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="9">
         <v>40929</v>
       </c>
@@ -9729,7 +9735,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="14" thickBot="1">
+    <row r="161" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="9">
         <v>40936</v>
       </c>
@@ -9747,7 +9753,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="14" thickBot="1">
+    <row r="162" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="9">
         <v>40943</v>
       </c>
@@ -9765,7 +9771,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="14" thickBot="1">
+    <row r="163" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="9">
         <v>40950</v>
       </c>
@@ -9783,7 +9789,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="14" thickBot="1">
+    <row r="164" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="9">
         <v>40957</v>
       </c>
@@ -9801,7 +9807,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="14" thickBot="1">
+    <row r="165" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="9">
         <v>40964</v>
       </c>
@@ -9819,7 +9825,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="14" thickBot="1">
+    <row r="166" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="9">
         <v>40971</v>
       </c>
@@ -9837,7 +9843,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="14" thickBot="1">
+    <row r="167" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="9">
         <v>40978</v>
       </c>
@@ -9855,7 +9861,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="14" thickBot="1">
+    <row r="168" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="9">
         <v>40985</v>
       </c>
@@ -9873,7 +9879,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="14" thickBot="1">
+    <row r="169" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="9">
         <v>40992</v>
       </c>
@@ -9891,7 +9897,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="14" thickBot="1">
+    <row r="170" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="9">
         <v>40999</v>
       </c>
@@ -9909,7 +9915,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="14" thickBot="1">
+    <row r="171" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="9">
         <v>41006</v>
       </c>
@@ -9927,7 +9933,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="14" thickBot="1">
+    <row r="172" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="9">
         <v>41013</v>
       </c>
@@ -9945,7 +9951,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="14" thickBot="1">
+    <row r="173" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="9">
         <v>41020</v>
       </c>
@@ -9963,7 +9969,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="14" thickBot="1">
+    <row r="174" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="9">
         <v>41027</v>
       </c>
@@ -9981,7 +9987,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="14" thickBot="1">
+    <row r="175" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="9">
         <v>41034</v>
       </c>
@@ -9999,7 +10005,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="14" thickBot="1">
+    <row r="176" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="11">
         <v>41041</v>
       </c>
@@ -10017,7 +10023,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="14" thickBot="1">
+    <row r="177" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="9">
         <v>41048</v>
       </c>
@@ -10035,7 +10041,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="14" thickBot="1">
+    <row r="178" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="9">
         <v>41055</v>
       </c>
@@ -10053,7 +10059,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="14" thickBot="1">
+    <row r="179" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="9">
         <v>41062</v>
       </c>
@@ -10071,7 +10077,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="14" thickBot="1">
+    <row r="180" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="9">
         <v>41069</v>
       </c>
@@ -10089,7 +10095,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="14" thickBot="1">
+    <row r="181" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="9">
         <v>41076</v>
       </c>
@@ -10107,7 +10113,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="14" thickBot="1">
+    <row r="182" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="9">
         <v>41083</v>
       </c>
@@ -10125,7 +10131,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="14" thickBot="1">
+    <row r="183" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="9">
         <v>41090</v>
       </c>
@@ -10143,7 +10149,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="14" thickBot="1">
+    <row r="184" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="9">
         <v>41097</v>
       </c>
@@ -10161,7 +10167,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="14" thickBot="1">
+    <row r="185" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="9">
         <v>41104</v>
       </c>
@@ -10179,7 +10185,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="14" thickBot="1">
+    <row r="186" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="9">
         <v>41111</v>
       </c>
@@ -10197,7 +10203,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="14" thickBot="1">
+    <row r="187" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="9">
         <v>41118</v>
       </c>
@@ -10215,7 +10221,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="14" thickBot="1">
+    <row r="188" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="9">
         <v>41125</v>
       </c>
@@ -10233,7 +10239,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="14" thickBot="1">
+    <row r="189" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="9">
         <v>41132</v>
       </c>
@@ -10251,7 +10257,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="14" thickBot="1">
+    <row r="190" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="9">
         <v>41139</v>
       </c>
@@ -10269,7 +10275,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="14" thickBot="1">
+    <row r="191" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="9">
         <v>41146</v>
       </c>
@@ -10287,7 +10293,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="14" thickBot="1">
+    <row r="192" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="9">
         <v>41153</v>
       </c>
@@ -10305,7 +10311,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="14" thickBot="1">
+    <row r="193" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="9">
         <v>41160</v>
       </c>
@@ -10323,7 +10329,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="14" thickBot="1">
+    <row r="194" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="9">
         <v>41167</v>
       </c>
@@ -10356,7 +10362,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="14" thickBot="1">
+    <row r="195" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="9">
         <v>41174</v>
       </c>
@@ -10374,7 +10380,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="14" thickBot="1">
+    <row r="196" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="9">
         <v>41181</v>
       </c>
@@ -10392,7 +10398,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="14" thickBot="1">
+    <row r="197" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="9">
         <v>41188</v>
       </c>
@@ -10410,7 +10416,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="14" thickBot="1">
+    <row r="198" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="9">
         <v>41195</v>
       </c>
@@ -10428,7 +10434,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="14" thickBot="1">
+    <row r="199" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="9">
         <v>41202</v>
       </c>
@@ -10446,7 +10452,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="14" thickBot="1">
+    <row r="200" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="9">
         <v>41209</v>
       </c>
@@ -10464,7 +10470,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="14" thickBot="1">
+    <row r="201" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>41216</v>
       </c>
@@ -10482,7 +10488,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="14" thickBot="1">
+    <row r="202" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="9">
         <v>41223</v>
       </c>
@@ -10500,7 +10506,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="14" thickBot="1">
+    <row r="203" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="9">
         <v>41230</v>
       </c>
@@ -10518,7 +10524,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="14" thickBot="1">
+    <row r="204" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="9">
         <v>41237</v>
       </c>
@@ -10536,7 +10542,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="14" thickBot="1">
+    <row r="205" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="9">
         <v>41244</v>
       </c>
@@ -10554,7 +10560,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="14" thickBot="1">
+    <row r="206" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="9">
         <v>41251</v>
       </c>
@@ -10572,7 +10578,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="14" thickBot="1">
+    <row r="207" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="9">
         <v>41258</v>
       </c>
@@ -10590,7 +10596,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="14" thickBot="1">
+    <row r="208" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="9">
         <v>41265</v>
       </c>
@@ -10608,7 +10614,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="14" thickBot="1">
+    <row r="209" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="9">
         <v>41272</v>
       </c>
@@ -10626,7 +10632,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="14" thickBot="1">
+    <row r="210" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="9">
         <v>41279</v>
       </c>
@@ -10644,7 +10650,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="14" thickBot="1">
+    <row r="211" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="9">
         <v>41286</v>
       </c>
@@ -10662,7 +10668,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="14" thickBot="1">
+    <row r="212" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="9">
         <v>41293</v>
       </c>
@@ -10680,7 +10686,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="14" thickBot="1">
+    <row r="213" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="9">
         <v>41300</v>
       </c>
@@ -10698,7 +10704,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="14" thickBot="1">
+    <row r="214" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="9">
         <v>41307</v>
       </c>
@@ -10716,7 +10722,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="14" thickBot="1">
+    <row r="215" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="9">
         <v>41314</v>
       </c>
@@ -10734,7 +10740,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="14" thickBot="1">
+    <row r="216" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="9">
         <v>41321</v>
       </c>
@@ -10752,7 +10758,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="14" thickBot="1">
+    <row r="217" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="9">
         <v>41328</v>
       </c>
@@ -10770,7 +10776,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="14" thickBot="1">
+    <row r="218" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="9">
         <v>41335</v>
       </c>
@@ -10788,7 +10794,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="14" thickBot="1">
+    <row r="219" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="9">
         <v>41342</v>
       </c>
@@ -10806,7 +10812,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="14" thickBot="1">
+    <row r="220" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="9">
         <v>41349</v>
       </c>
@@ -10824,7 +10830,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="14" thickBot="1">
+    <row r="221" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="9">
         <v>41356</v>
       </c>
@@ -10842,7 +10848,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="14" thickBot="1">
+    <row r="222" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="9">
         <v>41363</v>
       </c>
@@ -10860,7 +10866,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="14" thickBot="1">
+    <row r="223" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="9">
         <v>41370</v>
       </c>
@@ -10878,7 +10884,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="14" thickBot="1">
+    <row r="224" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="9">
         <v>41377</v>
       </c>
@@ -10896,7 +10902,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="14" thickBot="1">
+    <row r="225" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="9">
         <v>41384</v>
       </c>
@@ -10914,7 +10920,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="14" thickBot="1">
+    <row r="226" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="11">
         <v>41391</v>
       </c>
@@ -10932,7 +10938,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="14" thickBot="1">
+    <row r="227" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="9">
         <v>41398</v>
       </c>
@@ -10950,7 +10956,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="14" thickBot="1">
+    <row r="228" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="9">
         <v>41405</v>
       </c>
@@ -10968,7 +10974,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="14" thickBot="1">
+    <row r="229" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="9">
         <v>41412</v>
       </c>
@@ -10986,7 +10992,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="14" thickBot="1">
+    <row r="230" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="9">
         <v>41419</v>
       </c>
@@ -11004,7 +11010,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="14" thickBot="1">
+    <row r="231" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="9">
         <v>41426</v>
       </c>
@@ -11022,7 +11028,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="14" thickBot="1">
+    <row r="232" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="9">
         <v>41433</v>
       </c>
@@ -11040,7 +11046,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="14" thickBot="1">
+    <row r="233" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="9">
         <v>41440</v>
       </c>
@@ -11058,7 +11064,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="14" thickBot="1">
+    <row r="234" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="9">
         <v>41447</v>
       </c>
@@ -11076,7 +11082,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="14" thickBot="1">
+    <row r="235" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="9">
         <v>41454</v>
       </c>
@@ -11094,7 +11100,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="14" thickBot="1">
+    <row r="236" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="9">
         <v>41461</v>
       </c>
@@ -11112,7 +11118,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="14" thickBot="1">
+    <row r="237" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="9">
         <v>41468</v>
       </c>
@@ -11130,7 +11136,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="14" thickBot="1">
+    <row r="238" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="9">
         <v>41475</v>
       </c>
@@ -11148,7 +11154,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="14" thickBot="1">
+    <row r="239" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="9">
         <v>41482</v>
       </c>
@@ -11166,7 +11172,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="14" thickBot="1">
+    <row r="240" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="9">
         <v>41489</v>
       </c>
@@ -11184,7 +11190,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="14" thickBot="1">
+    <row r="241" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="9">
         <v>41496</v>
       </c>
@@ -11202,7 +11208,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="14" thickBot="1">
+    <row r="242" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="9">
         <v>41503</v>
       </c>
@@ -11220,7 +11226,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="14" thickBot="1">
+    <row r="243" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="9">
         <v>41510</v>
       </c>
@@ -11238,7 +11244,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="14" thickBot="1">
+    <row r="244" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="9">
         <v>41517</v>
       </c>
@@ -11256,7 +11262,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="14" thickBot="1">
+    <row r="245" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="9">
         <v>41524</v>
       </c>
@@ -11274,7 +11280,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="14" thickBot="1">
+    <row r="246" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="9">
         <v>41531</v>
       </c>
@@ -11292,7 +11298,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="14" thickBot="1">
+    <row r="247" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="9">
         <v>41538</v>
       </c>
@@ -11310,7 +11316,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="14" thickBot="1">
+    <row r="248" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="9">
         <v>41545</v>
       </c>
@@ -11328,7 +11334,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="14" thickBot="1">
+    <row r="249" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="9">
         <v>41552</v>
       </c>
@@ -11346,7 +11352,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="14" thickBot="1">
+    <row r="250" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="9">
         <v>41559</v>
       </c>
@@ -11364,7 +11370,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="14" thickBot="1">
+    <row r="251" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="11">
         <v>41566</v>
       </c>
@@ -11382,7 +11388,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="14" thickBot="1">
+    <row r="252" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="9">
         <v>41573</v>
       </c>
@@ -11400,7 +11406,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="14" thickBot="1">
+    <row r="253" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="9">
         <v>41580</v>
       </c>
@@ -11418,7 +11424,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="14" thickBot="1">
+    <row r="254" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="9">
         <v>41587</v>
       </c>
@@ -11436,7 +11442,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="14" thickBot="1">
+    <row r="255" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="9">
         <v>41594</v>
       </c>
@@ -11454,7 +11460,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="14" thickBot="1">
+    <row r="256" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="9">
         <v>41601</v>
       </c>
@@ -11472,7 +11478,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="14" thickBot="1">
+    <row r="257" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="9">
         <v>41608</v>
       </c>
@@ -11490,7 +11496,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="14" thickBot="1">
+    <row r="258" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="9">
         <v>41615</v>
       </c>
@@ -11523,7 +11529,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="14" thickBot="1">
+    <row r="259" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="9">
         <v>41622</v>
       </c>
@@ -11541,7 +11547,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="14" thickBot="1">
+    <row r="260" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="9">
         <v>41629</v>
       </c>
@@ -11559,7 +11565,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="14" thickBot="1">
+    <row r="261" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="9">
         <v>41636</v>
       </c>
@@ -11577,7 +11583,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="14" thickBot="1">
+    <row r="262" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="9">
         <v>41643</v>
       </c>
@@ -11595,7 +11601,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="14" thickBot="1">
+    <row r="263" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="9">
         <v>41650</v>
       </c>
@@ -11613,7 +11619,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="14" thickBot="1">
+    <row r="264" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="9">
         <v>41657</v>
       </c>
@@ -11631,7 +11637,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="14" thickBot="1">
+    <row r="265" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="9">
         <v>41664</v>
       </c>
@@ -11649,7 +11655,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="14" thickBot="1">
+    <row r="266" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="9">
         <v>41671</v>
       </c>
@@ -11667,7 +11673,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="14" thickBot="1">
+    <row r="267" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="9">
         <v>41678</v>
       </c>
@@ -11685,7 +11691,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="14" thickBot="1">
+    <row r="268" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="9">
         <v>41685</v>
       </c>
@@ -11703,7 +11709,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="14" thickBot="1">
+    <row r="269" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="9">
         <v>41692</v>
       </c>
@@ -11721,7 +11727,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="14" thickBot="1">
+    <row r="270" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="9">
         <v>41699</v>
       </c>
@@ -11739,7 +11745,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="14" thickBot="1">
+    <row r="271" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="9">
         <v>41706</v>
       </c>
@@ -11757,7 +11763,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="14" thickBot="1">
+    <row r="272" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="9">
         <v>41713</v>
       </c>
@@ -11775,7 +11781,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="14" thickBot="1">
+    <row r="273" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="9">
         <v>41720</v>
       </c>
@@ -11793,7 +11799,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="14" thickBot="1">
+    <row r="274" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="9">
         <v>41727</v>
       </c>
@@ -11811,7 +11817,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="14" thickBot="1">
+    <row r="275" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="9">
         <v>41734</v>
       </c>
@@ -11829,7 +11835,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="14" thickBot="1">
+    <row r="276" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="11">
         <v>41741</v>
       </c>
@@ -11847,7 +11853,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14" thickBot="1">
+    <row r="277" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="9">
         <v>41748</v>
       </c>
@@ -11865,7 +11871,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14" thickBot="1">
+    <row r="278" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="9">
         <v>41755</v>
       </c>
@@ -11883,7 +11889,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="14" thickBot="1">
+    <row r="279" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="9">
         <v>41762</v>
       </c>
@@ -11901,7 +11907,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="14" thickBot="1">
+    <row r="280" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="9">
         <v>41769</v>
       </c>
@@ -11919,7 +11925,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="14" thickBot="1">
+    <row r="281" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="9">
         <v>41783</v>
       </c>
@@ -11937,7 +11943,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="14" thickBot="1">
+    <row r="282" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="9">
         <v>41790</v>
       </c>
@@ -11955,7 +11961,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="14" thickBot="1">
+    <row r="283" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="9">
         <v>41797</v>
       </c>
@@ -11973,7 +11979,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="14" thickBot="1">
+    <row r="284" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="9">
         <v>41804</v>
       </c>
@@ -11991,7 +11997,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="14" thickBot="1">
+    <row r="285" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="9">
         <v>41811</v>
       </c>
@@ -12009,7 +12015,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="14" thickBot="1">
+    <row r="286" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="9">
         <v>41818</v>
       </c>
@@ -12027,7 +12033,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="14" thickBot="1">
+    <row r="287" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="9">
         <v>41825</v>
       </c>
@@ -12045,7 +12051,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="14" thickBot="1">
+    <row r="288" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="9">
         <v>41832</v>
       </c>
@@ -12063,7 +12069,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="14" thickBot="1">
+    <row r="289" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="9">
         <v>41839</v>
       </c>
@@ -12081,7 +12087,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="14" thickBot="1">
+    <row r="290" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="9">
         <v>41846</v>
       </c>
@@ -12099,7 +12105,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="14" thickBot="1">
+    <row r="291" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="9">
         <v>41853</v>
       </c>
@@ -12117,7 +12123,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="14" thickBot="1">
+    <row r="292" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="9">
         <v>41860</v>
       </c>
@@ -12135,7 +12141,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="14" thickBot="1">
+    <row r="293" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="9">
         <v>41867</v>
       </c>
@@ -12153,7 +12159,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="14" thickBot="1">
+    <row r="294" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="9">
         <v>41874</v>
       </c>
@@ -12171,7 +12177,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="14" thickBot="1">
+    <row r="295" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="9">
         <v>41881</v>
       </c>
@@ -12189,7 +12195,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="14" thickBot="1">
+    <row r="296" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="9">
         <v>41888</v>
       </c>
@@ -12207,7 +12213,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="14" thickBot="1">
+    <row r="297" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="9">
         <v>41895</v>
       </c>
@@ -12225,7 +12231,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="14" thickBot="1">
+    <row r="298" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="9">
         <v>41902</v>
       </c>
@@ -12243,7 +12249,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="14" thickBot="1">
+    <row r="299" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="9">
         <v>41909</v>
       </c>
@@ -12261,7 +12267,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="14" thickBot="1">
+    <row r="300" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="9">
         <v>41916</v>
       </c>
@@ -12279,7 +12285,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="14" thickBot="1">
+    <row r="301" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="11">
         <v>41923</v>
       </c>
@@ -12297,7 +12303,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="14" thickBot="1">
+    <row r="302" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="9">
         <v>41930</v>
       </c>
@@ -12315,7 +12321,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="14" thickBot="1">
+    <row r="303" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="9">
         <v>41937</v>
       </c>
@@ -12333,7 +12339,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="14" thickBot="1">
+    <row r="304" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="9">
         <v>41944</v>
       </c>
@@ -12351,7 +12357,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="14" thickBot="1">
+    <row r="305" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="9">
         <v>41951</v>
       </c>
@@ -12369,7 +12375,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="14" thickBot="1">
+    <row r="306" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="9">
         <v>41958</v>
       </c>
@@ -12387,7 +12393,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="14" thickBot="1">
+    <row r="307" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="9">
         <v>41965</v>
       </c>
@@ -12405,7 +12411,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="14" thickBot="1">
+    <row r="308" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="9">
         <v>41972</v>
       </c>
@@ -12423,7 +12429,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="14" thickBot="1">
+    <row r="309" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="9">
         <v>41979</v>
       </c>
@@ -12441,7 +12447,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="14" thickBot="1">
+    <row r="310" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="9">
         <v>41986</v>
       </c>
@@ -12459,7 +12465,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="14" thickBot="1">
+    <row r="311" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="9">
         <v>41993</v>
       </c>
@@ -12477,7 +12483,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="14" thickBot="1">
+    <row r="312" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="9">
         <v>42000</v>
       </c>
@@ -12495,7 +12501,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="14" thickBot="1">
+    <row r="313" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="9">
         <v>42007</v>
       </c>
@@ -12513,7 +12519,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="14" thickBot="1">
+    <row r="314" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="9">
         <v>42014</v>
       </c>
@@ -12531,7 +12537,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="14" thickBot="1">
+    <row r="315" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="9">
         <v>42021</v>
       </c>
@@ -12549,7 +12555,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="14" thickBot="1">
+    <row r="316" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="9">
         <v>42028</v>
       </c>
@@ -12567,7 +12573,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="14" thickBot="1">
+    <row r="317" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="9">
         <v>42035</v>
       </c>
@@ -12585,7 +12591,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="14" thickBot="1">
+    <row r="318" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="9">
         <v>42042</v>
       </c>
@@ -12603,7 +12609,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="14" thickBot="1">
+    <row r="319" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="9">
         <v>42049</v>
       </c>
@@ -12621,7 +12627,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="14" thickBot="1">
+    <row r="320" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="9">
         <v>42056</v>
       </c>
@@ -12639,7 +12645,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="14" thickBot="1">
+    <row r="321" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="9">
         <v>42063</v>
       </c>
@@ -12657,7 +12663,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="14" thickBot="1">
+    <row r="322" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="9">
         <v>42070</v>
       </c>
@@ -12690,7 +12696,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="14" thickBot="1">
+    <row r="323" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="9">
         <v>42077</v>
       </c>
@@ -12708,7 +12714,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="14" thickBot="1">
+    <row r="324" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="9">
         <v>42084</v>
       </c>
@@ -12726,7 +12732,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="14" thickBot="1">
+    <row r="325" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="9">
         <v>42091</v>
       </c>
@@ -12744,7 +12750,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="14" thickBot="1">
+    <row r="326" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="11">
         <v>42098</v>
       </c>
@@ -12762,7 +12768,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="14" thickBot="1">
+    <row r="327" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="9">
         <v>42105</v>
       </c>
@@ -12780,7 +12786,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="14" thickBot="1">
+    <row r="328" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="9">
         <v>42112</v>
       </c>
@@ -12798,7 +12804,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="14" thickBot="1">
+    <row r="329" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="9">
         <v>42119</v>
       </c>
@@ -12816,7 +12822,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="14" thickBot="1">
+    <row r="330" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="9">
         <v>42126</v>
       </c>
@@ -12834,7 +12840,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="14" thickBot="1">
+    <row r="331" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="9">
         <v>42133</v>
       </c>
@@ -12852,7 +12858,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="14" thickBot="1">
+    <row r="332" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="9">
         <v>42140</v>
       </c>
@@ -12870,7 +12876,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="14" thickBot="1">
+    <row r="333" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="9">
         <v>42147</v>
       </c>
@@ -12888,7 +12894,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="14" thickBot="1">
+    <row r="334" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="9">
         <v>42154</v>
       </c>
@@ -12906,7 +12912,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="14" thickBot="1">
+    <row r="335" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="9">
         <v>42161</v>
       </c>
@@ -12924,7 +12930,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="14" thickBot="1">
+    <row r="336" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="9">
         <v>42168</v>
       </c>
@@ -12942,7 +12948,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="14" thickBot="1">
+    <row r="337" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="9">
         <v>42175</v>
       </c>
@@ -12960,7 +12966,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="14" thickBot="1">
+    <row r="338" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="9">
         <v>42182</v>
       </c>
@@ -12978,7 +12984,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="14" thickBot="1">
+    <row r="339" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="9">
         <v>42189</v>
       </c>
@@ -12996,7 +13002,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="14" thickBot="1">
+    <row r="340" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="9">
         <v>42196</v>
       </c>
@@ -13014,7 +13020,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="14" thickBot="1">
+    <row r="341" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="9">
         <v>42203</v>
       </c>
@@ -13032,7 +13038,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="14" thickBot="1">
+    <row r="342" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="9">
         <v>42210</v>
       </c>
@@ -13050,7 +13056,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="14" thickBot="1">
+    <row r="343" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="9">
         <v>42217</v>
       </c>
@@ -13068,7 +13074,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="14" thickBot="1">
+    <row r="344" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="9">
         <v>42224</v>
       </c>
@@ -13086,7 +13092,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="14" thickBot="1">
+    <row r="345" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="9">
         <v>42238</v>
       </c>
@@ -13104,7 +13110,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="14" thickBot="1">
+    <row r="346" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="9">
         <v>42245</v>
       </c>
@@ -13122,7 +13128,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="14" thickBot="1">
+    <row r="347" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="9">
         <v>42252</v>
       </c>
@@ -13140,7 +13146,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="14" thickBot="1">
+    <row r="348" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="9">
         <v>42259</v>
       </c>
@@ -13158,7 +13164,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="14" thickBot="1">
+    <row r="349" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="9">
         <v>42266</v>
       </c>
@@ -13176,7 +13182,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="14" thickBot="1">
+    <row r="350" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="9">
         <v>42273</v>
       </c>
@@ -13194,7 +13200,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="14" thickBot="1">
+    <row r="351" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="11">
         <v>42280</v>
       </c>
@@ -13212,7 +13218,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="14" thickBot="1">
+    <row r="352" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="9">
         <v>42287</v>
       </c>
@@ -13230,7 +13236,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="14" thickBot="1">
+    <row r="353" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="9">
         <v>42294</v>
       </c>
@@ -13248,7 +13254,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="14" thickBot="1">
+    <row r="354" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="9">
         <v>42301</v>
       </c>
@@ -13266,7 +13272,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="14" thickBot="1">
+    <row r="355" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="9">
         <v>42308</v>
       </c>
@@ -13284,7 +13290,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="14" thickBot="1">
+    <row r="356" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="9">
         <v>42315</v>
       </c>
@@ -13302,7 +13308,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="14" thickBot="1">
+    <row r="357" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="9">
         <v>42322</v>
       </c>
@@ -13320,7 +13326,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="14" thickBot="1">
+    <row r="358" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="9">
         <v>42336</v>
       </c>
@@ -13338,7 +13344,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="14" thickBot="1">
+    <row r="359" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="9">
         <v>42343</v>
       </c>
@@ -13356,7 +13362,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="14" thickBot="1">
+    <row r="360" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="9">
         <v>42350</v>
       </c>
@@ -13374,7 +13380,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="14" thickBot="1">
+    <row r="361" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="9">
         <v>42357</v>
       </c>
@@ -13392,7 +13398,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="14" thickBot="1">
+    <row r="362" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="9">
         <v>42364</v>
       </c>
@@ -13410,7 +13416,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="14" thickBot="1">
+    <row r="363" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="9">
         <v>42371</v>
       </c>
@@ -13428,7 +13434,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="14" thickBot="1">
+    <row r="364" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="9">
         <v>42378</v>
       </c>
@@ -13446,7 +13452,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="14" thickBot="1">
+    <row r="365" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="9">
         <v>42385</v>
       </c>
@@ -13464,7 +13470,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="14" thickBot="1">
+    <row r="366" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="9">
         <v>42392</v>
       </c>
@@ -13482,7 +13488,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="14" thickBot="1">
+    <row r="367" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="9">
         <v>42399</v>
       </c>
@@ -13500,7 +13506,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="14" thickBot="1">
+    <row r="368" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="9">
         <v>42406</v>
       </c>
@@ -13518,7 +13524,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="14" thickBot="1">
+    <row r="369" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="9">
         <v>42413</v>
       </c>
@@ -13536,7 +13542,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="14" thickBot="1">
+    <row r="370" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="9">
         <v>42420</v>
       </c>
@@ -13554,7 +13560,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="14" thickBot="1">
+    <row r="371" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="9">
         <v>42427</v>
       </c>
@@ -13572,7 +13578,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="14" thickBot="1">
+    <row r="372" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="9">
         <v>42434</v>
       </c>
@@ -13590,7 +13596,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="14" thickBot="1">
+    <row r="373" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="9">
         <v>42441</v>
       </c>
@@ -13608,7 +13614,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="14" thickBot="1">
+    <row r="374" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="9">
         <v>42448</v>
       </c>
@@ -13626,7 +13632,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="14" thickBot="1">
+    <row r="375" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="9">
         <v>42455</v>
       </c>
@@ -13644,7 +13650,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="14" thickBot="1">
+    <row r="376" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="11">
         <v>42462</v>
       </c>
@@ -13662,7 +13668,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="14" thickBot="1">
+    <row r="377" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="9">
         <v>42469</v>
       </c>
@@ -13680,7 +13686,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="14" thickBot="1">
+    <row r="378" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="9">
         <v>42476</v>
       </c>
@@ -13698,7 +13704,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="14" thickBot="1">
+    <row r="379" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="9">
         <v>42483</v>
       </c>
@@ -13716,7 +13722,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="14" thickBot="1">
+    <row r="380" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="9">
         <v>42490</v>
       </c>
@@ -13734,7 +13740,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="14" thickBot="1">
+    <row r="381" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="9">
         <v>42497</v>
       </c>
@@ -13752,7 +13758,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="14" thickBot="1">
+    <row r="382" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="9">
         <v>42504</v>
       </c>
@@ -13770,7 +13776,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="14" thickBot="1">
+    <row r="383" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="9">
         <v>42511</v>
       </c>
@@ -13788,7 +13794,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="14" thickBot="1">
+    <row r="384" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="9">
         <v>42518</v>
       </c>
@@ -13806,7 +13812,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="14" thickBot="1">
+    <row r="385" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="9">
         <v>42525</v>
       </c>
@@ -13824,7 +13830,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="14" thickBot="1">
+    <row r="386" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="9">
         <v>42532</v>
       </c>
@@ -13857,7 +13863,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="14" thickBot="1">
+    <row r="387" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="9">
         <v>42539</v>
       </c>
@@ -13875,7 +13881,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="14" thickBot="1">
+    <row r="388" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="9">
         <v>42546</v>
       </c>
@@ -13893,7 +13899,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="14" thickBot="1">
+    <row r="389" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="9">
         <v>42553</v>
       </c>
@@ -13911,7 +13917,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="14" thickBot="1">
+    <row r="390" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="9">
         <v>42560</v>
       </c>
@@ -13929,7 +13935,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="14" thickBot="1">
+    <row r="391" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="9">
         <v>42567</v>
       </c>
@@ -13947,7 +13953,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="14" thickBot="1">
+    <row r="392" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="9">
         <v>42574</v>
       </c>
@@ -13965,7 +13971,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="14" thickBot="1">
+    <row r="393" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="9">
         <v>42581</v>
       </c>
@@ -13983,7 +13989,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="14" thickBot="1">
+    <row r="394" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="9">
         <v>42588</v>
       </c>
@@ -14001,7 +14007,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="14" thickBot="1">
+    <row r="395" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="9">
         <v>42595</v>
       </c>
@@ -14019,7 +14025,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="14" thickBot="1">
+    <row r="396" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="9">
         <v>42602</v>
       </c>
@@ -14037,7 +14043,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="14" thickBot="1">
+    <row r="397" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="9">
         <v>42609</v>
       </c>
@@ -14055,7 +14061,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="14" thickBot="1">
+    <row r="398" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="9">
         <v>42616</v>
       </c>
@@ -14073,7 +14079,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="14" thickBot="1">
+    <row r="399" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="9">
         <v>42623</v>
       </c>
@@ -14091,7 +14097,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="14" thickBot="1">
+    <row r="400" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="9">
         <v>42630</v>
       </c>
@@ -14109,7 +14115,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="14" thickBot="1">
+    <row r="401" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="11">
         <v>42637</v>
       </c>
@@ -14127,7 +14133,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="14" thickBot="1">
+    <row r="402" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="9">
         <v>42644</v>
       </c>
@@ -14145,7 +14151,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="14" thickBot="1">
+    <row r="403" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="9">
         <v>42651</v>
       </c>
@@ -14163,7 +14169,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="14" thickBot="1">
+    <row r="404" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="9">
         <v>42658</v>
       </c>
@@ -14181,7 +14187,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="14" thickBot="1">
+    <row r="405" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="9">
         <v>42665</v>
       </c>
@@ -14199,7 +14205,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="14" thickBot="1">
+    <row r="406" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="9">
         <v>42672</v>
       </c>
@@ -14217,7 +14223,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="14" thickBot="1">
+    <row r="407" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="9">
         <v>42679</v>
       </c>
@@ -14235,7 +14241,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="14" thickBot="1">
+    <row r="408" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="9">
         <v>42686</v>
       </c>
@@ -14253,7 +14259,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="14" thickBot="1">
+    <row r="409" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="9">
         <v>42693</v>
       </c>
@@ -14271,7 +14277,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="14" thickBot="1">
+    <row r="410" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="9">
         <v>42700</v>
       </c>
@@ -14289,7 +14295,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="14" thickBot="1">
+    <row r="411" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="9">
         <v>42707</v>
       </c>
@@ -14307,7 +14313,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="14" thickBot="1">
+    <row r="412" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="9">
         <v>42714</v>
       </c>
@@ -14325,7 +14331,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="14" thickBot="1">
+    <row r="413" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="9">
         <v>42721</v>
       </c>
@@ -14343,7 +14349,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="14" thickBot="1">
+    <row r="414" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="9">
         <v>42728</v>
       </c>
@@ -14361,7 +14367,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="14" thickBot="1">
+    <row r="415" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="9">
         <v>42735</v>
       </c>
@@ -14379,7 +14385,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="14" thickBot="1">
+    <row r="416" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="9">
         <v>42742</v>
       </c>
@@ -14397,7 +14403,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="14" thickBot="1">
+    <row r="417" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="9">
         <v>42749</v>
       </c>
@@ -14415,7 +14421,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="14" thickBot="1">
+    <row r="418" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="9">
         <v>42756</v>
       </c>
@@ -14433,7 +14439,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="14" thickBot="1">
+    <row r="419" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="9">
         <v>42763</v>
       </c>
@@ -14451,7 +14457,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="14" thickBot="1">
+    <row r="420" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="9">
         <v>42770</v>
       </c>
@@ -14469,7 +14475,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="14" thickBot="1">
+    <row r="421" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="9">
         <v>42777</v>
       </c>
@@ -14487,7 +14493,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="14" thickBot="1">
+    <row r="422" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="9">
         <v>42784</v>
       </c>
@@ -14505,7 +14511,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="14" thickBot="1">
+    <row r="423" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="9">
         <v>42791</v>
       </c>
@@ -14523,7 +14529,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="14" thickBot="1">
+    <row r="424" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="9">
         <v>42798</v>
       </c>
@@ -14541,7 +14547,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="14" thickBot="1">
+    <row r="425" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="9">
         <v>42805</v>
       </c>
@@ -14559,7 +14565,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="14" thickBot="1">
+    <row r="426" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="11">
         <v>42812</v>
       </c>
@@ -14577,7 +14583,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="14" thickBot="1">
+    <row r="427" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="9">
         <v>42819</v>
       </c>
@@ -14595,7 +14601,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="14" thickBot="1">
+    <row r="428" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="9">
         <v>42826</v>
       </c>
@@ -14613,7 +14619,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="14" thickBot="1">
+    <row r="429" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="9">
         <v>42833</v>
       </c>
@@ -14631,7 +14637,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="14" thickBot="1">
+    <row r="430" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="9">
         <v>42840</v>
       </c>
@@ -14649,7 +14655,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="14" thickBot="1">
+    <row r="431" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="9">
         <v>42847</v>
       </c>
@@ -14667,7 +14673,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="14" thickBot="1">
+    <row r="432" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="9">
         <v>42854</v>
       </c>
@@ -14685,7 +14691,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="14" thickBot="1">
+    <row r="433" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="9">
         <v>42861</v>
       </c>
@@ -14703,7 +14709,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="14" thickBot="1">
+    <row r="434" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="9">
         <v>42868</v>
       </c>
@@ -14721,7 +14727,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="14" thickBot="1">
+    <row r="435" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="9">
         <v>42875</v>
       </c>
@@ -14739,7 +14745,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="14" thickBot="1">
+    <row r="436" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="9">
         <v>42882</v>
       </c>
@@ -14757,7 +14763,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="14" thickBot="1">
+    <row r="437" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="9">
         <v>42889</v>
       </c>
@@ -14775,7 +14781,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="14" thickBot="1">
+    <row r="438" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="9">
         <v>42896</v>
       </c>
@@ -14793,7 +14799,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="14" thickBot="1">
+    <row r="439" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="9">
         <v>42903</v>
       </c>
@@ -14811,7 +14817,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="14" thickBot="1">
+    <row r="440" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="9">
         <v>42910</v>
       </c>
@@ -14829,7 +14835,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="14" thickBot="1">
+    <row r="441" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="9">
         <v>42917</v>
       </c>
@@ -14847,7 +14853,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="14" thickBot="1">
+    <row r="442" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="9">
         <v>42924</v>
       </c>
@@ -14865,7 +14871,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="14" thickBot="1">
+    <row r="443" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="9">
         <v>42931</v>
       </c>
@@ -14883,7 +14889,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="14" thickBot="1">
+    <row r="444" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="9">
         <v>42938</v>
       </c>
@@ -14901,7 +14907,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="14" thickBot="1">
+    <row r="445" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="9">
         <v>42945</v>
       </c>
@@ -14919,7 +14925,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="14" thickBot="1">
+    <row r="446" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="9">
         <v>42952</v>
       </c>
@@ -14937,7 +14943,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="14" thickBot="1">
+    <row r="447" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="9">
         <v>42959</v>
       </c>
@@ -14955,7 +14961,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="14" thickBot="1">
+    <row r="448" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="9">
         <v>42966</v>
       </c>
@@ -14973,7 +14979,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="14" thickBot="1">
+    <row r="449" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="9">
         <v>42973</v>
       </c>
@@ -14991,7 +14997,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="14" thickBot="1">
+    <row r="450" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="9">
         <v>42980</v>
       </c>
@@ -15024,7 +15030,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="14" thickBot="1">
+    <row r="451" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="11">
         <v>42987</v>
       </c>
@@ -15042,7 +15048,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="14" thickBot="1">
+    <row r="452" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="9">
         <v>42994</v>
       </c>
@@ -15060,7 +15066,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="14" thickBot="1">
+    <row r="453" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="9">
         <v>43001</v>
       </c>
@@ -15078,7 +15084,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="14" thickBot="1">
+    <row r="454" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="9">
         <v>43008</v>
       </c>
@@ -15096,7 +15102,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="14" thickBot="1">
+    <row r="455" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="9">
         <v>43015</v>
       </c>
@@ -15114,7 +15120,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="14" thickBot="1">
+    <row r="456" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="9">
         <v>43022</v>
       </c>
@@ -15132,7 +15138,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="14" thickBot="1">
+    <row r="457" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="9">
         <v>43029</v>
       </c>
@@ -15150,7 +15156,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="14" thickBot="1">
+    <row r="458" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="9">
         <v>43036</v>
       </c>
@@ -15168,7 +15174,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="14" thickBot="1">
+    <row r="459" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="9">
         <v>43043</v>
       </c>
@@ -15186,7 +15192,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="14" thickBot="1">
+    <row r="460" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="9">
         <v>43050</v>
       </c>
@@ -15204,7 +15210,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="14" thickBot="1">
+    <row r="461" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="9">
         <v>43057</v>
       </c>
@@ -15222,7 +15228,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="14" thickBot="1">
+    <row r="462" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="9">
         <v>43064</v>
       </c>
@@ -15240,7 +15246,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="14" thickBot="1">
+    <row r="463" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="9">
         <v>43071</v>
       </c>
@@ -15258,7 +15264,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="14" thickBot="1">
+    <row r="464" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="9">
         <v>43078</v>
       </c>
@@ -15276,7 +15282,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="14" thickBot="1">
+    <row r="465" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="9">
         <v>43085</v>
       </c>
@@ -15294,7 +15300,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="14" thickBot="1">
+    <row r="466" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="9">
         <v>43092</v>
       </c>
@@ -15312,7 +15318,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="14" thickBot="1">
+    <row r="467" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="9">
         <v>43099</v>
       </c>
@@ -15330,7 +15336,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="14" thickBot="1">
+    <row r="468" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="9">
         <v>43113</v>
       </c>
@@ -15348,7 +15354,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="14" thickBot="1">
+    <row r="469" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="9">
         <v>43120</v>
       </c>
@@ -15366,7 +15372,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="14" thickBot="1">
+    <row r="470" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="9">
         <v>43127</v>
       </c>
@@ -15384,7 +15390,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="14" thickBot="1">
+    <row r="471" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="9">
         <v>43134</v>
       </c>
@@ -15402,7 +15408,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="14" thickBot="1">
+    <row r="472" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="9">
         <v>43141</v>
       </c>
@@ -15420,7 +15426,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="14" thickBot="1">
+    <row r="473" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="9">
         <v>43148</v>
       </c>
@@ -15438,7 +15444,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="14" thickBot="1">
+    <row r="474" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="9">
         <v>43155</v>
       </c>
@@ -15456,7 +15462,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="14" thickBot="1">
+    <row r="475" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="9">
         <v>43162</v>
       </c>
@@ -15474,7 +15480,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="14" thickBot="1">
+    <row r="476" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="11">
         <v>43169</v>
       </c>
@@ -15492,7 +15498,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="14" thickBot="1">
+    <row r="477" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="9">
         <v>43176</v>
       </c>
@@ -15510,7 +15516,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="14" thickBot="1">
+    <row r="478" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="9">
         <v>43183</v>
       </c>
@@ -15528,7 +15534,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="14" thickBot="1">
+    <row r="479" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="9">
         <v>43190</v>
       </c>
@@ -15546,7 +15552,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="14" thickBot="1">
+    <row r="480" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="9">
         <v>43197</v>
       </c>
@@ -15564,7 +15570,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="14" thickBot="1">
+    <row r="481" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="9">
         <v>43204</v>
       </c>
@@ -15582,7 +15588,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="14" thickBot="1">
+    <row r="482" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="9">
         <v>43211</v>
       </c>
@@ -15600,7 +15606,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="14" thickBot="1">
+    <row r="483" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="9">
         <v>43218</v>
       </c>
@@ -15618,7 +15624,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="14" thickBot="1">
+    <row r="484" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="9">
         <v>43225</v>
       </c>
@@ -15636,7 +15642,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="14" thickBot="1">
+    <row r="485" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="9">
         <v>43232</v>
       </c>
@@ -15654,7 +15660,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="14" thickBot="1">
+    <row r="486" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="9">
         <v>43239</v>
       </c>
@@ -15672,7 +15678,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="14" thickBot="1">
+    <row r="487" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="9">
         <v>43246</v>
       </c>
@@ -15690,7 +15696,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="14" thickBot="1">
+    <row r="488" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="9">
         <v>43253</v>
       </c>
@@ -15708,7 +15714,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="14" thickBot="1">
+    <row r="489" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="9">
         <v>43260</v>
       </c>
@@ -15726,7 +15732,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="14" thickBot="1">
+    <row r="490" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="9">
         <v>43267</v>
       </c>
@@ -15744,7 +15750,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="14" thickBot="1">
+    <row r="491" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="9">
         <v>43274</v>
       </c>
@@ -15762,7 +15768,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="14" thickBot="1">
+    <row r="492" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="9">
         <v>43281</v>
       </c>
@@ -15780,7 +15786,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="14" thickBot="1">
+    <row r="493" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="9">
         <v>43288</v>
       </c>
@@ -15798,7 +15804,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="14" thickBot="1">
+    <row r="494" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="9">
         <v>43295</v>
       </c>
@@ -15816,7 +15822,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="14" thickBot="1">
+    <row r="495" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="9">
         <v>43302</v>
       </c>
@@ -15834,7 +15840,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="14" thickBot="1">
+    <row r="496" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="9">
         <v>43309</v>
       </c>
@@ -15852,7 +15858,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="14" thickBot="1">
+    <row r="497" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="9">
         <v>43316</v>
       </c>
@@ -15870,7 +15876,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="14" thickBot="1">
+    <row r="498" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="9">
         <v>43323</v>
       </c>
@@ -15888,7 +15894,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="14" thickBot="1">
+    <row r="499" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="9">
         <v>43330</v>
       </c>
@@ -15906,7 +15912,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="14" thickBot="1">
+    <row r="500" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="9">
         <v>43337</v>
       </c>
@@ -15924,7 +15930,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="14" thickBot="1">
+    <row r="501" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="11">
         <v>43344</v>
       </c>
@@ -15942,7 +15948,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="14" thickBot="1">
+    <row r="502" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="9">
         <v>43351</v>
       </c>
@@ -15960,7 +15966,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="14" thickBot="1">
+    <row r="503" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="9">
         <v>43358</v>
       </c>
@@ -15978,7 +15984,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="14" thickBot="1">
+    <row r="504" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="9">
         <v>43365</v>
       </c>
@@ -15996,7 +16002,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="14" thickBot="1">
+    <row r="505" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="9">
         <v>43372</v>
       </c>
@@ -16014,7 +16020,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="14" thickBot="1">
+    <row r="506" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="9">
         <v>43379</v>
       </c>
@@ -16032,7 +16038,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="14" thickBot="1">
+    <row r="507" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="9">
         <v>43386</v>
       </c>
@@ -16050,7 +16056,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="14" thickBot="1">
+    <row r="508" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="9">
         <v>43393</v>
       </c>
@@ -16068,7 +16074,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="14" thickBot="1">
+    <row r="509" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="9">
         <v>43400</v>
       </c>
@@ -16086,7 +16092,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="14" thickBot="1">
+    <row r="510" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="9">
         <v>43407</v>
       </c>
@@ -16104,7 +16110,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="14" thickBot="1">
+    <row r="511" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="9">
         <v>43414</v>
       </c>
@@ -16122,7 +16128,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="14" thickBot="1">
+    <row r="512" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="9">
         <v>43421</v>
       </c>
@@ -16140,7 +16146,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="14" thickBot="1">
+    <row r="513" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="9">
         <v>43428</v>
       </c>
@@ -16158,7 +16164,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="14" thickBot="1">
+    <row r="514" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="9">
         <v>43435</v>
       </c>
@@ -16191,7 +16197,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="14" thickBot="1">
+    <row r="515" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="9">
         <v>43442</v>
       </c>
@@ -16209,7 +16215,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="14" thickBot="1">
+    <row r="516" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="9">
         <v>43449</v>
       </c>
@@ -16227,7 +16233,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="14" thickBot="1">
+    <row r="517" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="9">
         <v>43456</v>
       </c>
@@ -16245,7 +16251,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="14" thickBot="1">
+    <row r="518" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="9">
         <v>43463</v>
       </c>
@@ -16263,7 +16269,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="14" thickBot="1">
+    <row r="519" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="9">
         <v>43470</v>
       </c>
@@ -16281,7 +16287,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="14" thickBot="1">
+    <row r="520" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="9">
         <v>43477</v>
       </c>
@@ -16299,7 +16305,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="14" thickBot="1">
+    <row r="521" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="9">
         <v>43484</v>
       </c>
@@ -16317,7 +16323,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="14" thickBot="1">
+    <row r="522" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="9">
         <v>43491</v>
       </c>
@@ -16335,7 +16341,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="14" thickBot="1">
+    <row r="523" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="9">
         <v>43498</v>
       </c>
@@ -16353,7 +16359,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="14" thickBot="1">
+    <row r="524" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="9">
         <v>43505</v>
       </c>
@@ -16371,7 +16377,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="14" thickBot="1">
+    <row r="525" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="9">
         <v>43512</v>
       </c>
@@ -16389,7 +16395,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="14" thickBot="1">
+    <row r="526" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="11">
         <v>43519</v>
       </c>
@@ -16407,7 +16413,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="14" thickBot="1">
+    <row r="527" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="9">
         <v>43526</v>
       </c>
@@ -16425,7 +16431,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="14" thickBot="1">
+    <row r="528" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="9">
         <v>43533</v>
       </c>
@@ -16443,7 +16449,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="14" thickBot="1">
+    <row r="529" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="9">
         <v>43540</v>
       </c>
@@ -16461,7 +16467,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="14" thickBot="1">
+    <row r="530" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="9">
         <v>43547</v>
       </c>
@@ -16479,7 +16485,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="14" thickBot="1">
+    <row r="531" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="9">
         <v>43554</v>
       </c>
@@ -16497,7 +16503,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="14" thickBot="1">
+    <row r="532" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="9">
         <v>43561</v>
       </c>
@@ -16515,7 +16521,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="14" thickBot="1">
+    <row r="533" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="9">
         <v>43568</v>
       </c>
@@ -16533,7 +16539,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="14" thickBot="1">
+    <row r="534" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="9">
         <v>43575</v>
       </c>
@@ -16551,7 +16557,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="14" thickBot="1">
+    <row r="535" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="9">
         <v>43582</v>
       </c>
@@ -16569,7 +16575,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="14" thickBot="1">
+    <row r="536" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="9">
         <v>43589</v>
       </c>
@@ -16587,7 +16593,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="14" thickBot="1">
+    <row r="537" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="9">
         <v>43596</v>
       </c>
@@ -16605,7 +16611,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="14" thickBot="1">
+    <row r="538" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="9">
         <v>43603</v>
       </c>
@@ -16623,7 +16629,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="14" thickBot="1">
+    <row r="539" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="9">
         <v>43610</v>
       </c>
@@ -16641,7 +16647,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="14" thickBot="1">
+    <row r="540" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="9">
         <v>43617</v>
       </c>
@@ -16659,7 +16665,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="14" thickBot="1">
+    <row r="541" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="9">
         <v>43624</v>
       </c>
@@ -16677,7 +16683,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="14" thickBot="1">
+    <row r="542" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="9">
         <v>43631</v>
       </c>
@@ -16695,7 +16701,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="14" thickBot="1">
+    <row r="543" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="9">
         <v>43638</v>
       </c>
@@ -16713,7 +16719,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="14" thickBot="1">
+    <row r="544" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="9">
         <v>43645</v>
       </c>
@@ -16731,7 +16737,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="14" thickBot="1">
+    <row r="545" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="9">
         <v>43652</v>
       </c>
@@ -16749,7 +16755,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="14" thickBot="1">
+    <row r="546" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="9">
         <v>43659</v>
       </c>
@@ -16767,7 +16773,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="14" thickBot="1">
+    <row r="547" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="9">
         <v>43666</v>
       </c>
@@ -16785,7 +16791,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="14" thickBot="1">
+    <row r="548" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="9">
         <v>43673</v>
       </c>
@@ -16803,7 +16809,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="14" thickBot="1">
+    <row r="549" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="9">
         <v>43680</v>
       </c>
@@ -16821,7 +16827,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="14" thickBot="1">
+    <row r="550" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="9">
         <v>43687</v>
       </c>
@@ -16839,7 +16845,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="14" thickBot="1">
+    <row r="551" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="11">
         <v>43694</v>
       </c>
@@ -16857,7 +16863,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="14" thickBot="1">
+    <row r="552" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="9">
         <v>43701</v>
       </c>
@@ -16875,7 +16881,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="14" thickBot="1">
+    <row r="553" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="9">
         <v>43708</v>
       </c>
@@ -16893,7 +16899,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="14" thickBot="1">
+    <row r="554" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="9">
         <v>43715</v>
       </c>
@@ -16911,7 +16917,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="14" thickBot="1">
+    <row r="555" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="9">
         <v>43722</v>
       </c>
@@ -16929,7 +16935,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="14" thickBot="1">
+    <row r="556" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="9">
         <v>43729</v>
       </c>
@@ -16947,7 +16953,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="14" thickBot="1">
+    <row r="557" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="9">
         <v>43736</v>
       </c>
@@ -16965,7 +16971,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="14" thickBot="1">
+    <row r="558" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="9">
         <v>43743</v>
       </c>
@@ -16983,7 +16989,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="14" thickBot="1">
+    <row r="559" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="9">
         <v>43750</v>
       </c>
@@ -17001,7 +17007,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="14" thickBot="1">
+    <row r="560" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="9">
         <v>43757</v>
       </c>
@@ -17019,7 +17025,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="14" thickBot="1">
+    <row r="561" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="9">
         <v>43764</v>
       </c>
@@ -17037,7 +17043,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="14" thickBot="1">
+    <row r="562" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="9">
         <v>43771</v>
       </c>
@@ -17055,7 +17061,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="14" thickBot="1">
+    <row r="563" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="9">
         <v>43778</v>
       </c>
@@ -17073,7 +17079,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="14" thickBot="1">
+    <row r="564" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="9">
         <v>43785</v>
       </c>
@@ -17091,7 +17097,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="14" thickBot="1">
+    <row r="565" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="9">
         <v>43792</v>
       </c>
@@ -17109,7 +17115,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="14" thickBot="1">
+    <row r="566" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="9">
         <v>43813</v>
       </c>
@@ -17127,7 +17133,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="14" thickBot="1">
+    <row r="567" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="9">
         <v>43820</v>
       </c>
@@ -17145,7 +17151,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="14" thickBot="1">
+    <row r="568" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="9">
         <v>43827</v>
       </c>
@@ -17163,7 +17169,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="14" thickBot="1">
+    <row r="569" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="9">
         <v>43834</v>
       </c>
@@ -17181,7 +17187,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="14" thickBot="1">
+    <row r="570" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="9">
         <v>43841</v>
       </c>
@@ -17199,7 +17205,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="14" thickBot="1">
+    <row r="571" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="9">
         <v>43848</v>
       </c>
@@ -17217,7 +17223,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="14" thickBot="1">
+    <row r="572" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="9">
         <v>43855</v>
       </c>
@@ -17235,7 +17241,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="14" thickBot="1">
+    <row r="573" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="9">
         <v>43862</v>
       </c>
@@ -17253,7 +17259,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="14" thickBot="1">
+    <row r="574" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="9">
         <v>43869</v>
       </c>
@@ -17271,7 +17277,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="14" thickBot="1">
+    <row r="575" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="9">
         <v>43876</v>
       </c>
@@ -17289,7 +17295,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="14" thickBot="1">
+    <row r="576" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="11">
         <v>43883</v>
       </c>
@@ -17307,7 +17313,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="14" thickBot="1">
+    <row r="577" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="9">
         <v>43890</v>
       </c>
@@ -17325,7 +17331,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="14" thickBot="1">
+    <row r="578" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="9">
         <v>43897</v>
       </c>
@@ -17358,7 +17364,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="14" thickBot="1">
+    <row r="579" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="9">
         <v>43904</v>
       </c>
@@ -17376,7 +17382,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="14" thickBot="1">
+    <row r="580" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="9">
         <v>43911</v>
       </c>
@@ -17394,7 +17400,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="14" thickBot="1">
+    <row r="581" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="9">
         <v>43918</v>
       </c>
@@ -17412,7 +17418,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="14" thickBot="1">
+    <row r="582" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="9">
         <v>43925</v>
       </c>
@@ -17430,7 +17436,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="14" thickBot="1">
+    <row r="583" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="9">
         <v>43932</v>
       </c>
@@ -17448,7 +17454,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="14" thickBot="1">
+    <row r="584" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="9">
         <v>43939</v>
       </c>
@@ -17466,7 +17472,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="14" thickBot="1">
+    <row r="585" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="9">
         <v>43946</v>
       </c>
@@ -17484,7 +17490,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="14" thickBot="1">
+    <row r="586" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="9">
         <v>43953</v>
       </c>
@@ -17502,7 +17508,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="14" thickBot="1">
+    <row r="587" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="9">
         <v>43960</v>
       </c>
@@ -17520,7 +17526,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="14" thickBot="1">
+    <row r="588" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="9">
         <v>43967</v>
       </c>
@@ -17538,7 +17544,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="14" thickBot="1">
+    <row r="589" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="9">
         <v>43974</v>
       </c>
@@ -17556,7 +17562,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="14" thickBot="1">
+    <row r="590" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="9">
         <v>43981</v>
       </c>
@@ -17574,7 +17580,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="14" thickBot="1">
+    <row r="591" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="9">
         <v>43988</v>
       </c>
@@ -17592,7 +17598,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="14" thickBot="1">
+    <row r="592" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="9">
         <v>43995</v>
       </c>
@@ -17610,7 +17616,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="14" thickBot="1">
+    <row r="593" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="9">
         <v>44002</v>
       </c>
@@ -17628,7 +17634,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="14" thickBot="1">
+    <row r="594" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="9">
         <v>44009</v>
       </c>
@@ -17646,7 +17652,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="14" thickBot="1">
+    <row r="595" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="9">
         <v>44016</v>
       </c>
@@ -17664,7 +17670,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="14" thickBot="1">
+    <row r="596" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="9">
         <v>44023</v>
       </c>
@@ -17682,7 +17688,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="14" thickBot="1">
+    <row r="597" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="9">
         <v>44030</v>
       </c>
@@ -17700,7 +17706,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="14" thickBot="1">
+    <row r="598" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="9">
         <v>44037</v>
       </c>
@@ -17718,7 +17724,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="14" thickBot="1">
+    <row r="599" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="9">
         <v>44044</v>
       </c>
@@ -17736,7 +17742,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="14" thickBot="1">
+    <row r="600" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="9">
         <v>44051</v>
       </c>
@@ -17754,7 +17760,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="14" thickBot="1">
+    <row r="601" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="11">
         <v>44058</v>
       </c>
@@ -17772,7 +17778,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="14" thickBot="1">
+    <row r="602" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="9">
         <v>44072</v>
       </c>
@@ -17790,7 +17796,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="14" thickBot="1">
+    <row r="603" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="9">
         <v>44079</v>
       </c>
@@ -17808,7 +17814,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="14" thickBot="1">
+    <row r="604" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="9">
         <v>44086</v>
       </c>
@@ -17826,7 +17832,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="14" thickBot="1">
+    <row r="605" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="9">
         <v>44093</v>
       </c>
@@ -17844,7 +17850,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="14" thickBot="1">
+    <row r="606" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="9">
         <v>44100</v>
       </c>
@@ -17862,7 +17868,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="14" thickBot="1">
+    <row r="607" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="9">
         <v>44107</v>
       </c>
@@ -17880,7 +17886,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="14" thickBot="1">
+    <row r="608" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="9">
         <v>44114</v>
       </c>
@@ -17898,7 +17904,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="14" thickBot="1">
+    <row r="609" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="9">
         <v>44121</v>
       </c>
@@ -17916,7 +17922,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="14" thickBot="1">
+    <row r="610" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="9">
         <v>44128</v>
       </c>
@@ -17934,7 +17940,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="14" thickBot="1">
+    <row r="611" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="9">
         <v>44135</v>
       </c>
@@ -17952,7 +17958,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="14" thickBot="1">
+    <row r="612" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="9">
         <v>44142</v>
       </c>
@@ -17970,7 +17976,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="14" thickBot="1">
+    <row r="613" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="9">
         <v>44149</v>
       </c>
@@ -17988,7 +17994,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="14" thickBot="1">
+    <row r="614" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="9">
         <v>44156</v>
       </c>
@@ -18006,7 +18012,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="14" thickBot="1">
+    <row r="615" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="9">
         <v>44163</v>
       </c>
@@ -18024,7 +18030,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="14" thickBot="1">
+    <row r="616" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="9">
         <v>44170</v>
       </c>
@@ -18042,7 +18048,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="14" thickBot="1">
+    <row r="617" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="9">
         <v>44177</v>
       </c>
@@ -18060,7 +18066,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="14" thickBot="1">
+    <row r="618" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="9">
         <v>44191</v>
       </c>
@@ -18078,7 +18084,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="14" thickBot="1">
+    <row r="619" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="9">
         <v>44198</v>
       </c>
@@ -18096,7 +18102,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="14" thickBot="1">
+    <row r="620" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="9">
         <v>44205</v>
       </c>
@@ -18114,7 +18120,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="14" thickBot="1">
+    <row r="621" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="9">
         <v>44212</v>
       </c>
@@ -18132,7 +18138,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="14" thickBot="1">
+    <row r="622" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="9">
         <v>44219</v>
       </c>
@@ -18150,7 +18156,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="14" thickBot="1">
+    <row r="623" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="9">
         <v>44226</v>
       </c>
@@ -18168,7 +18174,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="14" thickBot="1">
+    <row r="624" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="9">
         <v>44233</v>
       </c>
@@ -18186,7 +18192,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="14" thickBot="1">
+    <row r="625" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="9">
         <v>44240</v>
       </c>
@@ -18204,7 +18210,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="14" thickBot="1">
+    <row r="626" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="11">
         <v>44247</v>
       </c>
@@ -18222,7 +18228,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="14" thickBot="1">
+    <row r="627" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="9">
         <v>44254</v>
       </c>
@@ -18240,7 +18246,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="14" thickBot="1">
+    <row r="628" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="9">
         <v>44261</v>
       </c>
@@ -18258,7 +18264,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="14" thickBot="1">
+    <row r="629" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="9">
         <v>44268</v>
       </c>
@@ -18276,7 +18282,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="14" thickBot="1">
+    <row r="630" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="9">
         <v>44275</v>
       </c>
@@ -18294,7 +18300,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="14" thickBot="1">
+    <row r="631" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="9">
         <v>44282</v>
       </c>
@@ -18312,7 +18318,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="14" thickBot="1">
+    <row r="632" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="9">
         <v>44289</v>
       </c>
@@ -18330,7 +18336,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="14" thickBot="1">
+    <row r="633" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="9">
         <v>44296</v>
       </c>
@@ -18348,7 +18354,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="14" thickBot="1">
+    <row r="634" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="9">
         <v>44303</v>
       </c>
@@ -18366,7 +18372,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="14" thickBot="1">
+    <row r="635" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="9">
         <v>44310</v>
       </c>
@@ -18384,7 +18390,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="14" thickBot="1">
+    <row r="636" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="9">
         <v>44317</v>
       </c>
@@ -18402,7 +18408,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="14" thickBot="1">
+    <row r="637" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="9">
         <v>44324</v>
       </c>
@@ -18420,7 +18426,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="14" thickBot="1">
+    <row r="638" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="9">
         <v>44331</v>
       </c>
@@ -18438,7 +18444,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="14" thickBot="1">
+    <row r="639" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="9">
         <v>44338</v>
       </c>
@@ -18456,7 +18462,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="14" thickBot="1">
+    <row r="640" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="9">
         <v>44345</v>
       </c>
@@ -18474,7 +18480,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="14" thickBot="1">
+    <row r="641" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="9">
         <v>44352</v>
       </c>
@@ -18492,7 +18498,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="14" thickBot="1">
+    <row r="642" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="9">
         <v>44359</v>
       </c>
@@ -18525,7 +18531,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="14" thickBot="1">
+    <row r="643" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="9">
         <v>44366</v>
       </c>
@@ -18543,7 +18549,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="14" thickBot="1">
+    <row r="644" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="9">
         <v>44373</v>
       </c>
@@ -18561,7 +18567,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="14" thickBot="1">
+    <row r="645" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="9">
         <v>44380</v>
       </c>
@@ -18579,7 +18585,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="14" thickBot="1">
+    <row r="646" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="9">
         <v>44387</v>
       </c>
@@ -18597,7 +18603,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="14" thickBot="1">
+    <row r="647" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="9">
         <v>44394</v>
       </c>
@@ -18615,7 +18621,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="14" thickBot="1">
+    <row r="648" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="9">
         <v>44401</v>
       </c>
@@ -18633,7 +18639,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="14" thickBot="1">
+    <row r="649" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="9">
         <v>44408</v>
       </c>
@@ -18651,7 +18657,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="14" thickBot="1">
+    <row r="650" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="9">
         <v>44415</v>
       </c>
@@ -18669,7 +18675,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="14" thickBot="1">
+    <row r="651" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="11">
         <v>44422</v>
       </c>
@@ -18687,7 +18693,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="14" thickBot="1">
+    <row r="652" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="9">
         <v>44429</v>
       </c>
@@ -18705,7 +18711,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="14" thickBot="1">
+    <row r="653" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="9">
         <v>44436</v>
       </c>
@@ -18723,7 +18729,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="14" thickBot="1">
+    <row r="654" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="9">
         <v>44443</v>
       </c>
@@ -18741,7 +18747,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="14" thickBot="1">
+    <row r="655" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="9">
         <v>44450</v>
       </c>
@@ -18759,7 +18765,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="14" thickBot="1">
+    <row r="656" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="9">
         <v>44457</v>
       </c>
@@ -18777,7 +18783,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="14" thickBot="1">
+    <row r="657" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="9">
         <v>44464</v>
       </c>
@@ -18795,7 +18801,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="14" thickBot="1">
+    <row r="658" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="9">
         <v>44471</v>
       </c>
@@ -18813,7 +18819,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="14" thickBot="1">
+    <row r="659" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="9">
         <v>44478</v>
       </c>
@@ -18831,7 +18837,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="14" thickBot="1">
+    <row r="660" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="9">
         <v>44485</v>
       </c>
@@ -18849,7 +18855,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="14" thickBot="1">
+    <row r="661" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="9">
         <v>44492</v>
       </c>
@@ -18867,7 +18873,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="14" thickBot="1">
+    <row r="662" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="9">
         <v>44499</v>
       </c>
@@ -18885,7 +18891,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="14" thickBot="1">
+    <row r="663" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="9">
         <v>44506</v>
       </c>
@@ -18903,7 +18909,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="14" thickBot="1">
+    <row r="664" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="9">
         <v>44513</v>
       </c>
@@ -18921,7 +18927,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="14" thickBot="1">
+    <row r="665" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="9">
         <v>44520</v>
       </c>
@@ -18939,7 +18945,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="14" thickBot="1">
+    <row r="666" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="9">
         <v>44527</v>
       </c>
@@ -18957,7 +18963,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="14" thickBot="1">
+    <row r="667" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="9">
         <v>44534</v>
       </c>
@@ -18975,7 +18981,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="14" thickBot="1">
+    <row r="668" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="9">
         <v>44541</v>
       </c>
@@ -18993,7 +18999,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="14" thickBot="1">
+    <row r="669" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="9">
         <v>44548</v>
       </c>
@@ -19011,7 +19017,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="14" thickBot="1">
+    <row r="670" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="9">
         <v>44555</v>
       </c>
@@ -19029,7 +19035,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="14" thickBot="1">
+    <row r="671" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="9">
         <v>44562</v>
       </c>
@@ -19047,7 +19053,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="14" thickBot="1">
+    <row r="672" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="9">
         <v>44569</v>
       </c>
@@ -19065,7 +19071,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="14" thickBot="1">
+    <row r="673" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="9">
         <v>44576</v>
       </c>
@@ -19083,7 +19089,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="14" thickBot="1">
+    <row r="674" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="9">
         <v>44583</v>
       </c>
@@ -19101,7 +19107,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="14" thickBot="1">
+    <row r="675" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="9">
         <v>44590</v>
       </c>
@@ -19119,7 +19125,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="14" thickBot="1">
+    <row r="676" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="11">
         <v>44597</v>
       </c>
@@ -19137,7 +19143,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="14" thickBot="1">
+    <row r="677" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="9">
         <v>44604</v>
       </c>
@@ -19155,7 +19161,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="14" thickBot="1">
+    <row r="678" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="9">
         <v>44611</v>
       </c>
@@ -19173,7 +19179,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="14" thickBot="1">
+    <row r="679" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="9">
         <v>44625</v>
       </c>
@@ -19191,7 +19197,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="14" thickBot="1">
+    <row r="680" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="9">
         <v>44632</v>
       </c>
@@ -19209,7 +19215,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="14" thickBot="1">
+    <row r="681" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="9">
         <v>44639</v>
       </c>
@@ -19227,7 +19233,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="14" thickBot="1">
+    <row r="682" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="9">
         <v>44646</v>
       </c>
@@ -19245,7 +19251,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="14" thickBot="1">
+    <row r="683" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="9">
         <v>44653</v>
       </c>
@@ -19263,7 +19269,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="14" thickBot="1">
+    <row r="684" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="9">
         <v>44660</v>
       </c>
@@ -19281,7 +19287,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="14" thickBot="1">
+    <row r="685" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="9">
         <v>44667</v>
       </c>
@@ -19299,7 +19305,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="14" thickBot="1">
+    <row r="686" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="9">
         <v>44674</v>
       </c>
@@ -19317,7 +19323,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="14" thickBot="1">
+    <row r="687" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="9">
         <v>44681</v>
       </c>
@@ -19335,7 +19341,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="14" thickBot="1">
+    <row r="688" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="9">
         <v>44688</v>
       </c>
@@ -19353,7 +19359,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="14" thickBot="1">
+    <row r="689" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="9">
         <v>44695</v>
       </c>
@@ -19371,7 +19377,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="14" thickBot="1">
+    <row r="690" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="9">
         <v>44702</v>
       </c>
@@ -19389,7 +19395,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="14" thickBot="1">
+    <row r="691" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="9">
         <v>44709</v>
       </c>
@@ -19407,7 +19413,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="14" thickBot="1">
+    <row r="692" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="9">
         <v>44716</v>
       </c>
@@ -19425,7 +19431,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="14" thickBot="1">
+    <row r="693" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="9">
         <v>44723</v>
       </c>
@@ -19443,7 +19449,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="14" thickBot="1">
+    <row r="694" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="9">
         <v>44730</v>
       </c>
@@ -19461,7 +19467,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="14" thickBot="1">
+    <row r="695" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="9">
         <v>44737</v>
       </c>
@@ -19479,7 +19485,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="14" thickBot="1">
+    <row r="696" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="9">
         <v>44744</v>
       </c>
@@ -19497,7 +19503,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="14" thickBot="1">
+    <row r="697" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="9">
         <v>44751</v>
       </c>
@@ -19515,7 +19521,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="14" thickBot="1">
+    <row r="698" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="9">
         <v>44758</v>
       </c>
@@ -19533,7 +19539,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="14" thickBot="1">
+    <row r="699" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="9">
         <v>44765</v>
       </c>
@@ -19551,7 +19557,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="14" thickBot="1">
+    <row r="700" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="9">
         <v>44772</v>
       </c>
@@ -19569,7 +19575,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="14" thickBot="1">
+    <row r="701" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="11">
         <v>44779</v>
       </c>
@@ -19587,7 +19593,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="14" thickBot="1">
+    <row r="702" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="9">
         <v>44786</v>
       </c>
@@ -19605,7 +19611,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="14" thickBot="1">
+    <row r="703" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="9">
         <v>44793</v>
       </c>
@@ -19623,7 +19629,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="14" thickBot="1">
+    <row r="704" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="9">
         <v>44800</v>
       </c>
@@ -19641,7 +19647,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="14" thickBot="1">
+    <row r="705" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="9">
         <v>44807</v>
       </c>
@@ -19659,7 +19665,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="14" thickBot="1">
+    <row r="706" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="9">
         <v>44814</v>
       </c>
@@ -19692,7 +19698,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="14" thickBot="1">
+    <row r="707" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="9">
         <v>44821</v>
       </c>
@@ -19710,7 +19716,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="14" thickBot="1">
+    <row r="708" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="9">
         <v>44828</v>
       </c>
@@ -19728,7 +19734,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="14" thickBot="1">
+    <row r="709" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="9">
         <v>44835</v>
       </c>
@@ -19746,7 +19752,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="14" thickBot="1">
+    <row r="710" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="9">
         <v>44842</v>
       </c>
@@ -19764,7 +19770,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="14" thickBot="1">
+    <row r="711" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="9">
         <v>44849</v>
       </c>
@@ -19782,7 +19788,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="14" thickBot="1">
+    <row r="712" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="9">
         <v>44856</v>
       </c>
@@ -19800,7 +19806,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="14" thickBot="1">
+    <row r="713" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="9">
         <v>44863</v>
       </c>
@@ -19818,7 +19824,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="14" thickBot="1">
+    <row r="714" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="9">
         <v>44870</v>
       </c>
@@ -19836,7 +19842,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="14" thickBot="1">
+    <row r="715" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="9">
         <v>44877</v>
       </c>
@@ -19854,7 +19860,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="14" thickBot="1">
+    <row r="716" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="9">
         <v>44884</v>
       </c>
@@ -19872,7 +19878,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="14" thickBot="1">
+    <row r="717" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="9">
         <v>44891</v>
       </c>
@@ -19890,7 +19896,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="14" thickBot="1">
+    <row r="718" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="9">
         <v>44898</v>
       </c>
@@ -19908,7 +19914,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="14" thickBot="1">
+    <row r="719" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="9">
         <v>44905</v>
       </c>
@@ -19926,7 +19932,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="14" thickBot="1">
+    <row r="720" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="9">
         <v>44912</v>
       </c>
@@ -19944,7 +19950,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="14" thickBot="1">
+    <row r="721" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="9">
         <v>44919</v>
       </c>
@@ -19962,7 +19968,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="14" thickBot="1">
+    <row r="722" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="9">
         <v>44926</v>
       </c>
@@ -19980,7 +19986,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="14" thickBot="1">
+    <row r="723" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="9">
         <v>44933</v>
       </c>
@@ -19998,7 +20004,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="14" thickBot="1">
+    <row r="724" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="9">
         <v>44940</v>
       </c>
@@ -20016,7 +20022,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="14" thickBot="1">
+    <row r="725" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="9">
         <v>44947</v>
       </c>
@@ -20034,7 +20040,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="14" thickBot="1">
+    <row r="726" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="11">
         <v>44954</v>
       </c>
@@ -20052,7 +20058,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="14" thickBot="1">
+    <row r="727" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="9">
         <v>44961</v>
       </c>
@@ -20070,7 +20076,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="14" thickBot="1">
+    <row r="728" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="9">
         <v>44968</v>
       </c>
@@ -20088,7 +20094,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="14" thickBot="1">
+    <row r="729" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="9">
         <v>44975</v>
       </c>
@@ -20106,7 +20112,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="14" thickBot="1">
+    <row r="730" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="9">
         <v>44982</v>
       </c>
@@ -20124,7 +20130,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="14" thickBot="1">
+    <row r="731" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="9">
         <v>44989</v>
       </c>
@@ -20142,7 +20148,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="14" thickBot="1">
+    <row r="732" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="9">
         <v>44996</v>
       </c>
@@ -20160,7 +20166,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="14" thickBot="1">
+    <row r="733" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="9">
         <v>45003</v>
       </c>
@@ -20178,7 +20184,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="14" thickBot="1">
+    <row r="734" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="9">
         <v>45010</v>
       </c>
@@ -20196,7 +20202,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="14" thickBot="1">
+    <row r="735" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="9">
         <v>45017</v>
       </c>
@@ -20214,7 +20220,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="14" thickBot="1">
+    <row r="736" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="9">
         <v>45024</v>
       </c>
@@ -20232,7 +20238,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="14" thickBot="1">
+    <row r="737" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="9">
         <v>45031</v>
       </c>
@@ -20250,7 +20256,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="14" thickBot="1">
+    <row r="738" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="9">
         <v>45038</v>
       </c>
@@ -20268,7 +20274,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="14" thickBot="1">
+    <row r="739" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="9">
         <v>45045</v>
       </c>
@@ -20286,7 +20292,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="14" thickBot="1">
+    <row r="740" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="9">
         <v>45052</v>
       </c>
@@ -20304,7 +20310,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="14" thickBot="1">
+    <row r="741" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="9">
         <v>45059</v>
       </c>
@@ -20322,7 +20328,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="14" thickBot="1">
+    <row r="742" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="9">
         <v>45066</v>
       </c>
@@ -20340,7 +20346,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="14" thickBot="1">
+    <row r="743" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="9">
         <v>45073</v>
       </c>
@@ -20358,7 +20364,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="14" thickBot="1">
+    <row r="744" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="9">
         <v>45080</v>
       </c>
@@ -20376,7 +20382,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="14" thickBot="1">
+    <row r="745" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="9">
         <v>45087</v>
       </c>
@@ -20394,7 +20400,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="14" thickBot="1">
+    <row r="746" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="9">
         <v>45094</v>
       </c>
@@ -20412,7 +20418,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="14" thickBot="1">
+    <row r="747" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="9">
         <v>45101</v>
       </c>
@@ -20430,7 +20436,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="14" thickBot="1">
+    <row r="748" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="9">
         <v>45108</v>
       </c>
@@ -20448,7 +20454,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="14" thickBot="1">
+    <row r="749" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="9">
         <v>45115</v>
       </c>
@@ -20466,7 +20472,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="14" thickBot="1">
+    <row r="750" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="9">
         <v>45122</v>
       </c>
@@ -20484,7 +20490,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="14" thickBot="1">
+    <row r="751" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="11">
         <v>45129</v>
       </c>
@@ -20502,7 +20508,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="14" thickBot="1">
+    <row r="752" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="9">
         <v>45136</v>
       </c>
@@ -20520,7 +20526,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="14" thickBot="1">
+    <row r="753" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="9">
         <v>45143</v>
       </c>
@@ -20538,7 +20544,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="14" thickBot="1">
+    <row r="754" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="9">
         <v>45150</v>
       </c>
@@ -20556,7 +20562,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="14" thickBot="1">
+    <row r="755" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="9">
         <v>45157</v>
       </c>
@@ -20574,7 +20580,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="14" thickBot="1">
+    <row r="756" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="9">
         <v>45164</v>
       </c>
@@ -20592,7 +20598,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="14" thickBot="1">
+    <row r="757" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="9">
         <v>45171</v>
       </c>
@@ -20610,7 +20616,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="14" thickBot="1">
+    <row r="758" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="9">
         <v>45178</v>
       </c>
@@ -20628,7 +20634,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="14" thickBot="1">
+    <row r="759" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="9">
         <v>45185</v>
       </c>
@@ -20646,7 +20652,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="14" thickBot="1">
+    <row r="760" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="9">
         <v>45192</v>
       </c>
@@ -20664,7 +20670,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="14" thickBot="1">
+    <row r="761" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="9">
         <v>45199</v>
       </c>
@@ -20682,7 +20688,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="14" thickBot="1">
+    <row r="762" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="9">
         <v>45206</v>
       </c>
@@ -20700,7 +20706,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="14" thickBot="1">
+    <row r="763" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="9">
         <v>45213</v>
       </c>
@@ -20718,7 +20724,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="14" thickBot="1">
+    <row r="764" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="9">
         <v>45220</v>
       </c>
@@ -20736,7 +20742,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="14" thickBot="1">
+    <row r="765" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="9">
         <v>45227</v>
       </c>
@@ -20754,7 +20760,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="14" thickBot="1">
+    <row r="766" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="9">
         <v>45234</v>
       </c>
@@ -20772,7 +20778,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="14" thickBot="1">
+    <row r="767" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="9">
         <v>45241</v>
       </c>
@@ -20790,7 +20796,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="14" thickBot="1">
+    <row r="768" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="9">
         <v>45248</v>
       </c>
@@ -20808,7 +20814,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="14" thickBot="1">
+    <row r="769" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="9">
         <v>45255</v>
       </c>
@@ -20826,7 +20832,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="14" thickBot="1">
+    <row r="770" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="9">
         <v>45262</v>
       </c>
@@ -20859,7 +20865,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="14" thickBot="1">
+    <row r="771" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="9">
         <v>45269</v>
       </c>
@@ -20877,7 +20883,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="14" thickBot="1">
+    <row r="772" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="9">
         <v>45276</v>
       </c>
@@ -20895,7 +20901,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="14" thickBot="1">
+    <row r="773" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="9">
         <v>45283</v>
       </c>
@@ -20913,7 +20919,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="14" thickBot="1">
+    <row r="774" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="9">
         <v>45297</v>
       </c>
@@ -20931,7 +20937,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="14" thickBot="1">
+    <row r="775" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="9">
         <v>45304</v>
       </c>
@@ -20949,7 +20955,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="14" thickBot="1">
+    <row r="776" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="13">
         <v>45311</v>
       </c>
@@ -20967,7 +20973,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="14" thickBot="1">
+    <row r="777" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="15">
         <v>45318</v>
       </c>
@@ -20985,7 +20991,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="14" thickBot="1">
+    <row r="778" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="15">
         <v>45325</v>
       </c>
@@ -21003,7 +21009,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="14" thickBot="1">
+    <row r="779" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="15">
         <v>45332</v>
       </c>
@@ -21021,7 +21027,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="14" thickBot="1">
+    <row r="780" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="15">
         <v>45339</v>
       </c>
@@ -21039,7 +21045,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="14" thickBot="1">
+    <row r="781" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="15">
         <v>45346</v>
       </c>
@@ -21057,7 +21063,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="14" thickBot="1">
+    <row r="782" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="15">
         <v>45353</v>
       </c>
@@ -21075,7 +21081,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="14" thickBot="1">
+    <row r="783" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="15">
         <v>45360</v>
       </c>
@@ -21093,7 +21099,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="14" thickBot="1">
+    <row r="784" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="15">
         <v>45367</v>
       </c>
@@ -21111,7 +21117,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="14" thickBot="1">
+    <row r="785" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="15">
         <v>45374</v>
       </c>
@@ -21129,7 +21135,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="14" thickBot="1">
+    <row r="786" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="15">
         <v>45381</v>
       </c>
@@ -21147,7 +21153,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="14" thickBot="1">
+    <row r="787" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="15">
         <v>45388</v>
       </c>
@@ -21165,7 +21171,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="14" thickBot="1">
+    <row r="788" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="15">
         <v>45395</v>
       </c>
@@ -21183,7 +21189,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="14" thickBot="1">
+    <row r="789" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="15">
         <v>45402</v>
       </c>
@@ -21201,7 +21207,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="14" thickBot="1">
+    <row r="790" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="15">
         <v>45409</v>
       </c>
@@ -21219,7 +21225,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="14" thickBot="1">
+    <row r="791" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="15">
         <v>45416</v>
       </c>
@@ -21237,7 +21243,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="14" thickBot="1">
+    <row r="792" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="15">
         <v>45423</v>
       </c>
@@ -21255,7 +21261,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="14" thickBot="1">
+    <row r="793" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="15">
         <v>45430</v>
       </c>
@@ -21273,7 +21279,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="14" thickBot="1">
+    <row r="794" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="15">
         <v>45437</v>
       </c>
@@ -21291,7 +21297,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="14" thickBot="1">
+    <row r="795" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="15">
         <v>45444</v>
       </c>
@@ -21309,7 +21315,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="14" thickBot="1">
+    <row r="796" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="15">
         <v>45451</v>
       </c>
@@ -21327,7 +21333,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="14" thickBot="1">
+    <row r="797" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="15">
         <v>45458</v>
       </c>
@@ -21345,7 +21351,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="14" thickBot="1">
+    <row r="798" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="15">
         <v>45465</v>
       </c>
@@ -21363,7 +21369,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="14" thickBot="1">
+    <row r="799" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="15">
         <v>45472</v>
       </c>
@@ -21381,7 +21387,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="14" thickBot="1">
+    <row r="800" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="15">
         <v>45479</v>
       </c>
@@ -21399,7 +21405,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="14" thickBot="1">
+    <row r="801" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="13">
         <v>45486</v>
       </c>
@@ -21417,7 +21423,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="14" thickBot="1">
+    <row r="802" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="15">
         <v>45493</v>
       </c>
@@ -21435,7 +21441,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="14" thickBot="1">
+    <row r="803" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="15">
         <v>45500</v>
       </c>
@@ -21453,7 +21459,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="14" thickBot="1">
+    <row r="804" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="15">
         <v>45507</v>
       </c>
@@ -21471,7 +21477,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="14" thickBot="1">
+    <row r="805" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="15">
         <v>45514</v>
       </c>
@@ -21489,7 +21495,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="14" thickBot="1">
+    <row r="806" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="15">
         <v>45521</v>
       </c>
@@ -21507,7 +21513,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="14" thickBot="1">
+    <row r="807" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="15">
         <v>45528</v>
       </c>
@@ -21525,7 +21531,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="14" thickBot="1">
+    <row r="808" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="15">
         <v>45535</v>
       </c>
@@ -21543,7 +21549,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="14" thickBot="1">
+    <row r="809" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="15">
         <v>45542</v>
       </c>
@@ -21561,7 +21567,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="14" thickBot="1">
+    <row r="810" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="15">
         <v>45549</v>
       </c>
@@ -21579,7 +21585,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="14" thickBot="1">
+    <row r="811" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="15">
         <v>45556</v>
       </c>
@@ -21597,7 +21603,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="14" thickBot="1">
+    <row r="812" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="15">
         <v>45563</v>
       </c>
@@ -21615,7 +21621,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="14" thickBot="1">
+    <row r="813" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="15">
         <v>45570</v>
       </c>
@@ -21633,7 +21639,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="14" thickBot="1">
+    <row r="814" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="15">
         <v>45577</v>
       </c>
@@ -21651,7 +21657,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="14" thickBot="1">
+    <row r="815" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="15">
         <v>45584</v>
       </c>
@@ -21669,7 +21675,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="14" thickBot="1">
+    <row r="816" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="15">
         <v>45591</v>
       </c>
@@ -21687,7 +21693,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="14" thickBot="1">
+    <row r="817" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="15">
         <v>45598</v>
       </c>
@@ -21705,7 +21711,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="14" thickBot="1">
+    <row r="818" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="15">
         <v>45612</v>
       </c>
@@ -21723,7 +21729,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="14" thickBot="1">
+    <row r="819" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="15">
         <v>45619</v>
       </c>
@@ -21741,7 +21747,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="14" thickBot="1">
+    <row r="820" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="15">
         <v>45626</v>
       </c>
@@ -21759,7 +21765,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="14" thickBot="1">
+    <row r="821" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="15">
         <v>45633</v>
       </c>
@@ -21777,7 +21783,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="14" thickBot="1">
+    <row r="822" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="15">
         <v>45640</v>
       </c>
@@ -21795,7 +21801,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="14" thickBot="1">
+    <row r="823" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="15">
         <v>45647</v>
       </c>
@@ -21813,7 +21819,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="14" thickBot="1">
+    <row r="824" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="15">
         <v>45654</v>
       </c>
@@ -21831,7 +21837,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="14" thickBot="1">
+    <row r="825" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="15">
         <v>45661</v>
       </c>
@@ -21849,7 +21855,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="14" thickBot="1">
+    <row r="826" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="13">
         <v>45668</v>
       </c>
@@ -21867,7 +21873,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="14" thickBot="1">
+    <row r="827" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="15">
         <v>45675</v>
       </c>
@@ -21885,7 +21891,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="14" thickBot="1">
+    <row r="828" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="15">
         <v>45682</v>
       </c>
@@ -21903,7 +21909,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="14" thickBot="1">
+    <row r="829" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="15">
         <v>45689</v>
       </c>
@@ -21921,7 +21927,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="14" thickBot="1">
+    <row r="830" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="15">
         <v>45696</v>
       </c>
@@ -21939,7 +21945,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="14" thickBot="1">
+    <row r="831" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="15">
         <v>45703</v>
       </c>
@@ -21957,7 +21963,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="14" thickBot="1">
+    <row r="832" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="15">
         <v>45710</v>
       </c>
@@ -21975,7 +21981,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="14" thickBot="1">
+    <row r="833" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="15">
         <v>45717</v>
       </c>
@@ -21993,7 +21999,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="14" thickBot="1">
+    <row r="834" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="15">
         <v>45724</v>
       </c>
@@ -22026,7 +22032,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="14" thickBot="1">
+    <row r="835" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="15">
         <v>45731</v>
       </c>
@@ -22044,7 +22050,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="14" thickBot="1">
+    <row r="836" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="15">
         <v>45738</v>
       </c>
@@ -22062,7 +22068,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="14" thickBot="1">
+    <row r="837" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="15">
         <v>45745</v>
       </c>
@@ -22080,7 +22086,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="14" thickBot="1">
+    <row r="838" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="15">
         <v>45752</v>
       </c>
@@ -22098,7 +22104,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="14" thickBot="1">
+    <row r="839" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="15">
         <v>45759</v>
       </c>
@@ -22116,7 +22122,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="14" thickBot="1">
+    <row r="840" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="15">
         <v>45766</v>
       </c>
@@ -22134,7 +22140,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="14" thickBot="1">
+    <row r="841" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="15">
         <v>45773</v>
       </c>
@@ -22152,7 +22158,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="14" thickBot="1">
+    <row r="842" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="15">
         <v>45780</v>
       </c>
@@ -22170,7 +22176,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="14" thickBot="1">
+    <row r="843" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="15">
         <v>45787</v>
       </c>
@@ -22188,7 +22194,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="14" thickBot="1">
+    <row r="844" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="15">
         <v>45794</v>
       </c>
@@ -22206,7 +22212,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="14" thickBot="1">
+    <row r="845" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="15">
         <v>45801</v>
       </c>
@@ -22224,7 +22230,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="14" thickBot="1">
+    <row r="846" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="15">
         <v>45808</v>
       </c>
@@ -22242,7 +22248,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="14" thickBot="1">
+    <row r="847" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="15">
         <v>45815</v>
       </c>
@@ -22260,7 +22266,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="14" thickBot="1">
+    <row r="848" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="15">
         <v>45822</v>
       </c>
@@ -22278,7 +22284,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="14" thickBot="1">
+    <row r="849" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="15">
         <v>45829</v>
       </c>
@@ -22296,7 +22302,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="14" thickBot="1">
+    <row r="850" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="15">
         <v>45836</v>
       </c>
@@ -22314,7 +22320,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="14" thickBot="1">
+    <row r="851" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="13">
         <v>45843</v>
       </c>
@@ -22332,7 +22338,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="14" thickBot="1">
+    <row r="852" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="15">
         <v>45850</v>
       </c>
@@ -22350,7 +22356,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="14" thickBot="1">
+    <row r="853" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="15">
         <v>45857</v>
       </c>
@@ -22368,7 +22374,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="14" thickBot="1">
+    <row r="854" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="15">
         <v>45864</v>
       </c>
@@ -22386,7 +22392,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="14" thickBot="1">
+    <row r="855" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="15">
         <v>45871</v>
       </c>
@@ -22404,7 +22410,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="14" thickBot="1">
+    <row r="856" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="15">
         <v>45878</v>
       </c>
@@ -22422,7 +22428,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="14" thickBot="1">
+    <row r="857" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="15">
         <v>45885</v>
       </c>
@@ -22440,7 +22446,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="14" thickBot="1">
+    <row r="858" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="15">
         <v>45892</v>
       </c>
@@ -22458,7 +22464,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="14" thickBot="1">
+    <row r="859" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="15">
         <v>45899</v>
       </c>
@@ -22476,7 +22482,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="14" thickBot="1">
+    <row r="860" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="15">
         <v>45906</v>
       </c>
@@ -22494,7 +22500,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="14" thickBot="1">
+    <row r="861" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="15">
         <v>45913</v>
       </c>
@@ -22512,7 +22518,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="14" thickBot="1">
+    <row r="862" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="15">
         <v>45920</v>
       </c>
@@ -22530,7 +22536,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="14" thickBot="1">
+    <row r="863" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="13">
         <v>45927</v>
       </c>
@@ -22548,7 +22554,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="14" thickBot="1">
+    <row r="864" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="15">
         <v>45934</v>
       </c>
@@ -22566,7 +22572,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="14" thickBot="1">
+    <row r="865" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="15">
         <v>45941</v>
       </c>
@@ -22584,7 +22590,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="14" thickBot="1">
+    <row r="866" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="15">
         <v>45948</v>
       </c>
@@ -22602,7 +22608,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="14" thickBot="1">
+    <row r="867" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="15">
         <v>45955</v>
       </c>
@@ -22620,7 +22626,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="14" thickBot="1">
+    <row r="868" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="15">
         <v>45962</v>
       </c>
@@ -22638,7 +22644,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="14" thickBot="1">
+    <row r="869" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="15">
         <v>45969</v>
       </c>
@@ -22656,7 +22662,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="14" thickBot="1">
+    <row r="870" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="15">
         <v>45976</v>
       </c>
@@ -22674,7 +22680,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="14" thickBot="1">
+    <row r="871" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="15">
         <v>45983</v>
       </c>
@@ -22692,7 +22698,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="14" thickBot="1">
+    <row r="872" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="15">
         <v>45990</v>
       </c>
@@ -22710,7 +22716,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="14" thickBot="1">
+    <row r="873" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="15">
         <v>45997</v>
       </c>
@@ -22728,7 +22734,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="14" thickBot="1">
+    <row r="874" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="15">
         <v>46004</v>
       </c>
@@ -22746,7 +22752,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="14" thickBot="1">
+    <row r="875" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="13">
         <v>46018</v>
       </c>
@@ -22764,7 +22770,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="14" thickBot="1">
+    <row r="876" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="7">
         <v>46025</v>
       </c>
@@ -22782,7 +22788,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="14" thickBot="1">
+    <row r="877" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="13">
         <v>46032</v>
       </c>
@@ -22800,7 +22806,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="14" thickBot="1">
+    <row r="878" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="7">
         <v>46039</v>
       </c>
@@ -22833,7 +22839,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="14" thickBot="1">
+    <row r="879" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="13">
         <v>46046</v>
       </c>
@@ -22866,7 +22872,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="14" thickBot="1">
+    <row r="880" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="13">
         <v>46053</v>
       </c>
@@ -22899,7 +22905,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="14" thickBot="1">
+    <row r="881" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="13">
         <v>46060</v>
       </c>
@@ -22917,7 +22923,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="14" thickBot="1">
+    <row r="882" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="7">
         <v>46067</v>
       </c>
@@ -22950,7 +22956,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="14" thickBot="1">
+    <row r="883" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="13">
         <v>46074</v>
       </c>
@@ -22983,7 +22989,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="14" thickBot="1">
+    <row r="884" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="7">
         <v>46081</v>
       </c>
@@ -23001,7 +23007,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="14" thickBot="1">
+    <row r="885" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="13">
         <v>46088</v>
       </c>
@@ -23034,7 +23040,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="7">
         <v>46102</v>
       </c>
@@ -23067,7 +23073,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="7">
         <v>46109</v>
       </c>
@@ -23100,7 +23106,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="7">
         <v>46116</v>
       </c>
@@ -23133,7 +23139,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A889" s="7">
         <v>46123</v>
       </c>
@@ -23166,6 +23172,39 @@
         <v>500040</v>
       </c>
     </row>
+    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A890" s="7">
+        <v>46130</v>
+      </c>
+      <c r="B890" s="7">
+        <v>46134</v>
+      </c>
+      <c r="C890" s="21">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="D890" s="7" t="str">
+        <f>IF(
+ AND(
+  A890 &gt;= IF(
+         YEAR(A890)&gt;=2007,
+         DATE(YEAR(A890),3,14)-WEEKDAY(DATE(YEAR(A890),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A890),4,7)-WEEKDAY(DATE(YEAR(A890),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A890 &lt;  IF(
+         YEAR(A890)&gt;=2007,
+         DATE(YEAR(A890),11,7)-WEEKDAY(DATE(YEAR(A890),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A890),10,31)-WEEKDAY(DATE(YEAR(A890),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E890" s="17">
+        <v>508303</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
     <sortCondition ref="B2:B876"/>
@@ -23179,7 +23218,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23190,12 +23229,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23203,7 +23242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23211,7 +23250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C39E3E47-BC69-43F6-893C-5D7FEE03549C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A03D3-F3A7-4388-8263-EEEBD8E0395D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -22967,7 +22967,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="D883" s="6" t="str">
-        <f t="shared" ref="D883:D884" si="15">IF(
+        <f t="shared" ref="D883:D890" si="15">IF(
  AND(
   A883 &gt;= IF(
          YEAR(A883)&gt;=2007,
@@ -23018,22 +23018,7 @@
         <v>0.51388888888888895</v>
       </c>
       <c r="D885" s="6" t="str">
-        <f t="shared" ref="D885" si="16">IF(
- AND(
-  A885 &gt;= IF(
-         YEAR(A885)&gt;=2007,
-         DATE(YEAR(A885),3,14)-WEEKDAY(DATE(YEAR(A885),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A885),4,7)-WEEKDAY(DATE(YEAR(A885),4,7),1)+1 + TIME(2,0,0)
-       ),
-  A885 &lt;  IF(
-         YEAR(A885)&gt;=2007,
-         DATE(YEAR(A885),11,7)-WEEKDAY(DATE(YEAR(A885),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A885),10,31)-WEEKDAY(DATE(YEAR(A885),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
+        <f t="shared" si="15"/>
         <v>UTC-5</v>
       </c>
       <c r="E885" s="17">
@@ -23051,22 +23036,7 @@
         <v>0.50069444444444444</v>
       </c>
       <c r="D886" s="6" t="str">
-        <f>IF(
- AND(
-  A886 &gt;= IF(
-         YEAR(A886)&gt;=2007,
-         DATE(YEAR(A886),3,14)-WEEKDAY(DATE(YEAR(A886),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A886),4,7)-WEEKDAY(DATE(YEAR(A886),4,7),1)+1 + TIME(2,0,0)
-       ),
-  A886 &lt;  IF(
-         YEAR(A886)&gt;=2007,
-         DATE(YEAR(A886),11,7)-WEEKDAY(DATE(YEAR(A886),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A886),10,31)-WEEKDAY(DATE(YEAR(A886),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
+        <f t="shared" si="15"/>
         <v>UTC-4</v>
       </c>
       <c r="E886" s="17">
@@ -23083,23 +23053,8 @@
       <c r="C887" s="21">
         <v>0.50069444444444444</v>
       </c>
-      <c r="D887" s="7" t="str">
-        <f>IF(
- AND(
-  A887 &gt;= IF(
-         YEAR(A887)&gt;=2007,
-         DATE(YEAR(A887),3,14)-WEEKDAY(DATE(YEAR(A887),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A887),4,7)-WEEKDAY(DATE(YEAR(A887),4,7),1)+1 + TIME(2,0,0)
-       ),
-  A887 &lt;  IF(
-         YEAR(A887)&gt;=2007,
-         DATE(YEAR(A887),11,7)-WEEKDAY(DATE(YEAR(A887),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A887),10,31)-WEEKDAY(DATE(YEAR(A887),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
+      <c r="D887" s="6" t="str">
+        <f t="shared" si="15"/>
         <v>UTC-4</v>
       </c>
       <c r="E887" s="17">
@@ -23117,22 +23072,7 @@
         <v>0.500694444444444</v>
       </c>
       <c r="D888" s="6" t="str">
-        <f>IF(
- AND(
-  A888 &gt;= IF(
-         YEAR(A888)&gt;=2007,
-         DATE(YEAR(A888),3,14)-WEEKDAY(DATE(YEAR(A888),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A888),4,7)-WEEKDAY(DATE(YEAR(A888),4,7),1)+1 + TIME(2,0,0)
-       ),
-  A888 &lt;  IF(
-         YEAR(A888)&gt;=2007,
-         DATE(YEAR(A888),11,7)-WEEKDAY(DATE(YEAR(A888),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A888),10,31)-WEEKDAY(DATE(YEAR(A888),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
+        <f t="shared" si="15"/>
         <v>UTC-4</v>
       </c>
       <c r="E888" s="17">
@@ -23150,22 +23090,7 @@
         <v>0.500694444444444</v>
       </c>
       <c r="D889" s="6" t="str">
-        <f>IF(
- AND(
-  A889 &gt;= IF(
-         YEAR(A889)&gt;=2007,
-         DATE(YEAR(A889),3,14)-WEEKDAY(DATE(YEAR(A889),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A889),4,7)-WEEKDAY(DATE(YEAR(A889),4,7),1)+1 + TIME(2,0,0)
-       ),
-  A889 &lt;  IF(
-         YEAR(A889)&gt;=2007,
-         DATE(YEAR(A889),11,7)-WEEKDAY(DATE(YEAR(A889),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A889),10,31)-WEEKDAY(DATE(YEAR(A889),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
+        <f t="shared" si="15"/>
         <v>UTC-4</v>
       </c>
       <c r="E889" s="17">
@@ -23182,23 +23107,8 @@
       <c r="C890" s="21">
         <v>0.50208333333333333</v>
       </c>
-      <c r="D890" s="7" t="str">
-        <f>IF(
- AND(
-  A890 &gt;= IF(
-         YEAR(A890)&gt;=2007,
-         DATE(YEAR(A890),3,14)-WEEKDAY(DATE(YEAR(A890),3,14),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A890),4,7)-WEEKDAY(DATE(YEAR(A890),4,7),1)+1 + TIME(2,0,0)
-       ),
-  A890 &lt;  IF(
-         YEAR(A890)&gt;=2007,
-         DATE(YEAR(A890),11,7)-WEEKDAY(DATE(YEAR(A890),11,7),1)+1 + TIME(2,0,0),
-         DATE(YEAR(A890),10,31)-WEEKDAY(DATE(YEAR(A890),10,31),1) + TIME(2,0,0)
-       )
- ),
- "UTC-4",
- "UTC-5"
-)</f>
+      <c r="D890" s="6" t="str">
+        <f t="shared" si="15"/>
         <v>UTC-4</v>
       </c>
       <c r="E890" s="17">

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A03D3-F3A7-4388-8263-EEEBD8E0395D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366AF35D-8A41-4A19-AF48-C2A51CE6154E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -79,6 +79,7 @@
   </si>
   <si>
     <t>https://ycharts.com/indicators/us_weekly_rail_traffic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3044,6 +3045,9 @@
                 <c:pt idx="888">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="889">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5719,6 +5723,9 @@
                 </c:pt>
                 <c:pt idx="888">
                   <c:v>508303</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>511616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6800,7 +6807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E890"/>
+  <dimension ref="A1:E891"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
@@ -22967,7 +22974,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="D883" s="6" t="str">
-        <f t="shared" ref="D883:D890" si="15">IF(
+        <f t="shared" ref="D883:D891" si="15">IF(
  AND(
   A883 &gt;= IF(
          YEAR(A883)&gt;=2007,
@@ -23113,6 +23120,24 @@
       </c>
       <c r="E890" s="17">
         <v>508303</v>
+      </c>
+    </row>
+    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A891" s="7">
+        <v>46137</v>
+      </c>
+      <c r="B891" s="7">
+        <v>46141</v>
+      </c>
+      <c r="C891" s="21">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="D891" s="6" t="str">
+        <f t="shared" si="15"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E891" s="17">
+        <v>511616</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366AF35D-8A41-4A19-AF48-C2A51CE6154E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEE92D5-7C67-4D94-8836-CED26B96F48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -3047,6 +3047,9 @@
                 </c:pt>
                 <c:pt idx="889">
                   <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>46148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6807,7 +6810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E891"/>
+  <dimension ref="A1:E892"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
@@ -22974,7 +22977,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="D883" s="6" t="str">
-        <f t="shared" ref="D883:D891" si="15">IF(
+        <f t="shared" ref="D883:D892" si="15">IF(
  AND(
   A883 &gt;= IF(
          YEAR(A883)&gt;=2007,
@@ -23138,6 +23141,21 @@
       </c>
       <c r="E891" s="17">
         <v>511616</v>
+      </c>
+    </row>
+    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A892" s="7">
+        <v>46144</v>
+      </c>
+      <c r="B892" s="7">
+        <v>46148</v>
+      </c>
+      <c r="C892" s="21">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D892" s="6" t="str">
+        <f t="shared" si="15"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590EDCE9-680D-4174-9F77-09AC26B98199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C19345A-6ACF-4E11-B46C-0C1F7CEFCC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -3051,6 +3051,9 @@
                 <c:pt idx="890">
                   <c:v>46148</c:v>
                 </c:pt>
+                <c:pt idx="891">
+                  <c:v>46155</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5732,6 +5735,9 @@
                 </c:pt>
                 <c:pt idx="890">
                   <c:v>518773</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>513755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6813,7 +6819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E892"/>
+  <dimension ref="A1:E893"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
@@ -23162,6 +23168,39 @@
       </c>
       <c r="E892" s="17">
         <v>518773</v>
+      </c>
+    </row>
+    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A893" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B893" s="7">
+        <v>46155</v>
+      </c>
+      <c r="C893" s="21">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D893" s="6" t="str">
+        <f t="shared" ref="D893" si="16">IF(
+ AND(
+  A893 &gt;= IF(
+         YEAR(A893)&gt;=2007,
+         DATE(YEAR(A893),3,14)-WEEKDAY(DATE(YEAR(A893),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A893),4,7)-WEEKDAY(DATE(YEAR(A893),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A893 &lt;  IF(
+         YEAR(A893)&gt;=2007,
+         DATE(YEAR(A893),11,7)-WEEKDAY(DATE(YEAR(A893),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A893),10,31)-WEEKDAY(DATE(YEAR(A893),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E893" s="17">
+        <v>513755</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C19345A-6ACF-4E11-B46C-0C1F7CEFCC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC9258F-8986-44A3-903D-90C4C103DDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
@@ -87,10 +87,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -190,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -207,61 +207,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3053,6 +3053,9 @@
                 </c:pt>
                 <c:pt idx="891">
                   <c:v>46155</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>46162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6819,7 +6822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E893"/>
+  <dimension ref="A1:E894"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
@@ -23181,7 +23184,7 @@
         <v>0.50069444444444444</v>
       </c>
       <c r="D893" s="6" t="str">
-        <f t="shared" ref="D893" si="16">IF(
+        <f t="shared" ref="D893:D894" si="16">IF(
  AND(
   A893 &gt;= IF(
          YEAR(A893)&gt;=2007,
@@ -23201,6 +23204,21 @@
       </c>
       <c r="E893" s="17">
         <v>513755</v>
+      </c>
+    </row>
+    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A894" s="7">
+        <v>46158</v>
+      </c>
+      <c r="B894" s="7">
+        <v>46162</v>
+      </c>
+      <c r="C894" s="21">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="D894" s="6" t="str">
+        <f t="shared" si="16"/>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4776DF8F-3CAF-4A22-BB7B-5B77173D17C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85D25C8-6489-4F93-B4FD-77C7866D012F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -6830,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E894"/>
+  <dimension ref="A1:E895"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
@@ -23192,7 +23192,7 @@
         <v>0.50069444444444444</v>
       </c>
       <c r="D893" s="6" t="str">
-        <f t="shared" ref="D893:D894" si="16">IF(
+        <f t="shared" ref="D893:D895" si="16">IF(
  AND(
   A893 &gt;= IF(
          YEAR(A893)&gt;=2007,
@@ -23230,6 +23230,24 @@
       </c>
       <c r="E894" s="17">
         <v>511216</v>
+      </c>
+    </row>
+    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A895" s="7">
+        <v>46165</v>
+      </c>
+      <c r="B895" s="7">
+        <v>46169</v>
+      </c>
+      <c r="C895" s="21">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D895" s="6" t="str">
+        <f t="shared" si="16"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E895" s="17">
+        <v>523574</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85D25C8-6489-4F93-B4FD-77C7866D012F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB239FD-B313-4594-A098-CA884F631184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -265,9 +265,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6830,18 +6830,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
-  <dimension ref="A1:E895"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E896"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.36328125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="17" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="5"/>
+    <col min="5" max="5" width="12.453125" style="17" customWidth="1"/>
+    <col min="6" max="16384" width="9.08984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" s="6">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" s="6">
         <v>39830</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" s="6">
         <v>39837</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="6">
         <v>39844</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="6">
         <v>39851</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5">
       <c r="A7" s="6">
         <v>39858</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5">
       <c r="A8" s="6">
         <v>39865</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5">
       <c r="A9" s="6">
         <v>39872</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5">
       <c r="A10" s="6">
         <v>39879</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5">
       <c r="A11" s="6">
         <v>39886</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5">
       <c r="A12" s="6">
         <v>39893</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5">
       <c r="A13" s="6">
         <v>39900</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5">
       <c r="A14" s="6">
         <v>39907</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5">
       <c r="A15" s="6">
         <v>39914</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5">
       <c r="A16" s="6">
         <v>39921</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" s="6">
         <v>39928</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" s="6">
         <v>39935</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" s="6">
         <v>39942</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" s="6">
         <v>39949</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5">
       <c r="A21" s="6">
         <v>39956</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5">
       <c r="A22" s="6">
         <v>39963</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5">
       <c r="A23" s="6">
         <v>39970</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5">
       <c r="A24" s="6">
         <v>39977</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5">
       <c r="A25" s="6">
         <v>39984</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5">
       <c r="A26" s="6">
         <v>39991</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5">
       <c r="A27" s="6">
         <v>39998</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5">
       <c r="A28" s="6">
         <v>40005</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5">
       <c r="A29" s="6">
         <v>40012</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5">
       <c r="A30" s="6">
         <v>40019</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5">
       <c r="A31" s="6">
         <v>40026</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5">
       <c r="A32" s="6">
         <v>40033</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5">
       <c r="A33" s="6">
         <v>40040</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5">
       <c r="A34" s="6">
         <v>40047</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5">
       <c r="A35" s="6">
         <v>40054</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5">
       <c r="A36" s="6">
         <v>40061</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5">
       <c r="A37" s="6">
         <v>40068</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5">
       <c r="A38" s="6">
         <v>40075</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5">
       <c r="A39" s="6">
         <v>40082</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5">
       <c r="A40" s="6">
         <v>40089</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5">
       <c r="A41" s="6">
         <v>40096</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5">
       <c r="A42" s="6">
         <v>40103</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5">
       <c r="A43" s="6">
         <v>40110</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5">
       <c r="A44" s="6">
         <v>40117</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5">
       <c r="A45" s="6">
         <v>40124</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5">
       <c r="A46" s="6">
         <v>40131</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5">
       <c r="A47" s="6">
         <v>40138</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5">
       <c r="A48" s="6">
         <v>40145</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5">
       <c r="A49" s="6">
         <v>40152</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5">
       <c r="A50" s="6">
         <v>40159</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5">
       <c r="A51" s="6">
         <v>40166</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5">
       <c r="A52" s="6">
         <v>40173</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5">
       <c r="A53" s="6">
         <v>40180</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5">
       <c r="A54" s="6">
         <v>40187</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5">
       <c r="A55" s="6">
         <v>40194</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5">
       <c r="A56" s="6">
         <v>40201</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5">
       <c r="A57" s="6">
         <v>40208</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5">
       <c r="A58" s="6">
         <v>40215</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5">
       <c r="A59" s="6">
         <v>40222</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5">
       <c r="A60" s="6">
         <v>40229</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5">
       <c r="A61" s="6">
         <v>40236</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5">
       <c r="A62" s="6">
         <v>40243</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5">
       <c r="A63" s="6">
         <v>40250</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5">
       <c r="A64" s="6">
         <v>40257</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5">
       <c r="A65" s="6">
         <v>40264</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5">
       <c r="A66" s="6">
         <v>40271</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5">
       <c r="A67" s="6">
         <v>40278</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5">
       <c r="A68" s="6">
         <v>40285</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5">
       <c r="A69" s="6">
         <v>40292</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5">
       <c r="A70" s="6">
         <v>40299</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5">
       <c r="A71" s="6">
         <v>40306</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5">
       <c r="A72" s="6">
         <v>40313</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5">
       <c r="A73" s="6">
         <v>40320</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5">
       <c r="A74" s="6">
         <v>40327</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5">
       <c r="A75" s="6">
         <v>40334</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5">
       <c r="A76" s="6">
         <v>40341</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5">
       <c r="A77" s="6">
         <v>40348</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5">
       <c r="A78" s="6">
         <v>40355</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5">
       <c r="A79" s="6">
         <v>40362</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5">
       <c r="A80" s="6">
         <v>40369</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5">
       <c r="A81" s="6">
         <v>40376</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5">
       <c r="A82" s="6">
         <v>40383</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5">
       <c r="A83" s="6">
         <v>40390</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5">
       <c r="A84" s="6">
         <v>40397</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5">
       <c r="A85" s="6">
         <v>40404</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5">
       <c r="A86" s="6">
         <v>40411</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5">
       <c r="A87" s="6">
         <v>40418</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5">
       <c r="A88" s="6">
         <v>40425</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5">
       <c r="A89" s="6">
         <v>40432</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5">
       <c r="A90" s="6">
         <v>40439</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5">
       <c r="A91" s="6">
         <v>40446</v>
       </c>
@@ -8508,7 +8508,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5">
       <c r="A92" s="6">
         <v>40453</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5">
       <c r="A93" s="6">
         <v>40460</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5">
       <c r="A94" s="6">
         <v>40467</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5">
       <c r="A95" s="6">
         <v>40474</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5">
       <c r="A96" s="6">
         <v>40481</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5">
       <c r="A97" s="6">
         <v>40488</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5">
       <c r="A98" s="6">
         <v>40495</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5">
       <c r="A99" s="6">
         <v>40502</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5">
       <c r="A100" s="6">
         <v>40509</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="14" thickBot="1">
       <c r="A101" s="6">
         <v>40516</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="14" thickBot="1">
       <c r="A102" s="9">
         <v>40523</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="14" thickBot="1">
       <c r="A103" s="9">
         <v>40530</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="14" thickBot="1">
       <c r="A104" s="9">
         <v>40537</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="14" thickBot="1">
       <c r="A105" s="9">
         <v>40544</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="14" thickBot="1">
       <c r="A106" s="9">
         <v>40551</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="14" thickBot="1">
       <c r="A107" s="9">
         <v>40558</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="14" thickBot="1">
       <c r="A108" s="9">
         <v>40565</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="14" thickBot="1">
       <c r="A109" s="9">
         <v>40572</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="14" thickBot="1">
       <c r="A110" s="9">
         <v>40579</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="14" thickBot="1">
       <c r="A111" s="9">
         <v>40586</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="14" thickBot="1">
       <c r="A112" s="9">
         <v>40593</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="14" thickBot="1">
       <c r="A113" s="9">
         <v>40600</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="14" thickBot="1">
       <c r="A114" s="9">
         <v>40607</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="14" thickBot="1">
       <c r="A115" s="9">
         <v>40614</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="14" thickBot="1">
       <c r="A116" s="9">
         <v>40621</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="14" thickBot="1">
       <c r="A117" s="9">
         <v>40628</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="14" thickBot="1">
       <c r="A118" s="9">
         <v>40635</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="14" thickBot="1">
       <c r="A119" s="9">
         <v>40642</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="14" thickBot="1">
       <c r="A120" s="9">
         <v>40649</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="14" thickBot="1">
       <c r="A121" s="9">
         <v>40656</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="14" thickBot="1">
       <c r="A122" s="9">
         <v>40663</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="14" thickBot="1">
       <c r="A123" s="9">
         <v>40670</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="14" thickBot="1">
       <c r="A124" s="9">
         <v>40677</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="14" thickBot="1">
       <c r="A125" s="9">
         <v>40684</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="14" thickBot="1">
       <c r="A126" s="11">
         <v>40691</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="14" thickBot="1">
       <c r="A127" s="9">
         <v>40698</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="14" thickBot="1">
       <c r="A128" s="9">
         <v>40705</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="14" thickBot="1">
       <c r="A129" s="9">
         <v>40712</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="14" thickBot="1">
       <c r="A130" s="9">
         <v>40719</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="14" thickBot="1">
       <c r="A131" s="9">
         <v>40726</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="14" thickBot="1">
       <c r="A132" s="9">
         <v>40733</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="14" thickBot="1">
       <c r="A133" s="9">
         <v>40740</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="14" thickBot="1">
       <c r="A134" s="9">
         <v>40747</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="14" thickBot="1">
       <c r="A135" s="9">
         <v>40754</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="14" thickBot="1">
       <c r="A136" s="9">
         <v>40761</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="14" thickBot="1">
       <c r="A137" s="9">
         <v>40768</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="14" thickBot="1">
       <c r="A138" s="9">
         <v>40775</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="14" thickBot="1">
       <c r="A139" s="9">
         <v>40782</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="14" thickBot="1">
       <c r="A140" s="9">
         <v>40789</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="14" thickBot="1">
       <c r="A141" s="9">
         <v>40796</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="14" thickBot="1">
       <c r="A142" s="9">
         <v>40803</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="14" thickBot="1">
       <c r="A143" s="9">
         <v>40810</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="14" thickBot="1">
       <c r="A144" s="9">
         <v>40817</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="14" thickBot="1">
       <c r="A145" s="9">
         <v>40824</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="14" thickBot="1">
       <c r="A146" s="9">
         <v>40831</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="14" thickBot="1">
       <c r="A147" s="9">
         <v>40838</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="14" thickBot="1">
       <c r="A148" s="9">
         <v>40845</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="14" thickBot="1">
       <c r="A149" s="9">
         <v>40852</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="14" thickBot="1">
       <c r="A150" s="9">
         <v>40859</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="14" thickBot="1">
       <c r="A151" s="11">
         <v>40866</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="14" thickBot="1">
       <c r="A152" s="9">
         <v>40873</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="14" thickBot="1">
       <c r="A153" s="9">
         <v>40880</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="14" thickBot="1">
       <c r="A154" s="9">
         <v>40887</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="14" thickBot="1">
       <c r="A155" s="9">
         <v>40894</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="14" thickBot="1">
       <c r="A156" s="9">
         <v>40901</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="14" thickBot="1">
       <c r="A157" s="9">
         <v>40908</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="14" thickBot="1">
       <c r="A158" s="9">
         <v>40915</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="14" thickBot="1">
       <c r="A159" s="9">
         <v>40922</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="14" thickBot="1">
       <c r="A160" s="9">
         <v>40929</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="14" thickBot="1">
       <c r="A161" s="9">
         <v>40936</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="14" thickBot="1">
       <c r="A162" s="9">
         <v>40943</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="14" thickBot="1">
       <c r="A163" s="9">
         <v>40950</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="14" thickBot="1">
       <c r="A164" s="9">
         <v>40957</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="14" thickBot="1">
       <c r="A165" s="9">
         <v>40964</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="14" thickBot="1">
       <c r="A166" s="9">
         <v>40971</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="14" thickBot="1">
       <c r="A167" s="9">
         <v>40978</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="14" thickBot="1">
       <c r="A168" s="9">
         <v>40985</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="14" thickBot="1">
       <c r="A169" s="9">
         <v>40992</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="14" thickBot="1">
       <c r="A170" s="9">
         <v>40999</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="14" thickBot="1">
       <c r="A171" s="9">
         <v>41006</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="14" thickBot="1">
       <c r="A172" s="9">
         <v>41013</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="14" thickBot="1">
       <c r="A173" s="9">
         <v>41020</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="14" thickBot="1">
       <c r="A174" s="9">
         <v>41027</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="14" thickBot="1">
       <c r="A175" s="9">
         <v>41034</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="14" thickBot="1">
       <c r="A176" s="11">
         <v>41041</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="14" thickBot="1">
       <c r="A177" s="9">
         <v>41048</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="14" thickBot="1">
       <c r="A178" s="9">
         <v>41055</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="14" thickBot="1">
       <c r="A179" s="9">
         <v>41062</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="14" thickBot="1">
       <c r="A180" s="9">
         <v>41069</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="14" thickBot="1">
       <c r="A181" s="9">
         <v>41076</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="14" thickBot="1">
       <c r="A182" s="9">
         <v>41083</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="14" thickBot="1">
       <c r="A183" s="9">
         <v>41090</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="14" thickBot="1">
       <c r="A184" s="9">
         <v>41097</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="14" thickBot="1">
       <c r="A185" s="9">
         <v>41104</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" ht="14" thickBot="1">
       <c r="A186" s="9">
         <v>41111</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" ht="14" thickBot="1">
       <c r="A187" s="9">
         <v>41118</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" ht="14" thickBot="1">
       <c r="A188" s="9">
         <v>41125</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" ht="14" thickBot="1">
       <c r="A189" s="9">
         <v>41132</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" ht="14" thickBot="1">
       <c r="A190" s="9">
         <v>41139</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" ht="14" thickBot="1">
       <c r="A191" s="9">
         <v>41146</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" ht="14" thickBot="1">
       <c r="A192" s="9">
         <v>41153</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:5" ht="14" thickBot="1">
       <c r="A193" s="9">
         <v>41160</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:5" ht="14" thickBot="1">
       <c r="A194" s="9">
         <v>41167</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="14" thickBot="1">
       <c r="A195" s="9">
         <v>41174</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="14" thickBot="1">
       <c r="A196" s="9">
         <v>41181</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="14" thickBot="1">
       <c r="A197" s="9">
         <v>41188</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="14" thickBot="1">
       <c r="A198" s="9">
         <v>41195</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:5" ht="14" thickBot="1">
       <c r="A199" s="9">
         <v>41202</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:5" ht="14" thickBot="1">
       <c r="A200" s="9">
         <v>41209</v>
       </c>
@@ -10500,7 +10500,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:5" ht="14" thickBot="1">
       <c r="A201" s="11">
         <v>41216</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:5" ht="14" thickBot="1">
       <c r="A202" s="9">
         <v>41223</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:5" ht="14" thickBot="1">
       <c r="A203" s="9">
         <v>41230</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:5" ht="14" thickBot="1">
       <c r="A204" s="9">
         <v>41237</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:5" ht="14" thickBot="1">
       <c r="A205" s="9">
         <v>41244</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:5" ht="14" thickBot="1">
       <c r="A206" s="9">
         <v>41251</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:5" ht="14" thickBot="1">
       <c r="A207" s="9">
         <v>41258</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:5" ht="14" thickBot="1">
       <c r="A208" s="9">
         <v>41265</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="14" thickBot="1">
       <c r="A209" s="9">
         <v>41272</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="14" thickBot="1">
       <c r="A210" s="9">
         <v>41279</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" ht="14" thickBot="1">
       <c r="A211" s="9">
         <v>41286</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:5" ht="14" thickBot="1">
       <c r="A212" s="9">
         <v>41293</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:5" ht="14" thickBot="1">
       <c r="A213" s="9">
         <v>41300</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:5" ht="14" thickBot="1">
       <c r="A214" s="9">
         <v>41307</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:5" ht="14" thickBot="1">
       <c r="A215" s="9">
         <v>41314</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:5" ht="14" thickBot="1">
       <c r="A216" s="9">
         <v>41321</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="14" thickBot="1">
       <c r="A217" s="9">
         <v>41328</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="14" thickBot="1">
       <c r="A218" s="9">
         <v>41335</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="14" thickBot="1">
       <c r="A219" s="9">
         <v>41342</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="14" thickBot="1">
       <c r="A220" s="9">
         <v>41349</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="14" thickBot="1">
       <c r="A221" s="9">
         <v>41356</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="14" thickBot="1">
       <c r="A222" s="9">
         <v>41363</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="14" thickBot="1">
       <c r="A223" s="9">
         <v>41370</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="14" thickBot="1">
       <c r="A224" s="9">
         <v>41377</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="14" thickBot="1">
       <c r="A225" s="9">
         <v>41384</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="14" thickBot="1">
       <c r="A226" s="11">
         <v>41391</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="14" thickBot="1">
       <c r="A227" s="9">
         <v>41398</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="14" thickBot="1">
       <c r="A228" s="9">
         <v>41405</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="14" thickBot="1">
       <c r="A229" s="9">
         <v>41412</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="14" thickBot="1">
       <c r="A230" s="9">
         <v>41419</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="14" thickBot="1">
       <c r="A231" s="9">
         <v>41426</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="14" thickBot="1">
       <c r="A232" s="9">
         <v>41433</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="14" thickBot="1">
       <c r="A233" s="9">
         <v>41440</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="14" thickBot="1">
       <c r="A234" s="9">
         <v>41447</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="14" thickBot="1">
       <c r="A235" s="9">
         <v>41454</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="14" thickBot="1">
       <c r="A236" s="9">
         <v>41461</v>
       </c>
@@ -11148,7 +11148,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="14" thickBot="1">
       <c r="A237" s="9">
         <v>41468</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:5" ht="14" thickBot="1">
       <c r="A238" s="9">
         <v>41475</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="14" thickBot="1">
       <c r="A239" s="9">
         <v>41482</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="14" thickBot="1">
       <c r="A240" s="9">
         <v>41489</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="14" thickBot="1">
       <c r="A241" s="9">
         <v>41496</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="14" thickBot="1">
       <c r="A242" s="9">
         <v>41503</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="14" thickBot="1">
       <c r="A243" s="9">
         <v>41510</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="14" thickBot="1">
       <c r="A244" s="9">
         <v>41517</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="14" thickBot="1">
       <c r="A245" s="9">
         <v>41524</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="14" thickBot="1">
       <c r="A246" s="9">
         <v>41531</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="14" thickBot="1">
       <c r="A247" s="9">
         <v>41538</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="14" thickBot="1">
       <c r="A248" s="9">
         <v>41545</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="14" thickBot="1">
       <c r="A249" s="9">
         <v>41552</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="14" thickBot="1">
       <c r="A250" s="9">
         <v>41559</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="14" thickBot="1">
       <c r="A251" s="11">
         <v>41566</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="14" thickBot="1">
       <c r="A252" s="9">
         <v>41573</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="14" thickBot="1">
       <c r="A253" s="9">
         <v>41580</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="14" thickBot="1">
       <c r="A254" s="9">
         <v>41587</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="14" thickBot="1">
       <c r="A255" s="9">
         <v>41594</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:5" ht="14" thickBot="1">
       <c r="A256" s="9">
         <v>41601</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="14" thickBot="1">
       <c r="A257" s="9">
         <v>41608</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="14" thickBot="1">
       <c r="A258" s="9">
         <v>41615</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="14" thickBot="1">
       <c r="A259" s="9">
         <v>41622</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="14" thickBot="1">
       <c r="A260" s="9">
         <v>41629</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="14" thickBot="1">
       <c r="A261" s="9">
         <v>41636</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="14" thickBot="1">
       <c r="A262" s="9">
         <v>41643</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="14" thickBot="1">
       <c r="A263" s="9">
         <v>41650</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="14" thickBot="1">
       <c r="A264" s="9">
         <v>41657</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="14" thickBot="1">
       <c r="A265" s="9">
         <v>41664</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="14" thickBot="1">
       <c r="A266" s="9">
         <v>41671</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="14" thickBot="1">
       <c r="A267" s="9">
         <v>41678</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="14" thickBot="1">
       <c r="A268" s="9">
         <v>41685</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:5" ht="14" thickBot="1">
       <c r="A269" s="9">
         <v>41692</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:5" ht="14" thickBot="1">
       <c r="A270" s="9">
         <v>41699</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:5" ht="14" thickBot="1">
       <c r="A271" s="9">
         <v>41706</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:5" ht="14" thickBot="1">
       <c r="A272" s="9">
         <v>41713</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:5" ht="14" thickBot="1">
       <c r="A273" s="9">
         <v>41720</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:5" ht="14" thickBot="1">
       <c r="A274" s="9">
         <v>41727</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:5" ht="14" thickBot="1">
       <c r="A275" s="9">
         <v>41734</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:5" ht="14" thickBot="1">
       <c r="A276" s="11">
         <v>41741</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:5" ht="14" thickBot="1">
       <c r="A277" s="9">
         <v>41748</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:5" ht="14" thickBot="1">
       <c r="A278" s="9">
         <v>41755</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="14" thickBot="1">
       <c r="A279" s="9">
         <v>41762</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="14" thickBot="1">
       <c r="A280" s="9">
         <v>41769</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:5" ht="14" thickBot="1">
       <c r="A281" s="9">
         <v>41783</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:5" ht="14" thickBot="1">
       <c r="A282" s="9">
         <v>41790</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:5" ht="14" thickBot="1">
       <c r="A283" s="9">
         <v>41797</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="14" thickBot="1">
       <c r="A284" s="9">
         <v>41804</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="14" thickBot="1">
       <c r="A285" s="9">
         <v>41811</v>
       </c>
@@ -12045,7 +12045,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="14" thickBot="1">
       <c r="A286" s="9">
         <v>41818</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="14" thickBot="1">
       <c r="A287" s="9">
         <v>41825</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="14" thickBot="1">
       <c r="A288" s="9">
         <v>41832</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="14" thickBot="1">
       <c r="A289" s="9">
         <v>41839</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="14" thickBot="1">
       <c r="A290" s="9">
         <v>41846</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="14" thickBot="1">
       <c r="A291" s="9">
         <v>41853</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="14" thickBot="1">
       <c r="A292" s="9">
         <v>41860</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="14" thickBot="1">
       <c r="A293" s="9">
         <v>41867</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="14" thickBot="1">
       <c r="A294" s="9">
         <v>41874</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="14" thickBot="1">
       <c r="A295" s="9">
         <v>41881</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="14" thickBot="1">
       <c r="A296" s="9">
         <v>41888</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="14" thickBot="1">
       <c r="A297" s="9">
         <v>41895</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="14" thickBot="1">
       <c r="A298" s="9">
         <v>41902</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="14" thickBot="1">
       <c r="A299" s="9">
         <v>41909</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="14" thickBot="1">
       <c r="A300" s="9">
         <v>41916</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="14" thickBot="1">
       <c r="A301" s="11">
         <v>41923</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="14" thickBot="1">
       <c r="A302" s="9">
         <v>41930</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="14" thickBot="1">
       <c r="A303" s="9">
         <v>41937</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="14" thickBot="1">
       <c r="A304" s="9">
         <v>41944</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="14" thickBot="1">
       <c r="A305" s="9">
         <v>41951</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="14" thickBot="1">
       <c r="A306" s="9">
         <v>41958</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="14" thickBot="1">
       <c r="A307" s="9">
         <v>41965</v>
       </c>
@@ -12441,7 +12441,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="14" thickBot="1">
       <c r="A308" s="9">
         <v>41972</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:5" ht="14" thickBot="1">
       <c r="A309" s="9">
         <v>41979</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:5" ht="14" thickBot="1">
       <c r="A310" s="9">
         <v>41986</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:5" ht="14" thickBot="1">
       <c r="A311" s="9">
         <v>41993</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:5" ht="14" thickBot="1">
       <c r="A312" s="9">
         <v>42000</v>
       </c>
@@ -12531,7 +12531,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:5" ht="14" thickBot="1">
       <c r="A313" s="9">
         <v>42007</v>
       </c>
@@ -12549,7 +12549,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:5" ht="14" thickBot="1">
       <c r="A314" s="9">
         <v>42014</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:5" ht="14" thickBot="1">
       <c r="A315" s="9">
         <v>42021</v>
       </c>
@@ -12585,7 +12585,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:5" ht="14" thickBot="1">
       <c r="A316" s="9">
         <v>42028</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:5" ht="14" thickBot="1">
       <c r="A317" s="9">
         <v>42035</v>
       </c>
@@ -12621,7 +12621,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:5" ht="14" thickBot="1">
       <c r="A318" s="9">
         <v>42042</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:5" ht="14" thickBot="1">
       <c r="A319" s="9">
         <v>42049</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:5" ht="14" thickBot="1">
       <c r="A320" s="9">
         <v>42056</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:5" ht="14" thickBot="1">
       <c r="A321" s="9">
         <v>42063</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:5" ht="14" thickBot="1">
       <c r="A322" s="9">
         <v>42070</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:5" ht="14" thickBot="1">
       <c r="A323" s="9">
         <v>42077</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:5" ht="14" thickBot="1">
       <c r="A324" s="9">
         <v>42084</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:5" ht="14" thickBot="1">
       <c r="A325" s="9">
         <v>42091</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:5" ht="14" thickBot="1">
       <c r="A326" s="11">
         <v>42098</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:5" ht="14" thickBot="1">
       <c r="A327" s="9">
         <v>42105</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:5" ht="14" thickBot="1">
       <c r="A328" s="9">
         <v>42112</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:5" ht="14" thickBot="1">
       <c r="A329" s="9">
         <v>42119</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:5" ht="14" thickBot="1">
       <c r="A330" s="9">
         <v>42126</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:5" ht="14" thickBot="1">
       <c r="A331" s="9">
         <v>42133</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:5" ht="14" thickBot="1">
       <c r="A332" s="9">
         <v>42140</v>
       </c>
@@ -12906,7 +12906,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:5" ht="14" thickBot="1">
       <c r="A333" s="9">
         <v>42147</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:5" ht="14" thickBot="1">
       <c r="A334" s="9">
         <v>42154</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:5" ht="14" thickBot="1">
       <c r="A335" s="9">
         <v>42161</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:5" ht="14" thickBot="1">
       <c r="A336" s="9">
         <v>42168</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:5" ht="14" thickBot="1">
       <c r="A337" s="9">
         <v>42175</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:5" ht="14" thickBot="1">
       <c r="A338" s="9">
         <v>42182</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:5" ht="14" thickBot="1">
       <c r="A339" s="9">
         <v>42189</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:5" ht="14" thickBot="1">
       <c r="A340" s="9">
         <v>42196</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:5" ht="14" thickBot="1">
       <c r="A341" s="9">
         <v>42203</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:5" ht="14" thickBot="1">
       <c r="A342" s="9">
         <v>42210</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:5" ht="14" thickBot="1">
       <c r="A343" s="9">
         <v>42217</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:5" ht="14" thickBot="1">
       <c r="A344" s="9">
         <v>42224</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:5" ht="14" thickBot="1">
       <c r="A345" s="9">
         <v>42238</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:5" ht="14" thickBot="1">
       <c r="A346" s="9">
         <v>42245</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:5" ht="14" thickBot="1">
       <c r="A347" s="9">
         <v>42252</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:5" ht="14" thickBot="1">
       <c r="A348" s="9">
         <v>42259</v>
       </c>
@@ -13194,7 +13194,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:5" ht="14" thickBot="1">
       <c r="A349" s="9">
         <v>42266</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:5" ht="14" thickBot="1">
       <c r="A350" s="9">
         <v>42273</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:5" ht="14" thickBot="1">
       <c r="A351" s="11">
         <v>42280</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:5" ht="14" thickBot="1">
       <c r="A352" s="9">
         <v>42287</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:5" ht="14" thickBot="1">
       <c r="A353" s="9">
         <v>42294</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:5" ht="14" thickBot="1">
       <c r="A354" s="9">
         <v>42301</v>
       </c>
@@ -13302,7 +13302,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:5" ht="14" thickBot="1">
       <c r="A355" s="9">
         <v>42308</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:5" ht="14" thickBot="1">
       <c r="A356" s="9">
         <v>42315</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:5" ht="14" thickBot="1">
       <c r="A357" s="9">
         <v>42322</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:5" ht="14" thickBot="1">
       <c r="A358" s="9">
         <v>42336</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:5" ht="14" thickBot="1">
       <c r="A359" s="9">
         <v>42343</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:5" ht="14" thickBot="1">
       <c r="A360" s="9">
         <v>42350</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:5" ht="14" thickBot="1">
       <c r="A361" s="9">
         <v>42357</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:5" ht="14" thickBot="1">
       <c r="A362" s="9">
         <v>42364</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:5" ht="14" thickBot="1">
       <c r="A363" s="9">
         <v>42371</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:5" ht="14" thickBot="1">
       <c r="A364" s="9">
         <v>42378</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:5" ht="14" thickBot="1">
       <c r="A365" s="9">
         <v>42385</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:5" ht="14" thickBot="1">
       <c r="A366" s="9">
         <v>42392</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:5" ht="14" thickBot="1">
       <c r="A367" s="9">
         <v>42399</v>
       </c>
@@ -13536,7 +13536,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:5" ht="14" thickBot="1">
       <c r="A368" s="9">
         <v>42406</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:5" ht="14" thickBot="1">
       <c r="A369" s="9">
         <v>42413</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:5" ht="14" thickBot="1">
       <c r="A370" s="9">
         <v>42420</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:5" ht="14" thickBot="1">
       <c r="A371" s="9">
         <v>42427</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:5" ht="14" thickBot="1">
       <c r="A372" s="9">
         <v>42434</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:5" ht="14" thickBot="1">
       <c r="A373" s="9">
         <v>42441</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:5" ht="14" thickBot="1">
       <c r="A374" s="9">
         <v>42448</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:5" ht="14" thickBot="1">
       <c r="A375" s="9">
         <v>42455</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:5" ht="14" thickBot="1">
       <c r="A376" s="11">
         <v>42462</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:5" ht="14" thickBot="1">
       <c r="A377" s="9">
         <v>42469</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:5" ht="14" thickBot="1">
       <c r="A378" s="9">
         <v>42476</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:5" ht="14" thickBot="1">
       <c r="A379" s="9">
         <v>42483</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:5" ht="14" thickBot="1">
       <c r="A380" s="9">
         <v>42490</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:5" ht="14" thickBot="1">
       <c r="A381" s="9">
         <v>42497</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:5" ht="14" thickBot="1">
       <c r="A382" s="9">
         <v>42504</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:5" ht="14" thickBot="1">
       <c r="A383" s="9">
         <v>42511</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:5" ht="14" thickBot="1">
       <c r="A384" s="9">
         <v>42518</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:5" ht="14" thickBot="1">
       <c r="A385" s="9">
         <v>42525</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:5" ht="14" thickBot="1">
       <c r="A386" s="9">
         <v>42532</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:5" ht="14" thickBot="1">
       <c r="A387" s="9">
         <v>42539</v>
       </c>
@@ -13911,7 +13911,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:5" ht="14" thickBot="1">
       <c r="A388" s="9">
         <v>42546</v>
       </c>
@@ -13929,7 +13929,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:5" ht="14" thickBot="1">
       <c r="A389" s="9">
         <v>42553</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:5" ht="14" thickBot="1">
       <c r="A390" s="9">
         <v>42560</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:5" ht="14" thickBot="1">
       <c r="A391" s="9">
         <v>42567</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:5" ht="14" thickBot="1">
       <c r="A392" s="9">
         <v>42574</v>
       </c>
@@ -14001,7 +14001,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:5" ht="14" thickBot="1">
       <c r="A393" s="9">
         <v>42581</v>
       </c>
@@ -14019,7 +14019,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:5" ht="14" thickBot="1">
       <c r="A394" s="9">
         <v>42588</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:5" ht="14" thickBot="1">
       <c r="A395" s="9">
         <v>42595</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:5" ht="14" thickBot="1">
       <c r="A396" s="9">
         <v>42602</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:5" ht="14" thickBot="1">
       <c r="A397" s="9">
         <v>42609</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:5" ht="14" thickBot="1">
       <c r="A398" s="9">
         <v>42616</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:5" ht="14" thickBot="1">
       <c r="A399" s="9">
         <v>42623</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:5" ht="14" thickBot="1">
       <c r="A400" s="9">
         <v>42630</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:5" ht="14" thickBot="1">
       <c r="A401" s="11">
         <v>42637</v>
       </c>
@@ -14163,7 +14163,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:5" ht="14" thickBot="1">
       <c r="A402" s="9">
         <v>42644</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:5" ht="14" thickBot="1">
       <c r="A403" s="9">
         <v>42651</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:5" ht="14" thickBot="1">
       <c r="A404" s="9">
         <v>42658</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:5" ht="14" thickBot="1">
       <c r="A405" s="9">
         <v>42665</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:5" ht="14" thickBot="1">
       <c r="A406" s="9">
         <v>42672</v>
       </c>
@@ -14253,7 +14253,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:5" ht="14" thickBot="1">
       <c r="A407" s="9">
         <v>42679</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:5" ht="14" thickBot="1">
       <c r="A408" s="9">
         <v>42686</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:5" ht="14" thickBot="1">
       <c r="A409" s="9">
         <v>42693</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:5" ht="14" thickBot="1">
       <c r="A410" s="9">
         <v>42700</v>
       </c>
@@ -14325,7 +14325,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:5" ht="14" thickBot="1">
       <c r="A411" s="9">
         <v>42707</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:5" ht="14" thickBot="1">
       <c r="A412" s="9">
         <v>42714</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:5" ht="14" thickBot="1">
       <c r="A413" s="9">
         <v>42721</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:5" ht="14" thickBot="1">
       <c r="A414" s="9">
         <v>42728</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:5" ht="14" thickBot="1">
       <c r="A415" s="9">
         <v>42735</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:5" ht="14" thickBot="1">
       <c r="A416" s="9">
         <v>42742</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:5" ht="14" thickBot="1">
       <c r="A417" s="9">
         <v>42749</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:5" ht="14" thickBot="1">
       <c r="A418" s="9">
         <v>42756</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:5" ht="14" thickBot="1">
       <c r="A419" s="9">
         <v>42763</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:5" ht="14" thickBot="1">
       <c r="A420" s="9">
         <v>42770</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:5" ht="14" thickBot="1">
       <c r="A421" s="9">
         <v>42777</v>
       </c>
@@ -14523,7 +14523,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:5" ht="14" thickBot="1">
       <c r="A422" s="9">
         <v>42784</v>
       </c>
@@ -14541,7 +14541,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:5" ht="14" thickBot="1">
       <c r="A423" s="9">
         <v>42791</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:5" ht="14" thickBot="1">
       <c r="A424" s="9">
         <v>42798</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:5" ht="14" thickBot="1">
       <c r="A425" s="9">
         <v>42805</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:5" ht="14" thickBot="1">
       <c r="A426" s="11">
         <v>42812</v>
       </c>
@@ -14613,7 +14613,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:5" ht="14" thickBot="1">
       <c r="A427" s="9">
         <v>42819</v>
       </c>
@@ -14631,7 +14631,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:5" ht="14" thickBot="1">
       <c r="A428" s="9">
         <v>42826</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:5" ht="14" thickBot="1">
       <c r="A429" s="9">
         <v>42833</v>
       </c>
@@ -14667,7 +14667,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:5" ht="14" thickBot="1">
       <c r="A430" s="9">
         <v>42840</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:5" ht="14" thickBot="1">
       <c r="A431" s="9">
         <v>42847</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:5" ht="14" thickBot="1">
       <c r="A432" s="9">
         <v>42854</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:5" ht="14" thickBot="1">
       <c r="A433" s="9">
         <v>42861</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:5" ht="14" thickBot="1">
       <c r="A434" s="9">
         <v>42868</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:5" ht="14" thickBot="1">
       <c r="A435" s="9">
         <v>42875</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:5" ht="14" thickBot="1">
       <c r="A436" s="9">
         <v>42882</v>
       </c>
@@ -14793,7 +14793,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:5" ht="14" thickBot="1">
       <c r="A437" s="9">
         <v>42889</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:5" ht="14" thickBot="1">
       <c r="A438" s="9">
         <v>42896</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:5" ht="14" thickBot="1">
       <c r="A439" s="9">
         <v>42903</v>
       </c>
@@ -14847,7 +14847,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:5" ht="14" thickBot="1">
       <c r="A440" s="9">
         <v>42910</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:5" ht="14" thickBot="1">
       <c r="A441" s="9">
         <v>42917</v>
       </c>
@@ -14883,7 +14883,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:5" ht="14" thickBot="1">
       <c r="A442" s="9">
         <v>42924</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:5" ht="14" thickBot="1">
       <c r="A443" s="9">
         <v>42931</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:5" ht="14" thickBot="1">
       <c r="A444" s="9">
         <v>42938</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:5" ht="14" thickBot="1">
       <c r="A445" s="9">
         <v>42945</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:5" ht="14" thickBot="1">
       <c r="A446" s="9">
         <v>42952</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:5" ht="14" thickBot="1">
       <c r="A447" s="9">
         <v>42959</v>
       </c>
@@ -14991,7 +14991,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:5" ht="14" thickBot="1">
       <c r="A448" s="9">
         <v>42966</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:5" ht="14" thickBot="1">
       <c r="A449" s="9">
         <v>42973</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:5" ht="14" thickBot="1">
       <c r="A450" s="9">
         <v>42980</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:5" ht="14" thickBot="1">
       <c r="A451" s="11">
         <v>42987</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:5" ht="14" thickBot="1">
       <c r="A452" s="9">
         <v>42994</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:5" ht="14" thickBot="1">
       <c r="A453" s="9">
         <v>43001</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:5" ht="14" thickBot="1">
       <c r="A454" s="9">
         <v>43008</v>
       </c>
@@ -15132,7 +15132,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:5" ht="14" thickBot="1">
       <c r="A455" s="9">
         <v>43015</v>
       </c>
@@ -15150,7 +15150,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:5" ht="14" thickBot="1">
       <c r="A456" s="9">
         <v>43022</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:5" ht="14" thickBot="1">
       <c r="A457" s="9">
         <v>43029</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:5" ht="14" thickBot="1">
       <c r="A458" s="9">
         <v>43036</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:5" ht="14" thickBot="1">
       <c r="A459" s="9">
         <v>43043</v>
       </c>
@@ -15222,7 +15222,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:5" ht="14" thickBot="1">
       <c r="A460" s="9">
         <v>43050</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:5" ht="14" thickBot="1">
       <c r="A461" s="9">
         <v>43057</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:5" ht="14" thickBot="1">
       <c r="A462" s="9">
         <v>43064</v>
       </c>
@@ -15276,7 +15276,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:5" ht="14" thickBot="1">
       <c r="A463" s="9">
         <v>43071</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:5" ht="14" thickBot="1">
       <c r="A464" s="9">
         <v>43078</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:5" ht="14" thickBot="1">
       <c r="A465" s="9">
         <v>43085</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:5" ht="14" thickBot="1">
       <c r="A466" s="9">
         <v>43092</v>
       </c>
@@ -15348,7 +15348,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:5" ht="14" thickBot="1">
       <c r="A467" s="9">
         <v>43099</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:5" ht="14" thickBot="1">
       <c r="A468" s="9">
         <v>43113</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:5" ht="14" thickBot="1">
       <c r="A469" s="9">
         <v>43120</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:5" ht="14" thickBot="1">
       <c r="A470" s="9">
         <v>43127</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:5" ht="14" thickBot="1">
       <c r="A471" s="9">
         <v>43134</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:5" ht="14" thickBot="1">
       <c r="A472" s="9">
         <v>43141</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:5" ht="14" thickBot="1">
       <c r="A473" s="9">
         <v>43148</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:5" ht="14" thickBot="1">
       <c r="A474" s="9">
         <v>43155</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:5" ht="14" thickBot="1">
       <c r="A475" s="9">
         <v>43162</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:5" ht="14" thickBot="1">
       <c r="A476" s="11">
         <v>43169</v>
       </c>
@@ -15528,7 +15528,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:5" ht="14" thickBot="1">
       <c r="A477" s="9">
         <v>43176</v>
       </c>
@@ -15546,7 +15546,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:5" ht="14" thickBot="1">
       <c r="A478" s="9">
         <v>43183</v>
       </c>
@@ -15564,7 +15564,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:5" ht="14" thickBot="1">
       <c r="A479" s="9">
         <v>43190</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:5" ht="14" thickBot="1">
       <c r="A480" s="9">
         <v>43197</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:5" ht="14" thickBot="1">
       <c r="A481" s="9">
         <v>43204</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:5" ht="14" thickBot="1">
       <c r="A482" s="9">
         <v>43211</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:5" ht="14" thickBot="1">
       <c r="A483" s="9">
         <v>43218</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:5" ht="14" thickBot="1">
       <c r="A484" s="9">
         <v>43225</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:5" ht="14" thickBot="1">
       <c r="A485" s="9">
         <v>43232</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:5" ht="14" thickBot="1">
       <c r="A486" s="9">
         <v>43239</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:5" ht="14" thickBot="1">
       <c r="A487" s="9">
         <v>43246</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:5" ht="14" thickBot="1">
       <c r="A488" s="9">
         <v>43253</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:5" ht="14" thickBot="1">
       <c r="A489" s="9">
         <v>43260</v>
       </c>
@@ -15762,7 +15762,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:5" ht="14" thickBot="1">
       <c r="A490" s="9">
         <v>43267</v>
       </c>
@@ -15780,7 +15780,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:5" ht="14" thickBot="1">
       <c r="A491" s="9">
         <v>43274</v>
       </c>
@@ -15798,7 +15798,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:5" ht="14" thickBot="1">
       <c r="A492" s="9">
         <v>43281</v>
       </c>
@@ -15816,7 +15816,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:5" ht="14" thickBot="1">
       <c r="A493" s="9">
         <v>43288</v>
       </c>
@@ -15834,7 +15834,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:5" ht="14" thickBot="1">
       <c r="A494" s="9">
         <v>43295</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:5" ht="14" thickBot="1">
       <c r="A495" s="9">
         <v>43302</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:5" ht="14" thickBot="1">
       <c r="A496" s="9">
         <v>43309</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:5" ht="14" thickBot="1">
       <c r="A497" s="9">
         <v>43316</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:5" ht="14" thickBot="1">
       <c r="A498" s="9">
         <v>43323</v>
       </c>
@@ -15924,7 +15924,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:5" ht="14" thickBot="1">
       <c r="A499" s="9">
         <v>43330</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:5" ht="14" thickBot="1">
       <c r="A500" s="9">
         <v>43337</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:5" ht="14" thickBot="1">
       <c r="A501" s="11">
         <v>43344</v>
       </c>
@@ -15978,7 +15978,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:5" ht="14" thickBot="1">
       <c r="A502" s="9">
         <v>43351</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:5" ht="14" thickBot="1">
       <c r="A503" s="9">
         <v>43358</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:5" ht="14" thickBot="1">
       <c r="A504" s="9">
         <v>43365</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:5" ht="14" thickBot="1">
       <c r="A505" s="9">
         <v>43372</v>
       </c>
@@ -16050,7 +16050,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:5" ht="14" thickBot="1">
       <c r="A506" s="9">
         <v>43379</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:5" ht="14" thickBot="1">
       <c r="A507" s="9">
         <v>43386</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:5" ht="14" thickBot="1">
       <c r="A508" s="9">
         <v>43393</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:5" ht="14" thickBot="1">
       <c r="A509" s="9">
         <v>43400</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:5" ht="14" thickBot="1">
       <c r="A510" s="9">
         <v>43407</v>
       </c>
@@ -16140,7 +16140,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:5" ht="14" thickBot="1">
       <c r="A511" s="9">
         <v>43414</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:5" ht="14" thickBot="1">
       <c r="A512" s="9">
         <v>43421</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:5" ht="14" thickBot="1">
       <c r="A513" s="9">
         <v>43428</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:5" ht="14" thickBot="1">
       <c r="A514" s="9">
         <v>43435</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:5" ht="14" thickBot="1">
       <c r="A515" s="9">
         <v>43442</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:5" ht="14" thickBot="1">
       <c r="A516" s="9">
         <v>43449</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:5" ht="14" thickBot="1">
       <c r="A517" s="9">
         <v>43456</v>
       </c>
@@ -16281,7 +16281,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:5" ht="14" thickBot="1">
       <c r="A518" s="9">
         <v>43463</v>
       </c>
@@ -16299,7 +16299,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:5" ht="14" thickBot="1">
       <c r="A519" s="9">
         <v>43470</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:5" ht="14" thickBot="1">
       <c r="A520" s="9">
         <v>43477</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:5" ht="14" thickBot="1">
       <c r="A521" s="9">
         <v>43484</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:5" ht="14" thickBot="1">
       <c r="A522" s="9">
         <v>43491</v>
       </c>
@@ -16371,7 +16371,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:5" ht="14" thickBot="1">
       <c r="A523" s="9">
         <v>43498</v>
       </c>
@@ -16389,7 +16389,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:5" ht="14" thickBot="1">
       <c r="A524" s="9">
         <v>43505</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:5" ht="14" thickBot="1">
       <c r="A525" s="9">
         <v>43512</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:5" ht="14" thickBot="1">
       <c r="A526" s="11">
         <v>43519</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:5" ht="14" thickBot="1">
       <c r="A527" s="9">
         <v>43526</v>
       </c>
@@ -16461,7 +16461,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:5" ht="14" thickBot="1">
       <c r="A528" s="9">
         <v>43533</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:5" ht="14" thickBot="1">
       <c r="A529" s="9">
         <v>43540</v>
       </c>
@@ -16497,7 +16497,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:5" ht="14" thickBot="1">
       <c r="A530" s="9">
         <v>43547</v>
       </c>
@@ -16515,7 +16515,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:5" ht="14" thickBot="1">
       <c r="A531" s="9">
         <v>43554</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:5" ht="14" thickBot="1">
       <c r="A532" s="9">
         <v>43561</v>
       </c>
@@ -16551,7 +16551,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:5" ht="14" thickBot="1">
       <c r="A533" s="9">
         <v>43568</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:5" ht="14" thickBot="1">
       <c r="A534" s="9">
         <v>43575</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:5" ht="14" thickBot="1">
       <c r="A535" s="9">
         <v>43582</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:5" ht="14" thickBot="1">
       <c r="A536" s="9">
         <v>43589</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:5" ht="14" thickBot="1">
       <c r="A537" s="9">
         <v>43596</v>
       </c>
@@ -16641,7 +16641,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:5" ht="14" thickBot="1">
       <c r="A538" s="9">
         <v>43603</v>
       </c>
@@ -16659,7 +16659,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:5" ht="14" thickBot="1">
       <c r="A539" s="9">
         <v>43610</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:5" ht="14" thickBot="1">
       <c r="A540" s="9">
         <v>43617</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:5" ht="14" thickBot="1">
       <c r="A541" s="9">
         <v>43624</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:5" ht="14" thickBot="1">
       <c r="A542" s="9">
         <v>43631</v>
       </c>
@@ -16731,7 +16731,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:5" ht="14" thickBot="1">
       <c r="A543" s="9">
         <v>43638</v>
       </c>
@@ -16749,7 +16749,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:5" ht="14" thickBot="1">
       <c r="A544" s="9">
         <v>43645</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:5" ht="14" thickBot="1">
       <c r="A545" s="9">
         <v>43652</v>
       </c>
@@ -16785,7 +16785,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:5" ht="14" thickBot="1">
       <c r="A546" s="9">
         <v>43659</v>
       </c>
@@ -16803,7 +16803,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:5" ht="14" thickBot="1">
       <c r="A547" s="9">
         <v>43666</v>
       </c>
@@ -16821,7 +16821,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:5" ht="14" thickBot="1">
       <c r="A548" s="9">
         <v>43673</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:5" ht="14" thickBot="1">
       <c r="A549" s="9">
         <v>43680</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:5" ht="14" thickBot="1">
       <c r="A550" s="9">
         <v>43687</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:5" ht="14" thickBot="1">
       <c r="A551" s="11">
         <v>43694</v>
       </c>
@@ -16893,7 +16893,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:5" ht="14" thickBot="1">
       <c r="A552" s="9">
         <v>43701</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:5" ht="14" thickBot="1">
       <c r="A553" s="9">
         <v>43708</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:5" ht="14" thickBot="1">
       <c r="A554" s="9">
         <v>43715</v>
       </c>
@@ -16947,7 +16947,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:5" ht="14" thickBot="1">
       <c r="A555" s="9">
         <v>43722</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:5" ht="14" thickBot="1">
       <c r="A556" s="9">
         <v>43729</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:5" ht="14" thickBot="1">
       <c r="A557" s="9">
         <v>43736</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:5" ht="14" thickBot="1">
       <c r="A558" s="9">
         <v>43743</v>
       </c>
@@ -17019,7 +17019,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:5" ht="14" thickBot="1">
       <c r="A559" s="9">
         <v>43750</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:5" ht="14" thickBot="1">
       <c r="A560" s="9">
         <v>43757</v>
       </c>
@@ -17055,7 +17055,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:5" ht="14" thickBot="1">
       <c r="A561" s="9">
         <v>43764</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:5" ht="14" thickBot="1">
       <c r="A562" s="9">
         <v>43771</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:5" ht="14" thickBot="1">
       <c r="A563" s="9">
         <v>43778</v>
       </c>
@@ -17109,7 +17109,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:5" ht="14" thickBot="1">
       <c r="A564" s="9">
         <v>43785</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:5" ht="14" thickBot="1">
       <c r="A565" s="9">
         <v>43792</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:5" ht="14" thickBot="1">
       <c r="A566" s="9">
         <v>43813</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:5" ht="14" thickBot="1">
       <c r="A567" s="9">
         <v>43820</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:5" ht="14" thickBot="1">
       <c r="A568" s="9">
         <v>43827</v>
       </c>
@@ -17199,7 +17199,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:5" ht="14" thickBot="1">
       <c r="A569" s="9">
         <v>43834</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:5" ht="14" thickBot="1">
       <c r="A570" s="9">
         <v>43841</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:5" ht="14" thickBot="1">
       <c r="A571" s="9">
         <v>43848</v>
       </c>
@@ -17253,7 +17253,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:5" ht="14" thickBot="1">
       <c r="A572" s="9">
         <v>43855</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:5" ht="14" thickBot="1">
       <c r="A573" s="9">
         <v>43862</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:5" ht="14" thickBot="1">
       <c r="A574" s="9">
         <v>43869</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:5" ht="14" thickBot="1">
       <c r="A575" s="9">
         <v>43876</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:5" ht="14" thickBot="1">
       <c r="A576" s="11">
         <v>43883</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:5" ht="14" thickBot="1">
       <c r="A577" s="9">
         <v>43890</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:5" ht="14" thickBot="1">
       <c r="A578" s="9">
         <v>43897</v>
       </c>
@@ -17394,7 +17394,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:5" ht="14" thickBot="1">
       <c r="A579" s="9">
         <v>43904</v>
       </c>
@@ -17412,7 +17412,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:5" ht="14" thickBot="1">
       <c r="A580" s="9">
         <v>43911</v>
       </c>
@@ -17430,7 +17430,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:5" ht="14" thickBot="1">
       <c r="A581" s="9">
         <v>43918</v>
       </c>
@@ -17448,7 +17448,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:5" ht="14" thickBot="1">
       <c r="A582" s="9">
         <v>43925</v>
       </c>
@@ -17466,7 +17466,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:5" ht="14" thickBot="1">
       <c r="A583" s="9">
         <v>43932</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:5" ht="14" thickBot="1">
       <c r="A584" s="9">
         <v>43939</v>
       </c>
@@ -17502,7 +17502,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:5" ht="14" thickBot="1">
       <c r="A585" s="9">
         <v>43946</v>
       </c>
@@ -17520,7 +17520,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:5" ht="14" thickBot="1">
       <c r="A586" s="9">
         <v>43953</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:5" ht="14" thickBot="1">
       <c r="A587" s="9">
         <v>43960</v>
       </c>
@@ -17556,7 +17556,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:5" ht="14" thickBot="1">
       <c r="A588" s="9">
         <v>43967</v>
       </c>
@@ -17574,7 +17574,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:5" ht="14" thickBot="1">
       <c r="A589" s="9">
         <v>43974</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:5" ht="14" thickBot="1">
       <c r="A590" s="9">
         <v>43981</v>
       </c>
@@ -17610,7 +17610,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:5" ht="14" thickBot="1">
       <c r="A591" s="9">
         <v>43988</v>
       </c>
@@ -17628,7 +17628,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:5" ht="14" thickBot="1">
       <c r="A592" s="9">
         <v>43995</v>
       </c>
@@ -17646,7 +17646,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:5" ht="14" thickBot="1">
       <c r="A593" s="9">
         <v>44002</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:5" ht="14" thickBot="1">
       <c r="A594" s="9">
         <v>44009</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:5" ht="14" thickBot="1">
       <c r="A595" s="9">
         <v>44016</v>
       </c>
@@ -17700,7 +17700,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:5" ht="14" thickBot="1">
       <c r="A596" s="9">
         <v>44023</v>
       </c>
@@ -17718,7 +17718,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:5" ht="14" thickBot="1">
       <c r="A597" s="9">
         <v>44030</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:5" ht="14" thickBot="1">
       <c r="A598" s="9">
         <v>44037</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:5" ht="14" thickBot="1">
       <c r="A599" s="9">
         <v>44044</v>
       </c>
@@ -17772,7 +17772,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:5" ht="14" thickBot="1">
       <c r="A600" s="9">
         <v>44051</v>
       </c>
@@ -17790,7 +17790,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:5" ht="14" thickBot="1">
       <c r="A601" s="11">
         <v>44058</v>
       </c>
@@ -17808,7 +17808,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:5" ht="14" thickBot="1">
       <c r="A602" s="9">
         <v>44072</v>
       </c>
@@ -17826,7 +17826,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:5" ht="14" thickBot="1">
       <c r="A603" s="9">
         <v>44079</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:5" ht="14" thickBot="1">
       <c r="A604" s="9">
         <v>44086</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:5" ht="14" thickBot="1">
       <c r="A605" s="9">
         <v>44093</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:5" ht="14" thickBot="1">
       <c r="A606" s="9">
         <v>44100</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:5" ht="14" thickBot="1">
       <c r="A607" s="9">
         <v>44107</v>
       </c>
@@ -17916,7 +17916,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:5" ht="14" thickBot="1">
       <c r="A608" s="9">
         <v>44114</v>
       </c>
@@ -17934,7 +17934,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:5" ht="14" thickBot="1">
       <c r="A609" s="9">
         <v>44121</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:5" ht="14" thickBot="1">
       <c r="A610" s="9">
         <v>44128</v>
       </c>
@@ -17970,7 +17970,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:5" ht="14" thickBot="1">
       <c r="A611" s="9">
         <v>44135</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:5" ht="14" thickBot="1">
       <c r="A612" s="9">
         <v>44142</v>
       </c>
@@ -18006,7 +18006,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:5" ht="14" thickBot="1">
       <c r="A613" s="9">
         <v>44149</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:5" ht="14" thickBot="1">
       <c r="A614" s="9">
         <v>44156</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:5" ht="14" thickBot="1">
       <c r="A615" s="9">
         <v>44163</v>
       </c>
@@ -18060,7 +18060,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:5" ht="14" thickBot="1">
       <c r="A616" s="9">
         <v>44170</v>
       </c>
@@ -18078,7 +18078,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:5" ht="14" thickBot="1">
       <c r="A617" s="9">
         <v>44177</v>
       </c>
@@ -18096,7 +18096,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:5" ht="14" thickBot="1">
       <c r="A618" s="9">
         <v>44191</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:5" ht="14" thickBot="1">
       <c r="A619" s="9">
         <v>44198</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:5" ht="14" thickBot="1">
       <c r="A620" s="9">
         <v>44205</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:5" ht="14" thickBot="1">
       <c r="A621" s="9">
         <v>44212</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:5" ht="14" thickBot="1">
       <c r="A622" s="9">
         <v>44219</v>
       </c>
@@ -18186,7 +18186,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:5" ht="14" thickBot="1">
       <c r="A623" s="9">
         <v>44226</v>
       </c>
@@ -18204,7 +18204,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:5" ht="14" thickBot="1">
       <c r="A624" s="9">
         <v>44233</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:5" ht="14" thickBot="1">
       <c r="A625" s="9">
         <v>44240</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:5" ht="14" thickBot="1">
       <c r="A626" s="11">
         <v>44247</v>
       </c>
@@ -18258,7 +18258,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:5" ht="14" thickBot="1">
       <c r="A627" s="9">
         <v>44254</v>
       </c>
@@ -18276,7 +18276,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:5" ht="14" thickBot="1">
       <c r="A628" s="9">
         <v>44261</v>
       </c>
@@ -18294,7 +18294,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:5" ht="14" thickBot="1">
       <c r="A629" s="9">
         <v>44268</v>
       </c>
@@ -18312,7 +18312,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:5" ht="14" thickBot="1">
       <c r="A630" s="9">
         <v>44275</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:5" ht="14" thickBot="1">
       <c r="A631" s="9">
         <v>44282</v>
       </c>
@@ -18348,7 +18348,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:5" ht="14" thickBot="1">
       <c r="A632" s="9">
         <v>44289</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:5" ht="14" thickBot="1">
       <c r="A633" s="9">
         <v>44296</v>
       </c>
@@ -18384,7 +18384,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:5" ht="14" thickBot="1">
       <c r="A634" s="9">
         <v>44303</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:5" ht="14" thickBot="1">
       <c r="A635" s="9">
         <v>44310</v>
       </c>
@@ -18420,7 +18420,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:5" ht="14" thickBot="1">
       <c r="A636" s="9">
         <v>44317</v>
       </c>
@@ -18438,7 +18438,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:5" ht="14" thickBot="1">
       <c r="A637" s="9">
         <v>44324</v>
       </c>
@@ -18456,7 +18456,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:5" ht="14" thickBot="1">
       <c r="A638" s="9">
         <v>44331</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:5" ht="14" thickBot="1">
       <c r="A639" s="9">
         <v>44338</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:5" ht="14" thickBot="1">
       <c r="A640" s="9">
         <v>44345</v>
       </c>
@@ -18510,7 +18510,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:5" ht="14" thickBot="1">
       <c r="A641" s="9">
         <v>44352</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:5" ht="14" thickBot="1">
       <c r="A642" s="9">
         <v>44359</v>
       </c>
@@ -18561,7 +18561,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:5" ht="14" thickBot="1">
       <c r="A643" s="9">
         <v>44366</v>
       </c>
@@ -18579,7 +18579,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:5" ht="14" thickBot="1">
       <c r="A644" s="9">
         <v>44373</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:5" ht="14" thickBot="1">
       <c r="A645" s="9">
         <v>44380</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:5" ht="14" thickBot="1">
       <c r="A646" s="9">
         <v>44387</v>
       </c>
@@ -18633,7 +18633,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:5" ht="14" thickBot="1">
       <c r="A647" s="9">
         <v>44394</v>
       </c>
@@ -18651,7 +18651,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:5" ht="14" thickBot="1">
       <c r="A648" s="9">
         <v>44401</v>
       </c>
@@ -18669,7 +18669,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:5" ht="14" thickBot="1">
       <c r="A649" s="9">
         <v>44408</v>
       </c>
@@ -18687,7 +18687,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:5" ht="14" thickBot="1">
       <c r="A650" s="9">
         <v>44415</v>
       </c>
@@ -18705,7 +18705,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:5" ht="14" thickBot="1">
       <c r="A651" s="11">
         <v>44422</v>
       </c>
@@ -18723,7 +18723,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:5" ht="14" thickBot="1">
       <c r="A652" s="9">
         <v>44429</v>
       </c>
@@ -18741,7 +18741,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:5" ht="14" thickBot="1">
       <c r="A653" s="9">
         <v>44436</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:5" ht="14" thickBot="1">
       <c r="A654" s="9">
         <v>44443</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:5" ht="14" thickBot="1">
       <c r="A655" s="9">
         <v>44450</v>
       </c>
@@ -18795,7 +18795,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:5" ht="14" thickBot="1">
       <c r="A656" s="9">
         <v>44457</v>
       </c>
@@ -18813,7 +18813,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:5" ht="14" thickBot="1">
       <c r="A657" s="9">
         <v>44464</v>
       </c>
@@ -18831,7 +18831,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:5" ht="14" thickBot="1">
       <c r="A658" s="9">
         <v>44471</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:5" ht="14" thickBot="1">
       <c r="A659" s="9">
         <v>44478</v>
       </c>
@@ -18867,7 +18867,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:5" ht="14" thickBot="1">
       <c r="A660" s="9">
         <v>44485</v>
       </c>
@@ -18885,7 +18885,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:5" ht="14" thickBot="1">
       <c r="A661" s="9">
         <v>44492</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:5" ht="14" thickBot="1">
       <c r="A662" s="9">
         <v>44499</v>
       </c>
@@ -18921,7 +18921,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:5" ht="14" thickBot="1">
       <c r="A663" s="9">
         <v>44506</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:5" ht="14" thickBot="1">
       <c r="A664" s="9">
         <v>44513</v>
       </c>
@@ -18957,7 +18957,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:5" ht="14" thickBot="1">
       <c r="A665" s="9">
         <v>44520</v>
       </c>
@@ -18975,7 +18975,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:5" ht="14" thickBot="1">
       <c r="A666" s="9">
         <v>44527</v>
       </c>
@@ -18993,7 +18993,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:5" ht="14" thickBot="1">
       <c r="A667" s="9">
         <v>44534</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:5" ht="14" thickBot="1">
       <c r="A668" s="9">
         <v>44541</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:5" ht="14" thickBot="1">
       <c r="A669" s="9">
         <v>44548</v>
       </c>
@@ -19047,7 +19047,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:5" ht="14" thickBot="1">
       <c r="A670" s="9">
         <v>44555</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:5" ht="14" thickBot="1">
       <c r="A671" s="9">
         <v>44562</v>
       </c>
@@ -19083,7 +19083,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:5" ht="14" thickBot="1">
       <c r="A672" s="9">
         <v>44569</v>
       </c>
@@ -19101,7 +19101,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:5" ht="14" thickBot="1">
       <c r="A673" s="9">
         <v>44576</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:5" ht="14" thickBot="1">
       <c r="A674" s="9">
         <v>44583</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:5" ht="14" thickBot="1">
       <c r="A675" s="9">
         <v>44590</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:5" ht="14" thickBot="1">
       <c r="A676" s="11">
         <v>44597</v>
       </c>
@@ -19173,7 +19173,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:5" ht="14" thickBot="1">
       <c r="A677" s="9">
         <v>44604</v>
       </c>
@@ -19191,7 +19191,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:5" ht="14" thickBot="1">
       <c r="A678" s="9">
         <v>44611</v>
       </c>
@@ -19209,7 +19209,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:5" ht="14" thickBot="1">
       <c r="A679" s="9">
         <v>44625</v>
       </c>
@@ -19227,7 +19227,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:5" ht="14" thickBot="1">
       <c r="A680" s="9">
         <v>44632</v>
       </c>
@@ -19245,7 +19245,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:5" ht="14" thickBot="1">
       <c r="A681" s="9">
         <v>44639</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:5" ht="14" thickBot="1">
       <c r="A682" s="9">
         <v>44646</v>
       </c>
@@ -19281,7 +19281,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:5" ht="14" thickBot="1">
       <c r="A683" s="9">
         <v>44653</v>
       </c>
@@ -19299,7 +19299,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:5" ht="14" thickBot="1">
       <c r="A684" s="9">
         <v>44660</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:5" ht="14" thickBot="1">
       <c r="A685" s="9">
         <v>44667</v>
       </c>
@@ -19335,7 +19335,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:5" ht="14" thickBot="1">
       <c r="A686" s="9">
         <v>44674</v>
       </c>
@@ -19353,7 +19353,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:5" ht="14" thickBot="1">
       <c r="A687" s="9">
         <v>44681</v>
       </c>
@@ -19371,7 +19371,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:5" ht="14" thickBot="1">
       <c r="A688" s="9">
         <v>44688</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:5" ht="14" thickBot="1">
       <c r="A689" s="9">
         <v>44695</v>
       </c>
@@ -19407,7 +19407,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:5" ht="14" thickBot="1">
       <c r="A690" s="9">
         <v>44702</v>
       </c>
@@ -19425,7 +19425,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:5" ht="14" thickBot="1">
       <c r="A691" s="9">
         <v>44709</v>
       </c>
@@ -19443,7 +19443,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:5" ht="14" thickBot="1">
       <c r="A692" s="9">
         <v>44716</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:5" ht="14" thickBot="1">
       <c r="A693" s="9">
         <v>44723</v>
       </c>
@@ -19479,7 +19479,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:5" ht="14" thickBot="1">
       <c r="A694" s="9">
         <v>44730</v>
       </c>
@@ -19497,7 +19497,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:5" ht="14" thickBot="1">
       <c r="A695" s="9">
         <v>44737</v>
       </c>
@@ -19515,7 +19515,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:5" ht="14" thickBot="1">
       <c r="A696" s="9">
         <v>44744</v>
       </c>
@@ -19533,7 +19533,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:5" ht="14" thickBot="1">
       <c r="A697" s="9">
         <v>44751</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:5" ht="14" thickBot="1">
       <c r="A698" s="9">
         <v>44758</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:5" ht="14" thickBot="1">
       <c r="A699" s="9">
         <v>44765</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:5" ht="14" thickBot="1">
       <c r="A700" s="9">
         <v>44772</v>
       </c>
@@ -19605,7 +19605,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:5" ht="14" thickBot="1">
       <c r="A701" s="11">
         <v>44779</v>
       </c>
@@ -19623,7 +19623,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:5" ht="14" thickBot="1">
       <c r="A702" s="9">
         <v>44786</v>
       </c>
@@ -19641,7 +19641,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:5" ht="14" thickBot="1">
       <c r="A703" s="9">
         <v>44793</v>
       </c>
@@ -19659,7 +19659,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:5" ht="14" thickBot="1">
       <c r="A704" s="9">
         <v>44800</v>
       </c>
@@ -19677,7 +19677,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:5" ht="14" thickBot="1">
       <c r="A705" s="9">
         <v>44807</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:5" ht="14" thickBot="1">
       <c r="A706" s="9">
         <v>44814</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:5" ht="14" thickBot="1">
       <c r="A707" s="9">
         <v>44821</v>
       </c>
@@ -19746,7 +19746,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:5" ht="14" thickBot="1">
       <c r="A708" s="9">
         <v>44828</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:5" ht="14" thickBot="1">
       <c r="A709" s="9">
         <v>44835</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:5" ht="14" thickBot="1">
       <c r="A710" s="9">
         <v>44842</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:5" ht="14" thickBot="1">
       <c r="A711" s="9">
         <v>44849</v>
       </c>
@@ -19818,7 +19818,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:5" ht="14" thickBot="1">
       <c r="A712" s="9">
         <v>44856</v>
       </c>
@@ -19836,7 +19836,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:5" ht="14" thickBot="1">
       <c r="A713" s="9">
         <v>44863</v>
       </c>
@@ -19854,7 +19854,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:5" ht="14" thickBot="1">
       <c r="A714" s="9">
         <v>44870</v>
       </c>
@@ -19872,7 +19872,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:5" ht="14" thickBot="1">
       <c r="A715" s="9">
         <v>44877</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:5" ht="14" thickBot="1">
       <c r="A716" s="9">
         <v>44884</v>
       </c>
@@ -19908,7 +19908,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:5" ht="14" thickBot="1">
       <c r="A717" s="9">
         <v>44891</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:5" ht="14" thickBot="1">
       <c r="A718" s="9">
         <v>44898</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:5" ht="14" thickBot="1">
       <c r="A719" s="9">
         <v>44905</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:5" ht="14" thickBot="1">
       <c r="A720" s="9">
         <v>44912</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:5" ht="14" thickBot="1">
       <c r="A721" s="9">
         <v>44919</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:5" ht="14" thickBot="1">
       <c r="A722" s="9">
         <v>44926</v>
       </c>
@@ -20016,7 +20016,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:5" ht="14" thickBot="1">
       <c r="A723" s="9">
         <v>44933</v>
       </c>
@@ -20034,7 +20034,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:5" ht="14" thickBot="1">
       <c r="A724" s="9">
         <v>44940</v>
       </c>
@@ -20052,7 +20052,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:5" ht="14" thickBot="1">
       <c r="A725" s="9">
         <v>44947</v>
       </c>
@@ -20070,7 +20070,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:5" ht="14" thickBot="1">
       <c r="A726" s="11">
         <v>44954</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:5" ht="14" thickBot="1">
       <c r="A727" s="9">
         <v>44961</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:5" ht="14" thickBot="1">
       <c r="A728" s="9">
         <v>44968</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:5" ht="14" thickBot="1">
       <c r="A729" s="9">
         <v>44975</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:5" ht="14" thickBot="1">
       <c r="A730" s="9">
         <v>44982</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:5" ht="14" thickBot="1">
       <c r="A731" s="9">
         <v>44989</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:5" ht="14" thickBot="1">
       <c r="A732" s="9">
         <v>44996</v>
       </c>
@@ -20196,7 +20196,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:5" ht="14" thickBot="1">
       <c r="A733" s="9">
         <v>45003</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:5" ht="14" thickBot="1">
       <c r="A734" s="9">
         <v>45010</v>
       </c>
@@ -20232,7 +20232,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:5" ht="14" thickBot="1">
       <c r="A735" s="9">
         <v>45017</v>
       </c>
@@ -20250,7 +20250,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:5" ht="14" thickBot="1">
       <c r="A736" s="9">
         <v>45024</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:5" ht="14" thickBot="1">
       <c r="A737" s="9">
         <v>45031</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:5" ht="14" thickBot="1">
       <c r="A738" s="9">
         <v>45038</v>
       </c>
@@ -20304,7 +20304,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:5" ht="14" thickBot="1">
       <c r="A739" s="9">
         <v>45045</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:5" ht="14" thickBot="1">
       <c r="A740" s="9">
         <v>45052</v>
       </c>
@@ -20340,7 +20340,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:5" ht="14" thickBot="1">
       <c r="A741" s="9">
         <v>45059</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:5" ht="14" thickBot="1">
       <c r="A742" s="9">
         <v>45066</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:5" ht="14" thickBot="1">
       <c r="A743" s="9">
         <v>45073</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:5" ht="14" thickBot="1">
       <c r="A744" s="9">
         <v>45080</v>
       </c>
@@ -20412,7 +20412,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:5" ht="14" thickBot="1">
       <c r="A745" s="9">
         <v>45087</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:5" ht="14" thickBot="1">
       <c r="A746" s="9">
         <v>45094</v>
       </c>
@@ -20448,7 +20448,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:5" ht="14" thickBot="1">
       <c r="A747" s="9">
         <v>45101</v>
       </c>
@@ -20466,7 +20466,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:5" ht="14" thickBot="1">
       <c r="A748" s="9">
         <v>45108</v>
       </c>
@@ -20484,7 +20484,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:5" ht="14" thickBot="1">
       <c r="A749" s="9">
         <v>45115</v>
       </c>
@@ -20502,7 +20502,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:5" ht="14" thickBot="1">
       <c r="A750" s="9">
         <v>45122</v>
       </c>
@@ -20520,7 +20520,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:5" ht="14" thickBot="1">
       <c r="A751" s="11">
         <v>45129</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:5" ht="14" thickBot="1">
       <c r="A752" s="9">
         <v>45136</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:5" ht="14" thickBot="1">
       <c r="A753" s="9">
         <v>45143</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:5" ht="14" thickBot="1">
       <c r="A754" s="9">
         <v>45150</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:5" ht="14" thickBot="1">
       <c r="A755" s="9">
         <v>45157</v>
       </c>
@@ -20610,7 +20610,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:5" ht="14" thickBot="1">
       <c r="A756" s="9">
         <v>45164</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:5" ht="14" thickBot="1">
       <c r="A757" s="9">
         <v>45171</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:5" ht="14" thickBot="1">
       <c r="A758" s="9">
         <v>45178</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:5" ht="14" thickBot="1">
       <c r="A759" s="9">
         <v>45185</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:5" ht="14" thickBot="1">
       <c r="A760" s="9">
         <v>45192</v>
       </c>
@@ -20700,7 +20700,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:5" ht="14" thickBot="1">
       <c r="A761" s="9">
         <v>45199</v>
       </c>
@@ -20718,7 +20718,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:5" ht="14" thickBot="1">
       <c r="A762" s="9">
         <v>45206</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:5" ht="14" thickBot="1">
       <c r="A763" s="9">
         <v>45213</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:5" ht="14" thickBot="1">
       <c r="A764" s="9">
         <v>45220</v>
       </c>
@@ -20772,7 +20772,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:5" ht="14" thickBot="1">
       <c r="A765" s="9">
         <v>45227</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:5" ht="14" thickBot="1">
       <c r="A766" s="9">
         <v>45234</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:5" ht="14" thickBot="1">
       <c r="A767" s="9">
         <v>45241</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:5" ht="14" thickBot="1">
       <c r="A768" s="9">
         <v>45248</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:5" ht="14" thickBot="1">
       <c r="A769" s="9">
         <v>45255</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:5" ht="14" thickBot="1">
       <c r="A770" s="9">
         <v>45262</v>
       </c>
@@ -20895,7 +20895,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:5" ht="14" thickBot="1">
       <c r="A771" s="9">
         <v>45269</v>
       </c>
@@ -20913,7 +20913,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:5" ht="14" thickBot="1">
       <c r="A772" s="9">
         <v>45276</v>
       </c>
@@ -20931,7 +20931,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:5" ht="14" thickBot="1">
       <c r="A773" s="9">
         <v>45283</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:5" ht="14" thickBot="1">
       <c r="A774" s="9">
         <v>45297</v>
       </c>
@@ -20967,7 +20967,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:5" ht="14" thickBot="1">
       <c r="A775" s="9">
         <v>45304</v>
       </c>
@@ -20985,7 +20985,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:5" ht="14" thickBot="1">
       <c r="A776" s="13">
         <v>45311</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:5" ht="14" thickBot="1">
       <c r="A777" s="15">
         <v>45318</v>
       </c>
@@ -21021,7 +21021,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:5" ht="14" thickBot="1">
       <c r="A778" s="15">
         <v>45325</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:5" ht="14" thickBot="1">
       <c r="A779" s="15">
         <v>45332</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:5" ht="14" thickBot="1">
       <c r="A780" s="15">
         <v>45339</v>
       </c>
@@ -21075,7 +21075,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:5" ht="14" thickBot="1">
       <c r="A781" s="15">
         <v>45346</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:5" ht="14" thickBot="1">
       <c r="A782" s="15">
         <v>45353</v>
       </c>
@@ -21111,7 +21111,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:5" ht="14" thickBot="1">
       <c r="A783" s="15">
         <v>45360</v>
       </c>
@@ -21129,7 +21129,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:5" ht="14" thickBot="1">
       <c r="A784" s="15">
         <v>45367</v>
       </c>
@@ -21147,7 +21147,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:5" ht="14" thickBot="1">
       <c r="A785" s="15">
         <v>45374</v>
       </c>
@@ -21165,7 +21165,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:5" ht="14" thickBot="1">
       <c r="A786" s="15">
         <v>45381</v>
       </c>
@@ -21183,7 +21183,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:5" ht="14" thickBot="1">
       <c r="A787" s="15">
         <v>45388</v>
       </c>
@@ -21201,7 +21201,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:5" ht="14" thickBot="1">
       <c r="A788" s="15">
         <v>45395</v>
       </c>
@@ -21219,7 +21219,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:5" ht="14" thickBot="1">
       <c r="A789" s="15">
         <v>45402</v>
       </c>
@@ -21237,7 +21237,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:5" ht="14" thickBot="1">
       <c r="A790" s="15">
         <v>45409</v>
       </c>
@@ -21255,7 +21255,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:5" ht="14" thickBot="1">
       <c r="A791" s="15">
         <v>45416</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:5" ht="14" thickBot="1">
       <c r="A792" s="15">
         <v>45423</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:5" ht="14" thickBot="1">
       <c r="A793" s="15">
         <v>45430</v>
       </c>
@@ -21309,7 +21309,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:5" ht="14" thickBot="1">
       <c r="A794" s="15">
         <v>45437</v>
       </c>
@@ -21327,7 +21327,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:5" ht="14" thickBot="1">
       <c r="A795" s="15">
         <v>45444</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:5" ht="14" thickBot="1">
       <c r="A796" s="15">
         <v>45451</v>
       </c>
@@ -21363,7 +21363,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:5" ht="14" thickBot="1">
       <c r="A797" s="15">
         <v>45458</v>
       </c>
@@ -21381,7 +21381,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:5" ht="14" thickBot="1">
       <c r="A798" s="15">
         <v>45465</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:5" ht="14" thickBot="1">
       <c r="A799" s="15">
         <v>45472</v>
       </c>
@@ -21417,7 +21417,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:5" ht="14" thickBot="1">
       <c r="A800" s="15">
         <v>45479</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:5" ht="14" thickBot="1">
       <c r="A801" s="13">
         <v>45486</v>
       </c>
@@ -21453,7 +21453,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:5" ht="14" thickBot="1">
       <c r="A802" s="15">
         <v>45493</v>
       </c>
@@ -21471,7 +21471,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:5" ht="14" thickBot="1">
       <c r="A803" s="15">
         <v>45500</v>
       </c>
@@ -21489,7 +21489,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:5" ht="14" thickBot="1">
       <c r="A804" s="15">
         <v>45507</v>
       </c>
@@ -21507,7 +21507,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:5" ht="14" thickBot="1">
       <c r="A805" s="15">
         <v>45514</v>
       </c>
@@ -21525,7 +21525,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:5" ht="14" thickBot="1">
       <c r="A806" s="15">
         <v>45521</v>
       </c>
@@ -21543,7 +21543,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:5" ht="14" thickBot="1">
       <c r="A807" s="15">
         <v>45528</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:5" ht="14" thickBot="1">
       <c r="A808" s="15">
         <v>45535</v>
       </c>
@@ -21579,7 +21579,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:5" ht="14" thickBot="1">
       <c r="A809" s="15">
         <v>45542</v>
       </c>
@@ -21597,7 +21597,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:5" ht="14" thickBot="1">
       <c r="A810" s="15">
         <v>45549</v>
       </c>
@@ -21615,7 +21615,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:5" ht="14" thickBot="1">
       <c r="A811" s="15">
         <v>45556</v>
       </c>
@@ -21633,7 +21633,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:5" ht="14" thickBot="1">
       <c r="A812" s="15">
         <v>45563</v>
       </c>
@@ -21651,7 +21651,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:5" ht="14" thickBot="1">
       <c r="A813" s="15">
         <v>45570</v>
       </c>
@@ -21669,7 +21669,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:5" ht="14" thickBot="1">
       <c r="A814" s="15">
         <v>45577</v>
       </c>
@@ -21687,7 +21687,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:5" ht="14" thickBot="1">
       <c r="A815" s="15">
         <v>45584</v>
       </c>
@@ -21705,7 +21705,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:5" ht="14" thickBot="1">
       <c r="A816" s="15">
         <v>45591</v>
       </c>
@@ -21723,7 +21723,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:5" ht="14" thickBot="1">
       <c r="A817" s="15">
         <v>45598</v>
       </c>
@@ -21741,7 +21741,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:5" ht="14" thickBot="1">
       <c r="A818" s="15">
         <v>45612</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:5" ht="14" thickBot="1">
       <c r="A819" s="15">
         <v>45619</v>
       </c>
@@ -21777,7 +21777,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:5" ht="14" thickBot="1">
       <c r="A820" s="15">
         <v>45626</v>
       </c>
@@ -21795,7 +21795,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:5" ht="14" thickBot="1">
       <c r="A821" s="15">
         <v>45633</v>
       </c>
@@ -21813,7 +21813,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:5" ht="14" thickBot="1">
       <c r="A822" s="15">
         <v>45640</v>
       </c>
@@ -21831,7 +21831,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:5" ht="14" thickBot="1">
       <c r="A823" s="15">
         <v>45647</v>
       </c>
@@ -21849,7 +21849,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:5" ht="14" thickBot="1">
       <c r="A824" s="15">
         <v>45654</v>
       </c>
@@ -21867,7 +21867,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:5" ht="14" thickBot="1">
       <c r="A825" s="15">
         <v>45661</v>
       </c>
@@ -21885,7 +21885,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:5" ht="14" thickBot="1">
       <c r="A826" s="13">
         <v>45668</v>
       </c>
@@ -21903,7 +21903,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:5" ht="14" thickBot="1">
       <c r="A827" s="15">
         <v>45675</v>
       </c>
@@ -21921,7 +21921,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:5" ht="14" thickBot="1">
       <c r="A828" s="15">
         <v>45682</v>
       </c>
@@ -21939,7 +21939,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:5" ht="14" thickBot="1">
       <c r="A829" s="15">
         <v>45689</v>
       </c>
@@ -21957,7 +21957,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:5" ht="14" thickBot="1">
       <c r="A830" s="15">
         <v>45696</v>
       </c>
@@ -21975,7 +21975,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:5" ht="14" thickBot="1">
       <c r="A831" s="15">
         <v>45703</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:5" ht="14" thickBot="1">
       <c r="A832" s="15">
         <v>45710</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:5" ht="14" thickBot="1">
       <c r="A833" s="15">
         <v>45717</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:5" ht="14" thickBot="1">
       <c r="A834" s="15">
         <v>45724</v>
       </c>
@@ -22062,7 +22062,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:5" ht="14" thickBot="1">
       <c r="A835" s="15">
         <v>45731</v>
       </c>
@@ -22080,7 +22080,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:5" ht="14" thickBot="1">
       <c r="A836" s="15">
         <v>45738</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:5" ht="14" thickBot="1">
       <c r="A837" s="15">
         <v>45745</v>
       </c>
@@ -22116,7 +22116,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:5" ht="14" thickBot="1">
       <c r="A838" s="15">
         <v>45752</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:5" ht="14" thickBot="1">
       <c r="A839" s="15">
         <v>45759</v>
       </c>
@@ -22152,7 +22152,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:5" ht="14" thickBot="1">
       <c r="A840" s="15">
         <v>45766</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:5" ht="14" thickBot="1">
       <c r="A841" s="15">
         <v>45773</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:5" ht="14" thickBot="1">
       <c r="A842" s="15">
         <v>45780</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:5" ht="14" thickBot="1">
       <c r="A843" s="15">
         <v>45787</v>
       </c>
@@ -22224,7 +22224,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:5" ht="14" thickBot="1">
       <c r="A844" s="15">
         <v>45794</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:5" ht="14" thickBot="1">
       <c r="A845" s="15">
         <v>45801</v>
       </c>
@@ -22260,7 +22260,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:5" ht="14" thickBot="1">
       <c r="A846" s="15">
         <v>45808</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:5" ht="14" thickBot="1">
       <c r="A847" s="15">
         <v>45815</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:5" ht="14" thickBot="1">
       <c r="A848" s="15">
         <v>45822</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:5" ht="14" thickBot="1">
       <c r="A849" s="15">
         <v>45829</v>
       </c>
@@ -22332,7 +22332,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:5" ht="14" thickBot="1">
       <c r="A850" s="15">
         <v>45836</v>
       </c>
@@ -22350,7 +22350,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:5" ht="14" thickBot="1">
       <c r="A851" s="13">
         <v>45843</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:5" ht="14" thickBot="1">
       <c r="A852" s="15">
         <v>45850</v>
       </c>
@@ -22386,7 +22386,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:5" ht="14" thickBot="1">
       <c r="A853" s="15">
         <v>45857</v>
       </c>
@@ -22404,7 +22404,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:5" ht="14" thickBot="1">
       <c r="A854" s="15">
         <v>45864</v>
       </c>
@@ -22422,7 +22422,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:5" ht="14" thickBot="1">
       <c r="A855" s="15">
         <v>45871</v>
       </c>
@@ -22440,7 +22440,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:5" ht="14" thickBot="1">
       <c r="A856" s="15">
         <v>45878</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:5" ht="14" thickBot="1">
       <c r="A857" s="15">
         <v>45885</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:5" ht="14" thickBot="1">
       <c r="A858" s="15">
         <v>45892</v>
       </c>
@@ -22494,7 +22494,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:5" ht="14" thickBot="1">
       <c r="A859" s="15">
         <v>45899</v>
       </c>
@@ -22512,7 +22512,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:5" ht="14" thickBot="1">
       <c r="A860" s="15">
         <v>45906</v>
       </c>
@@ -22530,7 +22530,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:5" ht="14" thickBot="1">
       <c r="A861" s="15">
         <v>45913</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:5" ht="14" thickBot="1">
       <c r="A862" s="15">
         <v>45920</v>
       </c>
@@ -22566,7 +22566,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:5" ht="14" thickBot="1">
       <c r="A863" s="13">
         <v>45927</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:5" ht="14" thickBot="1">
       <c r="A864" s="15">
         <v>45934</v>
       </c>
@@ -22602,7 +22602,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:5" ht="14" thickBot="1">
       <c r="A865" s="15">
         <v>45941</v>
       </c>
@@ -22620,7 +22620,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:5" ht="14" thickBot="1">
       <c r="A866" s="15">
         <v>45948</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:5" ht="14" thickBot="1">
       <c r="A867" s="15">
         <v>45955</v>
       </c>
@@ -22656,7 +22656,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:5" ht="14" thickBot="1">
       <c r="A868" s="15">
         <v>45962</v>
       </c>
@@ -22674,7 +22674,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:5" ht="14" thickBot="1">
       <c r="A869" s="15">
         <v>45969</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:5" ht="14" thickBot="1">
       <c r="A870" s="15">
         <v>45976</v>
       </c>
@@ -22710,7 +22710,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:5" ht="14" thickBot="1">
       <c r="A871" s="15">
         <v>45983</v>
       </c>
@@ -22728,7 +22728,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:5" ht="14" thickBot="1">
       <c r="A872" s="15">
         <v>45990</v>
       </c>
@@ -22746,7 +22746,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:5" ht="14" thickBot="1">
       <c r="A873" s="15">
         <v>45997</v>
       </c>
@@ -22764,7 +22764,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:5" ht="14" thickBot="1">
       <c r="A874" s="15">
         <v>46004</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:5" ht="14" thickBot="1">
       <c r="A875" s="13">
         <v>46018</v>
       </c>
@@ -22800,7 +22800,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:5" ht="14" thickBot="1">
       <c r="A876" s="7">
         <v>46025</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:5" ht="14" thickBot="1">
       <c r="A877" s="13">
         <v>46032</v>
       </c>
@@ -22836,7 +22836,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:5" ht="14" thickBot="1">
       <c r="A878" s="7">
         <v>46039</v>
       </c>
@@ -22869,7 +22869,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:5" ht="14" thickBot="1">
       <c r="A879" s="13">
         <v>46046</v>
       </c>
@@ -22902,7 +22902,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:5" ht="14" thickBot="1">
       <c r="A880" s="13">
         <v>46053</v>
       </c>
@@ -22935,7 +22935,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:5" ht="14" thickBot="1">
       <c r="A881" s="13">
         <v>46060</v>
       </c>
@@ -22953,7 +22953,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:5" ht="14" thickBot="1">
       <c r="A882" s="7">
         <v>46067</v>
       </c>
@@ -22986,7 +22986,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:5" ht="14" thickBot="1">
       <c r="A883" s="13">
         <v>46074</v>
       </c>
@@ -23019,7 +23019,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:5" ht="14" thickBot="1">
       <c r="A884" s="7">
         <v>46081</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:5" ht="14" thickBot="1">
       <c r="A885" s="13">
         <v>46088</v>
       </c>
@@ -23055,7 +23055,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:5">
       <c r="A886" s="7">
         <v>46102</v>
       </c>
@@ -23073,7 +23073,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:5">
       <c r="A887" s="7">
         <v>46109</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:5">
       <c r="A888" s="7">
         <v>46116</v>
       </c>
@@ -23109,7 +23109,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:5">
       <c r="A889" s="7">
         <v>46123</v>
       </c>
@@ -23127,7 +23127,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:5">
       <c r="A890" s="7">
         <v>46130</v>
       </c>
@@ -23145,7 +23145,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:5">
       <c r="A891" s="7">
         <v>46137</v>
       </c>
@@ -23163,7 +23163,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:5">
       <c r="A892" s="7">
         <v>46144</v>
       </c>
@@ -23181,7 +23181,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:5">
       <c r="A893" s="7">
         <v>46151</v>
       </c>
@@ -23214,7 +23214,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:5">
       <c r="A894" s="7">
         <v>46158</v>
       </c>
@@ -23232,7 +23232,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:5">
       <c r="A895" s="7">
         <v>46165</v>
       </c>
@@ -23248,6 +23248,36 @@
       </c>
       <c r="E895" s="17">
         <v>523574</v>
+      </c>
+    </row>
+    <row r="896" spans="1:5">
+      <c r="A896" s="7">
+        <v>46172</v>
+      </c>
+      <c r="B896" s="7">
+        <v>46176</v>
+      </c>
+      <c r="C896" s="21">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D896" s="6" t="str">
+        <f t="shared" ref="D896" si="17">IF(
+ AND(
+  A896 &gt;= IF(
+         YEAR(A896)&gt;=2007,
+         DATE(YEAR(A896),3,14)-WEEKDAY(DATE(YEAR(A896),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A896),4,7)-WEEKDAY(DATE(YEAR(A896),4,7),1)+1 + TIME(2,0,0)
+       ),
+  A896 &lt;  IF(
+         YEAR(A896)&gt;=2007,
+         DATE(YEAR(A896),11,7)-WEEKDAY(DATE(YEAR(A896),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(A896),10,31)-WEEKDAY(DATE(YEAR(A896),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
@@ -23263,7 +23293,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23274,12 +23304,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23287,7 +23317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23295,7 +23325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:3">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>

--- a/data/freight/US Rail Traffic.xlsx
+++ b/data/freight/US Rail Traffic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB239FD-B313-4594-A098-CA884F631184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A94987-9107-44BC-B992-F8762E3FA7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55EF15CE-83DB-4E42-B75D-C3DAE3AA4C48}"/>
   </bookViews>
   <sheets>
     <sheet name="USRT" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -265,9 +265,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -285,7 +285,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6534,9 +6534,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6574,7 +6574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6680,7 +6680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6822,7 +6822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6831,17 +6831,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FCC8DB-37A0-4531-B65E-34C65BAF4830}">
   <dimension ref="A1:E896"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" style="17" customWidth="1"/>
-    <col min="6" max="16384" width="9.08984375" style="5"/>
+    <col min="5" max="5" width="12.44140625" style="17" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>39823</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>474565</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>39830</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>465386</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>39837</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>462128</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>39844</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>449966</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>39851</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>455757</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>39858</v>
       </c>
@@ -6981,7 +6981,7 @@
         <v>471961</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>39865</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>446575</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>39872</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>458242</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>39879</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>455041</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>39886</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>455686</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>39893</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>459547</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>39900</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>439844</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>39907</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>447103</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>39914</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>426107</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>39921</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>438602</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>39928</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>444794</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>39935</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>442378</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>39942</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>435052</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>39949</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>438329</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>39956</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>451355</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>39963</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>401248</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>39970</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>448743</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>39977</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>451065</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39984</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>449103</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>39991</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>444212</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>39998</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>410661</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>40005</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>439041</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>40012</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>456926</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>40019</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>467395</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>40026</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>468150</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>40033</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>469814</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>40040</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>469727</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>40047</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>472644</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>40054</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>488273</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>40061</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>486009</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>40068</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>439238</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>40075</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>487236</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>40082</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>477434</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>40089</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>484157</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>40096</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>481944</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>40103</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>481827</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>40110</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>483850</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>40117</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>479450</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>40124</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>481493</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>40131</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>489073</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>40138</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>500284</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>40145</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>412036</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>40152</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>491440</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>40159</v>
       </c>
@@ -7755,7 +7755,7 @@
         <v>464948</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>40166</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>481426</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>40173</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>339702</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>40180</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>376455</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>40187</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>433584</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>40194</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>465758</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>40201</v>
       </c>
@@ -7863,7 +7863,7 @@
         <v>478227</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>40208</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>482390</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>40215</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>469221</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>40222</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>450177</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>40229</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>474203</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>40236</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>496078</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>40243</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>497456</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>40250</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>491463</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>40257</v>
       </c>
@@ -8007,7 +8007,7 @@
         <v>488939</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>40264</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>504028</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>40271</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>40278</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>492044</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>40285</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>506502</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>40292</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>510565</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>40299</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>508731</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>40306</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>497714</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>40313</v>
       </c>
@@ -8166,7 +8166,7 @@
         <v>508469</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>40320</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>503232</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>40327</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>511776</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>40334</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>462009</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>40341</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>512048</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>40348</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>512898</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>40355</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>511945</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>40362</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>518063</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>40369</v>
       </c>
@@ -8310,7 +8310,7 @@
         <v>445917</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>40376</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>509860</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>40383</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>517297</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>40390</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>533187</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>40397</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>515715</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>40404</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>529715</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>40411</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>533038</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>40418</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>539552</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>40425</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>542006</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="6">
         <v>40432</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>484380</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="6">
         <v>40439</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>544692</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="6">
         <v>40446</v>
       </c>
@@ -8508,7 +8508,7 @@
         <v>542075</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="6">
         <v>40453</v>
       </c>
@@ -8526,7 +8526,7 @@
         <v>539646</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="6">
         <v>40460</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>533301</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="6">
         <v>40467</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>540844</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="6">
         <v>40474</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>538461</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="6">
         <v>40481</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>525601</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="6">
         <v>40488</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>519134</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="6">
         <v>40495</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>530157</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="6">
         <v>40502</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>533989</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="6">
         <v>40509</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>437911</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="14" thickBot="1">
+    <row r="101" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6">
         <v>40516</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>539405</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="14" thickBot="1">
+    <row r="102" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="9">
         <v>40523</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>520326</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="14" thickBot="1">
+    <row r="103" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="9">
         <v>40530</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>491896</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="14" thickBot="1">
+    <row r="104" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="9">
         <v>40537</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>433347</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="14" thickBot="1">
+    <row r="105" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="9">
         <v>40544</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>406967</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="14" thickBot="1">
+    <row r="106" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="9">
         <v>40551</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>498773</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="14" thickBot="1">
+    <row r="107" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="9">
         <v>40558</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>496473</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="14" thickBot="1">
+    <row r="108" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="9">
         <v>40565</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>496043</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="14" thickBot="1">
+    <row r="109" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="9">
         <v>40572</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>513889</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="14" thickBot="1">
+    <row r="110" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="9">
         <v>40579</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>465931</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="14" thickBot="1">
+    <row r="111" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="9">
         <v>40586</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>502078</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="14" thickBot="1">
+    <row r="112" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="9">
         <v>40593</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>530973</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="14" thickBot="1">
+    <row r="113" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="9">
         <v>40600</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>516841</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="14" thickBot="1">
+    <row r="114" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="9">
         <v>40607</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>515296</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="14" thickBot="1">
+    <row r="115" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="9">
         <v>40614</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>508992</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="14" thickBot="1">
+    <row r="116" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="9">
         <v>40621</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>516560</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="14" thickBot="1">
+    <row r="117" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="9">
         <v>40628</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>522937</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="14" thickBot="1">
+    <row r="118" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="9">
         <v>40635</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>540213</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="14" thickBot="1">
+    <row r="119" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="9">
         <v>40642</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>522511</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="14" thickBot="1">
+    <row r="120" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="9">
         <v>40649</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>525886</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="14" thickBot="1">
+    <row r="121" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="9">
         <v>40656</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>518374</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="14" thickBot="1">
+    <row r="122" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="9">
         <v>40663</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>525024</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="14" thickBot="1">
+    <row r="123" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="9">
         <v>40670</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>514038</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14" thickBot="1">
+    <row r="124" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="9">
         <v>40677</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>526146</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="14" thickBot="1">
+    <row r="125" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="9">
         <v>40684</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>529383</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="14" thickBot="1">
+    <row r="126" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="11">
         <v>40691</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>522717</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="14" thickBot="1">
+    <row r="127" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="9">
         <v>40698</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>479149</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="14" thickBot="1">
+    <row r="128" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="9">
         <v>40705</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>527603</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="14" thickBot="1">
+    <row r="129" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="9">
         <v>40712</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>531992</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="14" thickBot="1">
+    <row r="130" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="9">
         <v>40719</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>519337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="14" thickBot="1">
+    <row r="131" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="9">
         <v>40726</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>522931</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14" thickBot="1">
+    <row r="132" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="9">
         <v>40733</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>438193</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="14" thickBot="1">
+    <row r="133" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="9">
         <v>40740</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>511711</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="14" thickBot="1">
+    <row r="134" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="9">
         <v>40747</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>524090</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="14" thickBot="1">
+    <row r="135" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="9">
         <v>40754</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>533337</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="14" thickBot="1">
+    <row r="136" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="9">
         <v>40761</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>522889</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="14" thickBot="1">
+    <row r="137" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="9">
         <v>40768</v>
       </c>
@@ -9351,7 +9351,7 @@
         <v>527864</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="14" thickBot="1">
+    <row r="138" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="9">
         <v>40775</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>539201</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="14" thickBot="1">
+    <row r="139" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="9">
         <v>40782</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>535994</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="14" thickBot="1">
+    <row r="140" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="9">
         <v>40789</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>537201</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14" thickBot="1">
+    <row r="141" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="9">
         <v>40796</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>486472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="14" thickBot="1">
+    <row r="142" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="9">
         <v>40803</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>542164</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="14" thickBot="1">
+    <row r="143" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="9">
         <v>40810</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>553535</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14" thickBot="1">
+    <row r="144" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="9">
         <v>40817</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>563034</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14" thickBot="1">
+    <row r="145" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="9">
         <v>40824</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>544499</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14" thickBot="1">
+    <row r="146" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="9">
         <v>40831</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>547752</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="14" thickBot="1">
+    <row r="147" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="9">
         <v>40838</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>547268</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="14" thickBot="1">
+    <row r="148" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="9">
         <v>40845</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>551674</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="14" thickBot="1">
+    <row r="149" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="9">
         <v>40852</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>537645</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="14" thickBot="1">
+    <row r="150" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="9">
         <v>40859</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>544563</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="14" thickBot="1">
+    <row r="151" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="11">
         <v>40866</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>545153</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="14" thickBot="1">
+    <row r="152" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="9">
         <v>40873</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>456170</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="14" thickBot="1">
+    <row r="153" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="9">
         <v>40880</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>555353</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="14" thickBot="1">
+    <row r="154" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="9">
         <v>40887</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>538299</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="14" thickBot="1">
+    <row r="155" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="9">
         <v>40894</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>537699</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="14" thickBot="1">
+    <row r="156" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="9">
         <v>40901</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>505089</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="14" thickBot="1">
+    <row r="157" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="9">
         <v>40908</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>426883</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="14" thickBot="1">
+    <row r="158" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="9">
         <v>40915</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>468674</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="14" thickBot="1">
+    <row r="159" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="9">
         <v>40922</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>527651</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14" thickBot="1">
+    <row r="160" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="9">
         <v>40929</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>507440</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="14" thickBot="1">
+    <row r="161" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="9">
         <v>40936</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>518682</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="14" thickBot="1">
+    <row r="162" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="9">
         <v>40943</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>517136</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="14" thickBot="1">
+    <row r="163" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="9">
         <v>40950</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>506708</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="14" thickBot="1">
+    <row r="164" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="9">
         <v>40957</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>502992</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="14" thickBot="1">
+    <row r="165" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="9">
         <v>40964</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>496046</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="14" thickBot="1">
+    <row r="166" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="9">
         <v>40971</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>510568</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="14" thickBot="1">
+    <row r="167" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="9">
         <v>40978</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>504767</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="14" thickBot="1">
+    <row r="168" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="9">
         <v>40985</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>505558</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="14" thickBot="1">
+    <row r="169" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="9">
         <v>40992</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>510794</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="14" thickBot="1">
+    <row r="170" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="9">
         <v>40999</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>529734</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="14" thickBot="1">
+    <row r="171" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="9">
         <v>41006</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>502127</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="14" thickBot="1">
+    <row r="172" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="9">
         <v>41013</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>510946</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="14" thickBot="1">
+    <row r="173" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="9">
         <v>41020</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>521538</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="14" thickBot="1">
+    <row r="174" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="9">
         <v>41027</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>525445</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="14" thickBot="1">
+    <row r="175" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="9">
         <v>41034</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>515167</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="14" thickBot="1">
+    <row r="176" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="11">
         <v>41041</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>518043</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="14" thickBot="1">
+    <row r="177" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="9">
         <v>41048</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>522229</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="14" thickBot="1">
+    <row r="178" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="9">
         <v>41055</v>
       </c>
@@ -10089,7 +10089,7 @@
         <v>536107</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="14" thickBot="1">
+    <row r="179" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="9">
         <v>41062</v>
       </c>
@@ -10107,7 +10107,7 @@
         <v>479118</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="14" thickBot="1">
+    <row r="180" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="9">
         <v>41069</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>531835</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="14" thickBot="1">
+    <row r="181" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="9">
         <v>41076</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>537011</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="14" thickBot="1">
+    <row r="182" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="9">
         <v>41083</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>534858</v>
       </c>
     </row>
-    <row r="183" spans="1:5" ht="14" thickBot="1">
+    <row r="183" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="9">
         <v>41090</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>532131</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="14" thickBot="1">
+    <row r="184" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="9">
         <v>41097</v>
       </c>
@@ -10197,7 +10197,7 @@
         <v>446518</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="14" thickBot="1">
+    <row r="185" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="9">
         <v>41104</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>532071</v>
       </c>
     </row>
-    <row r="186" spans="1:5" ht="14" thickBot="1">
+    <row r="186" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="9">
         <v>41111</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>532729</v>
       </c>
     </row>
-    <row r="187" spans="1:5" ht="14" thickBot="1">
+    <row r="187" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="9">
         <v>41118</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>538486</v>
       </c>
     </row>
-    <row r="188" spans="1:5" ht="14" thickBot="1">
+    <row r="188" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="9">
         <v>41125</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>531490</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="14" thickBot="1">
+    <row r="189" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="9">
         <v>41132</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>532202</v>
       </c>
     </row>
-    <row r="190" spans="1:5" ht="14" thickBot="1">
+    <row r="190" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="9">
         <v>41139</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>541140</v>
       </c>
     </row>
-    <row r="191" spans="1:5" ht="14" thickBot="1">
+    <row r="191" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="9">
         <v>41146</v>
       </c>
@@ -10323,7 +10323,7 @@
         <v>545406</v>
       </c>
     </row>
-    <row r="192" spans="1:5" ht="14" thickBot="1">
+    <row r="192" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="9">
         <v>41153</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>541845</v>
       </c>
     </row>
-    <row r="193" spans="1:5" ht="14" thickBot="1">
+    <row r="193" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="9">
         <v>41160</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>486818</v>
       </c>
     </row>
-    <row r="194" spans="1:5" ht="14" thickBot="1">
+    <row r="194" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="9">
         <v>41167</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>543250</v>
       </c>
     </row>
-    <row r="195" spans="1:5" ht="14" thickBot="1">
+    <row r="195" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="9">
         <v>41174</v>
       </c>
@@ -10410,7 +10410,7 @@
         <v>542897</v>
       </c>
     </row>
-    <row r="196" spans="1:5" ht="14" thickBot="1">
+    <row r="196" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="9">
         <v>41181</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>552468</v>
       </c>
     </row>
-    <row r="197" spans="1:5" ht="14" thickBot="1">
+    <row r="197" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="9">
         <v>41188</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>534553</v>
       </c>
     </row>
-    <row r="198" spans="1:5" ht="14" thickBot="1">
+    <row r="198" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="9">
         <v>41195</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>535915</v>
       </c>
     </row>
-    <row r="199" spans="1:5" ht="14" thickBot="1">
+    <row r="199" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="9">
         <v>41202</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>542674</v>
       </c>
     </row>
-    <row r="200" spans="1:5" ht="14" thickBot="1">
+    <row r="200" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="9">
         <v>41209</v>
       </c>
@@ -10500,7 +10500,7 @@
         <v>540290</v>
       </c>
     </row>
-    <row r="201" spans="1:5" ht="14" thickBot="1">
+    <row r="201" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>41216</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>502697</v>
       </c>
     </row>
-    <row r="202" spans="1:5" ht="14" thickBot="1">
+    <row r="202" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="9">
         <v>41223</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>532945</v>
       </c>
     </row>
-    <row r="203" spans="1:5" ht="14" thickBot="1">
+    <row r="203" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="9">
         <v>41230</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>537832</v>
       </c>
     </row>
-    <row r="204" spans="1:5" ht="14" thickBot="1">
+    <row r="204" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="9">
         <v>41237</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>447469</v>
       </c>
     </row>
-    <row r="205" spans="1:5" ht="14" thickBot="1">
+    <row r="205" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="9">
         <v>41244</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>547119</v>
       </c>
     </row>
-    <row r="206" spans="1:5" ht="14" thickBot="1">
+    <row r="206" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="9">
         <v>41251</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>532304</v>
       </c>
     </row>
-    <row r="207" spans="1:5" ht="14" thickBot="1">
+    <row r="207" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="9">
         <v>41258</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>544625</v>
       </c>
     </row>
-    <row r="208" spans="1:5" ht="14" thickBot="1">
+    <row r="208" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="9">
         <v>41265</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>530342</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="14" thickBot="1">
+    <row r="209" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="9">
         <v>41272</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>367721</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="14" thickBot="1">
+    <row r="210" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="9">
         <v>41279</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>419999</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="14" thickBot="1">
+    <row r="211" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="9">
         <v>41286</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>532789</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="14" thickBot="1">
+    <row r="212" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="9">
         <v>41293</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>526887</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="14" thickBot="1">
+    <row r="213" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="9">
         <v>41300</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>504628</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="14" thickBot="1">
+    <row r="214" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="9">
         <v>41307</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>523931</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="14" thickBot="1">
+    <row r="215" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="9">
         <v>41314</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>518048</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="14" thickBot="1">
+    <row r="216" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="9">
         <v>41321</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>529674</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="14" thickBot="1">
+    <row r="217" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="9">
         <v>41328</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>516142</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="14" thickBot="1">
+    <row r="218" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="9">
         <v>41335</v>
       </c>
@@ -10824,7 +10824,7 @@
         <v>533057</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="14" thickBot="1">
+    <row r="219" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="9">
         <v>41342</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>511872</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="14" thickBot="1">
+    <row r="220" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="9">
         <v>41349</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>509430</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="14" thickBot="1">
+    <row r="221" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="9">
         <v>41356</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>514379</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="14" thickBot="1">
+    <row r="222" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="9">
         <v>41363</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>514954</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="14" thickBot="1">
+    <row r="223" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="9">
         <v>41370</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>512396</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="14" thickBot="1">
+    <row r="224" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="9">
         <v>41377</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>517662</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="14" thickBot="1">
+    <row r="225" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="9">
         <v>41384</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>517360</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="14" thickBot="1">
+    <row r="226" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="11">
         <v>41391</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>523207</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="14" thickBot="1">
+    <row r="227" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="9">
         <v>41398</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>529594</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="14" thickBot="1">
+    <row r="228" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="9">
         <v>41405</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>529252</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="14" thickBot="1">
+    <row r="229" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="9">
         <v>41412</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>535835</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="14" thickBot="1">
+    <row r="230" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="9">
         <v>41419</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>529937</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="14" thickBot="1">
+    <row r="231" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="9">
         <v>41426</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>491082</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="14" thickBot="1">
+    <row r="232" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="9">
         <v>41433</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>530890</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="14" thickBot="1">
+    <row r="233" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="9">
         <v>41440</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>543145</v>
       </c>
     </row>
-    <row r="234" spans="1:5" ht="14" thickBot="1">
+    <row r="234" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="9">
         <v>41447</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>541031</v>
       </c>
     </row>
-    <row r="235" spans="1:5" ht="14" thickBot="1">
+    <row r="235" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="9">
         <v>41454</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>531040</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="14" thickBot="1">
+    <row r="236" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="9">
         <v>41461</v>
       </c>
@@ -11148,7 +11148,7 @@
         <v>453493</v>
       </c>
     </row>
-    <row r="237" spans="1:5" ht="14" thickBot="1">
+    <row r="237" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="9">
         <v>41468</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>525333</v>
       </c>
     </row>
-    <row r="238" spans="1:5" ht="14" thickBot="1">
+    <row r="238" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="9">
         <v>41475</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>531357</v>
       </c>
     </row>
-    <row r="239" spans="1:5" ht="14" thickBot="1">
+    <row r="239" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="9">
         <v>41482</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>551911</v>
       </c>
     </row>
-    <row r="240" spans="1:5" ht="14" thickBot="1">
+    <row r="240" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="9">
         <v>41489</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>542396</v>
       </c>
     </row>
-    <row r="241" spans="1:5" ht="14" thickBot="1">
+    <row r="241" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="9">
         <v>41496</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>546772</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="14" thickBot="1">
+    <row r="242" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="9">
         <v>41503</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>552359</v>
       </c>
     </row>
-    <row r="243" spans="1:5" ht="14" thickBot="1">
+    <row r="243" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="9">
         <v>41510</v>
       </c>
@@ -11274,7 +11274,7 @@
         <v>548969</v>
       </c>
     </row>
-    <row r="244" spans="1:5" ht="14" thickBot="1">
+    <row r="244" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="9">
         <v>41517</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>561698</v>
       </c>
     </row>
-    <row r="245" spans="1:5" ht="14" thickBot="1">
+    <row r="245" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="9">
         <v>41524</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>507493</v>
       </c>
     </row>
-    <row r="246" spans="1:5" ht="14" thickBot="1">
+    <row r="246" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="9">
         <v>41531</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>562094</v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="14" thickBot="1">
+    <row r="247" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="9">
         <v>41538</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>551057</v>
       </c>
     </row>
-    <row r="248" spans="1:5" ht="14" thickBot="1">
+    <row r="248" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="9">
         <v>41545</v>
       </c>
@@ -11364,7 +11364,7 @@
         <v>566662</v>
       </c>
     </row>
-    <row r="249" spans="1:5" ht="14" thickBot="1">
+    <row r="249" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="9">
         <v>41552</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>545708</v>
       </c>
     </row>
-    <row r="250" spans="1:5" ht="14" thickBot="1">
+    <row r="250" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="9">
         <v>41559</v>
       </c>
@@ -11400,7 +11400,7 @@
         <v>546211</v>
       </c>
     </row>
-    <row r="251" spans="1:5" ht="14" thickBot="1">
+    <row r="251" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="11">
         <v>41566</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>553943</v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="14" thickBot="1">
+    <row r="252" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="9">
         <v>41573</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>558686</v>
       </c>
     </row>
-    <row r="253" spans="1:5" ht="14" thickBot="1">
+    <row r="253" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="9">
         <v>41580</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>556662</v>
       </c>
     </row>
-    <row r="254" spans="1:5" ht="14" thickBot="1">
+    <row r="254" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="9">
         <v>41587</v>
       </c>
@@ -11472,7 +11472,7 @@
         <v>562840</v>
       </c>
     </row>
-    <row r="255" spans="1:5" ht="14" thickBot="1">
+    <row r="255" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="9">
         <v>41594</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>562206</v>
       </c>
     </row>
-    <row r="256" spans="1:5" ht="14" thickBot="1">
+    <row r="256" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="9">
         <v>41601</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>564340</v>
       </c>
     </row>
-    <row r="257" spans="1:5" ht="14" thickBot="1">
+    <row r="257" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="9">
         <v>41608</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>463516</v>
       </c>
     </row>
-    <row r="258" spans="1:5" ht="14" thickBot="1">
+    <row r="258" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="9">
         <v>41615</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>541978</v>
       </c>
     </row>
-    <row r="259" spans="1:5" ht="14" thickBot="1">
+    <row r="259" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="9">
         <v>41622</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>546825</v>
       </c>
     </row>
-    <row r="260" spans="1:5" ht="14" thickBot="1">
+    <row r="260" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="9">
         <v>41629</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>544984</v>
       </c>
     </row>
-    <row r="261" spans="1:5" ht="14" thickBot="1">
+    <row r="261" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="9">
         <v>41636</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>403329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" ht="14" thickBot="1">
+    <row r="262" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="9">
         <v>41643</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>433724</v>
       </c>
     </row>
-    <row r="263" spans="1:5" ht="14" thickBot="1">
+    <row r="263" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="9">
         <v>41650</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>492836</v>
       </c>
     </row>
-    <row r="264" spans="1:5" ht="14" thickBot="1">
+    <row r="264" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="9">
         <v>41657</v>
       </c>
@@ -11667,7 +11667,7 @@
         <v>557253</v>
       </c>
     </row>
-    <row r="265" spans="1:5" ht="14" thickBot="1">
+    <row r="265" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="9">
         <v>41664</v>
       </c>
@@ -11685,7 +11685,7 @@
         <v>526644</v>
       </c>
     </row>
-    <row r="266" spans="1:5" ht="14" thickBot="1">
+    <row r="266" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="9">
         <v>41671</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>518012</v>
       </c>
     </row>
-    <row r="267" spans="1:5" ht="14" thickBot="1">
+    <row r="267" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="9">
         <v>41678</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>507368</v>
       </c>
     </row>
-    <row r="268" spans="1:5" ht="14" thickBot="1">
+    <row r="268" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="9">
         <v>41685</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>507257</v>
       </c>
     </row>
-    <row r="269" spans="1:5" ht="14" thickBot="1">
+    <row r="269" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="9">
         <v>41692</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>535036</v>
       </c>
     </row>
-    <row r="270" spans="1:5" ht="14" thickBot="1">
+    <row r="270" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="9">
         <v>41699</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>545004</v>
       </c>
     </row>
-    <row r="271" spans="1:5" ht="14" thickBot="1">
+    <row r="271" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="9">
         <v>41706</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>518495</v>
       </c>
     </row>
-    <row r="272" spans="1:5" ht="14" thickBot="1">
+    <row r="272" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="9">
         <v>41713</v>
       </c>
@@ -11811,7 +11811,7 @@
         <v>545366</v>
       </c>
     </row>
-    <row r="273" spans="1:5" ht="14" thickBot="1">
+    <row r="273" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="9">
         <v>41720</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>552238</v>
       </c>
     </row>
-    <row r="274" spans="1:5" ht="14" thickBot="1">
+    <row r="274" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="9">
         <v>41727</v>
       </c>
@@ -11847,7 +11847,7 @@
         <v>566505</v>
       </c>
     </row>
-    <row r="275" spans="1:5" ht="14" thickBot="1">
+    <row r="275" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="9">
         <v>41734</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>557123</v>
       </c>
     </row>
-    <row r="276" spans="1:5" ht="14" thickBot="1">
+    <row r="276" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="11">
         <v>41741</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>559676</v>
       </c>
     </row>
-    <row r="277" spans="1:5" ht="14" thickBot="1">
+    <row r="277" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="9">
         <v>41748</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>549826</v>
       </c>
     </row>
-    <row r="278" spans="1:5" ht="14" thickBot="1">
+    <row r="278" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="9">
         <v>41755</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>566336</v>
       </c>
     </row>
-    <row r="279" spans="1:5" ht="14" thickBot="1">
+    <row r="279" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="9">
         <v>41762</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>564801</v>
       </c>
     </row>
-    <row r="280" spans="1:5" ht="14" thickBot="1">
+    <row r="280" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="9">
         <v>41769</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>564096</v>
       </c>
     </row>
-    <row r="281" spans="1:5" ht="14" thickBot="1">
+    <row r="281" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="9">
         <v>41783</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>570380</v>
       </c>
     </row>
-    <row r="282" spans="1:5" ht="14" thickBot="1">
+    <row r="282" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="9">
         <v>41790</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>531725</v>
       </c>
     </row>
-    <row r="283" spans="1:5" ht="14" thickBot="1">
+    <row r="283" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="9">
         <v>41797</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>562747</v>
       </c>
     </row>
-    <row r="284" spans="1:5" ht="14" thickBot="1">
+    <row r="284" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="9">
         <v>41804</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>565375</v>
       </c>
     </row>
-    <row r="285" spans="1:5" ht="14" thickBot="1">
+    <row r="285" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="9">
         <v>41811</v>
       </c>
@@ -12045,7 +12045,7 @@
         <v>563695</v>
       </c>
     </row>
-    <row r="286" spans="1:5" ht="14" thickBot="1">
+    <row r="286" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="9">
         <v>41818</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>563223</v>
       </c>
     </row>
-    <row r="287" spans="1:5" ht="14" thickBot="1">
+    <row r="287" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="9">
         <v>41825</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>497828</v>
       </c>
     </row>
-    <row r="288" spans="1:5" ht="14" thickBot="1">
+    <row r="288" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="9">
         <v>41832</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>546863</v>
       </c>
     </row>
-    <row r="289" spans="1:5" ht="14" thickBot="1">
+    <row r="289" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="9">
         <v>41839</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>566931</v>
       </c>
     </row>
-    <row r="290" spans="1:5" ht="14" thickBot="1">
+    <row r="290" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="9">
         <v>41846</v>
       </c>
@@ -12135,7 +12135,7 @@
         <v>571797</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="14" thickBot="1">
+    <row r="291" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="9">
         <v>41853</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>574552</v>
       </c>
     </row>
-    <row r="292" spans="1:5" ht="14" thickBot="1">
+    <row r="292" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="9">
         <v>41860</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>567908</v>
       </c>
     </row>
-    <row r="293" spans="1:5" ht="14" thickBot="1">
+    <row r="293" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="9">
         <v>41867</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>574592</v>
       </c>
     </row>
-    <row r="294" spans="1:5" ht="14" thickBot="1">
+    <row r="294" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="9">
         <v>41874</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>566266</v>
       </c>
     </row>
-    <row r="295" spans="1:5" ht="14" thickBot="1">
+    <row r="295" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="9">
         <v>41881</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>579209</v>
       </c>
     </row>
-    <row r="296" spans="1:5" ht="14" thickBot="1">
+    <row r="296" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A296" s="9">
         <v>41888</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>525144</v>
       </c>
     </row>
-    <row r="297" spans="1:5" ht="14" thickBot="1">
+    <row r="297" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="9">
         <v>41895</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>579440</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="14" thickBot="1">
+    <row r="298" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="9">
         <v>41902</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>581955</v>
       </c>
     </row>
-    <row r="299" spans="1:5" ht="14" thickBot="1">
+    <row r="299" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="9">
         <v>41909</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>576934</v>
       </c>
     </row>
-    <row r="300" spans="1:5" ht="14" thickBot="1">
+    <row r="300" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="9">
         <v>41916</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>576356</v>
       </c>
     </row>
-    <row r="301" spans="1:5" ht="14" thickBot="1">
+    <row r="301" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="11">
         <v>41923</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>571812</v>
       </c>
     </row>
-    <row r="302" spans="1:5" ht="14" thickBot="1">
+    <row r="302" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="9">
         <v>41930</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>569684</v>
       </c>
     </row>
-    <row r="303" spans="1:5" ht="14" thickBot="1">
+    <row r="303" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="9">
         <v>41937</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>586115</v>
       </c>
     </row>
-    <row r="304" spans="1:5" ht="14" thickBot="1">
+    <row r="304" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="9">
         <v>41944</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>585208</v>
       </c>
     </row>
-    <row r="305" spans="1:5" ht="14" thickBot="1">
+    <row r="305" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="9">
         <v>41951</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>568807</v>
       </c>
     </row>
-    <row r="306" spans="1:5" ht="14" thickBot="1">
+    <row r="306" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="9">
         <v>41958</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>570350</v>
       </c>
     </row>
-    <row r="307" spans="1:5" ht="14" thickBot="1">
+    <row r="307" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="9">
         <v>41965</v>
       </c>
@@ -12441,7 +12441,7 @@
         <v>565185</v>
       </c>
     </row>
-    <row r="308" spans="1:5" ht="14" thickBot="1">
+    <row r="308" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="9">
         <v>41972</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>492532</v>
       </c>
     </row>
-    <row r="309" spans="1:5" ht="14" thickBot="1">
+    <row r="309" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="9">
         <v>41979</v>
       </c>
@@ -12477,7 +12477,7 @@
         <v>580108</v>
       </c>
     </row>
-    <row r="310" spans="1:5" ht="14" thickBot="1">
+    <row r="310" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="9">
         <v>41986</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>592608</v>
       </c>
     </row>
-    <row r="311" spans="1:5" ht="14" thickBot="1">
+    <row r="311" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="9">
         <v>41993</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>580559</v>
       </c>
     </row>
-    <row r="312" spans="1:5" ht="14" thickBot="1">
+    <row r="312" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="9">
         <v>42000</v>
       </c>
@@ -12531,7 +12531,7 @@
         <v>433338</v>
       </c>
     </row>
-    <row r="313" spans="1:5" ht="14" thickBot="1">
+    <row r="313" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="9">
         <v>42007</v>
       </c>
@@ -12549,7 +12549,7 @@
         <v>446201</v>
       </c>
     </row>
-    <row r="314" spans="1:5" ht="14" thickBot="1">
+    <row r="314" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="9">
         <v>42014</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>517520</v>
       </c>
     </row>
-    <row r="315" spans="1:5" ht="14" thickBot="1">
+    <row r="315" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="9">
         <v>42021</v>
       </c>
@@ -12585,7 +12585,7 @@
         <v>551856</v>
       </c>
     </row>
-    <row r="316" spans="1:5" ht="14" thickBot="1">
+    <row r="316" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="9">
         <v>42028</v>
       </c>
@@ -12603,7 +12603,7 @@
         <v>548055</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="14" thickBot="1">
+    <row r="317" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="9">
         <v>42035</v>
       </c>
@@ -12621,7 +12621,7 @@
         <v>548478</v>
       </c>
     </row>
-    <row r="318" spans="1:5" ht="14" thickBot="1">
+    <row r="318" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="9">
         <v>42042</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>511563</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="14" thickBot="1">
+    <row r="319" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="9">
         <v>42049</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>525224</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="14" thickBot="1">
+    <row r="320" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="9">
         <v>42056</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>473161</v>
       </c>
     </row>
-    <row r="321" spans="1:5" ht="14" thickBot="1">
+    <row r="321" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="9">
         <v>42063</v>
       </c>
@@ -12693,7 +12693,7 @@
         <v>508658</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="14" thickBot="1">
+    <row r="322" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="9">
         <v>42070</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>522382</v>
       </c>
     </row>
-    <row r="323" spans="1:5" ht="14" thickBot="1">
+    <row r="323" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="9">
         <v>42077</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>553031</v>
       </c>
     </row>
-    <row r="324" spans="1:5" ht="14" thickBot="1">
+    <row r="324" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="9">
         <v>42084</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>562472</v>
       </c>
     </row>
-    <row r="325" spans="1:5" ht="14" thickBot="1">
+    <row r="325" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="9">
         <v>42091</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>563280</v>
       </c>
     </row>
-    <row r="326" spans="1:5" ht="14" thickBot="1">
+    <row r="326" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="11">
         <v>42098</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>549021</v>
       </c>
     </row>
-    <row r="327" spans="1:5" ht="14" thickBot="1">
+    <row r="327" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="9">
         <v>42105</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>557812</v>
       </c>
     </row>
-    <row r="328" spans="1:5" ht="14" thickBot="1">
+    <row r="328" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="9">
         <v>42112</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>556432</v>
       </c>
     </row>
-    <row r="329" spans="1:5" ht="14" thickBot="1">
+    <row r="329" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="9">
         <v>42119</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>557306</v>
       </c>
     </row>
-    <row r="330" spans="1:5" ht="14" thickBot="1">
+    <row r="330" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="9">
         <v>42126</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>565787</v>
       </c>
     </row>
-    <row r="331" spans="1:5" ht="14" thickBot="1">
+    <row r="331" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="9">
         <v>42133</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>551034</v>
       </c>
     </row>
-    <row r="332" spans="1:5" ht="14" thickBot="1">
+    <row r="332" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="9">
         <v>42140</v>
       </c>
@@ -12906,7 +12906,7 @@
         <v>549199</v>
       </c>
     </row>
-    <row r="333" spans="1:5" ht="14" thickBot="1">
+    <row r="333" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="9">
         <v>42147</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>554477</v>
       </c>
     </row>
-    <row r="334" spans="1:5" ht="14" thickBot="1">
+    <row r="334" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="9">
         <v>42154</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>505543</v>
       </c>
     </row>
-    <row r="335" spans="1:5" ht="14" thickBot="1">
+    <row r="335" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="9">
         <v>42161</v>
       </c>
@@ -12960,7 +12960,7 @@
         <v>550037</v>
       </c>
     </row>
-    <row r="336" spans="1:5" ht="14" thickBot="1">
+    <row r="336" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="9">
         <v>42168</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>554461</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="14" thickBot="1">
+    <row r="337" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="9">
         <v>42175</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>550839</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="14" thickBot="1">
+    <row r="338" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="9">
         <v>42182</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>547969</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="14" thickBot="1">
+    <row r="339" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="9">
         <v>42189</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>506284</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="14" thickBot="1">
+    <row r="340" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="9">
         <v>42196</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>534097</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="14" thickBot="1">
+    <row r="341" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="9">
         <v>42203</v>
       </c>
@@ -13068,7 +13068,7 @@
         <v>551181</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="14" thickBot="1">
+    <row r="342" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="9">
         <v>42210</v>
       </c>
@@ -13086,7 +13086,7 @@
         <v>557612</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="14" thickBot="1">
+    <row r="343" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="9">
         <v>42217</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>559125</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="14" thickBot="1">
+    <row r="344" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="9">
         <v>42224</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>562884</v>
       </c>
     </row>
-    <row r="345" spans="1:5" ht="14" thickBot="1">
+    <row r="345" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="9">
         <v>42238</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>567943</v>
       </c>
     </row>
-    <row r="346" spans="1:5" ht="14" thickBot="1">
+    <row r="346" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="9">
         <v>42245</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>575323</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="14" thickBot="1">
+    <row r="347" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="9">
         <v>42252</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>567206</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="14" thickBot="1">
+    <row r="348" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="9">
         <v>42259</v>
       </c>
@@ -13194,7 +13194,7 @@
         <v>510797</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="14" thickBot="1">
+    <row r="349" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="9">
         <v>42266</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>566734</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="14" thickBot="1">
+    <row r="350" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="9">
         <v>42273</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>566700</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="14" thickBot="1">
+    <row r="351" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="11">
         <v>42280</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>572293</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="14" thickBot="1">
+    <row r="352" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="9">
         <v>42287</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>556233</v>
       </c>
     </row>
-    <row r="353" spans="1:5" ht="14" thickBot="1">
+    <row r="353" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="9">
         <v>42294</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>554696</v>
       </c>
     </row>
-    <row r="354" spans="1:5" ht="14" thickBot="1">
+    <row r="354" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="9">
         <v>42301</v>
       </c>
@@ -13302,7 +13302,7 @@
         <v>553144</v>
       </c>
     </row>
-    <row r="355" spans="1:5" ht="14" thickBot="1">
+    <row r="355" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="9">
         <v>42308</v>
       </c>
@@ -13320,7 +13320,7 @@
         <v>549707</v>
       </c>
     </row>
-    <row r="356" spans="1:5" ht="14" thickBot="1">
+    <row r="356" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="9">
         <v>42315</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>539165</v>
       </c>
     </row>
-    <row r="357" spans="1:5" ht="14" thickBot="1">
+    <row r="357" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="9">
         <v>42322</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>543681</v>
       </c>
     </row>
-    <row r="358" spans="1:5" ht="14" thickBot="1">
+    <row r="358" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="9">
         <v>42336</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>450389</v>
       </c>
     </row>
-    <row r="359" spans="1:5" ht="14" thickBot="1">
+    <row r="359" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="9">
         <v>42343</v>
       </c>
@@ -13392,7 +13392,7 @@
         <v>542050</v>
       </c>
     </row>
-    <row r="360" spans="1:5" ht="14" thickBot="1">
+    <row r="360" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="9">
         <v>42350</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>544975</v>
       </c>
     </row>
-    <row r="361" spans="1:5" ht="14" thickBot="1">
+    <row r="361" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="9">
         <v>42357</v>
       </c>
@@ -13428,7 +13428,7 @@
         <v>525555</v>
       </c>
     </row>
-    <row r="362" spans="1:5" ht="14" thickBot="1">
+    <row r="362" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="9">
         <v>42364</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>391107</v>
       </c>
     </row>
-    <row r="363" spans="1:5" ht="14" thickBot="1">
+    <row r="363" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="9">
         <v>42371</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>395663</v>
       </c>
     </row>
-    <row r="364" spans="1:5" ht="14" thickBot="1">
+    <row r="364" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="9">
         <v>42378</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>498160</v>
       </c>
     </row>
-    <row r="365" spans="1:5" ht="14" thickBot="1">
+    <row r="365" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="9">
         <v>42385</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>506433</v>
       </c>
     </row>
-    <row r="366" spans="1:5" ht="14" thickBot="1">
+    <row r="366" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="9">
         <v>42392</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>490324</v>
       </c>
     </row>
-    <row r="367" spans="1:5" ht="14" thickBot="1">
+    <row r="367" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="9">
         <v>42399</v>
       </c>
@@ -13536,7 +13536,7 @@
         <v>512746</v>
       </c>
     </row>
-    <row r="368" spans="1:5" ht="14" thickBot="1">
+    <row r="368" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="9">
         <v>42406</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>504510</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="14" thickBot="1">
+    <row r="369" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="9">
         <v>42413</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>505148</v>
       </c>
     </row>
-    <row r="370" spans="1:5" ht="14" thickBot="1">
+    <row r="370" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="9">
         <v>42420</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>497210</v>
       </c>
     </row>
-    <row r="371" spans="1:5" ht="14" thickBot="1">
+    <row r="371" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="9">
         <v>42427</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>521300</v>
       </c>
     </row>
-    <row r="372" spans="1:5" ht="14" thickBot="1">
+    <row r="372" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="9">
         <v>42434</v>
       </c>
@@ -13626,7 +13626,7 @@
         <v>512202</v>
       </c>
     </row>
-    <row r="373" spans="1:5" ht="14" thickBot="1">
+    <row r="373" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="9">
         <v>42441</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>489177</v>
       </c>
     </row>
-    <row r="374" spans="1:5" ht="14" thickBot="1">
+    <row r="374" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="9">
         <v>42448</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>483463</v>
       </c>
     </row>
-    <row r="375" spans="1:5" ht="14" thickBot="1">
+    <row r="375" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="9">
         <v>42455</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>470271</v>
       </c>
     </row>
-    <row r="376" spans="1:5" ht="14" thickBot="1">
+    <row r="376" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="11">
         <v>42462</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>491979</v>
       </c>
     </row>
-    <row r="377" spans="1:5" ht="14" thickBot="1">
+    <row r="377" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="9">
         <v>42469</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>479059</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="14" thickBot="1">
+    <row r="378" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="9">
         <v>42476</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>499779</v>
       </c>
     </row>
-    <row r="379" spans="1:5" ht="14" thickBot="1">
+    <row r="379" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="9">
         <v>42483</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>491946</v>
       </c>
     </row>
-    <row r="380" spans="1:5" ht="14" thickBot="1">
+    <row r="380" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="9">
         <v>42490</v>
       </c>
@@ -13770,7 +13770,7 @@
         <v>502045</v>
       </c>
     </row>
-    <row r="381" spans="1:5" ht="14" thickBot="1">
+    <row r="381" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="9">
         <v>42497</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>492923</v>
       </c>
     </row>
-    <row r="382" spans="1:5" ht="14" thickBot="1">
+    <row r="382" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="9">
         <v>42504</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>498379</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="14" thickBot="1">
+    <row r="383" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="9">
         <v>42511</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>506983</v>
       </c>
     </row>
-    <row r="384" spans="1:5" ht="14" thickBot="1">
+    <row r="384" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="9">
         <v>42518</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>513917</v>
       </c>
     </row>
-    <row r="385" spans="1:5" ht="14" thickBot="1">
+    <row r="385" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="9">
         <v>42525</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>455346</v>
       </c>
     </row>
-    <row r="386" spans="1:5" ht="14" thickBot="1">
+    <row r="386" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="9">
         <v>42532</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>513471</v>
       </c>
     </row>
-    <row r="387" spans="1:5" ht="14" thickBot="1">
+    <row r="387" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="9">
         <v>42539</v>
       </c>
@@ -13911,7 +13911,7 @@
         <v>516096</v>
       </c>
     </row>
-    <row r="388" spans="1:5" ht="14" thickBot="1">
+    <row r="388" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="9">
         <v>42546</v>
       </c>
@@ -13929,7 +13929,7 @@
         <v>526161</v>
       </c>
     </row>
-    <row r="389" spans="1:5" ht="14" thickBot="1">
+    <row r="389" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="9">
         <v>42553</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>529191</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="14" thickBot="1">
+    <row r="390" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="9">
         <v>42560</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>442113</v>
       </c>
     </row>
-    <row r="391" spans="1:5" ht="14" thickBot="1">
+    <row r="391" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="9">
         <v>42567</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>520222</v>
       </c>
     </row>
-    <row r="392" spans="1:5" ht="14" thickBot="1">
+    <row r="392" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="9">
         <v>42574</v>
       </c>
@@ -14001,7 +14001,7 @@
         <v>528070</v>
       </c>
     </row>
-    <row r="393" spans="1:5" ht="14" thickBot="1">
+    <row r="393" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="9">
         <v>42581</v>
       </c>
@@ -14019,7 +14019,7 @@
         <v>536916</v>
       </c>
     </row>
-    <row r="394" spans="1:5" ht="14" thickBot="1">
+    <row r="394" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="9">
         <v>42588</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>531595</v>
       </c>
     </row>
-    <row r="395" spans="1:5" ht="14" thickBot="1">
+    <row r="395" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="9">
         <v>42595</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>534533</v>
       </c>
     </row>
-    <row r="396" spans="1:5" ht="14" thickBot="1">
+    <row r="396" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="9">
         <v>42602</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>531484</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="14" thickBot="1">
+    <row r="397" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="9">
         <v>42609</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>539657</v>
       </c>
     </row>
-    <row r="398" spans="1:5" ht="14" thickBot="1">
+    <row r="398" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="9">
         <v>42616</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>538826</v>
       </c>
     </row>
-    <row r="399" spans="1:5" ht="14" thickBot="1">
+    <row r="399" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="9">
         <v>42623</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="400" spans="1:5" ht="14" thickBot="1">
+    <row r="400" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="9">
         <v>42630</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>537904</v>
       </c>
     </row>
-    <row r="401" spans="1:5" ht="14" thickBot="1">
+    <row r="401" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="11">
         <v>42637</v>
       </c>
@@ -14163,7 +14163,7 @@
         <v>539609</v>
       </c>
     </row>
-    <row r="402" spans="1:5" ht="14" thickBot="1">
+    <row r="402" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="9">
         <v>42644</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>549171</v>
       </c>
     </row>
-    <row r="403" spans="1:5" ht="14" thickBot="1">
+    <row r="403" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="9">
         <v>42651</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>521789</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="14" thickBot="1">
+    <row r="404" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="9">
         <v>42658</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>531936</v>
       </c>
     </row>
-    <row r="405" spans="1:5" ht="14" thickBot="1">
+    <row r="405" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="9">
         <v>42665</v>
       </c>
@@ -14235,7 +14235,7 @@
         <v>544092</v>
       </c>
     </row>
-    <row r="406" spans="1:5" ht="14" thickBot="1">
+    <row r="406" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="9">
         <v>42672</v>
       </c>
@@ -14253,7 +14253,7 @@
         <v>544997</v>
       </c>
     </row>
-    <row r="407" spans="1:5" ht="14" thickBot="1">
+    <row r="407" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="9">
         <v>42679</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>543377</v>
       </c>
     </row>
-    <row r="408" spans="1:5" ht="14" thickBot="1">
+    <row r="408" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="9">
         <v>42686</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>541127</v>
       </c>
     </row>
-    <row r="409" spans="1:5" ht="14" thickBot="1">
+    <row r="409" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="9">
         <v>42693</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>547804</v>
       </c>
     </row>
-    <row r="410" spans="1:5" ht="14" thickBot="1">
+    <row r="410" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="9">
         <v>42700</v>
       </c>
@@ -14325,7 +14325,7 @@
         <v>452759</v>
       </c>
     </row>
-    <row r="411" spans="1:5" ht="14" thickBot="1">
+    <row r="411" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="9">
         <v>42707</v>
       </c>
@@ -14343,7 +14343,7 @@
         <v>553130</v>
       </c>
     </row>
-    <row r="412" spans="1:5" ht="14" thickBot="1">
+    <row r="412" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="9">
         <v>42714</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>538932</v>
       </c>
     </row>
-    <row r="413" spans="1:5" ht="14" thickBot="1">
+    <row r="413" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="9">
         <v>42721</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>523949</v>
       </c>
     </row>
-    <row r="414" spans="1:5" ht="14" thickBot="1">
+    <row r="414" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="9">
         <v>42728</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>496633</v>
       </c>
     </row>
-    <row r="415" spans="1:5" ht="14" thickBot="1">
+    <row r="415" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="9">
         <v>42735</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>425998</v>
       </c>
     </row>
-    <row r="416" spans="1:5" ht="14" thickBot="1">
+    <row r="416" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="9">
         <v>42742</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>441417</v>
       </c>
     </row>
-    <row r="417" spans="1:5" ht="14" thickBot="1">
+    <row r="417" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="9">
         <v>42749</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>516229</v>
       </c>
     </row>
-    <row r="418" spans="1:5" ht="14" thickBot="1">
+    <row r="418" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="9">
         <v>42756</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>530299</v>
       </c>
     </row>
-    <row r="419" spans="1:5" ht="14" thickBot="1">
+    <row r="419" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="9">
         <v>42763</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>529696</v>
       </c>
     </row>
-    <row r="420" spans="1:5" ht="14" thickBot="1">
+    <row r="420" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="9">
         <v>42770</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>541474</v>
       </c>
     </row>
-    <row r="421" spans="1:5" ht="14" thickBot="1">
+    <row r="421" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="9">
         <v>42777</v>
       </c>
@@ -14523,7 +14523,7 @@
         <v>518431</v>
       </c>
     </row>
-    <row r="422" spans="1:5" ht="14" thickBot="1">
+    <row r="422" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="9">
         <v>42784</v>
       </c>
@@ -14541,7 +14541,7 @@
         <v>531123</v>
       </c>
     </row>
-    <row r="423" spans="1:5" ht="14" thickBot="1">
+    <row r="423" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="9">
         <v>42791</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>521451</v>
       </c>
     </row>
-    <row r="424" spans="1:5" ht="14" thickBot="1">
+    <row r="424" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="9">
         <v>42798</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>521607</v>
       </c>
     </row>
-    <row r="425" spans="1:5" ht="14" thickBot="1">
+    <row r="425" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="9">
         <v>42805</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>510638</v>
       </c>
     </row>
-    <row r="426" spans="1:5" ht="14" thickBot="1">
+    <row r="426" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="11">
         <v>42812</v>
       </c>
@@ -14613,7 +14613,7 @@
         <v>495281</v>
       </c>
     </row>
-    <row r="427" spans="1:5" ht="14" thickBot="1">
+    <row r="427" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="9">
         <v>42819</v>
       </c>
@@ -14631,7 +14631,7 @@
         <v>526471</v>
       </c>
     </row>
-    <row r="428" spans="1:5" ht="14" thickBot="1">
+    <row r="428" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="9">
         <v>42826</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>527665</v>
       </c>
     </row>
-    <row r="429" spans="1:5" ht="14" thickBot="1">
+    <row r="429" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="9">
         <v>42833</v>
       </c>
@@ -14667,7 +14667,7 @@
         <v>513022</v>
       </c>
     </row>
-    <row r="430" spans="1:5" ht="14" thickBot="1">
+    <row r="430" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="9">
         <v>42840</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>519318</v>
       </c>
     </row>
-    <row r="431" spans="1:5" ht="14" thickBot="1">
+    <row r="431" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="9">
         <v>42847</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>515131</v>
       </c>
     </row>
-    <row r="432" spans="1:5" ht="14" thickBot="1">
+    <row r="432" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="9">
         <v>42854</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>527830</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="14" thickBot="1">
+    <row r="433" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="9">
         <v>42861</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>515305</v>
       </c>
     </row>
-    <row r="434" spans="1:5" ht="14" thickBot="1">
+    <row r="434" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="9">
         <v>42868</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>526970</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="14" thickBot="1">
+    <row r="435" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="9">
         <v>42875</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>534922</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="14" thickBot="1">
+    <row r="436" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="9">
         <v>42882</v>
       </c>
@@ -14793,7 +14793,7 @@
         <v>548103</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="14" thickBot="1">
+    <row r="437" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="9">
         <v>42889</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>500192</v>
       </c>
     </row>
-    <row r="438" spans="1:5" ht="14" thickBot="1">
+    <row r="438" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="9">
         <v>42896</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>545317</v>
       </c>
     </row>
-    <row r="439" spans="1:5" ht="14" thickBot="1">
+    <row r="439" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="9">
         <v>42903</v>
       </c>
@@ -14847,7 +14847,7 @@
         <v>543179</v>
       </c>
     </row>
-    <row r="440" spans="1:5" ht="14" thickBot="1">
+    <row r="440" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="9">
         <v>42910</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>544694</v>
       </c>
     </row>
-    <row r="441" spans="1:5" ht="14" thickBot="1">
+    <row r="441" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="9">
         <v>42917</v>
       </c>
@@ -14883,7 +14883,7 @@
         <v>546361</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="14" thickBot="1">
+    <row r="442" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="9">
         <v>42924</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>453080</v>
       </c>
     </row>
-    <row r="443" spans="1:5" ht="14" thickBot="1">
+    <row r="443" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="9">
         <v>42931</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>540005</v>
       </c>
     </row>
-    <row r="444" spans="1:5" ht="14" thickBot="1">
+    <row r="444" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="9">
         <v>42938</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>534152</v>
       </c>
     </row>
-    <row r="445" spans="1:5" ht="14" thickBot="1">
+    <row r="445" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="9">
         <v>42945</v>
       </c>
@@ -14955,7 +14955,7 @@
         <v>550356</v>
       </c>
     </row>
-    <row r="446" spans="1:5" ht="14" thickBot="1">
+    <row r="446" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="9">
         <v>42952</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>554822</v>
       </c>
     </row>
-    <row r="447" spans="1:5" ht="14" thickBot="1">
+    <row r="447" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="9">
         <v>42959</v>
       </c>
@@ -14991,7 +14991,7 @@
         <v>548790</v>
       </c>
     </row>
-    <row r="448" spans="1:5" ht="14" thickBot="1">
+    <row r="448" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="9">
         <v>42966</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>554021</v>
       </c>
     </row>
-    <row r="449" spans="1:5" ht="14" thickBot="1">
+    <row r="449" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="9">
         <v>42973</v>
       </c>
@@ -15027,7 +15027,7 @@
         <v>551776</v>
       </c>
     </row>
-    <row r="450" spans="1:5" ht="14" thickBot="1">
+    <row r="450" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="9">
         <v>42980</v>
       </c>
@@ -15060,7 +15060,7 @@
         <v>534140</v>
       </c>
     </row>
-    <row r="451" spans="1:5" ht="14" thickBot="1">
+    <row r="451" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="11">
         <v>42987</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>486474</v>
       </c>
     </row>
-    <row r="452" spans="1:5" ht="14" thickBot="1">
+    <row r="452" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="9">
         <v>42994</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>530774</v>
       </c>
     </row>
-    <row r="453" spans="1:5" ht="14" thickBot="1">
+    <row r="453" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="9">
         <v>43001</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>548204</v>
       </c>
     </row>
-    <row r="454" spans="1:5" ht="14" thickBot="1">
+    <row r="454" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="9">
         <v>43008</v>
       </c>
@@ -15132,7 +15132,7 @@
         <v>559555</v>
       </c>
     </row>
-    <row r="455" spans="1:5" ht="14" thickBot="1">
+    <row r="455" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="9">
         <v>43015</v>
       </c>
@@ -15150,7 +15150,7 @@
         <v>554826</v>
       </c>
     </row>
-    <row r="456" spans="1:5" ht="14" thickBot="1">
+    <row r="456" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="9">
         <v>43022</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>548264</v>
       </c>
     </row>
-    <row r="457" spans="1:5" ht="14" thickBot="1">
+    <row r="457" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="9">
         <v>43029</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>559989</v>
       </c>
     </row>
-    <row r="458" spans="1:5" ht="14" thickBot="1">
+    <row r="458" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="9">
         <v>43036</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>546582</v>
       </c>
     </row>
-    <row r="459" spans="1:5" ht="14" thickBot="1">
+    <row r="459" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="9">
         <v>43043</v>
       </c>
@@ -15222,7 +15222,7 @@
         <v>538739</v>
       </c>
     </row>
-    <row r="460" spans="1:5" ht="14" thickBot="1">
+    <row r="460" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="9">
         <v>43050</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>547480</v>
       </c>
     </row>
-    <row r="461" spans="1:5" ht="14" thickBot="1">
+    <row r="461" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="9">
         <v>43057</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>554066</v>
       </c>
     </row>
-    <row r="462" spans="1:5" ht="14" thickBot="1">
+    <row r="462" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="9">
         <v>43064</v>
       </c>
@@ -15276,7 +15276,7 @@
         <v>463602</v>
       </c>
     </row>
-    <row r="463" spans="1:5" ht="14" thickBot="1">
+    <row r="463" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="9">
         <v>43071</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>572794</v>
       </c>
     </row>
-    <row r="464" spans="1:5" ht="14" thickBot="1">
+    <row r="464" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="9">
         <v>43078</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>560756</v>
       </c>
     </row>
-    <row r="465" spans="1:5" ht="14" thickBot="1">
+    <row r="465" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="9">
         <v>43085</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>554779</v>
       </c>
     </row>
-    <row r="466" spans="1:5" ht="14" thickBot="1">
+    <row r="466" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="9">
         <v>43092</v>
       </c>
@@ -15348,7 +15348,7 @@
         <v>551566</v>
       </c>
     </row>
-    <row r="467" spans="1:5" ht="14" thickBot="1">
+    <row r="467" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="9">
         <v>43099</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>397032</v>
       </c>
     </row>
-    <row r="468" spans="1:5" ht="14" thickBot="1">
+    <row r="468" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="9">
         <v>43113</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>511937</v>
       </c>
     </row>
-    <row r="469" spans="1:5" ht="14" thickBot="1">
+    <row r="469" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="9">
         <v>43120</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>508239</v>
       </c>
     </row>
-    <row r="470" spans="1:5" ht="14" thickBot="1">
+    <row r="470" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="9">
         <v>43127</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>543515</v>
       </c>
     </row>
-    <row r="471" spans="1:5" ht="14" thickBot="1">
+    <row r="471" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="9">
         <v>43134</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>547993</v>
       </c>
     </row>
-    <row r="472" spans="1:5" ht="14" thickBot="1">
+    <row r="472" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="9">
         <v>43141</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>519545</v>
       </c>
     </row>
-    <row r="473" spans="1:5" ht="14" thickBot="1">
+    <row r="473" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="9">
         <v>43148</v>
       </c>
@@ -15474,7 +15474,7 @@
         <v>539963</v>
       </c>
     </row>
-    <row r="474" spans="1:5" ht="14" thickBot="1">
+    <row r="474" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="9">
         <v>43155</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>528440</v>
       </c>
     </row>
-    <row r="475" spans="1:5" ht="14" thickBot="1">
+    <row r="475" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="9">
         <v>43162</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>544194</v>
       </c>
     </row>
-    <row r="476" spans="1:5" ht="14" thickBot="1">
+    <row r="476" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="11">
         <v>43169</v>
       </c>
@@ -15528,7 +15528,7 @@
         <v>534282</v>
       </c>
     </row>
-    <row r="477" spans="1:5" ht="14" thickBot="1">
+    <row r="477" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="9">
         <v>43176</v>
       </c>
@@ -15546,7 +15546,7 @@
         <v>537338</v>
       </c>
     </row>
-    <row r="478" spans="1:5" ht="14" thickBot="1">
+    <row r="478" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="9">
         <v>43183</v>
       </c>
@@ -15564,7 +15564,7 @@
         <v>526521</v>
       </c>
     </row>
-    <row r="479" spans="1:5" ht="14" thickBot="1">
+    <row r="479" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="9">
         <v>43190</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>534751</v>
       </c>
     </row>
-    <row r="480" spans="1:5" ht="14" thickBot="1">
+    <row r="480" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="9">
         <v>43197</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>524905</v>
       </c>
     </row>
-    <row r="481" spans="1:5" ht="14" thickBot="1">
+    <row r="481" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="9">
         <v>43204</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>534198</v>
       </c>
     </row>
-    <row r="482" spans="1:5" ht="14" thickBot="1">
+    <row r="482" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="9">
         <v>43211</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>539425</v>
       </c>
     </row>
-    <row r="483" spans="1:5" ht="14" thickBot="1">
+    <row r="483" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="9">
         <v>43218</v>
       </c>
@@ -15654,7 +15654,7 @@
         <v>551498</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="14" thickBot="1">
+    <row r="484" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="9">
         <v>43225</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>545937</v>
       </c>
     </row>
-    <row r="485" spans="1:5" ht="14" thickBot="1">
+    <row r="485" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="9">
         <v>43232</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>550029</v>
       </c>
     </row>
-    <row r="486" spans="1:5" ht="14" thickBot="1">
+    <row r="486" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="9">
         <v>43239</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>546415</v>
       </c>
     </row>
-    <row r="487" spans="1:5" ht="14" thickBot="1">
+    <row r="487" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="9">
         <v>43246</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>565502</v>
       </c>
     </row>
-    <row r="488" spans="1:5" ht="14" thickBot="1">
+    <row r="488" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="9">
         <v>43253</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>509740</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="14" thickBot="1">
+    <row r="489" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="9">
         <v>43260</v>
       </c>
@@ -15762,7 +15762,7 @@
         <v>561061</v>
       </c>
     </row>
-    <row r="490" spans="1:5" ht="14" thickBot="1">
+    <row r="490" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="9">
         <v>43267</v>
       </c>
@@ -15780,7 +15780,7 @@
         <v>558098</v>
       </c>
     </row>
-    <row r="491" spans="1:5" ht="14" thickBot="1">
+    <row r="491" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="9">
         <v>43274</v>
       </c>
@@ -15798,7 +15798,7 @@
         <v>557340</v>
       </c>
     </row>
-    <row r="492" spans="1:5" ht="14" thickBot="1">
+    <row r="492" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="9">
         <v>43281</v>
       </c>
@@ -15816,7 +15816,7 @@
         <v>564243</v>
       </c>
     </row>
-    <row r="493" spans="1:5" ht="14" thickBot="1">
+    <row r="493" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="9">
         <v>43288</v>
       </c>
@@ -15834,7 +15834,7 @@
         <v>485193</v>
       </c>
     </row>
-    <row r="494" spans="1:5" ht="14" thickBot="1">
+    <row r="494" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="9">
         <v>43295</v>
       </c>
@@ -15852,7 +15852,7 @@
         <v>559064</v>
       </c>
     </row>
-    <row r="495" spans="1:5" ht="14" thickBot="1">
+    <row r="495" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="9">
         <v>43302</v>
       </c>
@@ -15870,7 +15870,7 @@
         <v>553024</v>
       </c>
     </row>
-    <row r="496" spans="1:5" ht="14" thickBot="1">
+    <row r="496" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="9">
         <v>43309</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>559154</v>
       </c>
     </row>
-    <row r="497" spans="1:5" ht="14" thickBot="1">
+    <row r="497" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="9">
         <v>43316</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>570995</v>
       </c>
     </row>
-    <row r="498" spans="1:5" ht="14" thickBot="1">
+    <row r="498" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="9">
         <v>43323</v>
       </c>
@@ -15924,7 +15924,7 @@
         <v>556887</v>
       </c>
     </row>
-    <row r="499" spans="1:5" ht="14" thickBot="1">
+    <row r="499" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="9">
         <v>43330</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>567477</v>
       </c>
     </row>
-    <row r="500" spans="1:5" ht="14" thickBot="1">
+    <row r="500" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="9">
         <v>43337</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>565706</v>
       </c>
     </row>
-    <row r="501" spans="1:5" ht="14" thickBot="1">
+    <row r="501" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="11">
         <v>43344</v>
       </c>
@@ -15978,7 +15978,7 @@
         <v>567881</v>
       </c>
     </row>
-    <row r="502" spans="1:5" ht="14" thickBot="1">
+    <row r="502" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="9">
         <v>43351</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>502208</v>
       </c>
     </row>
-    <row r="503" spans="1:5" ht="14" thickBot="1">
+    <row r="503" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="9">
         <v>43358</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>553003</v>
       </c>
     </row>
-    <row r="504" spans="1:5" ht="14" thickBot="1">
+    <row r="504" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="9">
         <v>43365</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>567078</v>
       </c>
     </row>
-    <row r="505" spans="1:5" ht="14" thickBot="1">
+    <row r="505" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="9">
         <v>43372</v>
       </c>
@@ -16050,7 +16050,7 @@
         <v>571922</v>
       </c>
     </row>
-    <row r="506" spans="1:5" ht="14" thickBot="1">
+    <row r="506" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="9">
         <v>43379</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>554238</v>
       </c>
     </row>
-    <row r="507" spans="1:5" ht="14" thickBot="1">
+    <row r="507" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="9">
         <v>43386</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>549757</v>
       </c>
     </row>
-    <row r="508" spans="1:5" ht="14" thickBot="1">
+    <row r="508" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="9">
         <v>43393</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>555106</v>
       </c>
     </row>
-    <row r="509" spans="1:5" ht="14" thickBot="1">
+    <row r="509" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="9">
         <v>43400</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>562804</v>
       </c>
     </row>
-    <row r="510" spans="1:5" ht="14" thickBot="1">
+    <row r="510" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="9">
         <v>43407</v>
       </c>
@@ -16140,7 +16140,7 @@
         <v>560046</v>
       </c>
     </row>
-    <row r="511" spans="1:5" ht="14" thickBot="1">
+    <row r="511" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="9">
         <v>43414</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>547236</v>
       </c>
     </row>
-    <row r="512" spans="1:5" ht="14" thickBot="1">
+    <row r="512" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="9">
         <v>43421</v>
       </c>
@@ -16176,7 +16176,7 @@
         <v>546541</v>
       </c>
     </row>
-    <row r="513" spans="1:5" ht="14" thickBot="1">
+    <row r="513" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="9">
         <v>43428</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>470851</v>
       </c>
     </row>
-    <row r="514" spans="1:5" ht="14" thickBot="1">
+    <row r="514" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="9">
         <v>43435</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>567282</v>
       </c>
     </row>
-    <row r="515" spans="1:5" ht="14" thickBot="1">
+    <row r="515" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="9">
         <v>43442</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>570225</v>
       </c>
     </row>
-    <row r="516" spans="1:5" ht="14" thickBot="1">
+    <row r="516" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="9">
         <v>43449</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>568941</v>
       </c>
     </row>
-    <row r="517" spans="1:5" ht="14" thickBot="1">
+    <row r="517" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="9">
         <v>43456</v>
       </c>
@@ -16281,7 +16281,7 @@
         <v>567252</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="14" thickBot="1">
+    <row r="518" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="9">
         <v>43463</v>
       </c>
@@ -16299,7 +16299,7 @@
         <v>411676</v>
       </c>
     </row>
-    <row r="519" spans="1:5" ht="14" thickBot="1">
+    <row r="519" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="9">
         <v>43470</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>436103</v>
       </c>
     </row>
-    <row r="520" spans="1:5" ht="14" thickBot="1">
+    <row r="520" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="9">
         <v>43477</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>555127</v>
       </c>
     </row>
-    <row r="521" spans="1:5" ht="14" thickBot="1">
+    <row r="521" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="9">
         <v>43484</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>543111</v>
       </c>
     </row>
-    <row r="522" spans="1:5" ht="14" thickBot="1">
+    <row r="522" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="9">
         <v>43491</v>
       </c>
@@ -16371,7 +16371,7 @@
         <v>522026</v>
       </c>
     </row>
-    <row r="523" spans="1:5" ht="14" thickBot="1">
+    <row r="523" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="9">
         <v>43498</v>
       </c>
@@ -16389,7 +16389,7 @@
         <v>498288</v>
       </c>
     </row>
-    <row r="524" spans="1:5" ht="14" thickBot="1">
+    <row r="524" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="9">
         <v>43505</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>519779</v>
       </c>
     </row>
-    <row r="525" spans="1:5" ht="14" thickBot="1">
+    <row r="525" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="9">
         <v>43512</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>523915</v>
       </c>
     </row>
-    <row r="526" spans="1:5" ht="14" thickBot="1">
+    <row r="526" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="11">
         <v>43519</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>522630</v>
       </c>
     </row>
-    <row r="527" spans="1:5" ht="14" thickBot="1">
+    <row r="527" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="9">
         <v>43526</v>
       </c>
@@ -16461,7 +16461,7 @@
         <v>528153</v>
       </c>
     </row>
-    <row r="528" spans="1:5" ht="14" thickBot="1">
+    <row r="528" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="9">
         <v>43533</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>508958</v>
       </c>
     </row>
-    <row r="529" spans="1:5" ht="14" thickBot="1">
+    <row r="529" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="9">
         <v>43540</v>
       </c>
@@ -16497,7 +16497,7 @@
         <v>501001</v>
       </c>
     </row>
-    <row r="530" spans="1:5" ht="14" thickBot="1">
+    <row r="530" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="9">
         <v>43547</v>
       </c>
@@ -16515,7 +16515,7 @@
         <v>503017</v>
       </c>
     </row>
-    <row r="531" spans="1:5" ht="14" thickBot="1">
+    <row r="531" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="9">
         <v>43554</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>509958</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="14" thickBot="1">
+    <row r="532" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="9">
         <v>43561</v>
       </c>
@@ -16551,7 +16551,7 @@
         <v>510192</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="14" thickBot="1">
+    <row r="533" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="9">
         <v>43568</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>528167</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="14" thickBot="1">
+    <row r="534" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="9">
         <v>43575</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>526141</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="14" thickBot="1">
+    <row r="535" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="9">
         <v>43582</v>
       </c>
@@ -16605,7 +16605,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="14" thickBot="1">
+    <row r="536" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="9">
         <v>43589</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>535089</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="14" thickBot="1">
+    <row r="537" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="9">
         <v>43596</v>
       </c>
@@ -16641,7 +16641,7 @@
         <v>529263</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="14" thickBot="1">
+    <row r="538" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="9">
         <v>43603</v>
       </c>
@@ -16659,7 +16659,7 @@
         <v>536358</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="14" thickBot="1">
+    <row r="539" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="9">
         <v>43610</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>527966</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="14" thickBot="1">
+    <row r="540" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="9">
         <v>43617</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>478679</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="14" thickBot="1">
+    <row r="541" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="9">
         <v>43624</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>513099</v>
       </c>
     </row>
-    <row r="542" spans="1:5" ht="14" thickBot="1">
+    <row r="542" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="9">
         <v>43631</v>
       </c>
@@ -16731,7 +16731,7 @@
         <v>527989</v>
       </c>
     </row>
-    <row r="543" spans="1:5" ht="14" thickBot="1">
+    <row r="543" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="9">
         <v>43638</v>
       </c>
@@ -16749,7 +16749,7 @@
         <v>525116</v>
       </c>
     </row>
-    <row r="544" spans="1:5" ht="14" thickBot="1">
+    <row r="544" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="9">
         <v>43645</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>533164</v>
       </c>
     </row>
-    <row r="545" spans="1:5" ht="14" thickBot="1">
+    <row r="545" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="9">
         <v>43652</v>
       </c>
@@ -16785,7 +16785,7 @@
         <v>448459</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="14" thickBot="1">
+    <row r="546" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="9">
         <v>43659</v>
       </c>
@@ -16803,7 +16803,7 @@
         <v>527908</v>
       </c>
     </row>
-    <row r="547" spans="1:5" ht="14" thickBot="1">
+    <row r="547" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="9">
         <v>43666</v>
       </c>
@@ -16821,7 +16821,7 @@
         <v>526010</v>
       </c>
     </row>
-    <row r="548" spans="1:5" ht="14" thickBot="1">
+    <row r="548" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="9">
         <v>43673</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>534498</v>
       </c>
     </row>
-    <row r="549" spans="1:5" ht="14" thickBot="1">
+    <row r="549" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="9">
         <v>43680</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>541558</v>
       </c>
     </row>
-    <row r="550" spans="1:5" ht="14" thickBot="1">
+    <row r="550" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="9">
         <v>43687</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>533190</v>
       </c>
     </row>
-    <row r="551" spans="1:5" ht="14" thickBot="1">
+    <row r="551" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="11">
         <v>43694</v>
       </c>
@@ -16893,7 +16893,7 @@
         <v>537617</v>
       </c>
     </row>
-    <row r="552" spans="1:5" ht="14" thickBot="1">
+    <row r="552" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="9">
         <v>43701</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>532483</v>
       </c>
     </row>
-    <row r="553" spans="1:5" ht="14" thickBot="1">
+    <row r="553" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="9">
         <v>43708</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>541945</v>
       </c>
     </row>
-    <row r="554" spans="1:5" ht="14" thickBot="1">
+    <row r="554" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="9">
         <v>43715</v>
       </c>
@@ -16947,7 +16947,7 @@
         <v>469285</v>
       </c>
     </row>
-    <row r="555" spans="1:5" ht="14" thickBot="1">
+    <row r="555" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="9">
         <v>43722</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>526734</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="14" thickBot="1">
+    <row r="556" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="9">
         <v>43729</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>528670</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="14" thickBot="1">
+    <row r="557" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="9">
         <v>43736</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>529336</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="14" thickBot="1">
+    <row r="558" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="9">
         <v>43743</v>
       </c>
@@ -17019,7 +17019,7 @@
         <v>515061</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="14" thickBot="1">
+    <row r="559" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="9">
         <v>43750</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>510820</v>
       </c>
     </row>
-    <row r="560" spans="1:5" ht="14" thickBot="1">
+    <row r="560" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="9">
         <v>43757</v>
       </c>
@@ -17055,7 +17055,7 @@
         <v>507381</v>
       </c>
     </row>
-    <row r="561" spans="1:5" ht="14" thickBot="1">
+    <row r="561" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="9">
         <v>43764</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>513147</v>
       </c>
     </row>
-    <row r="562" spans="1:5" ht="14" thickBot="1">
+    <row r="562" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="9">
         <v>43771</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>510012</v>
       </c>
     </row>
-    <row r="563" spans="1:5" ht="14" thickBot="1">
+    <row r="563" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="9">
         <v>43778</v>
       </c>
@@ -17109,7 +17109,7 @@
         <v>515269</v>
       </c>
     </row>
-    <row r="564" spans="1:5" ht="14" thickBot="1">
+    <row r="564" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="9">
         <v>43785</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>501249</v>
       </c>
     </row>
-    <row r="565" spans="1:5" ht="14" thickBot="1">
+    <row r="565" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="9">
         <v>43792</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>521927</v>
       </c>
     </row>
-    <row r="566" spans="1:5" ht="14" thickBot="1">
+    <row r="566" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="9">
         <v>43813</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>520589</v>
       </c>
     </row>
-    <row r="567" spans="1:5" ht="14" thickBot="1">
+    <row r="567" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="9">
         <v>43820</v>
       </c>
@@ -17181,7 +17181,7 @@
         <v>507589</v>
       </c>
     </row>
-    <row r="568" spans="1:5" ht="14" thickBot="1">
+    <row r="568" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="9">
         <v>43827</v>
       </c>
@@ -17199,7 +17199,7 @@
         <v>373728</v>
       </c>
     </row>
-    <row r="569" spans="1:5" ht="14" thickBot="1">
+    <row r="569" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="9">
         <v>43834</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>414014</v>
       </c>
     </row>
-    <row r="570" spans="1:5" ht="14" thickBot="1">
+    <row r="570" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="9">
         <v>43841</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>501624</v>
       </c>
     </row>
-    <row r="571" spans="1:5" ht="14" thickBot="1">
+    <row r="571" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="9">
         <v>43848</v>
       </c>
@@ -17253,7 +17253,7 @@
         <v>499732</v>
       </c>
     </row>
-    <row r="572" spans="1:5" ht="14" thickBot="1">
+    <row r="572" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="9">
         <v>43855</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>485282</v>
       </c>
     </row>
-    <row r="573" spans="1:5" ht="14" thickBot="1">
+    <row r="573" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="9">
         <v>43862</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>510161</v>
       </c>
     </row>
-    <row r="574" spans="1:5" ht="14" thickBot="1">
+    <row r="574" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="9">
         <v>43869</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>485329</v>
       </c>
     </row>
-    <row r="575" spans="1:5" ht="14" thickBot="1">
+    <row r="575" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="9">
         <v>43876</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>479137</v>
       </c>
     </row>
-    <row r="576" spans="1:5" ht="14" thickBot="1">
+    <row r="576" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="11">
         <v>43883</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>482690</v>
       </c>
     </row>
-    <row r="577" spans="1:5" ht="14" thickBot="1">
+    <row r="577" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="9">
         <v>43890</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>477611</v>
       </c>
     </row>
-    <row r="578" spans="1:5" ht="14" thickBot="1">
+    <row r="578" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="9">
         <v>43897</v>
       </c>
@@ -17394,7 +17394,7 @@
         <v>462303</v>
       </c>
     </row>
-    <row r="579" spans="1:5" ht="14" thickBot="1">
+    <row r="579" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="9">
         <v>43904</v>
       </c>
@@ -17412,7 +17412,7 @@
         <v>463017</v>
       </c>
     </row>
-    <row r="580" spans="1:5" ht="14" thickBot="1">
+    <row r="580" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="9">
         <v>43911</v>
       </c>
@@ -17430,7 +17430,7 @@
         <v>459966</v>
       </c>
     </row>
-    <row r="581" spans="1:5" ht="14" thickBot="1">
+    <row r="581" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="9">
         <v>43918</v>
       </c>
@@ -17448,7 +17448,7 @@
         <v>449767</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="14" thickBot="1">
+    <row r="582" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="9">
         <v>43925</v>
       </c>
@@ -17466,7 +17466,7 @@
         <v>429095</v>
       </c>
     </row>
-    <row r="583" spans="1:5" ht="14" thickBot="1">
+    <row r="583" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="9">
         <v>43932</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>412503</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="14" thickBot="1">
+    <row r="584" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="9">
         <v>43939</v>
       </c>
@@ -17502,7 +17502,7 @@
         <v>403283</v>
       </c>
     </row>
-    <row r="585" spans="1:5" ht="14" thickBot="1">
+    <row r="585" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="9">
         <v>43946</v>
       </c>
@@ -17520,7 +17520,7 @@
         <v>414123</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="14" thickBot="1">
+    <row r="586" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="9">
         <v>43953</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>416954</v>
       </c>
     </row>
-    <row r="587" spans="1:5" ht="14" thickBot="1">
+    <row r="587" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="9">
         <v>43960</v>
       </c>
@@ -17556,7 +17556,7 @@
         <v>412549</v>
       </c>
     </row>
-    <row r="588" spans="1:5" ht="14" thickBot="1">
+    <row r="588" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="9">
         <v>43967</v>
       </c>
@@ -17574,7 +17574,7 @@
         <v>416115</v>
       </c>
     </row>
-    <row r="589" spans="1:5" ht="14" thickBot="1">
+    <row r="589" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="9">
         <v>43974</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>428715</v>
       </c>
     </row>
-    <row r="590" spans="1:5" ht="14" thickBot="1">
+    <row r="590" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="9">
         <v>43981</v>
       </c>
@@ -17610,7 +17610,7 @@
         <v>395714</v>
       </c>
     </row>
-    <row r="591" spans="1:5" ht="14" thickBot="1">
+    <row r="591" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="9">
         <v>43988</v>
       </c>
@@ -17628,7 +17628,7 @@
         <v>433171</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="14" thickBot="1">
+    <row r="592" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="9">
         <v>43995</v>
       </c>
@@ -17646,7 +17646,7 @@
         <v>449291</v>
       </c>
     </row>
-    <row r="593" spans="1:5" ht="14" thickBot="1">
+    <row r="593" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="9">
         <v>44002</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>457278</v>
       </c>
     </row>
-    <row r="594" spans="1:5" ht="14" thickBot="1">
+    <row r="594" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="9">
         <v>44009</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>459449</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="14" thickBot="1">
+    <row r="595" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="9">
         <v>44016</v>
       </c>
@@ -17700,7 +17700,7 @@
         <v>437989</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="14" thickBot="1">
+    <row r="596" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="9">
         <v>44023</v>
       </c>
@@ -17718,7 +17718,7 @@
         <v>449092</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="14" thickBot="1">
+    <row r="597" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="9">
         <v>44030</v>
       </c>
@@ -17736,7 +17736,7 @@
         <v>481597</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="14" thickBot="1">
+    <row r="598" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="9">
         <v>44037</v>
       </c>
@@ -17754,7 +17754,7 @@
         <v>481331</v>
       </c>
     </row>
-    <row r="599" spans="1:5" ht="14" thickBot="1">
+    <row r="599" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="9">
         <v>44044</v>
       </c>
@@ -17772,7 +17772,7 @@
         <v>487968</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="14" thickBot="1">
+    <row r="600" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="9">
         <v>44051</v>
       </c>
@@ -17790,7 +17790,7 @@
         <v>497397</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="14" thickBot="1">
+    <row r="601" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="11">
         <v>44058</v>
       </c>
@@ -17808,7 +17808,7 @@
         <v>500563</v>
       </c>
     </row>
-    <row r="602" spans="1:5" ht="14" thickBot="1">
+    <row r="602" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="9">
         <v>44072</v>
       </c>
@@ -17826,7 +17826,7 @@
         <v>508307</v>
       </c>
     </row>
-    <row r="603" spans="1:5" ht="14" thickBot="1">
+    <row r="603" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="9">
         <v>44079</v>
       </c>
@@ -17844,7 +17844,7 @@
         <v>509637</v>
       </c>
     </row>
-    <row r="604" spans="1:5" ht="14" thickBot="1">
+    <row r="604" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="9">
         <v>44086</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>474785</v>
       </c>
     </row>
-    <row r="605" spans="1:5" ht="14" thickBot="1">
+    <row r="605" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="9">
         <v>44093</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>521956</v>
       </c>
     </row>
-    <row r="606" spans="1:5" ht="14" thickBot="1">
+    <row r="606" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="9">
         <v>44100</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>518290</v>
       </c>
     </row>
-    <row r="607" spans="1:5" ht="14" thickBot="1">
+    <row r="607" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="9">
         <v>44107</v>
       </c>
@@ -17916,7 +17916,7 @@
         <v>518761</v>
       </c>
     </row>
-    <row r="608" spans="1:5" ht="14" thickBot="1">
+    <row r="608" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="9">
         <v>44114</v>
       </c>
@@ -17934,7 +17934,7 @@
         <v>520452</v>
       </c>
     </row>
-    <row r="609" spans="1:5" ht="14" thickBot="1">
+    <row r="609" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="9">
         <v>44121</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>518763</v>
       </c>
     </row>
-    <row r="610" spans="1:5" ht="14" thickBot="1">
+    <row r="610" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="9">
         <v>44128</v>
       </c>
@@ -17970,7 +17970,7 @@
         <v>522653</v>
       </c>
     </row>
-    <row r="611" spans="1:5" ht="14" thickBot="1">
+    <row r="611" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="9">
         <v>44135</v>
       </c>
@@ -17988,7 +17988,7 @@
         <v>520778</v>
       </c>
     </row>
-    <row r="612" spans="1:5" ht="14" thickBot="1">
+    <row r="612" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="9">
         <v>44142</v>
       </c>
@@ -18006,7 +18006,7 @@
         <v>522028</v>
       </c>
     </row>
-    <row r="613" spans="1:5" ht="14" thickBot="1">
+    <row r="613" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="9">
         <v>44149</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>527462</v>
       </c>
     </row>
-    <row r="614" spans="1:5" ht="14" thickBot="1">
+    <row r="614" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="9">
         <v>44156</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>534607</v>
       </c>
     </row>
-    <row r="615" spans="1:5" ht="14" thickBot="1">
+    <row r="615" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="9">
         <v>44163</v>
       </c>
@@ -18060,7 +18060,7 @@
         <v>452792</v>
       </c>
     </row>
-    <row r="616" spans="1:5" ht="14" thickBot="1">
+    <row r="616" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="9">
         <v>44170</v>
       </c>
@@ -18078,7 +18078,7 @@
         <v>542203</v>
       </c>
     </row>
-    <row r="617" spans="1:5" ht="14" thickBot="1">
+    <row r="617" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="9">
         <v>44177</v>
       </c>
@@ -18096,7 +18096,7 @@
         <v>546209</v>
       </c>
     </row>
-    <row r="618" spans="1:5" ht="14" thickBot="1">
+    <row r="618" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="9">
         <v>44191</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>405111</v>
       </c>
     </row>
-    <row r="619" spans="1:5" ht="14" thickBot="1">
+    <row r="619" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="9">
         <v>44198</v>
       </c>
@@ -18132,7 +18132,7 @@
         <v>421991</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="14" thickBot="1">
+    <row r="620" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="9">
         <v>44205</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>525253</v>
       </c>
     </row>
-    <row r="621" spans="1:5" ht="14" thickBot="1">
+    <row r="621" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="9">
         <v>44212</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>528547</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="14" thickBot="1">
+    <row r="622" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="9">
         <v>44219</v>
       </c>
@@ -18186,7 +18186,7 @@
         <v>529030</v>
       </c>
     </row>
-    <row r="623" spans="1:5" ht="14" thickBot="1">
+    <row r="623" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="9">
         <v>44226</v>
       </c>
@@ -18204,7 +18204,7 @@
         <v>520693</v>
       </c>
     </row>
-    <row r="624" spans="1:5" ht="14" thickBot="1">
+    <row r="624" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="9">
         <v>44233</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>495815</v>
       </c>
     </row>
-    <row r="625" spans="1:5" ht="14" thickBot="1">
+    <row r="625" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="9">
         <v>44240</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>480483</v>
       </c>
     </row>
-    <row r="626" spans="1:5" ht="14" thickBot="1">
+    <row r="626" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="11">
         <v>44247</v>
       </c>
@@ -18258,7 +18258,7 @@
         <v>377904</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="14" thickBot="1">
+    <row r="627" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="9">
         <v>44254</v>
       </c>
@@ -18276,7 +18276,7 @@
         <v>486429</v>
       </c>
     </row>
-    <row r="628" spans="1:5" ht="14" thickBot="1">
+    <row r="628" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="9">
         <v>44261</v>
       </c>
@@ -18294,7 +18294,7 @@
         <v>515135</v>
       </c>
     </row>
-    <row r="629" spans="1:5" ht="14" thickBot="1">
+    <row r="629" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="9">
         <v>44268</v>
       </c>
@@ -18312,7 +18312,7 @@
         <v>520736</v>
       </c>
     </row>
-    <row r="630" spans="1:5" ht="14" thickBot="1">
+    <row r="630" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="9">
         <v>44275</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>513325</v>
       </c>
     </row>
-    <row r="631" spans="1:5" ht="14" thickBot="1">
+    <row r="631" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="9">
         <v>44282</v>
       </c>
@@ -18348,7 +18348,7 @@
         <v>521731</v>
       </c>
     </row>
-    <row r="632" spans="1:5" ht="14" thickBot="1">
+    <row r="632" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="9">
         <v>44289</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>515562</v>
       </c>
     </row>
-    <row r="633" spans="1:5" ht="14" thickBot="1">
+    <row r="633" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="9">
         <v>44296</v>
       </c>
@@ -18384,7 +18384,7 @@
         <v>513724</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="14" thickBot="1">
+    <row r="634" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="9">
         <v>44303</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>533217</v>
       </c>
     </row>
-    <row r="635" spans="1:5" ht="14" thickBot="1">
+    <row r="635" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="9">
         <v>44310</v>
       </c>
@@ -18420,7 +18420,7 @@
         <v>538184</v>
       </c>
     </row>
-    <row r="636" spans="1:5" ht="14" thickBot="1">
+    <row r="636" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="9">
         <v>44317</v>
       </c>
@@ -18438,7 +18438,7 @@
         <v>540667</v>
       </c>
     </row>
-    <row r="637" spans="1:5" ht="14" thickBot="1">
+    <row r="637" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="9">
         <v>44324</v>
       </c>
@@ -18456,7 +18456,7 @@
         <v>523309</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="14" thickBot="1">
+    <row r="638" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="9">
         <v>44331</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>533872</v>
       </c>
     </row>
-    <row r="639" spans="1:5" ht="14" thickBot="1">
+    <row r="639" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="9">
         <v>44338</v>
       </c>
@@ -18492,7 +18492,7 @@
         <v>528774</v>
       </c>
     </row>
-    <row r="640" spans="1:5" ht="14" thickBot="1">
+    <row r="640" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="9">
         <v>44345</v>
       </c>
@@ -18510,7 +18510,7 @@
         <v>530225</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="14" thickBot="1">
+    <row r="641" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="9">
         <v>44352</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>489144</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="14" thickBot="1">
+    <row r="642" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="9">
         <v>44359</v>
       </c>
@@ -18561,7 +18561,7 @@
         <v>529635</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="14" thickBot="1">
+    <row r="643" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="9">
         <v>44366</v>
       </c>
@@ -18579,7 +18579,7 @@
         <v>514112</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="14" thickBot="1">
+    <row r="644" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="9">
         <v>44373</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>516167</v>
       </c>
     </row>
-    <row r="645" spans="1:5" ht="14" thickBot="1">
+    <row r="645" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="9">
         <v>44380</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>512919</v>
       </c>
     </row>
-    <row r="646" spans="1:5" ht="14" thickBot="1">
+    <row r="646" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="9">
         <v>44387</v>
       </c>
@@ -18633,7 +18633,7 @@
         <v>451825</v>
       </c>
     </row>
-    <row r="647" spans="1:5" ht="14" thickBot="1">
+    <row r="647" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="9">
         <v>44394</v>
       </c>
@@ -18651,7 +18651,7 @@
         <v>513255</v>
       </c>
     </row>
-    <row r="648" spans="1:5" ht="14" thickBot="1">
+    <row r="648" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="9">
         <v>44401</v>
       </c>
@@ -18669,7 +18669,7 @@
         <v>503219</v>
       </c>
     </row>
-    <row r="649" spans="1:5" ht="14" thickBot="1">
+    <row r="649" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="9">
         <v>44408</v>
       </c>
@@ -18687,7 +18687,7 @@
         <v>502540</v>
       </c>
     </row>
-    <row r="650" spans="1:5" ht="14" thickBot="1">
+    <row r="650" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="9">
         <v>44415</v>
       </c>
@@ -18705,7 +18705,7 @@
         <v>509607</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="14" thickBot="1">
+    <row r="651" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="11">
         <v>44422</v>
       </c>
@@ -18723,7 +18723,7 @@
         <v>504810</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="14" thickBot="1">
+    <row r="652" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="9">
         <v>44429</v>
       </c>
@@ -18741,7 +18741,7 @@
         <v>501273</v>
       </c>
     </row>
-    <row r="653" spans="1:5" ht="14" thickBot="1">
+    <row r="653" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="9">
         <v>44436</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>504417</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="14" thickBot="1">
+    <row r="654" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="9">
         <v>44443</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>494415</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="14" thickBot="1">
+    <row r="655" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="9">
         <v>44450</v>
       </c>
@@ -18795,7 +18795,7 @@
         <v>468610</v>
       </c>
     </row>
-    <row r="656" spans="1:5" ht="14" thickBot="1">
+    <row r="656" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="9">
         <v>44457</v>
       </c>
@@ -18813,7 +18813,7 @@
         <v>505622</v>
       </c>
     </row>
-    <row r="657" spans="1:5" ht="14" thickBot="1">
+    <row r="657" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="9">
         <v>44464</v>
       </c>
@@ -18831,7 +18831,7 @@
         <v>511713</v>
       </c>
     </row>
-    <row r="658" spans="1:5" ht="14" thickBot="1">
+    <row r="658" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="9">
         <v>44471</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>515849</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="14" thickBot="1">
+    <row r="659" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="9">
         <v>44478</v>
       </c>
@@ -18867,7 +18867,7 @@
         <v>506642</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="14" thickBot="1">
+    <row r="660" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="9">
         <v>44485</v>
       </c>
@@ -18885,7 +18885,7 @@
         <v>496983</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="14" thickBot="1">
+    <row r="661" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="9">
         <v>44492</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>510762</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="14" thickBot="1">
+    <row r="662" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="9">
         <v>44499</v>
       </c>
@@ -18921,7 +18921,7 @@
         <v>510141</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="14" thickBot="1">
+    <row r="663" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="9">
         <v>44506</v>
       </c>
@@ -18939,7 +18939,7 @@
         <v>504111</v>
       </c>
     </row>
-    <row r="664" spans="1:5" ht="14" thickBot="1">
+    <row r="664" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="9">
         <v>44513</v>
       </c>
@@ -18957,7 +18957,7 @@
         <v>502613</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="14" thickBot="1">
+    <row r="665" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="9">
         <v>44520</v>
       </c>
@@ -18975,7 +18975,7 @@
         <v>508309</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="14" thickBot="1">
+    <row r="666" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="9">
         <v>44527</v>
       </c>
@@ -18993,7 +18993,7 @@
         <v>430793</v>
       </c>
     </row>
-    <row r="667" spans="1:5" ht="14" thickBot="1">
+    <row r="667" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="9">
         <v>44534</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>527406</v>
       </c>
     </row>
-    <row r="668" spans="1:5" ht="14" thickBot="1">
+    <row r="668" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="9">
         <v>44541</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>513366</v>
       </c>
     </row>
-    <row r="669" spans="1:5" ht="14" thickBot="1">
+    <row r="669" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="9">
         <v>44548</v>
       </c>
@@ -19047,7 +19047,7 @@
         <v>504099</v>
       </c>
     </row>
-    <row r="670" spans="1:5" ht="14" thickBot="1">
+    <row r="670" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="9">
         <v>44555</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>420373</v>
       </c>
     </row>
-    <row r="671" spans="1:5" ht="14" thickBot="1">
+    <row r="671" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="9">
         <v>44562</v>
       </c>
@@ -19083,7 +19083,7 @@
         <v>395371</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="14" thickBot="1">
+    <row r="672" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="9">
         <v>44569</v>
       </c>
@@ -19101,7 +19101,7 @@
         <v>440761</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="14" thickBot="1">
+    <row r="673" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="9">
         <v>44576</v>
       </c>
@@ -19119,7 +19119,7 @@
         <v>493617</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="14" thickBot="1">
+    <row r="674" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="9">
         <v>44583</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>477462</v>
       </c>
     </row>
-    <row r="675" spans="1:5" ht="14" thickBot="1">
+    <row r="675" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="9">
         <v>44590</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>491868</v>
       </c>
     </row>
-    <row r="676" spans="1:5" ht="14" thickBot="1">
+    <row r="676" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="11">
         <v>44597</v>
       </c>
@@ -19173,7 +19173,7 @@
         <v>458152</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="14" thickBot="1">
+    <row r="677" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="9">
         <v>44604</v>
       </c>
@@ -19191,7 +19191,7 @@
         <v>504482</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="14" thickBot="1">
+    <row r="678" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="9">
         <v>44611</v>
       </c>
@@ -19209,7 +19209,7 @@
         <v>497822</v>
       </c>
     </row>
-    <row r="679" spans="1:5" ht="14" thickBot="1">
+    <row r="679" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="9">
         <v>44625</v>
       </c>
@@ -19227,7 +19227,7 @@
         <v>505177</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="14" thickBot="1">
+    <row r="680" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="9">
         <v>44632</v>
       </c>
@@ -19245,7 +19245,7 @@
         <v>496134</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="14" thickBot="1">
+    <row r="681" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="9">
         <v>44639</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>499362</v>
       </c>
     </row>
-    <row r="682" spans="1:5" ht="14" thickBot="1">
+    <row r="682" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="9">
         <v>44646</v>
       </c>
@@ -19281,7 +19281,7 @@
         <v>504817</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="14" thickBot="1">
+    <row r="683" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="9">
         <v>44653</v>
       </c>
@@ -19299,7 +19299,7 @@
         <v>502194</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="14" thickBot="1">
+    <row r="684" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="9">
         <v>44660</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>508343</v>
       </c>
     </row>
-    <row r="685" spans="1:5" ht="14" thickBot="1">
+    <row r="685" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="9">
         <v>44667</v>
       </c>
@@ -19335,7 +19335,7 @@
         <v>489801</v>
       </c>
     </row>
-    <row r="686" spans="1:5" ht="14" thickBot="1">
+    <row r="686" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="9">
         <v>44674</v>
       </c>
@@ -19353,7 +19353,7 @@
         <v>498011</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="14" thickBot="1">
+    <row r="687" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="9">
         <v>44681</v>
       </c>
@@ -19371,7 +19371,7 @@
         <v>506699</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="14" thickBot="1">
+    <row r="688" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="9">
         <v>44688</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>504927</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="14" thickBot="1">
+    <row r="689" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="9">
         <v>44695</v>
       </c>
@@ -19407,7 +19407,7 @@
         <v>505120</v>
       </c>
     </row>
-    <row r="690" spans="1:5" ht="14" thickBot="1">
+    <row r="690" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="9">
         <v>44702</v>
       </c>
@@ -19425,7 +19425,7 @@
         <v>506976</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="14" thickBot="1">
+    <row r="691" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="9">
         <v>44709</v>
       </c>
@@ -19443,7 +19443,7 @@
         <v>514277</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="14" thickBot="1">
+    <row r="692" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="9">
         <v>44716</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>475513</v>
       </c>
     </row>
-    <row r="693" spans="1:5" ht="14" thickBot="1">
+    <row r="693" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="9">
         <v>44723</v>
       </c>
@@ -19479,7 +19479,7 @@
         <v>510295</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="14" thickBot="1">
+    <row r="694" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="9">
         <v>44730</v>
       </c>
@@ -19497,7 +19497,7 @@
         <v>501207</v>
       </c>
     </row>
-    <row r="695" spans="1:5" ht="14" thickBot="1">
+    <row r="695" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="9">
         <v>44737</v>
       </c>
@@ -19515,7 +19515,7 @@
         <v>493374</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="14" thickBot="1">
+    <row r="696" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="9">
         <v>44744</v>
       </c>
@@ -19533,7 +19533,7 @@
         <v>500285</v>
       </c>
     </row>
-    <row r="697" spans="1:5" ht="14" thickBot="1">
+    <row r="697" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="9">
         <v>44751</v>
       </c>
@@ -19551,7 +19551,7 @@
         <v>437600</v>
       </c>
     </row>
-    <row r="698" spans="1:5" ht="14" thickBot="1">
+    <row r="698" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="9">
         <v>44758</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>498899</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="14" thickBot="1">
+    <row r="699" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="9">
         <v>44765</v>
       </c>
@@ -19587,7 +19587,7 @@
         <v>498901</v>
       </c>
     </row>
-    <row r="700" spans="1:5" ht="14" thickBot="1">
+    <row r="700" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="9">
         <v>44772</v>
       </c>
@@ -19605,7 +19605,7 @@
         <v>505409</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="14" thickBot="1">
+    <row r="701" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="11">
         <v>44779</v>
       </c>
@@ -19623,7 +19623,7 @@
         <v>496526</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="14" thickBot="1">
+    <row r="702" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="9">
         <v>44786</v>
       </c>
@@ -19641,7 +19641,7 @@
         <v>502775</v>
       </c>
     </row>
-    <row r="703" spans="1:5" ht="14" thickBot="1">
+    <row r="703" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="9">
         <v>44793</v>
       </c>
@@ -19659,7 +19659,7 @@
         <v>501548</v>
       </c>
     </row>
-    <row r="704" spans="1:5" ht="14" thickBot="1">
+    <row r="704" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="9">
         <v>44800</v>
       </c>
@@ -19677,7 +19677,7 @@
         <v>511574</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="14" thickBot="1">
+    <row r="705" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="9">
         <v>44807</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>513087</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="14" thickBot="1">
+    <row r="706" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="9">
         <v>44814</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>464261</v>
       </c>
     </row>
-    <row r="707" spans="1:5" ht="14" thickBot="1">
+    <row r="707" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="9">
         <v>44821</v>
       </c>
@@ -19746,7 +19746,7 @@
         <v>490654</v>
       </c>
     </row>
-    <row r="708" spans="1:5" ht="14" thickBot="1">
+    <row r="708" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="9">
         <v>44828</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>489111</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="14" thickBot="1">
+    <row r="709" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="9">
         <v>44835</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>495868</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="14" thickBot="1">
+    <row r="710" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="9">
         <v>44842</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>494413</v>
       </c>
     </row>
-    <row r="711" spans="1:5" ht="14" thickBot="1">
+    <row r="711" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="9">
         <v>44849</v>
       </c>
@@ -19818,7 +19818,7 @@
         <v>500304</v>
       </c>
     </row>
-    <row r="712" spans="1:5" ht="14" thickBot="1">
+    <row r="712" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="9">
         <v>44856</v>
       </c>
@@ -19836,7 +19836,7 @@
         <v>505322</v>
       </c>
     </row>
-    <row r="713" spans="1:5" ht="14" thickBot="1">
+    <row r="713" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="9">
         <v>44863</v>
       </c>
@@ -19854,7 +19854,7 @@
         <v>514457</v>
       </c>
     </row>
-    <row r="714" spans="1:5" ht="14" thickBot="1">
+    <row r="714" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="9">
         <v>44870</v>
       </c>
@@ -19872,7 +19872,7 @@
         <v>502106</v>
       </c>
     </row>
-    <row r="715" spans="1:5" ht="14" thickBot="1">
+    <row r="715" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="9">
         <v>44877</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>490350</v>
       </c>
     </row>
-    <row r="716" spans="1:5" ht="14" thickBot="1">
+    <row r="716" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A716" s="9">
         <v>44884</v>
       </c>
@@ -19908,7 +19908,7 @@
         <v>491794</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="14" thickBot="1">
+    <row r="717" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A717" s="9">
         <v>44891</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>413305</v>
       </c>
     </row>
-    <row r="718" spans="1:5" ht="14" thickBot="1">
+    <row r="718" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A718" s="9">
         <v>44898</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>495472</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="14" thickBot="1">
+    <row r="719" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A719" s="9">
         <v>44905</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>500310</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="14" thickBot="1">
+    <row r="720" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A720" s="9">
         <v>44912</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>476232</v>
       </c>
     </row>
-    <row r="721" spans="1:5" ht="14" thickBot="1">
+    <row r="721" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A721" s="9">
         <v>44919</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>400289</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="14" thickBot="1">
+    <row r="722" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A722" s="9">
         <v>44926</v>
       </c>
@@ -20016,7 +20016,7 @@
         <v>365553</v>
       </c>
     </row>
-    <row r="723" spans="1:5" ht="14" thickBot="1">
+    <row r="723" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A723" s="9">
         <v>44933</v>
       </c>
@@ -20034,7 +20034,7 @@
         <v>416489</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="14" thickBot="1">
+    <row r="724" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A724" s="9">
         <v>44940</v>
       </c>
@@ -20052,7 +20052,7 @@
         <v>486000</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="14" thickBot="1">
+    <row r="725" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A725" s="9">
         <v>44947</v>
       </c>
@@ -20070,7 +20070,7 @@
         <v>467485</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="14" thickBot="1">
+    <row r="726" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A726" s="11">
         <v>44954</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>473650</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="14" thickBot="1">
+    <row r="727" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A727" s="9">
         <v>44961</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>449586</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="14" thickBot="1">
+    <row r="728" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A728" s="9">
         <v>44968</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>473972</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="14" thickBot="1">
+    <row r="729" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A729" s="9">
         <v>44975</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>466932</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="14" thickBot="1">
+    <row r="730" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A730" s="9">
         <v>44982</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>459233</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="14" thickBot="1">
+    <row r="731" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A731" s="9">
         <v>44989</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>474191</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="14" thickBot="1">
+    <row r="732" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A732" s="9">
         <v>44996</v>
       </c>
@@ -20196,7 +20196,7 @@
         <v>458629</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="14" thickBot="1">
+    <row r="733" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A733" s="9">
         <v>45003</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>453500</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="14" thickBot="1">
+    <row r="734" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A734" s="9">
         <v>45010</v>
       </c>
@@ -20232,7 +20232,7 @@
         <v>469958</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="14" thickBot="1">
+    <row r="735" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A735" s="9">
         <v>45017</v>
       </c>
@@ -20250,7 +20250,7 @@
         <v>467430</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="14" thickBot="1">
+    <row r="736" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A736" s="9">
         <v>45024</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>451336</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="14" thickBot="1">
+    <row r="737" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A737" s="9">
         <v>45031</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>468197</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="14" thickBot="1">
+    <row r="738" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A738" s="9">
         <v>45038</v>
       </c>
@@ -20304,7 +20304,7 @@
         <v>480457</v>
       </c>
     </row>
-    <row r="739" spans="1:5" ht="14" thickBot="1">
+    <row r="739" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A739" s="9">
         <v>45045</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>481960</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="14" thickBot="1">
+    <row r="740" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A740" s="9">
         <v>45052</v>
       </c>
@@ -20340,7 +20340,7 @@
         <v>471859</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="14" thickBot="1">
+    <row r="741" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A741" s="9">
         <v>45059</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>466381</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="14" thickBot="1">
+    <row r="742" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A742" s="9">
         <v>45066</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>470694</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="14" thickBot="1">
+    <row r="743" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A743" s="9">
         <v>45073</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>480998</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="14" thickBot="1">
+    <row r="744" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A744" s="9">
         <v>45080</v>
       </c>
@@ -20412,7 +20412,7 @@
         <v>439601</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="14" thickBot="1">
+    <row r="745" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A745" s="9">
         <v>45087</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>471141</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="14" thickBot="1">
+    <row r="746" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A746" s="9">
         <v>45094</v>
       </c>
@@ -20448,7 +20448,7 @@
         <v>477126</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="14" thickBot="1">
+    <row r="747" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A747" s="9">
         <v>45101</v>
       </c>
@@ -20466,7 +20466,7 @@
         <v>469453</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="14" thickBot="1">
+    <row r="748" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A748" s="9">
         <v>45108</v>
       </c>
@@ -20484,7 +20484,7 @@
         <v>474443</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="14" thickBot="1">
+    <row r="749" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A749" s="9">
         <v>45115</v>
       </c>
@@ -20502,7 +20502,7 @@
         <v>407843</v>
       </c>
     </row>
-    <row r="750" spans="1:5" ht="14" thickBot="1">
+    <row r="750" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A750" s="9">
         <v>45122</v>
       </c>
@@ -20520,7 +20520,7 @@
         <v>478153</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="14" thickBot="1">
+    <row r="751" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A751" s="11">
         <v>45129</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>473736</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="14" thickBot="1">
+    <row r="752" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A752" s="9">
         <v>45136</v>
       </c>
@@ -20556,7 +20556,7 @@
         <v>483481</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="14" thickBot="1">
+    <row r="753" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A753" s="9">
         <v>45143</v>
       </c>
@@ -20574,7 +20574,7 @@
         <v>471938</v>
       </c>
     </row>
-    <row r="754" spans="1:5" ht="14" thickBot="1">
+    <row r="754" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A754" s="9">
         <v>45150</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>472498</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="14" thickBot="1">
+    <row r="755" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A755" s="9">
         <v>45157</v>
       </c>
@@ -20610,7 +20610,7 @@
         <v>478853</v>
       </c>
     </row>
-    <row r="756" spans="1:5" ht="14" thickBot="1">
+    <row r="756" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A756" s="9">
         <v>45164</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>472525</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="14" thickBot="1">
+    <row r="757" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A757" s="9">
         <v>45171</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>476851</v>
       </c>
     </row>
-    <row r="758" spans="1:5" ht="14" thickBot="1">
+    <row r="758" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A758" s="9">
         <v>45178</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>447345</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="14" thickBot="1">
+    <row r="759" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A759" s="9">
         <v>45185</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>489790</v>
       </c>
     </row>
-    <row r="760" spans="1:5" ht="14" thickBot="1">
+    <row r="760" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A760" s="9">
         <v>45192</v>
       </c>
@@ -20700,7 +20700,7 @@
         <v>493323</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="14" thickBot="1">
+    <row r="761" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A761" s="9">
         <v>45199</v>
       </c>
@@ -20718,7 +20718,7 @@
         <v>500154</v>
       </c>
     </row>
-    <row r="762" spans="1:5" ht="14" thickBot="1">
+    <row r="762" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A762" s="9">
         <v>45206</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>499217</v>
       </c>
     </row>
-    <row r="763" spans="1:5" ht="14" thickBot="1">
+    <row r="763" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A763" s="9">
         <v>45213</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>492781</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="14" thickBot="1">
+    <row r="764" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A764" s="9">
         <v>45220</v>
       </c>
@@ -20772,7 +20772,7 @@
         <v>505985</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="14" thickBot="1">
+    <row r="765" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A765" s="9">
         <v>45227</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>499389</v>
       </c>
     </row>
-    <row r="766" spans="1:5" ht="14" thickBot="1">
+    <row r="766" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A766" s="9">
         <v>45234</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>484757</v>
       </c>
     </row>
-    <row r="767" spans="1:5" ht="14" thickBot="1">
+    <row r="767" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A767" s="9">
         <v>45241</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>497348</v>
       </c>
     </row>
-    <row r="768" spans="1:5" ht="14" thickBot="1">
+    <row r="768" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A768" s="9">
         <v>45248</v>
       </c>
@@ -20844,7 +20844,7 @@
         <v>501416</v>
       </c>
     </row>
-    <row r="769" spans="1:5" ht="14" thickBot="1">
+    <row r="769" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A769" s="9">
         <v>45255</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>415332</v>
       </c>
     </row>
-    <row r="770" spans="1:5" ht="14" thickBot="1">
+    <row r="770" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A770" s="9">
         <v>45262</v>
       </c>
@@ -20895,7 +20895,7 @@
         <v>509626</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="14" thickBot="1">
+    <row r="771" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A771" s="9">
         <v>45269</v>
       </c>
@@ -20913,7 +20913,7 @@
         <v>499094</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="14" thickBot="1">
+    <row r="772" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A772" s="9">
         <v>45276</v>
       </c>
@@ -20931,7 +20931,7 @@
         <v>502583</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="14" thickBot="1">
+    <row r="773" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A773" s="9">
         <v>45283</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>486787</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="14" thickBot="1">
+    <row r="774" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A774" s="9">
         <v>45297</v>
       </c>
@@ -20967,7 +20967,7 @@
         <v>417257</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="14" thickBot="1">
+    <row r="775" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A775" s="9">
         <v>45304</v>
       </c>
@@ -20985,7 +20985,7 @@
         <v>457453</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="14" thickBot="1">
+    <row r="776" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A776" s="13">
         <v>45311</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>397553</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="14" thickBot="1">
+    <row r="777" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A777" s="15">
         <v>45318</v>
       </c>
@@ -21021,7 +21021,7 @@
         <v>467222</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="14" thickBot="1">
+    <row r="778" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A778" s="15">
         <v>45325</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>491697</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="14" thickBot="1">
+    <row r="779" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A779" s="15">
         <v>45332</v>
       </c>
@@ -21057,7 +21057,7 @@
         <v>484840</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="14" thickBot="1">
+    <row r="780" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A780" s="15">
         <v>45339</v>
       </c>
@@ -21075,7 +21075,7 @@
         <v>474226</v>
       </c>
     </row>
-    <row r="781" spans="1:5" ht="14" thickBot="1">
+    <row r="781" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A781" s="15">
         <v>45346</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>483656</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="14" thickBot="1">
+    <row r="782" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A782" s="15">
         <v>45353</v>
       </c>
@@ -21111,7 +21111,7 @@
         <v>483138</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="14" thickBot="1">
+    <row r="783" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A783" s="15">
         <v>45360</v>
       </c>
@@ -21129,7 +21129,7 @@
         <v>472662</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="14" thickBot="1">
+    <row r="784" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A784" s="15">
         <v>45367</v>
       </c>
@@ -21147,7 +21147,7 @@
         <v>474596</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="14" thickBot="1">
+    <row r="785" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A785" s="15">
         <v>45374</v>
       </c>
@@ -21165,7 +21165,7 @@
         <v>470593</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="14" thickBot="1">
+    <row r="786" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A786" s="15">
         <v>45381</v>
       </c>
@@ -21183,7 +21183,7 @@
         <v>472651</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="14" thickBot="1">
+    <row r="787" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A787" s="15">
         <v>45388</v>
       </c>
@@ -21201,7 +21201,7 @@
         <v>450142</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="14" thickBot="1">
+    <row r="788" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A788" s="15">
         <v>45395</v>
       </c>
@@ -21219,7 +21219,7 @@
         <v>466463</v>
       </c>
     </row>
-    <row r="789" spans="1:5" ht="14" thickBot="1">
+    <row r="789" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A789" s="15">
         <v>45402</v>
       </c>
@@ -21237,7 +21237,7 @@
         <v>474544</v>
       </c>
     </row>
-    <row r="790" spans="1:5" ht="14" thickBot="1">
+    <row r="790" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A790" s="15">
         <v>45409</v>
       </c>
@@ -21255,7 +21255,7 @@
         <v>476302</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="14" thickBot="1">
+    <row r="791" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A791" s="15">
         <v>45416</v>
       </c>
@@ -21273,7 +21273,7 @@
         <v>463106</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="14" thickBot="1">
+    <row r="792" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A792" s="15">
         <v>45423</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>468748</v>
       </c>
     </row>
-    <row r="793" spans="1:5" ht="14" thickBot="1">
+    <row r="793" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A793" s="15">
         <v>45430</v>
       </c>
@@ -21309,7 +21309,7 @@
         <v>474886</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="14" thickBot="1">
+    <row r="794" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A794" s="15">
         <v>45437</v>
       </c>
@@ -21327,7 +21327,7 @@
         <v>485232</v>
       </c>
     </row>
-    <row r="795" spans="1:5" ht="14" thickBot="1">
+    <row r="795" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A795" s="15">
         <v>45444</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>450077</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="14" thickBot="1">
+    <row r="796" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A796" s="15">
         <v>45451</v>
       </c>
@@ -21363,7 +21363,7 @@
         <v>489916</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="14" thickBot="1">
+    <row r="797" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A797" s="15">
         <v>45458</v>
       </c>
@@ -21381,7 +21381,7 @@
         <v>493138</v>
       </c>
     </row>
-    <row r="798" spans="1:5" ht="14" thickBot="1">
+    <row r="798" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A798" s="15">
         <v>45465</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>485557</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="14" thickBot="1">
+    <row r="799" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A799" s="15">
         <v>45472</v>
       </c>
@@ -21417,7 +21417,7 @@
         <v>491899</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="14" thickBot="1">
+    <row r="800" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A800" s="15">
         <v>45479</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>421817</v>
       </c>
     </row>
-    <row r="801" spans="1:5" ht="14" thickBot="1">
+    <row r="801" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A801" s="13">
         <v>45486</v>
       </c>
@@ -21453,7 +21453,7 @@
         <v>483806</v>
       </c>
     </row>
-    <row r="802" spans="1:5" ht="14" thickBot="1">
+    <row r="802" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A802" s="15">
         <v>45493</v>
       </c>
@@ -21471,7 +21471,7 @@
         <v>480083</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="14" thickBot="1">
+    <row r="803" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A803" s="15">
         <v>45500</v>
       </c>
@@ -21489,7 +21489,7 @@
         <v>508496</v>
       </c>
     </row>
-    <row r="804" spans="1:5" ht="14" thickBot="1">
+    <row r="804" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A804" s="15">
         <v>45507</v>
       </c>
@@ -21507,7 +21507,7 @@
         <v>498807</v>
       </c>
     </row>
-    <row r="805" spans="1:5" ht="14" thickBot="1">
+    <row r="805" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A805" s="15">
         <v>45514</v>
       </c>
@@ -21525,7 +21525,7 @@
         <v>496509</v>
       </c>
     </row>
-    <row r="806" spans="1:5" ht="14" thickBot="1">
+    <row r="806" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A806" s="15">
         <v>45521</v>
       </c>
@@ -21543,7 +21543,7 @@
         <v>516819</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="14" thickBot="1">
+    <row r="807" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A807" s="15">
         <v>45528</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>516807</v>
       </c>
     </row>
-    <row r="808" spans="1:5" ht="14" thickBot="1">
+    <row r="808" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A808" s="15">
         <v>45535</v>
       </c>
@@ -21579,7 +21579,7 @@
         <v>516632</v>
       </c>
     </row>
-    <row r="809" spans="1:5" ht="14" thickBot="1">
+    <row r="809" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A809" s="15">
         <v>45542</v>
       </c>
@@ -21597,7 +21597,7 @@
         <v>479179</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="14" thickBot="1">
+    <row r="810" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A810" s="15">
         <v>45549</v>
       </c>
@@ -21615,7 +21615,7 @@
         <v>522557</v>
       </c>
     </row>
-    <row r="811" spans="1:5" ht="14" thickBot="1">
+    <row r="811" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A811" s="15">
         <v>45556</v>
       </c>
@@ -21633,7 +21633,7 @@
         <v>522112</v>
       </c>
     </row>
-    <row r="812" spans="1:5" ht="14" thickBot="1">
+    <row r="812" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A812" s="15">
         <v>45563</v>
       </c>
@@ -21651,7 +21651,7 @@
         <v>507537</v>
       </c>
     </row>
-    <row r="813" spans="1:5" ht="14" thickBot="1">
+    <row r="813" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A813" s="15">
         <v>45570</v>
       </c>
@@ -21669,7 +21669,7 @@
         <v>486187</v>
       </c>
     </row>
-    <row r="814" spans="1:5" ht="14" thickBot="1">
+    <row r="814" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A814" s="15">
         <v>45577</v>
       </c>
@@ -21687,7 +21687,7 @@
         <v>505033</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="14" thickBot="1">
+    <row r="815" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A815" s="15">
         <v>45584</v>
       </c>
@@ -21705,7 +21705,7 @@
         <v>510730</v>
       </c>
     </row>
-    <row r="816" spans="1:5" ht="14" thickBot="1">
+    <row r="816" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A816" s="15">
         <v>45591</v>
       </c>
@@ -21723,7 +21723,7 @@
         <v>519415</v>
       </c>
     </row>
-    <row r="817" spans="1:5" ht="14" thickBot="1">
+    <row r="817" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A817" s="15">
         <v>45598</v>
       </c>
@@ -21741,7 +21741,7 @@
         <v>516743</v>
       </c>
     </row>
-    <row r="818" spans="1:5" ht="14" thickBot="1">
+    <row r="818" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A818" s="15">
         <v>45612</v>
       </c>
@@ -21759,7 +21759,7 @@
         <v>516886</v>
       </c>
     </row>
-    <row r="819" spans="1:5" ht="14" thickBot="1">
+    <row r="819" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A819" s="15">
         <v>45619</v>
       </c>
@@ -21777,7 +21777,7 @@
         <v>520798</v>
       </c>
     </row>
-    <row r="820" spans="1:5" ht="14" thickBot="1">
+    <row r="820" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A820" s="15">
         <v>45626</v>
       </c>
@@ -21795,7 +21795,7 @@
         <v>439362</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="14" thickBot="1">
+    <row r="821" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A821" s="15">
         <v>45633</v>
       </c>
@@ -21813,7 +21813,7 @@
         <v>520894</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="14" thickBot="1">
+    <row r="822" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A822" s="15">
         <v>45640</v>
       </c>
@@ -21831,7 +21831,7 @@
         <v>526166</v>
       </c>
     </row>
-    <row r="823" spans="1:5" ht="14" thickBot="1">
+    <row r="823" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A823" s="15">
         <v>45647</v>
       </c>
@@ -21849,7 +21849,7 @@
         <v>523912</v>
       </c>
     </row>
-    <row r="824" spans="1:5" ht="14" thickBot="1">
+    <row r="824" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A824" s="15">
         <v>45654</v>
       </c>
@@ -21867,7 +21867,7 @@
         <v>389700</v>
       </c>
     </row>
-    <row r="825" spans="1:5" ht="14" thickBot="1">
+    <row r="825" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A825" s="15">
         <v>45661</v>
       </c>
@@ -21885,7 +21885,7 @@
         <v>421410</v>
       </c>
     </row>
-    <row r="826" spans="1:5" ht="14" thickBot="1">
+    <row r="826" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A826" s="13">
         <v>45668</v>
       </c>
@@ -21903,7 +21903,7 @@
         <v>465390</v>
       </c>
     </row>
-    <row r="827" spans="1:5" ht="14" thickBot="1">
+    <row r="827" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A827" s="15">
         <v>45675</v>
       </c>
@@ -21921,7 +21921,7 @@
         <v>500160</v>
       </c>
     </row>
-    <row r="828" spans="1:5" ht="14" thickBot="1">
+    <row r="828" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A828" s="15">
         <v>45682</v>
       </c>
@@ -21939,7 +21939,7 @@
         <v>454797</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="14" thickBot="1">
+    <row r="829" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A829" s="15">
         <v>45689</v>
       </c>
@@ -21957,7 +21957,7 @@
         <v>513622</v>
       </c>
     </row>
-    <row r="830" spans="1:5" ht="14" thickBot="1">
+    <row r="830" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A830" s="15">
         <v>45696</v>
       </c>
@@ -21975,7 +21975,7 @@
         <v>502449</v>
       </c>
     </row>
-    <row r="831" spans="1:5" ht="14" thickBot="1">
+    <row r="831" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A831" s="15">
         <v>45703</v>
       </c>
@@ -21993,7 +21993,7 @@
         <v>480740</v>
       </c>
     </row>
-    <row r="832" spans="1:5" ht="14" thickBot="1">
+    <row r="832" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A832" s="15">
         <v>45710</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>458513</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="14" thickBot="1">
+    <row r="833" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A833" s="15">
         <v>45717</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>508531</v>
       </c>
     </row>
-    <row r="834" spans="1:5" ht="14" thickBot="1">
+    <row r="834" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A834" s="15">
         <v>45724</v>
       </c>
@@ -22062,7 +22062,7 @@
         <v>497412</v>
       </c>
     </row>
-    <row r="835" spans="1:5" ht="14" thickBot="1">
+    <row r="835" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A835" s="15">
         <v>45731</v>
       </c>
@@ -22080,7 +22080,7 @@
         <v>503473</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="14" thickBot="1">
+    <row r="836" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A836" s="15">
         <v>45738</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>496214</v>
       </c>
     </row>
-    <row r="837" spans="1:5" ht="14" thickBot="1">
+    <row r="837" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A837" s="15">
         <v>45745</v>
       </c>
@@ -22116,7 +22116,7 @@
         <v>513553</v>
       </c>
     </row>
-    <row r="838" spans="1:5" ht="14" thickBot="1">
+    <row r="838" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A838" s="15">
         <v>45752</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>500584</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="14" thickBot="1">
+    <row r="839" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A839" s="15">
         <v>45759</v>
       </c>
@@ -22152,7 +22152,7 @@
         <v>491908</v>
       </c>
     </row>
-    <row r="840" spans="1:5" ht="14" thickBot="1">
+    <row r="840" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A840" s="15">
         <v>45766</v>
       </c>
@@ -22170,7 +22170,7 @@
         <v>496053</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="14" thickBot="1">
+    <row r="841" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A841" s="15">
         <v>45773</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>502105</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="14" thickBot="1">
+    <row r="842" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A842" s="15">
         <v>45780</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>498693</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="14" thickBot="1">
+    <row r="843" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A843" s="15">
         <v>45787</v>
       </c>
@@ -22224,7 +22224,7 @@
         <v>495552</v>
       </c>
     </row>
-    <row r="844" spans="1:5" ht="14" thickBot="1">
+    <row r="844" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A844" s="15">
         <v>45794</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>490775</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="14" thickBot="1">
+    <row r="845" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A845" s="15">
         <v>45801</v>
       </c>
@@ -22260,7 +22260,7 @@
         <v>488709</v>
       </c>
     </row>
-    <row r="846" spans="1:5" ht="14" thickBot="1">
+    <row r="846" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A846" s="15">
         <v>45808</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>459884</v>
       </c>
     </row>
-    <row r="847" spans="1:5" ht="14" thickBot="1">
+    <row r="847" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A847" s="15">
         <v>45815</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>483807</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="14" thickBot="1">
+    <row r="848" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A848" s="15">
         <v>45822</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>485810</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="14" thickBot="1">
+    <row r="849" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A849" s="15">
         <v>45829</v>
       </c>
@@ -22332,7 +22332,7 @@
         <v>487328</v>
       </c>
     </row>
-    <row r="850" spans="1:5" ht="14" thickBot="1">
+    <row r="850" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A850" s="15">
         <v>45836</v>
       </c>
@@ -22350,7 +22350,7 @@
         <v>491424</v>
       </c>
     </row>
-    <row r="851" spans="1:5" ht="14" thickBot="1">
+    <row r="851" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A851" s="13">
         <v>45843</v>
       </c>
@@ -22368,7 +22368,7 @@
         <v>443049</v>
       </c>
     </row>
-    <row r="852" spans="1:5" ht="14" thickBot="1">
+    <row r="852" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A852" s="15">
         <v>45850</v>
       </c>
@@ -22386,7 +22386,7 @@
         <v>496188</v>
       </c>
     </row>
-    <row r="853" spans="1:5" ht="14" thickBot="1">
+    <row r="853" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A853" s="15">
         <v>45857</v>
       </c>
@@ -22404,7 +22404,7 @@
         <v>506882</v>
       </c>
     </row>
-    <row r="854" spans="1:5" ht="14" thickBot="1">
+    <row r="854" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A854" s="15">
         <v>45864</v>
       </c>
@@ -22422,7 +22422,7 @@
         <v>514279</v>
       </c>
     </row>
-    <row r="855" spans="1:5" ht="14" thickBot="1">
+    <row r="855" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A855" s="15">
         <v>45871</v>
       </c>
@@ -22440,7 +22440,7 @@
         <v>513529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="14" thickBot="1">
+    <row r="856" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A856" s="15">
         <v>45878</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>511194</v>
       </c>
     </row>
-    <row r="857" spans="1:5" ht="14" thickBot="1">
+    <row r="857" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A857" s="15">
         <v>45885</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>512970</v>
       </c>
     </row>
-    <row r="858" spans="1:5" ht="14" thickBot="1">
+    <row r="858" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A858" s="15">
         <v>45892</v>
       </c>
@@ -22494,7 +22494,7 @@
         <v>512333</v>
       </c>
     </row>
-    <row r="859" spans="1:5" ht="14" thickBot="1">
+    <row r="859" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A859" s="15">
         <v>45899</v>
       </c>
@@ -22512,7 +22512,7 @@
         <v>521502</v>
       </c>
     </row>
-    <row r="860" spans="1:5" ht="14" thickBot="1">
+    <row r="860" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A860" s="15">
         <v>45906</v>
       </c>
@@ -22530,7 +22530,7 @@
         <v>467880</v>
       </c>
     </row>
-    <row r="861" spans="1:5" ht="14" thickBot="1">
+    <row r="861" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A861" s="15">
         <v>45913</v>
       </c>
@@ -22548,7 +22548,7 @@
         <v>514167</v>
       </c>
     </row>
-    <row r="862" spans="1:5" ht="14" thickBot="1">
+    <row r="862" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A862" s="15">
         <v>45920</v>
       </c>
@@ -22566,7 +22566,7 @@
         <v>510677</v>
       </c>
     </row>
-    <row r="863" spans="1:5" ht="14" thickBot="1">
+    <row r="863" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A863" s="13">
         <v>45927</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>512642</v>
       </c>
     </row>
-    <row r="864" spans="1:5" ht="14" thickBot="1">
+    <row r="864" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A864" s="15">
         <v>45934</v>
       </c>
@@ -22602,7 +22602,7 @@
         <v>503538</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="14" thickBot="1">
+    <row r="865" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A865" s="15">
         <v>45941</v>
       </c>
@@ -22620,7 +22620,7 @@
         <v>498462</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="14" thickBot="1">
+    <row r="866" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A866" s="15">
         <v>45948</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>497854</v>
       </c>
     </row>
-    <row r="867" spans="1:5" ht="14" thickBot="1">
+    <row r="867" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A867" s="15">
         <v>45955</v>
       </c>
@@ -22656,7 +22656,7 @@
         <v>499688</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="14" thickBot="1">
+    <row r="868" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A868" s="15">
         <v>45962</v>
       </c>
@@ -22674,7 +22674,7 @@
         <v>496928</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="14" thickBot="1">
+    <row r="869" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A869" s="15">
         <v>45969</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>493493</v>
       </c>
     </row>
-    <row r="870" spans="1:5" ht="14" thickBot="1">
+    <row r="870" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A870" s="15">
         <v>45976</v>
       </c>
@@ -22710,7 +22710,7 @@
         <v>493880</v>
       </c>
     </row>
-    <row r="871" spans="1:5" ht="14" thickBot="1">
+    <row r="871" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A871" s="15">
         <v>45983</v>
       </c>
@@ -22728,7 +22728,7 @@
         <v>516110</v>
       </c>
     </row>
-    <row r="872" spans="1:5" ht="14" thickBot="1">
+    <row r="872" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A872" s="15">
         <v>45990</v>
       </c>
@@ -22746,7 +22746,7 @@
         <v>431435</v>
       </c>
     </row>
-    <row r="873" spans="1:5" ht="14" thickBot="1">
+    <row r="873" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A873" s="15">
         <v>45997</v>
       </c>
@@ -22764,7 +22764,7 @@
         <v>508999</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="14" thickBot="1">
+    <row r="874" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A874" s="15">
         <v>46004</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>518904</v>
       </c>
     </row>
-    <row r="875" spans="1:5" ht="14" thickBot="1">
+    <row r="875" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A875" s="13">
         <v>46018</v>
       </c>
@@ -22800,7 +22800,7 @@
         <v>392295</v>
       </c>
     </row>
-    <row r="876" spans="1:5" ht="14" thickBot="1">
+    <row r="876" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A876" s="7">
         <v>46025</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>404293</v>
       </c>
     </row>
-    <row r="877" spans="1:5" ht="14" thickBot="1">
+    <row r="877" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A877" s="13">
         <v>46032</v>
       </c>
@@ -22836,7 +22836,7 @@
         <v>510457</v>
       </c>
     </row>
-    <row r="878" spans="1:5" ht="14" thickBot="1">
+    <row r="878" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A878" s="7">
         <v>46039</v>
       </c>
@@ -22869,7 +22869,7 @@
         <v>505385</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="14" thickBot="1">
+    <row r="879" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A879" s="13">
         <v>46046</v>
       </c>
@@ -22902,7 +22902,7 @@
         <v>481708</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="14" thickBot="1">
+    <row r="880" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A880" s="13">
         <v>46053</v>
       </c>
@@ -22935,7 +22935,7 @@
         <v>434361</v>
       </c>
     </row>
-    <row r="881" spans="1:5" ht="14" thickBot="1">
+    <row r="881" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A881" s="13">
         <v>46060</v>
       </c>
@@ -22953,7 +22953,7 @@
         <v>486854</v>
       </c>
     </row>
-    <row r="882" spans="1:5" ht="14" thickBot="1">
+    <row r="882" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A882" s="7">
         <v>46067</v>
       </c>
@@ -22986,7 +22986,7 @@
         <v>510399</v>
       </c>
     </row>
-    <row r="883" spans="1:5" ht="14" thickBot="1">
+    <row r="883" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A883" s="13">
         <v>46074</v>
       </c>
@@ -23019,7 +23019,7 @@
         <v>507712</v>
       </c>
     </row>
-    <row r="884" spans="1:5" ht="14" thickBot="1">
+    <row r="884" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="7">
         <v>46081</v>
       </c>
@@ -23037,7 +23037,7 @@
         <v>516729</v>
       </c>
     </row>
-    <row r="885" spans="1:5" ht="14" thickBot="1">
+    <row r="885" spans="1:5" ht="13.2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A885" s="13">
         <v>46088</v>
       </c>
@@ -23055,7 +23055,7 @@
         <v>514996</v>
       </c>
     </row>
-    <row r="886" spans="1:5">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A886" s="7">
         <v>46102</v>
       </c>
@@ -23073,7 +23073,7 @@
         <v>502252</v>
       </c>
     </row>
-    <row r="887" spans="1:5">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A887" s="7">
         <v>46109</v>
       </c>
@@ -23091,7 +23091,7 @@
         <v>515921</v>
       </c>
     </row>
-    <row r="888" spans="1:5">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A888" s="7">
         <v>46116</v>
       </c>
@@ -23109,7 +23109,7 @@
         <v>501328</v>
       </c>
     </row>
-    <row r="889" spans="1:5">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A889" s="7">
         <v>46123</v>
       </c>
@@ -23127,7 +23127,7 @@
         <v>500040</v>
       </c>
     </row>
-    <row r="890" spans="1:5">
+    <row r="890" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A890" s="7">
         <v>46130</v>
       </c>
@@ -23145,7 +23145,7 @@
         <v>508303</v>
       </c>
     </row>
-    <row r="891" spans="1:5">
+    <row r="891" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A891" s="7">
         <v>46137</v>
       </c>
@@ -23163,7 +23163,7 @@
         <v>511616</v>
       </c>
     </row>
-    <row r="892" spans="1:5">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A892" s="7">
         <v>46144</v>
       </c>
@@ -23181,7 +23181,7 @@
         <v>518773</v>
       </c>
     </row>
-    <row r="893" spans="1:5">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A893" s="7">
         <v>46151</v>
       </c>
@@ -23214,7 +23214,7 @@
         <v>513755</v>
       </c>
     </row>
-    <row r="894" spans="1:5">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A894" s="7">
         <v>46158</v>
       </c>
@@ -23232,7 +23232,7 @@
         <v>511216</v>
       </c>
     </row>
-    <row r="895" spans="1:5">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A895" s="7">
         <v>46165</v>
       </c>
@@ -23250,7 +23250,7 @@
         <v>523574</v>
       </c>
     </row>
-    <row r="896" spans="1:5">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A896" s="7">
         <v>46172</v>
       </c>
@@ -23258,7 +23258,7 @@
         <v>46176</v>
       </c>
       <c r="C896" s="21">
-        <v>0.50069444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="D896" s="6" t="str">
         <f t="shared" ref="D896" si="17">IF(
@@ -23279,6 +23279,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E896" s="17">
+        <v>492795</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E876">
@@ -23293,7 +23296,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300947AE-C9E8-48BA-99BA-AA00E1AFF02E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23304,12 +23307,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF96248-4EFB-4252-A059-6D65AEEDC293}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -23317,7 +23320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -23325,7 +23328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
